--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/pkg/data-raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F69C00-1A31-0D4B-AE90-B60C879C3EB2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D4B1DB-C209-4CD2-9C1E-16211B50C510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24800" yWindow="560" windowWidth="25020" windowHeight="28120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="59400" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -1730,9 +1730,6 @@
     <t>Stem mortality</t>
   </si>
   <si>
-    <t>var_8_5</t>
-  </si>
-  <si>
     <t>volume_extracted</t>
   </si>
   <si>
@@ -1998,13 +1995,16 @@
   </si>
   <si>
     <t>apar</t>
+  </si>
+  <si>
+    <t>test_output</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2016,6 +2016,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2039,8 +2052,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2060,9 +2075,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2100,7 +2115,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2206,7 +2221,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2348,7 +2363,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2357,9 +2372,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E287297-02C0-BF44-BF0C-8FADE2A87F8F}">
   <dimension ref="A1:D83"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -2373,7 +2388,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2387,7 +2402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2401,7 +2416,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2415,7 +2430,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2429,7 +2444,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2443,7 +2458,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2457,7 +2472,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2471,7 +2486,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2485,7 +2500,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2499,7 +2514,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2513,7 +2528,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2527,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2541,7 +2556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2555,7 +2570,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2569,7 +2584,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2583,7 +2598,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2597,7 +2612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2611,7 +2626,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2625,7 +2640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2639,7 +2654,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2653,7 +2668,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2667,7 +2682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2681,7 +2696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2695,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2709,7 +2724,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2723,7 +2738,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -2737,7 +2752,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -2751,7 +2766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2765,7 +2780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -2779,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -2793,7 +2808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2807,7 +2822,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -2821,7 +2836,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -2835,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -2849,7 +2864,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -2863,7 +2878,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -2877,7 +2892,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -2891,7 +2906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -2905,7 +2920,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -2919,7 +2934,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -2933,7 +2948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -2947,7 +2962,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -2961,7 +2976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -2975,7 +2990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -2989,7 +3004,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -3003,7 +3018,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -3017,7 +3032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -3031,7 +3046,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -3045,7 +3060,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -3059,7 +3074,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -3073,7 +3088,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -3087,7 +3102,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -3101,7 +3116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -3115,7 +3130,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -3129,7 +3144,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -3143,7 +3158,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -3157,7 +3172,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -3171,7 +3186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -3185,7 +3200,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -3199,7 +3214,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -3213,7 +3228,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>68</v>
       </c>
@@ -3227,7 +3242,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -3241,7 +3256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -3255,7 +3270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -3269,7 +3284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -3283,7 +3298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -3297,7 +3312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -3311,7 +3326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>67</v>
       </c>
@@ -3325,7 +3340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -3339,7 +3354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -3353,7 +3368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -3367,7 +3382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -3381,7 +3396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -3395,7 +3410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -3409,7 +3424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -3423,7 +3438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -3437,7 +3452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -3451,7 +3466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -3465,7 +3480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>109</v>
       </c>
@@ -3479,7 +3494,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>110</v>
       </c>
@@ -3493,7 +3508,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>111</v>
       </c>
@@ -3507,7 +3522,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>112</v>
       </c>
@@ -3529,9 +3544,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF000D6-A72C-6444-9177-22D437B8361A}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -3545,7 +3560,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -3559,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -3573,7 +3588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -3587,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -3601,7 +3616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -3615,7 +3630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -3629,7 +3644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -3643,7 +3658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -3657,7 +3672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -3671,7 +3686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -3685,7 +3700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -3699,7 +3714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -3713,7 +3728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -3727,7 +3742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -3741,7 +3756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -3755,7 +3770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -3769,7 +3784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -3783,7 +3798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -3797,7 +3812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>97</v>
       </c>
@@ -3811,7 +3826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -3825,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>99</v>
       </c>
@@ -3839,7 +3854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>100</v>
       </c>
@@ -3853,7 +3868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -3867,7 +3882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -3881,7 +3896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>103</v>
       </c>
@@ -3895,7 +3910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -3909,7 +3924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>105</v>
       </c>
@@ -3923,7 +3938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -3937,7 +3952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -3951,7 +3966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>108</v>
       </c>
@@ -3973,9 +3988,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA3706E6-9BD2-3A49-A255-D2B55C8D9AB1}">
   <dimension ref="A1:G151"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="179" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>256</v>
       </c>
@@ -3998,7 +4017,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4021,7 +4040,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4044,7 +4063,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4067,7 +4086,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4090,7 +4109,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4113,7 +4132,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4136,7 +4155,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4159,7 +4178,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -4182,7 +4201,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1</v>
       </c>
@@ -4205,7 +4224,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1</v>
       </c>
@@ -4225,7 +4244,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1</v>
       </c>
@@ -4248,7 +4267,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1</v>
       </c>
@@ -4262,7 +4281,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1</v>
       </c>
@@ -4276,7 +4295,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1</v>
       </c>
@@ -4290,7 +4309,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
@@ -4304,7 +4323,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
@@ -4327,7 +4346,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4350,7 +4369,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4373,7 +4392,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4396,7 +4415,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4419,7 +4438,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4442,7 +4461,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2</v>
       </c>
@@ -4465,7 +4484,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2</v>
       </c>
@@ -4488,7 +4507,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2</v>
       </c>
@@ -4511,7 +4530,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2</v>
       </c>
@@ -4534,7 +4553,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2</v>
       </c>
@@ -4557,7 +4576,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2</v>
       </c>
@@ -4580,7 +4599,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2</v>
       </c>
@@ -4603,7 +4622,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2</v>
       </c>
@@ -4617,7 +4636,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2</v>
       </c>
@@ -4631,7 +4650,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>3</v>
       </c>
@@ -4654,7 +4673,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>3</v>
       </c>
@@ -4677,7 +4696,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>3</v>
       </c>
@@ -4700,7 +4719,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4723,7 +4742,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4743,7 +4762,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4766,7 +4785,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4789,7 +4808,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>3</v>
       </c>
@@ -4812,7 +4831,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>3</v>
       </c>
@@ -4835,7 +4854,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>3</v>
       </c>
@@ -4858,7 +4877,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>3</v>
       </c>
@@ -4881,7 +4900,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>3</v>
       </c>
@@ -4895,7 +4914,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>3</v>
       </c>
@@ -4909,7 +4928,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>3</v>
       </c>
@@ -4923,7 +4942,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>3</v>
       </c>
@@ -4937,7 +4956,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>4</v>
       </c>
@@ -4960,7 +4979,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>4</v>
       </c>
@@ -4983,7 +5002,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>4</v>
       </c>
@@ -5006,7 +5025,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>4</v>
       </c>
@@ -5029,7 +5048,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>4</v>
       </c>
@@ -5052,7 +5071,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>4</v>
       </c>
@@ -5072,7 +5091,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>4</v>
       </c>
@@ -5095,7 +5114,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>4</v>
       </c>
@@ -5118,7 +5137,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>4</v>
       </c>
@@ -5141,7 +5160,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>4</v>
       </c>
@@ -5164,7 +5183,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>4</v>
       </c>
@@ -5187,7 +5206,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>4</v>
       </c>
@@ -5201,7 +5220,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>4</v>
       </c>
@@ -5215,7 +5234,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>4</v>
       </c>
@@ -5229,7 +5248,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>4</v>
       </c>
@@ -5243,7 +5262,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>5</v>
       </c>
@@ -5266,7 +5285,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>5</v>
       </c>
@@ -5289,7 +5308,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>5</v>
       </c>
@@ -5312,7 +5331,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>5</v>
       </c>
@@ -5335,7 +5354,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>5</v>
       </c>
@@ -5358,7 +5377,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>5</v>
       </c>
@@ -5381,7 +5400,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>5</v>
       </c>
@@ -5404,7 +5423,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>5</v>
       </c>
@@ -5427,7 +5446,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>5</v>
       </c>
@@ -5450,7 +5469,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>5</v>
       </c>
@@ -5473,7 +5492,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>5</v>
       </c>
@@ -5496,7 +5515,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>5</v>
       </c>
@@ -5516,7 +5535,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>5</v>
       </c>
@@ -5530,7 +5549,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>5</v>
       </c>
@@ -5544,7 +5563,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>5</v>
       </c>
@@ -5558,7 +5577,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>6</v>
       </c>
@@ -5581,7 +5600,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>6</v>
       </c>
@@ -5604,7 +5623,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>6</v>
       </c>
@@ -5612,7 +5631,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D79" t="s">
         <v>468</v>
@@ -5627,7 +5646,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>6</v>
       </c>
@@ -5650,7 +5669,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>6</v>
       </c>
@@ -5673,7 +5692,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>6</v>
       </c>
@@ -5696,7 +5715,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>6</v>
       </c>
@@ -5719,7 +5738,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>6</v>
       </c>
@@ -5742,7 +5761,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>6</v>
       </c>
@@ -5765,7 +5784,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>6</v>
       </c>
@@ -5788,7 +5807,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>6</v>
       </c>
@@ -5811,7 +5830,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>6</v>
       </c>
@@ -5834,7 +5853,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>6</v>
       </c>
@@ -5857,7 +5876,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>6</v>
       </c>
@@ -5871,7 +5890,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>6</v>
       </c>
@@ -5885,7 +5904,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>7</v>
       </c>
@@ -5908,7 +5927,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>7</v>
       </c>
@@ -5931,7 +5950,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>7</v>
       </c>
@@ -5954,7 +5973,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>7</v>
       </c>
@@ -5977,7 +5996,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>7</v>
       </c>
@@ -6000,7 +6019,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>7</v>
       </c>
@@ -6023,7 +6042,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>7</v>
       </c>
@@ -6046,7 +6065,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>7</v>
       </c>
@@ -6069,7 +6088,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>7</v>
       </c>
@@ -6092,7 +6111,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>7</v>
       </c>
@@ -6115,7 +6134,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>7</v>
       </c>
@@ -6138,7 +6157,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>7</v>
       </c>
@@ -6161,7 +6180,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>7</v>
       </c>
@@ -6184,7 +6203,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>7</v>
       </c>
@@ -6198,7 +6217,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>7</v>
       </c>
@@ -6212,7 +6231,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>8</v>
       </c>
@@ -6235,7 +6254,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>8</v>
       </c>
@@ -6258,7 +6277,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>8</v>
       </c>
@@ -6281,7 +6300,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>8</v>
       </c>
@@ -6304,21 +6323,21 @@
         <v>566</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A111">
+    <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
         <v>8</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="2">
         <v>5</v>
       </c>
-      <c r="C111" t="s">
-        <v>567</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="C111" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>8</v>
       </c>
@@ -6326,22 +6345,22 @@
         <v>6</v>
       </c>
       <c r="C112" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D112" t="s">
         <v>554</v>
       </c>
       <c r="E112" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F112" t="s">
         <v>333</v>
       </c>
       <c r="G112" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>8</v>
       </c>
@@ -6349,13 +6368,13 @@
         <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D113" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>8</v>
       </c>
@@ -6363,22 +6382,22 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D114" t="s">
         <v>554</v>
       </c>
       <c r="E114" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F114" t="s">
         <v>305</v>
       </c>
       <c r="G114" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>8</v>
       </c>
@@ -6386,7 +6405,7 @@
         <v>9</v>
       </c>
       <c r="C115" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D115" t="s">
         <v>554</v>
@@ -6398,10 +6417,10 @@
         <v>317</v>
       </c>
       <c r="G115" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>8</v>
       </c>
@@ -6409,7 +6428,7 @@
         <v>10</v>
       </c>
       <c r="C116" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D116" t="s">
         <v>554</v>
@@ -6421,10 +6440,10 @@
         <v>309</v>
       </c>
       <c r="G116" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>8</v>
       </c>
@@ -6432,7 +6451,7 @@
         <v>11</v>
       </c>
       <c r="C117" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D117" t="s">
         <v>554</v>
@@ -6444,10 +6463,10 @@
         <v>333</v>
       </c>
       <c r="G117" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>8</v>
       </c>
@@ -6455,7 +6474,7 @@
         <v>12</v>
       </c>
       <c r="C118" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D118" t="s">
         <v>554</v>
@@ -6467,10 +6486,10 @@
         <v>320</v>
       </c>
       <c r="G118" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>8</v>
       </c>
@@ -6478,7 +6497,7 @@
         <v>13</v>
       </c>
       <c r="C119" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D119" t="s">
         <v>554</v>
@@ -6490,10 +6509,10 @@
         <v>391</v>
       </c>
       <c r="G119" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>8</v>
       </c>
@@ -6501,13 +6520,13 @@
         <v>14</v>
       </c>
       <c r="C120" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D120" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>8</v>
       </c>
@@ -6515,13 +6534,13 @@
         <v>15</v>
       </c>
       <c r="C121" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D121" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>9</v>
       </c>
@@ -6529,22 +6548,22 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
+        <v>586</v>
+      </c>
+      <c r="D122" t="s">
         <v>587</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>588</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>589</v>
       </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
         <v>590</v>
       </c>
-      <c r="G122" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>9</v>
       </c>
@@ -6552,22 +6571,22 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
+        <v>591</v>
+      </c>
+      <c r="D123" t="s">
+        <v>587</v>
+      </c>
+      <c r="E123" t="s">
         <v>592</v>
       </c>
-      <c r="D123" t="s">
-        <v>588</v>
-      </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
+        <v>589</v>
+      </c>
+      <c r="G123" t="s">
         <v>593</v>
       </c>
-      <c r="F123" t="s">
-        <v>590</v>
-      </c>
-      <c r="G123" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>9</v>
       </c>
@@ -6575,19 +6594,19 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
+        <v>594</v>
+      </c>
+      <c r="D124" t="s">
+        <v>587</v>
+      </c>
+      <c r="E124" t="s">
         <v>595</v>
       </c>
-      <c r="D124" t="s">
-        <v>588</v>
-      </c>
-      <c r="E124" t="s">
-        <v>596</v>
-      </c>
       <c r="G124" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>9</v>
       </c>
@@ -6595,19 +6614,19 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
+        <v>596</v>
+      </c>
+      <c r="D125" t="s">
+        <v>587</v>
+      </c>
+      <c r="E125" t="s">
         <v>597</v>
       </c>
-      <c r="D125" t="s">
-        <v>588</v>
-      </c>
-      <c r="E125" t="s">
-        <v>598</v>
-      </c>
       <c r="G125" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>9</v>
       </c>
@@ -6615,22 +6634,22 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
+        <v>598</v>
+      </c>
+      <c r="D126" t="s">
+        <v>587</v>
+      </c>
+      <c r="E126" t="s">
         <v>599</v>
-      </c>
-      <c r="D126" t="s">
-        <v>588</v>
-      </c>
-      <c r="E126" t="s">
-        <v>600</v>
       </c>
       <c r="F126" t="s">
         <v>288</v>
       </c>
       <c r="G126" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>9</v>
       </c>
@@ -6638,13 +6657,13 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D127" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>9</v>
       </c>
@@ -6652,13 +6671,13 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D128" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>9</v>
       </c>
@@ -6666,13 +6685,13 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D129" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>9</v>
       </c>
@@ -6680,13 +6699,13 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D130" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>9</v>
       </c>
@@ -6694,13 +6713,13 @@
         <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D131" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>9</v>
       </c>
@@ -6708,13 +6727,13 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D132" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>9</v>
       </c>
@@ -6722,13 +6741,13 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D133" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>9</v>
       </c>
@@ -6736,13 +6755,13 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D134" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>9</v>
       </c>
@@ -6750,13 +6769,13 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D135" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>9</v>
       </c>
@@ -6764,13 +6783,13 @@
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D136" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>10</v>
       </c>
@@ -6778,22 +6797,22 @@
         <v>1</v>
       </c>
       <c r="C137" t="s">
+        <v>611</v>
+      </c>
+      <c r="D137" t="s">
         <v>612</v>
       </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
         <v>613</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
+        <v>128</v>
+      </c>
+      <c r="G137" t="s">
         <v>614</v>
       </c>
-      <c r="F137" t="s">
-        <v>128</v>
-      </c>
-      <c r="G137" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>10</v>
       </c>
@@ -6801,22 +6820,22 @@
         <v>2</v>
       </c>
       <c r="C138" t="s">
+        <v>615</v>
+      </c>
+      <c r="D138" t="s">
+        <v>612</v>
+      </c>
+      <c r="E138" t="s">
         <v>616</v>
       </c>
-      <c r="D138" t="s">
-        <v>613</v>
-      </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
+        <v>128</v>
+      </c>
+      <c r="G138" t="s">
         <v>617</v>
       </c>
-      <c r="F138" t="s">
-        <v>128</v>
-      </c>
-      <c r="G138" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>10</v>
       </c>
@@ -6824,22 +6843,22 @@
         <v>3</v>
       </c>
       <c r="C139" t="s">
+        <v>618</v>
+      </c>
+      <c r="D139" t="s">
+        <v>612</v>
+      </c>
+      <c r="E139" t="s">
         <v>619</v>
       </c>
-      <c r="D139" t="s">
-        <v>613</v>
-      </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
+        <v>128</v>
+      </c>
+      <c r="G139" t="s">
         <v>620</v>
       </c>
-      <c r="F139" t="s">
-        <v>128</v>
-      </c>
-      <c r="G139" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>10</v>
       </c>
@@ -6847,22 +6866,22 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
+        <v>621</v>
+      </c>
+      <c r="D140" t="s">
+        <v>612</v>
+      </c>
+      <c r="E140" t="s">
         <v>622</v>
       </c>
-      <c r="D140" t="s">
-        <v>613</v>
-      </c>
-      <c r="E140" t="s">
+      <c r="F140" t="s">
+        <v>128</v>
+      </c>
+      <c r="G140" t="s">
         <v>623</v>
       </c>
-      <c r="F140" t="s">
-        <v>128</v>
-      </c>
-      <c r="G140" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>10</v>
       </c>
@@ -6870,22 +6889,22 @@
         <v>5</v>
       </c>
       <c r="C141" t="s">
+        <v>624</v>
+      </c>
+      <c r="D141" t="s">
+        <v>612</v>
+      </c>
+      <c r="E141" t="s">
         <v>625</v>
       </c>
-      <c r="D141" t="s">
-        <v>613</v>
-      </c>
-      <c r="E141" t="s">
+      <c r="F141" t="s">
+        <v>128</v>
+      </c>
+      <c r="G141" t="s">
         <v>626</v>
       </c>
-      <c r="F141" t="s">
-        <v>128</v>
-      </c>
-      <c r="G141" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>10</v>
       </c>
@@ -6893,22 +6912,22 @@
         <v>6</v>
       </c>
       <c r="C142" t="s">
+        <v>627</v>
+      </c>
+      <c r="D142" t="s">
+        <v>612</v>
+      </c>
+      <c r="E142" t="s">
         <v>628</v>
       </c>
-      <c r="D142" t="s">
-        <v>613</v>
-      </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
+        <v>128</v>
+      </c>
+      <c r="G142" t="s">
         <v>629</v>
       </c>
-      <c r="F142" t="s">
-        <v>128</v>
-      </c>
-      <c r="G142" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>10</v>
       </c>
@@ -6916,22 +6935,22 @@
         <v>7</v>
       </c>
       <c r="C143" t="s">
+        <v>630</v>
+      </c>
+      <c r="D143" t="s">
+        <v>612</v>
+      </c>
+      <c r="E143" t="s">
         <v>631</v>
-      </c>
-      <c r="D143" t="s">
-        <v>613</v>
-      </c>
-      <c r="E143" t="s">
-        <v>632</v>
       </c>
       <c r="F143" t="s">
         <v>367</v>
       </c>
       <c r="G143" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>10</v>
       </c>
@@ -6939,22 +6958,22 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
+        <v>633</v>
+      </c>
+      <c r="D144" t="s">
+        <v>612</v>
+      </c>
+      <c r="E144" t="s">
         <v>634</v>
-      </c>
-      <c r="D144" t="s">
-        <v>613</v>
-      </c>
-      <c r="E144" t="s">
-        <v>635</v>
       </c>
       <c r="F144" t="s">
         <v>367</v>
       </c>
       <c r="G144" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>10</v>
       </c>
@@ -6962,22 +6981,22 @@
         <v>9</v>
       </c>
       <c r="C145" t="s">
+        <v>636</v>
+      </c>
+      <c r="D145" t="s">
+        <v>612</v>
+      </c>
+      <c r="E145" t="s">
         <v>637</v>
-      </c>
-      <c r="D145" t="s">
-        <v>613</v>
-      </c>
-      <c r="E145" t="s">
-        <v>638</v>
       </c>
       <c r="F145" t="s">
         <v>367</v>
       </c>
       <c r="G145" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>10</v>
       </c>
@@ -6985,22 +7004,22 @@
         <v>10</v>
       </c>
       <c r="C146" t="s">
+        <v>639</v>
+      </c>
+      <c r="D146" t="s">
+        <v>612</v>
+      </c>
+      <c r="E146" t="s">
         <v>640</v>
-      </c>
-      <c r="D146" t="s">
-        <v>613</v>
-      </c>
-      <c r="E146" t="s">
-        <v>641</v>
       </c>
       <c r="F146" t="s">
         <v>367</v>
       </c>
       <c r="G146" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>10</v>
       </c>
@@ -7008,22 +7027,22 @@
         <v>11</v>
       </c>
       <c r="C147" t="s">
+        <v>642</v>
+      </c>
+      <c r="D147" t="s">
+        <v>612</v>
+      </c>
+      <c r="E147" t="s">
         <v>643</v>
-      </c>
-      <c r="D147" t="s">
-        <v>613</v>
-      </c>
-      <c r="E147" t="s">
-        <v>644</v>
       </c>
       <c r="F147" t="s">
         <v>367</v>
       </c>
       <c r="G147" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>10</v>
       </c>
@@ -7031,22 +7050,22 @@
         <v>12</v>
       </c>
       <c r="C148" t="s">
+        <v>645</v>
+      </c>
+      <c r="D148" t="s">
+        <v>612</v>
+      </c>
+      <c r="E148" t="s">
         <v>646</v>
-      </c>
-      <c r="D148" t="s">
-        <v>613</v>
-      </c>
-      <c r="E148" t="s">
-        <v>647</v>
       </c>
       <c r="F148" t="s">
         <v>367</v>
       </c>
       <c r="G148" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>10</v>
       </c>
@@ -7054,22 +7073,22 @@
         <v>13</v>
       </c>
       <c r="C149" t="s">
+        <v>648</v>
+      </c>
+      <c r="D149" t="s">
+        <v>612</v>
+      </c>
+      <c r="E149" t="s">
         <v>649</v>
-      </c>
-      <c r="D149" t="s">
-        <v>613</v>
-      </c>
-      <c r="E149" t="s">
-        <v>650</v>
       </c>
       <c r="F149" t="s">
         <v>367</v>
       </c>
       <c r="G149" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>10</v>
       </c>
@@ -7077,22 +7096,22 @@
         <v>14</v>
       </c>
       <c r="C150" t="s">
+        <v>651</v>
+      </c>
+      <c r="D150" t="s">
+        <v>612</v>
+      </c>
+      <c r="E150" t="s">
         <v>652</v>
-      </c>
-      <c r="D150" t="s">
-        <v>613</v>
-      </c>
-      <c r="E150" t="s">
-        <v>653</v>
       </c>
       <c r="F150" t="s">
         <v>367</v>
       </c>
       <c r="G150" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>10</v>
       </c>
@@ -7100,10 +7119,10 @@
         <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D151" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D4B1DB-C209-4CD2-9C1E-16211B50C510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C82BB0D-3538-4671-851F-A0E1C650C218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59400" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16920" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="669">
   <si>
     <t>pFS2</t>
   </si>
@@ -1998,6 +1998,42 @@
   </si>
   <si>
     <t>test_output</t>
+  </si>
+  <si>
+    <t>beta0</t>
+  </si>
+  <si>
+    <t>betaB</t>
+  </si>
+  <si>
+    <t>betaN</t>
+  </si>
+  <si>
+    <t>betafN</t>
+  </si>
+  <si>
+    <t>betafT</t>
+  </si>
+  <si>
+    <t>betafPhys</t>
+  </si>
+  <si>
+    <t>constant for self-thinning when mort_model = 2</t>
+  </si>
+  <si>
+    <t>Power for B when mort_model = 2</t>
+  </si>
+  <si>
+    <t>Power in tree density when mort_model = 2</t>
+  </si>
+  <si>
+    <t>Power in fertility modifier when mort_model = 2</t>
+  </si>
+  <si>
+    <t>Power in temperature modifier when mort_model = 2</t>
+  </si>
+  <si>
+    <t>Power in physmod modifier when mort_model = 2</t>
   </si>
 </sst>
 </file>
@@ -2019,24 +2055,28 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2052,10 +2092,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2371,10 +2412,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E287297-02C0-BF44-BF0C-8FADE2A87F8F}">
-  <dimension ref="A1:D83"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D89"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -2388,7 +2429,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2402,7 +2443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2416,7 +2457,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2430,7 +2471,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2444,7 +2485,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2458,7 +2499,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2472,7 +2513,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2486,7 +2527,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2500,7 +2541,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2514,7 +2555,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2528,7 +2569,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2542,7 +2583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2556,7 +2597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2570,7 +2611,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2584,7 +2625,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2598,7 +2639,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2612,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2626,7 +2667,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2640,7 +2681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2654,7 +2695,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2668,7 +2709,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2682,7 +2723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2696,7 +2737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2710,7 +2751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2724,7 +2765,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2738,7 +2779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -2752,7 +2793,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -2766,7 +2807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2780,7 +2821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -2794,7 +2835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -2808,7 +2849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2822,7 +2863,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -2836,502 +2877,490 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1">
+        <v>-20.399999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B40" t="s">
         <v>167</v>
       </c>
-      <c r="C34" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34">
+      <c r="C40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D40">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B41" t="s">
         <v>168</v>
       </c>
-      <c r="C35" t="s">
-        <v>128</v>
-      </c>
-      <c r="D35">
+      <c r="C41" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41">
         <v>0.2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B42" t="s">
         <v>169</v>
       </c>
-      <c r="C36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36">
+      <c r="C42" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42">
         <v>0.2</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B43" t="s">
         <v>170</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C43" t="s">
         <v>171</v>
       </c>
-      <c r="D37">
+      <c r="D43">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B44" t="s">
         <v>172</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C44" t="s">
         <v>171</v>
       </c>
-      <c r="D38">
+      <c r="D44">
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B45" t="s">
         <v>173</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C45" t="s">
         <v>156</v>
       </c>
-      <c r="D39">
+      <c r="D45">
         <v>2.5</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B46" t="s">
         <v>174</v>
       </c>
-      <c r="C40" t="s">
-        <v>128</v>
-      </c>
-      <c r="D40">
+      <c r="C46" t="s">
+        <v>128</v>
+      </c>
+      <c r="D46">
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B47" t="s">
         <v>175</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C47" t="s">
         <v>156</v>
       </c>
-      <c r="D41">
+      <c r="D47">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B48" t="s">
         <v>176</v>
       </c>
-      <c r="C42" t="s">
-        <v>128</v>
-      </c>
-      <c r="D42">
+      <c r="C48" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48">
         <v>0.15</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B49" t="s">
         <v>177</v>
       </c>
-      <c r="C43" t="s">
-        <v>128</v>
-      </c>
-      <c r="D43">
+      <c r="C49" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B50" t="s">
         <v>178</v>
       </c>
-      <c r="C44" t="s">
-        <v>128</v>
-      </c>
-      <c r="D44">
+      <c r="C50" t="s">
+        <v>128</v>
+      </c>
+      <c r="D50">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B51" t="s">
         <v>179</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C51" t="s">
         <v>180</v>
       </c>
-      <c r="D45">
+      <c r="D51">
         <v>0.06</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B52" t="s">
         <v>181</v>
       </c>
-      <c r="C46" t="s">
-        <v>128</v>
-      </c>
-      <c r="D46">
+      <c r="C52" t="s">
+        <v>128</v>
+      </c>
+      <c r="D52">
         <v>0.47</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B53" t="s">
         <v>182</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C53" t="s">
         <v>183</v>
       </c>
-      <c r="D47">
+      <c r="D53">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B54" t="s">
         <v>184</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C54" t="s">
         <v>183</v>
       </c>
-      <c r="D48">
+      <c r="D54">
         <v>0.02</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B55" t="s">
         <v>185</v>
       </c>
-      <c r="C49" t="s">
-        <v>128</v>
-      </c>
-      <c r="D49">
+      <c r="C55" t="s">
+        <v>128</v>
+      </c>
+      <c r="D55">
         <v>3.33</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B56" t="s">
         <v>186</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C56" t="s">
         <v>187</v>
       </c>
-      <c r="D50">
+      <c r="D56">
         <v>0.05</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B57" t="s">
         <v>188</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C57" t="s">
         <v>183</v>
       </c>
-      <c r="D51">
+      <c r="D57">
         <v>0.2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B58" t="s">
         <v>189</v>
       </c>
-      <c r="C52" t="s">
-        <v>128</v>
-      </c>
-      <c r="D52">
+      <c r="C58" t="s">
+        <v>128</v>
+      </c>
+      <c r="D58">
         <v>0.66</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B59" t="s">
         <v>190</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C59" t="s">
         <v>191</v>
       </c>
-      <c r="D53">
+      <c r="D59">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B60" t="s">
         <v>192</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C60" t="s">
         <v>191</v>
       </c>
-      <c r="D54">
+      <c r="D60">
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B61" t="s">
         <v>193</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C61" t="s">
         <v>191</v>
       </c>
-      <c r="D55">
+      <c r="D61">
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B62" t="s">
         <v>194</v>
       </c>
-      <c r="C56" t="s">
-        <v>128</v>
-      </c>
-      <c r="D56">
+      <c r="C62" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62">
         <v>0.75</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B63" t="s">
         <v>195</v>
       </c>
-      <c r="C57" t="s">
-        <v>128</v>
-      </c>
-      <c r="D57">
+      <c r="C63" t="s">
+        <v>128</v>
+      </c>
+      <c r="D63">
         <v>0.15</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B64" t="s">
         <v>196</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C64" t="s">
         <v>156</v>
       </c>
-      <c r="D58">
+      <c r="D64">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B65" t="s">
         <v>197</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C65" t="s">
         <v>198</v>
       </c>
-      <c r="D59">
+      <c r="D65">
         <v>0.45</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B66" t="s">
         <v>199</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C66" t="s">
         <v>198</v>
       </c>
-      <c r="D60">
+      <c r="D66">
         <v>0.45</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B67" t="s">
         <v>200</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C67" t="s">
         <v>156</v>
       </c>
-      <c r="D61">
+      <c r="D67">
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>68</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B68" t="s">
         <v>201</v>
       </c>
-      <c r="C62" t="s">
-        <v>128</v>
-      </c>
-      <c r="D62">
+      <c r="C68" t="s">
+        <v>128</v>
+      </c>
+      <c r="D68">
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>61</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B69" t="s">
         <v>202</v>
-      </c>
-      <c r="C63" t="s">
-        <v>128</v>
-      </c>
-      <c r="D63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>62</v>
-      </c>
-      <c r="B64" t="s">
-        <v>203</v>
-      </c>
-      <c r="C64" t="s">
-        <v>128</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>63</v>
-      </c>
-      <c r="B65" t="s">
-        <v>204</v>
-      </c>
-      <c r="C65" t="s">
-        <v>128</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>64</v>
-      </c>
-      <c r="B66" t="s">
-        <v>205</v>
-      </c>
-      <c r="C66" t="s">
-        <v>128</v>
-      </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" t="s">
-        <v>206</v>
-      </c>
-      <c r="C67" t="s">
-        <v>128</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>66</v>
-      </c>
-      <c r="B68" t="s">
-        <v>207</v>
-      </c>
-      <c r="C68" t="s">
-        <v>128</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>67</v>
-      </c>
-      <c r="B69" t="s">
-        <v>208</v>
       </c>
       <c r="C69" t="s">
         <v>128</v>
@@ -3340,12 +3369,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B70" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C70" t="s">
         <v>128</v>
@@ -3354,12 +3383,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B71" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C71" t="s">
         <v>128</v>
@@ -3368,12 +3397,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B72" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C72" t="s">
         <v>128</v>
@@ -3382,12 +3411,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B73" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C73" t="s">
         <v>128</v>
@@ -3396,12 +3425,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B74" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C74" t="s">
         <v>128</v>
@@ -3410,12 +3439,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B75" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C75" t="s">
         <v>128</v>
@@ -3424,12 +3453,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B76" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C76" t="s">
         <v>128</v>
@@ -3438,12 +3467,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B77" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C77" t="s">
         <v>128</v>
@@ -3452,12 +3481,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B78" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C78" t="s">
         <v>128</v>
@@ -3466,12 +3495,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B79" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C79" t="s">
         <v>128</v>
@@ -3480,59 +3509,143 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>73</v>
+      </c>
+      <c r="B80" t="s">
+        <v>213</v>
+      </c>
+      <c r="C80" t="s">
+        <v>128</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>74</v>
+      </c>
+      <c r="B81" t="s">
+        <v>214</v>
+      </c>
+      <c r="C81" t="s">
+        <v>128</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>75</v>
+      </c>
+      <c r="B82" t="s">
+        <v>215</v>
+      </c>
+      <c r="C82" t="s">
+        <v>128</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>76</v>
+      </c>
+      <c r="B83" t="s">
+        <v>216</v>
+      </c>
+      <c r="C83" t="s">
+        <v>128</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>77</v>
+      </c>
+      <c r="B84" t="s">
+        <v>217</v>
+      </c>
+      <c r="C84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>78</v>
+      </c>
+      <c r="B85" t="s">
+        <v>218</v>
+      </c>
+      <c r="C85" t="s">
+        <v>128</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>109</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B86" t="s">
         <v>219</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C86" t="s">
         <v>220</v>
       </c>
-      <c r="D80">
+      <c r="D86">
         <v>-90</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
         <v>110</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B87" t="s">
         <v>221</v>
       </c>
-      <c r="C81" t="s">
-        <v>128</v>
-      </c>
-      <c r="D81">
+      <c r="C87" t="s">
+        <v>128</v>
+      </c>
+      <c r="D87">
         <v>0.8</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>111</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B88" t="s">
         <v>222</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C88" t="s">
         <v>223</v>
       </c>
-      <c r="D82">
+      <c r="D88">
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>112</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B89" t="s">
         <v>224</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C89" t="s">
         <v>225</v>
       </c>
-      <c r="D83">
+      <c r="D89">
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -3544,9 +3657,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF000D6-A72C-6444-9177-22D437B8361A}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -3560,7 +3673,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -3574,7 +3687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -3588,7 +3701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -3602,7 +3715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -3616,7 +3729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -3630,7 +3743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -3644,7 +3757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -3658,7 +3771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -3672,7 +3785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -3686,7 +3799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -3700,7 +3813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -3714,7 +3827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -3728,7 +3841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -3742,7 +3855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -3756,7 +3869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -3770,7 +3883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -3784,7 +3897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -3798,7 +3911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -3812,7 +3925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>97</v>
       </c>
@@ -3826,7 +3939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -3840,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>99</v>
       </c>
@@ -3854,7 +3967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>100</v>
       </c>
@@ -3868,7 +3981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -3882,7 +3995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -3896,7 +4009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>103</v>
       </c>
@@ -3910,7 +4023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -3924,7 +4037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>105</v>
       </c>
@@ -3938,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -3952,7 +4065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -3966,7 +4079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>108</v>
       </c>
@@ -3988,13 +4101,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA3706E6-9BD2-3A49-A255-D2B55C8D9AB1}">
   <dimension ref="A1:G151"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="179" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>256</v>
       </c>
@@ -4017,7 +4130,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4040,7 +4153,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4063,7 +4176,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4086,7 +4199,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4109,7 +4222,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4132,7 +4245,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4155,7 +4268,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4178,7 +4291,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -4201,7 +4314,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -4224,7 +4337,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -4244,7 +4357,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -4267,7 +4380,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -4281,7 +4394,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -4295,7 +4408,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -4309,7 +4422,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -4323,7 +4436,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -4346,7 +4459,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4369,7 +4482,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4392,7 +4505,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4415,7 +4528,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4438,7 +4551,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4461,7 +4574,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -4484,7 +4597,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2</v>
       </c>
@@ -4507,7 +4620,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2</v>
       </c>
@@ -4530,7 +4643,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2</v>
       </c>
@@ -4553,7 +4666,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2</v>
       </c>
@@ -4576,7 +4689,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>2</v>
       </c>
@@ -4599,7 +4712,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>2</v>
       </c>
@@ -4622,7 +4735,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>2</v>
       </c>
@@ -4636,7 +4749,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>2</v>
       </c>
@@ -4650,7 +4763,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -4673,7 +4786,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -4696,7 +4809,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -4719,7 +4832,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4742,7 +4855,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4762,7 +4875,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4785,7 +4898,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4808,7 +4921,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -4831,7 +4944,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -4854,7 +4967,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -4877,7 +4990,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -4900,7 +5013,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -4914,7 +5027,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>3</v>
       </c>
@@ -4928,7 +5041,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>3</v>
       </c>
@@ -4942,7 +5055,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>3</v>
       </c>
@@ -4956,7 +5069,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -4979,7 +5092,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -5002,7 +5115,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -5025,7 +5138,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -5048,7 +5161,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -5071,7 +5184,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -5091,7 +5204,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -5114,7 +5227,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -5137,7 +5250,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -5160,7 +5273,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -5183,7 +5296,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -5206,7 +5319,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -5220,7 +5333,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>4</v>
       </c>
@@ -5234,7 +5347,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>4</v>
       </c>
@@ -5248,7 +5361,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>4</v>
       </c>
@@ -5262,7 +5375,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -5285,7 +5398,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -5308,7 +5421,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -5331,7 +5444,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>5</v>
       </c>
@@ -5354,7 +5467,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>5</v>
       </c>
@@ -5377,7 +5490,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>5</v>
       </c>
@@ -5400,7 +5513,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>5</v>
       </c>
@@ -5423,7 +5536,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>5</v>
       </c>
@@ -5446,7 +5559,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>5</v>
       </c>
@@ -5469,7 +5582,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>5</v>
       </c>
@@ -5492,7 +5605,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>5</v>
       </c>
@@ -5515,7 +5628,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>5</v>
       </c>
@@ -5535,7 +5648,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>5</v>
       </c>
@@ -5549,7 +5662,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>5</v>
       </c>
@@ -5563,7 +5676,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>5</v>
       </c>
@@ -5577,7 +5690,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>6</v>
       </c>
@@ -5600,7 +5713,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>6</v>
       </c>
@@ -5623,7 +5736,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>6</v>
       </c>
@@ -5646,7 +5759,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>6</v>
       </c>
@@ -5669,7 +5782,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>6</v>
       </c>
@@ -5692,7 +5805,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>6</v>
       </c>
@@ -5715,7 +5828,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>6</v>
       </c>
@@ -5738,7 +5851,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>6</v>
       </c>
@@ -5761,7 +5874,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>6</v>
       </c>
@@ -5784,7 +5897,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>6</v>
       </c>
@@ -5807,7 +5920,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>6</v>
       </c>
@@ -5830,7 +5943,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>6</v>
       </c>
@@ -5853,7 +5966,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>6</v>
       </c>
@@ -5876,7 +5989,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>6</v>
       </c>
@@ -5890,7 +6003,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>6</v>
       </c>
@@ -5904,7 +6017,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>7</v>
       </c>
@@ -5927,7 +6040,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>7</v>
       </c>
@@ -5950,7 +6063,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>7</v>
       </c>
@@ -5973,7 +6086,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>7</v>
       </c>
@@ -5996,7 +6109,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>7</v>
       </c>
@@ -6019,7 +6132,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>7</v>
       </c>
@@ -6042,7 +6155,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>7</v>
       </c>
@@ -6065,7 +6178,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>7</v>
       </c>
@@ -6088,7 +6201,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>7</v>
       </c>
@@ -6111,7 +6224,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>7</v>
       </c>
@@ -6134,7 +6247,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>7</v>
       </c>
@@ -6157,7 +6270,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>7</v>
       </c>
@@ -6180,7 +6293,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>7</v>
       </c>
@@ -6203,7 +6316,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>7</v>
       </c>
@@ -6217,7 +6330,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>7</v>
       </c>
@@ -6231,7 +6344,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>8</v>
       </c>
@@ -6254,7 +6367,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>8</v>
       </c>
@@ -6277,7 +6390,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>8</v>
       </c>
@@ -6300,7 +6413,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>8</v>
       </c>
@@ -6323,21 +6436,21 @@
         <v>566</v>
       </c>
     </row>
-    <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>8</v>
       </c>
       <c r="B111" s="2">
         <v>5</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="3" t="s">
         <v>656</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>8</v>
       </c>
@@ -6360,7 +6473,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>8</v>
       </c>
@@ -6374,7 +6487,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>8</v>
       </c>
@@ -6397,7 +6510,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>8</v>
       </c>
@@ -6420,7 +6533,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>8</v>
       </c>
@@ -6443,7 +6556,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>8</v>
       </c>
@@ -6466,7 +6579,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>8</v>
       </c>
@@ -6489,7 +6602,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>8</v>
       </c>
@@ -6512,7 +6625,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>8</v>
       </c>
@@ -6526,7 +6639,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>8</v>
       </c>
@@ -6540,7 +6653,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>9</v>
       </c>
@@ -6563,7 +6676,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>9</v>
       </c>
@@ -6586,7 +6699,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>9</v>
       </c>
@@ -6606,7 +6719,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>9</v>
       </c>
@@ -6626,7 +6739,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>9</v>
       </c>
@@ -6649,7 +6762,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>9</v>
       </c>
@@ -6663,7 +6776,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>9</v>
       </c>
@@ -6677,7 +6790,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>9</v>
       </c>
@@ -6691,7 +6804,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>9</v>
       </c>
@@ -6705,7 +6818,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>9</v>
       </c>
@@ -6719,7 +6832,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>9</v>
       </c>
@@ -6733,7 +6846,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>9</v>
       </c>
@@ -6747,7 +6860,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>9</v>
       </c>
@@ -6761,7 +6874,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>9</v>
       </c>
@@ -6775,7 +6888,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>9</v>
       </c>
@@ -6789,7 +6902,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>10</v>
       </c>
@@ -6812,7 +6925,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>10</v>
       </c>
@@ -6835,7 +6948,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>10</v>
       </c>
@@ -6858,7 +6971,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>10</v>
       </c>
@@ -6881,7 +6994,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>10</v>
       </c>
@@ -6904,7 +7017,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>10</v>
       </c>
@@ -6927,7 +7040,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>10</v>
       </c>
@@ -6950,7 +7063,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>10</v>
       </c>
@@ -6973,7 +7086,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>10</v>
       </c>
@@ -6996,7 +7109,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>10</v>
       </c>
@@ -7019,7 +7132,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>10</v>
       </c>
@@ -7042,7 +7155,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>10</v>
       </c>
@@ -7065,7 +7178,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>10</v>
       </c>
@@ -7088,7 +7201,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>10</v>
       </c>
@@ -7111,7 +7224,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>10</v>
       </c>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C82BB0D-3538-4671-851F-A0E1C650C218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10201B4-0DF6-47FB-8335-B8B0A023989D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16920" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="59400" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -1730,60 +1730,33 @@
     <t>Stem mortality</t>
   </si>
   <si>
-    <t>volume_extracted</t>
-  </si>
-  <si>
     <t>Volume extracted during the most recent thinning event</t>
   </si>
   <si>
     <t>Latest extracted volume</t>
   </si>
   <si>
-    <t>var_8_7</t>
-  </si>
-  <si>
-    <t>var_8_8</t>
-  </si>
-  <si>
     <t>Number of crop trees (x)</t>
   </si>
   <si>
     <t>CropTrees per ha</t>
   </si>
   <si>
-    <t>var_8_9</t>
-  </si>
-  <si>
     <t>CropTree Mean DBH</t>
   </si>
   <si>
-    <t>var_8_10</t>
-  </si>
-  <si>
     <t>CropTree Basal area</t>
   </si>
   <si>
-    <t>var_8_11</t>
-  </si>
-  <si>
     <t>CropTree volume</t>
   </si>
   <si>
-    <t>var_8_12</t>
-  </si>
-  <si>
     <t>CropTree Height</t>
   </si>
   <si>
-    <t>var_8_13</t>
-  </si>
-  <si>
     <t>CropTree Stem DM</t>
   </si>
   <si>
-    <t>var_8_14</t>
-  </si>
-  <si>
     <t>var_8_15</t>
   </si>
   <si>
@@ -2034,6 +2007,33 @@
   </si>
   <si>
     <t>Power in physmod modifier when mort_model = 2</t>
+  </si>
+  <si>
+    <t>mort_thinn_total</t>
+  </si>
+  <si>
+    <t>ave_lt_fN</t>
+  </si>
+  <si>
+    <t>ave_lt_fT</t>
+  </si>
+  <si>
+    <t>ave_lt_fPhys</t>
+  </si>
+  <si>
+    <t>lt_fN</t>
+  </si>
+  <si>
+    <t>lt_fT</t>
+  </si>
+  <si>
+    <t>lt_fPhys</t>
+  </si>
+  <si>
+    <t>dbh_total</t>
+  </si>
+  <si>
+    <t>stems_n_total</t>
   </si>
 </sst>
 </file>
@@ -2879,10 +2879,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -2891,10 +2891,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -2903,10 +2903,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -2927,10 +2927,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -2939,10 +2939,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -5744,7 +5744,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="D79" t="s">
         <v>468</v>
@@ -6444,7 +6444,7 @@
         <v>5</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>554</v>
@@ -6457,20 +6457,20 @@
       <c r="B112">
         <v>6</v>
       </c>
-      <c r="C112" t="s">
-        <v>567</v>
+      <c r="C112" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="D112" t="s">
         <v>554</v>
       </c>
       <c r="E112" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F112" t="s">
         <v>333</v>
       </c>
       <c r="G112" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
@@ -6480,8 +6480,8 @@
       <c r="B113">
         <v>7</v>
       </c>
-      <c r="C113" t="s">
-        <v>570</v>
+      <c r="C113" s="1" t="s">
+        <v>661</v>
       </c>
       <c r="D113" t="s">
         <v>554</v>
@@ -6494,20 +6494,20 @@
       <c r="B114">
         <v>8</v>
       </c>
-      <c r="C114" t="s">
-        <v>571</v>
+      <c r="C114" s="1" t="s">
+        <v>662</v>
       </c>
       <c r="D114" t="s">
         <v>554</v>
       </c>
       <c r="E114" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="F114" t="s">
         <v>305</v>
       </c>
       <c r="G114" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
@@ -6517,8 +6517,8 @@
       <c r="B115">
         <v>9</v>
       </c>
-      <c r="C115" t="s">
-        <v>574</v>
+      <c r="C115" s="1" t="s">
+        <v>663</v>
       </c>
       <c r="D115" t="s">
         <v>554</v>
@@ -6530,7 +6530,7 @@
         <v>317</v>
       </c>
       <c r="G115" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
@@ -6540,8 +6540,8 @@
       <c r="B116">
         <v>10</v>
       </c>
-      <c r="C116" t="s">
-        <v>576</v>
+      <c r="C116" s="1" t="s">
+        <v>664</v>
       </c>
       <c r="D116" t="s">
         <v>554</v>
@@ -6553,7 +6553,7 @@
         <v>309</v>
       </c>
       <c r="G116" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
@@ -6563,8 +6563,8 @@
       <c r="B117">
         <v>11</v>
       </c>
-      <c r="C117" t="s">
-        <v>578</v>
+      <c r="C117" s="1" t="s">
+        <v>665</v>
       </c>
       <c r="D117" t="s">
         <v>554</v>
@@ -6576,7 +6576,7 @@
         <v>333</v>
       </c>
       <c r="G117" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
@@ -6586,8 +6586,8 @@
       <c r="B118">
         <v>12</v>
       </c>
-      <c r="C118" t="s">
-        <v>580</v>
+      <c r="C118" s="1" t="s">
+        <v>666</v>
       </c>
       <c r="D118" t="s">
         <v>554</v>
@@ -6599,7 +6599,7 @@
         <v>320</v>
       </c>
       <c r="G118" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
@@ -6609,8 +6609,8 @@
       <c r="B119">
         <v>13</v>
       </c>
-      <c r="C119" t="s">
-        <v>582</v>
+      <c r="C119" s="1" t="s">
+        <v>667</v>
       </c>
       <c r="D119" t="s">
         <v>554</v>
@@ -6622,7 +6622,7 @@
         <v>391</v>
       </c>
       <c r="G119" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
@@ -6632,8 +6632,8 @@
       <c r="B120">
         <v>14</v>
       </c>
-      <c r="C120" t="s">
-        <v>584</v>
+      <c r="C120" s="1" t="s">
+        <v>668</v>
       </c>
       <c r="D120" t="s">
         <v>554</v>
@@ -6647,7 +6647,7 @@
         <v>15</v>
       </c>
       <c r="C121" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="D121" t="s">
         <v>554</v>
@@ -6661,19 +6661,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="D122" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E122" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="F122" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="G122" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
@@ -6684,19 +6684,19 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="D123" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E123" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="F123" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="G123" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
@@ -6707,16 +6707,16 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="D124" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E124" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="G124" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
@@ -6727,16 +6727,16 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="D125" t="s">
+        <v>578</v>
+      </c>
+      <c r="E125" t="s">
+        <v>588</v>
+      </c>
+      <c r="G125" t="s">
         <v>587</v>
-      </c>
-      <c r="E125" t="s">
-        <v>597</v>
-      </c>
-      <c r="G125" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
@@ -6747,19 +6747,19 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="D126" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E126" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="F126" t="s">
         <v>288</v>
       </c>
       <c r="G126" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
@@ -6770,10 +6770,10 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="D127" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
@@ -6784,10 +6784,10 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="D128" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
@@ -6798,10 +6798,10 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="D129" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
@@ -6812,10 +6812,10 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D130" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
@@ -6826,10 +6826,10 @@
         <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="D131" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
@@ -6840,10 +6840,10 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="D132" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
@@ -6854,10 +6854,10 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="D133" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
@@ -6868,10 +6868,10 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="D134" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
@@ -6882,10 +6882,10 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="D135" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
@@ -6896,10 +6896,10 @@
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="D136" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
@@ -6910,19 +6910,19 @@
         <v>1</v>
       </c>
       <c r="C137" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="D137" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E137" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="F137" t="s">
         <v>128</v>
       </c>
       <c r="G137" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
@@ -6933,19 +6933,19 @@
         <v>2</v>
       </c>
       <c r="C138" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="D138" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E138" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="F138" t="s">
         <v>128</v>
       </c>
       <c r="G138" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -6956,19 +6956,19 @@
         <v>3</v>
       </c>
       <c r="C139" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="D139" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E139" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="F139" t="s">
         <v>128</v>
       </c>
       <c r="G139" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -6979,19 +6979,19 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="D140" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E140" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="F140" t="s">
         <v>128</v>
       </c>
       <c r="G140" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -7002,19 +7002,19 @@
         <v>5</v>
       </c>
       <c r="C141" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="D141" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E141" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="F141" t="s">
         <v>128</v>
       </c>
       <c r="G141" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -7025,19 +7025,19 @@
         <v>6</v>
       </c>
       <c r="C142" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="D142" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E142" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="F142" t="s">
         <v>128</v>
       </c>
       <c r="G142" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -7048,19 +7048,19 @@
         <v>7</v>
       </c>
       <c r="C143" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="D143" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E143" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="F143" t="s">
         <v>367</v>
       </c>
       <c r="G143" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -7071,19 +7071,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="D144" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E144" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="F144" t="s">
         <v>367</v>
       </c>
       <c r="G144" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -7094,19 +7094,19 @@
         <v>9</v>
       </c>
       <c r="C145" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="D145" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E145" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="F145" t="s">
         <v>367</v>
       </c>
       <c r="G145" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -7117,19 +7117,19 @@
         <v>10</v>
       </c>
       <c r="C146" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="D146" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E146" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="F146" t="s">
         <v>367</v>
       </c>
       <c r="G146" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -7140,19 +7140,19 @@
         <v>11</v>
       </c>
       <c r="C147" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="D147" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E147" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="F147" t="s">
         <v>367</v>
       </c>
       <c r="G147" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -7163,19 +7163,19 @@
         <v>12</v>
       </c>
       <c r="C148" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="D148" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E148" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="F148" t="s">
         <v>367</v>
       </c>
       <c r="G148" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -7186,19 +7186,19 @@
         <v>13</v>
       </c>
       <c r="C149" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="D149" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E149" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="F149" t="s">
         <v>367</v>
       </c>
       <c r="G149" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -7209,19 +7209,19 @@
         <v>14</v>
       </c>
       <c r="C150" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="D150" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E150" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="F150" t="s">
         <v>367</v>
       </c>
       <c r="G150" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -7232,10 +7232,10 @@
         <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="D151" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10201B4-0DF6-47FB-8335-B8B0A023989D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EF81DE-07A2-5E4F-8014-C289F453FBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59400" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="1080" yWindow="500" windowWidth="50120" windowHeight="28300" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="670">
   <si>
     <t>pFS2</t>
   </si>
@@ -2034,6 +2034,9 @@
   </si>
   <si>
     <t>stems_n_total</t>
+  </si>
+  <si>
+    <t>Stems number of the active cohorts</t>
   </si>
 </sst>
 </file>
@@ -2413,9 +2416,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E287297-02C0-BF44-BF0C-8FADE2A87F8F}">
   <dimension ref="A1:D89"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -2429,7 +2432,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2443,7 +2446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2457,7 +2460,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2471,7 +2474,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2485,7 +2488,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2499,7 +2502,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2513,7 +2516,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2527,7 +2530,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2541,7 +2544,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2555,7 +2558,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2569,7 +2572,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2583,7 +2586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2597,7 +2600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2611,7 +2614,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2625,7 +2628,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2639,7 +2642,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2653,7 +2656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2667,7 +2670,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2681,7 +2684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2695,7 +2698,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2709,7 +2712,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2723,7 +2726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2737,7 +2740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2751,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2765,7 +2768,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2779,7 +2782,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -2793,7 +2796,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -2807,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2821,7 +2824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -2835,7 +2838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -2849,7 +2852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2863,7 +2866,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -2877,7 +2880,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>648</v>
       </c>
@@ -2889,7 +2892,7 @@
         <v>-20.399999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>649</v>
       </c>
@@ -2901,7 +2904,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>650</v>
       </c>
@@ -2913,7 +2916,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>651</v>
       </c>
@@ -2925,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>652</v>
       </c>
@@ -2937,7 +2940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>653</v>
       </c>
@@ -2949,7 +2952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>33</v>
       </c>
@@ -2963,7 +2966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>34</v>
       </c>
@@ -2977,7 +2980,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>35</v>
       </c>
@@ -2991,7 +2994,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>36</v>
       </c>
@@ -3005,7 +3008,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>37</v>
       </c>
@@ -3019,7 +3022,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -3033,7 +3036,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -3047,7 +3050,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>40</v>
       </c>
@@ -3061,7 +3064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>41</v>
       </c>
@@ -3075,7 +3078,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -3089,7 +3092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>43</v>
       </c>
@@ -3103,7 +3106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -3117,7 +3120,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -3131,7 +3134,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>46</v>
       </c>
@@ -3145,7 +3148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -3159,7 +3162,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>48</v>
       </c>
@@ -3173,7 +3176,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -3187,7 +3190,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>50</v>
       </c>
@@ -3201,7 +3204,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>51</v>
       </c>
@@ -3215,7 +3218,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -3229,7 +3232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>53</v>
       </c>
@@ -3243,7 +3246,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>54</v>
       </c>
@@ -3257,7 +3260,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -3271,7 +3274,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>56</v>
       </c>
@@ -3285,7 +3288,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>57</v>
       </c>
@@ -3299,7 +3302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>58</v>
       </c>
@@ -3313,7 +3316,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>59</v>
       </c>
@@ -3327,7 +3330,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>60</v>
       </c>
@@ -3341,7 +3344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -3355,7 +3358,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>61</v>
       </c>
@@ -3369,7 +3372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>62</v>
       </c>
@@ -3383,7 +3386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>63</v>
       </c>
@@ -3397,7 +3400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>64</v>
       </c>
@@ -3411,7 +3414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>65</v>
       </c>
@@ -3425,7 +3428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>66</v>
       </c>
@@ -3439,7 +3442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>67</v>
       </c>
@@ -3453,7 +3456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>69</v>
       </c>
@@ -3467,7 +3470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>70</v>
       </c>
@@ -3481,7 +3484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>71</v>
       </c>
@@ -3495,7 +3498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>72</v>
       </c>
@@ -3509,7 +3512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>73</v>
       </c>
@@ -3523,7 +3526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>74</v>
       </c>
@@ -3537,7 +3540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>75</v>
       </c>
@@ -3551,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>76</v>
       </c>
@@ -3565,7 +3568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>77</v>
       </c>
@@ -3579,7 +3582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>78</v>
       </c>
@@ -3593,7 +3596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>109</v>
       </c>
@@ -3607,7 +3610,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>110</v>
       </c>
@@ -3621,7 +3624,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>111</v>
       </c>
@@ -3635,7 +3638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>112</v>
       </c>
@@ -3657,9 +3660,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF000D6-A72C-6444-9177-22D437B8361A}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -3673,7 +3676,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -3687,7 +3690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -3701,7 +3704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -3715,7 +3718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -3729,7 +3732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -3743,7 +3746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -3757,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -3771,7 +3774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -3785,7 +3788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -3799,7 +3802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -3813,7 +3816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -3827,7 +3830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -3841,7 +3844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -3855,7 +3858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -3869,7 +3872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -3883,7 +3886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -3897,7 +3900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -3911,7 +3914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -3925,7 +3928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>97</v>
       </c>
@@ -3939,7 +3942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -3953,7 +3956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>99</v>
       </c>
@@ -3967,7 +3970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>100</v>
       </c>
@@ -3981,7 +3984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -3995,7 +3998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -4009,7 +4012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>103</v>
       </c>
@@ -4023,7 +4026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -4037,7 +4040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>105</v>
       </c>
@@ -4051,7 +4054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -4065,7 +4068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -4079,7 +4082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>108</v>
       </c>
@@ -4101,13 +4104,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA3706E6-9BD2-3A49-A255-D2B55C8D9AB1}">
   <dimension ref="A1:G151"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="51.1640625" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="179" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>256</v>
       </c>
@@ -4130,7 +4134,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4153,7 +4157,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4176,7 +4180,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4199,7 +4203,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4222,7 +4226,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4245,7 +4249,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4268,7 +4272,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4291,7 +4295,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
@@ -4314,7 +4318,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
@@ -4337,7 +4341,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
@@ -4357,7 +4361,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1</v>
       </c>
@@ -4380,7 +4384,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1</v>
       </c>
@@ -4394,7 +4398,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1</v>
       </c>
@@ -4408,7 +4412,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1</v>
       </c>
@@ -4422,7 +4426,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1</v>
       </c>
@@ -4436,7 +4440,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2</v>
       </c>
@@ -4459,7 +4463,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4482,7 +4486,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4505,7 +4509,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4528,7 +4532,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4551,7 +4555,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4574,7 +4578,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2</v>
       </c>
@@ -4597,7 +4601,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2</v>
       </c>
@@ -4620,7 +4624,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2</v>
       </c>
@@ -4643,7 +4647,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2</v>
       </c>
@@ -4666,7 +4670,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2</v>
       </c>
@@ -4689,7 +4693,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>2</v>
       </c>
@@ -4712,7 +4716,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2</v>
       </c>
@@ -4735,7 +4739,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2</v>
       </c>
@@ -4749,7 +4753,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2</v>
       </c>
@@ -4763,7 +4767,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>3</v>
       </c>
@@ -4786,7 +4790,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>3</v>
       </c>
@@ -4809,7 +4813,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>3</v>
       </c>
@@ -4832,7 +4836,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4855,7 +4859,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4875,7 +4879,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4898,7 +4902,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4921,7 +4925,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>3</v>
       </c>
@@ -4944,7 +4948,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>3</v>
       </c>
@@ -4967,7 +4971,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>3</v>
       </c>
@@ -4990,7 +4994,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>3</v>
       </c>
@@ -5013,7 +5017,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>3</v>
       </c>
@@ -5027,7 +5031,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>3</v>
       </c>
@@ -5041,7 +5045,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>3</v>
       </c>
@@ -5055,7 +5059,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>3</v>
       </c>
@@ -5069,7 +5073,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>4</v>
       </c>
@@ -5092,7 +5096,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>4</v>
       </c>
@@ -5115,7 +5119,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>4</v>
       </c>
@@ -5138,7 +5142,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>4</v>
       </c>
@@ -5161,7 +5165,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>4</v>
       </c>
@@ -5184,7 +5188,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>4</v>
       </c>
@@ -5204,7 +5208,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>4</v>
       </c>
@@ -5227,7 +5231,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>4</v>
       </c>
@@ -5250,7 +5254,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>4</v>
       </c>
@@ -5273,7 +5277,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>4</v>
       </c>
@@ -5296,7 +5300,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>4</v>
       </c>
@@ -5319,7 +5323,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>4</v>
       </c>
@@ -5333,7 +5337,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>4</v>
       </c>
@@ -5347,7 +5351,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>4</v>
       </c>
@@ -5361,7 +5365,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>4</v>
       </c>
@@ -5375,7 +5379,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>5</v>
       </c>
@@ -5398,7 +5402,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>5</v>
       </c>
@@ -5421,7 +5425,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>5</v>
       </c>
@@ -5444,7 +5448,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>5</v>
       </c>
@@ -5467,7 +5471,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>5</v>
       </c>
@@ -5490,7 +5494,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>5</v>
       </c>
@@ -5513,7 +5517,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>5</v>
       </c>
@@ -5536,7 +5540,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>5</v>
       </c>
@@ -5559,7 +5563,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>5</v>
       </c>
@@ -5582,7 +5586,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>5</v>
       </c>
@@ -5605,7 +5609,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>5</v>
       </c>
@@ -5628,7 +5632,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>5</v>
       </c>
@@ -5648,7 +5652,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>5</v>
       </c>
@@ -5662,7 +5666,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>5</v>
       </c>
@@ -5676,7 +5680,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>5</v>
       </c>
@@ -5690,7 +5694,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>6</v>
       </c>
@@ -5713,7 +5717,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>6</v>
       </c>
@@ -5736,7 +5740,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>6</v>
       </c>
@@ -5759,7 +5763,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>6</v>
       </c>
@@ -5782,7 +5786,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>6</v>
       </c>
@@ -5805,7 +5809,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>6</v>
       </c>
@@ -5828,7 +5832,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>6</v>
       </c>
@@ -5851,7 +5855,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>6</v>
       </c>
@@ -5874,7 +5878,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>6</v>
       </c>
@@ -5897,7 +5901,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>6</v>
       </c>
@@ -5920,7 +5924,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>6</v>
       </c>
@@ -5943,7 +5947,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>6</v>
       </c>
@@ -5966,7 +5970,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>6</v>
       </c>
@@ -5989,7 +5993,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>6</v>
       </c>
@@ -6003,7 +6007,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>6</v>
       </c>
@@ -6017,7 +6021,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>7</v>
       </c>
@@ -6040,7 +6044,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>7</v>
       </c>
@@ -6063,7 +6067,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>7</v>
       </c>
@@ -6086,7 +6090,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>7</v>
       </c>
@@ -6109,7 +6113,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>7</v>
       </c>
@@ -6132,7 +6136,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>7</v>
       </c>
@@ -6155,7 +6159,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>7</v>
       </c>
@@ -6178,7 +6182,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>7</v>
       </c>
@@ -6201,7 +6205,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>7</v>
       </c>
@@ -6224,7 +6228,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>7</v>
       </c>
@@ -6247,7 +6251,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>7</v>
       </c>
@@ -6270,7 +6274,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>7</v>
       </c>
@@ -6293,7 +6297,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>7</v>
       </c>
@@ -6316,7 +6320,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>7</v>
       </c>
@@ -6330,7 +6334,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>7</v>
       </c>
@@ -6344,7 +6348,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>8</v>
       </c>
@@ -6367,7 +6371,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>8</v>
       </c>
@@ -6390,7 +6394,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>8</v>
       </c>
@@ -6413,7 +6417,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>8</v>
       </c>
@@ -6436,7 +6440,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>8</v>
       </c>
@@ -6450,7 +6454,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>8</v>
       </c>
@@ -6473,7 +6477,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>8</v>
       </c>
@@ -6487,7 +6491,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>8</v>
       </c>
@@ -6510,7 +6514,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>8</v>
       </c>
@@ -6533,7 +6537,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>8</v>
       </c>
@@ -6556,7 +6560,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>8</v>
       </c>
@@ -6579,7 +6583,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>8</v>
       </c>
@@ -6602,7 +6606,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>8</v>
       </c>
@@ -6625,7 +6629,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>8</v>
       </c>
@@ -6638,8 +6642,11 @@
       <c r="D120" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E120" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>8</v>
       </c>
@@ -6653,7 +6660,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>9</v>
       </c>
@@ -6676,7 +6683,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>9</v>
       </c>
@@ -6699,7 +6706,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>9</v>
       </c>
@@ -6719,7 +6726,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>9</v>
       </c>
@@ -6739,7 +6746,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>9</v>
       </c>
@@ -6762,7 +6769,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>9</v>
       </c>
@@ -6776,7 +6783,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>9</v>
       </c>
@@ -6790,7 +6797,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>9</v>
       </c>
@@ -6804,7 +6811,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>9</v>
       </c>
@@ -6818,7 +6825,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>9</v>
       </c>
@@ -6832,7 +6839,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>9</v>
       </c>
@@ -6846,7 +6853,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>9</v>
       </c>
@@ -6860,7 +6867,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>9</v>
       </c>
@@ -6874,7 +6881,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>9</v>
       </c>
@@ -6888,7 +6895,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>9</v>
       </c>
@@ -6902,7 +6909,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>10</v>
       </c>
@@ -6925,7 +6932,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>10</v>
       </c>
@@ -6948,7 +6955,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>10</v>
       </c>
@@ -6971,7 +6978,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>10</v>
       </c>
@@ -6994,7 +7001,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>10</v>
       </c>
@@ -7017,7 +7024,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>10</v>
       </c>
@@ -7040,7 +7047,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>10</v>
       </c>
@@ -7063,7 +7070,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>10</v>
       </c>
@@ -7086,7 +7093,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>10</v>
       </c>
@@ -7109,7 +7116,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>10</v>
       </c>
@@ -7132,7 +7139,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>10</v>
       </c>
@@ -7155,7 +7162,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>10</v>
       </c>
@@ -7178,7 +7185,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>10</v>
       </c>
@@ -7201,7 +7208,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>10</v>
       </c>
@@ -7224,7 +7231,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>10</v>
       </c>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EF81DE-07A2-5E4F-8014-C289F453FBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47CA2A5-5A50-1149-9B29-EEBFA797CD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="500" windowWidth="50120" windowHeight="28300" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="41960" yWindow="6500" windowWidth="33860" windowHeight="28300" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="662">
   <si>
     <t>pFS2</t>
   </si>
@@ -1730,33 +1730,6 @@
     <t>Stem mortality</t>
   </si>
   <si>
-    <t>Volume extracted during the most recent thinning event</t>
-  </si>
-  <si>
-    <t>Latest extracted volume</t>
-  </si>
-  <si>
-    <t>Number of crop trees (x)</t>
-  </si>
-  <si>
-    <t>CropTrees per ha</t>
-  </si>
-  <si>
-    <t>CropTree Mean DBH</t>
-  </si>
-  <si>
-    <t>CropTree Basal area</t>
-  </si>
-  <si>
-    <t>CropTree volume</t>
-  </si>
-  <si>
-    <t>CropTree Height</t>
-  </si>
-  <si>
-    <t>CropTree Stem DM</t>
-  </si>
-  <si>
     <t>var_8_15</t>
   </si>
   <si>
@@ -1970,9 +1943,6 @@
     <t>apar</t>
   </si>
   <si>
-    <t>test_output</t>
-  </si>
-  <si>
     <t>beta0</t>
   </si>
   <si>
@@ -2012,31 +1982,37 @@
     <t>mort_thinn_total</t>
   </si>
   <si>
-    <t>ave_lt_fN</t>
-  </si>
-  <si>
-    <t>ave_lt_fT</t>
-  </si>
-  <si>
-    <t>ave_lt_fPhys</t>
-  </si>
-  <si>
-    <t>lt_fN</t>
-  </si>
-  <si>
-    <t>lt_fT</t>
-  </si>
-  <si>
-    <t>lt_fPhys</t>
-  </si>
-  <si>
     <t>dbh_total</t>
   </si>
   <si>
     <t>stems_n_total</t>
   </si>
   <si>
-    <t>Stems number of the active cohorts</t>
+    <t>var_8_11</t>
+  </si>
+  <si>
+    <t>var_8_12</t>
+  </si>
+  <si>
+    <t>var_8_13</t>
+  </si>
+  <si>
+    <t>var_8_14</t>
+  </si>
+  <si>
+    <t>Total number of trees that died due to density-dependent mortality</t>
+  </si>
+  <si>
+    <t>lt_fN_ave</t>
+  </si>
+  <si>
+    <t>lt_fT_ave</t>
+  </si>
+  <si>
+    <t>lt_fPhys_ave</t>
+  </si>
+  <si>
+    <t>Stems number of the alive cohorts</t>
   </si>
 </sst>
 </file>
@@ -2063,9 +2039,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Aptos"/>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2095,11 +2072,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2882,10 +2858,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -2894,10 +2870,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -2906,10 +2882,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -2918,10 +2894,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -2930,10 +2906,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -2942,10 +2918,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -5748,7 +5724,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="D79" t="s">
         <v>468</v>
@@ -6447,11 +6423,20 @@
       <c r="B111" s="2">
         <v>5</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="D111" s="2" t="s">
+      <c r="C111" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="D111" t="s">
         <v>554</v>
+      </c>
+      <c r="E111" t="s">
+        <v>657</v>
+      </c>
+      <c r="F111" t="s">
+        <v>305</v>
+      </c>
+      <c r="G111" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
@@ -6462,19 +6447,10 @@
         <v>6</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D112" t="s">
         <v>554</v>
-      </c>
-      <c r="E112" t="s">
-        <v>567</v>
-      </c>
-      <c r="F112" t="s">
-        <v>333</v>
-      </c>
-      <c r="G112" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
@@ -6485,7 +6461,7 @@
         <v>7</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D113" t="s">
         <v>554</v>
@@ -6499,19 +6475,13 @@
         <v>8</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D114" t="s">
         <v>554</v>
       </c>
       <c r="E114" t="s">
-        <v>569</v>
-      </c>
-      <c r="F114" t="s">
-        <v>305</v>
-      </c>
-      <c r="G114" t="s">
-        <v>570</v>
+        <v>316</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
@@ -6522,19 +6492,13 @@
         <v>9</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="D115" t="s">
         <v>554</v>
       </c>
       <c r="E115" t="s">
         <v>316</v>
-      </c>
-      <c r="F115" t="s">
-        <v>317</v>
-      </c>
-      <c r="G115" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
@@ -6545,19 +6509,13 @@
         <v>10</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="D116" t="s">
         <v>554</v>
       </c>
       <c r="E116" t="s">
-        <v>308</v>
-      </c>
-      <c r="F116" t="s">
-        <v>309</v>
-      </c>
-      <c r="G116" t="s">
-        <v>572</v>
+        <v>661</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
@@ -6568,19 +6526,10 @@
         <v>11</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="D117" t="s">
         <v>554</v>
-      </c>
-      <c r="E117" t="s">
-        <v>332</v>
-      </c>
-      <c r="F117" t="s">
-        <v>333</v>
-      </c>
-      <c r="G117" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
@@ -6591,19 +6540,10 @@
         <v>12</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D118" t="s">
         <v>554</v>
-      </c>
-      <c r="E118" t="s">
-        <v>319</v>
-      </c>
-      <c r="F118" t="s">
-        <v>320</v>
-      </c>
-      <c r="G118" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
@@ -6614,19 +6554,10 @@
         <v>13</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="D119" t="s">
         <v>554</v>
-      </c>
-      <c r="E119" t="s">
-        <v>390</v>
-      </c>
-      <c r="F119" t="s">
-        <v>391</v>
-      </c>
-      <c r="G119" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
@@ -6637,13 +6568,10 @@
         <v>14</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="D120" t="s">
         <v>554</v>
-      </c>
-      <c r="E120" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
@@ -6654,7 +6582,7 @@
         <v>15</v>
       </c>
       <c r="C121" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="D121" t="s">
         <v>554</v>
@@ -6668,19 +6596,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="D122" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="E122" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="F122" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="G122" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
@@ -6691,19 +6619,19 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="D123" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="E123" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="F123" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="G123" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
@@ -6714,16 +6642,16 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="D124" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="E124" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="G124" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
@@ -6734,16 +6662,16 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="D125" t="s">
+        <v>569</v>
+      </c>
+      <c r="E125" t="s">
+        <v>579</v>
+      </c>
+      <c r="G125" t="s">
         <v>578</v>
-      </c>
-      <c r="E125" t="s">
-        <v>588</v>
-      </c>
-      <c r="G125" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
@@ -6754,19 +6682,19 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="D126" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="E126" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="F126" t="s">
         <v>288</v>
       </c>
       <c r="G126" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
@@ -6777,10 +6705,10 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="D127" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
@@ -6791,10 +6719,10 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="D128" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
@@ -6805,10 +6733,10 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="D129" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
@@ -6819,10 +6747,10 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="D130" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
@@ -6833,10 +6761,10 @@
         <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="D131" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
@@ -6847,10 +6775,10 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="D132" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
@@ -6861,10 +6789,10 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="D133" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
@@ -6875,10 +6803,10 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="D134" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
@@ -6889,10 +6817,10 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="D135" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
@@ -6903,10 +6831,10 @@
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="D136" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
@@ -6917,19 +6845,19 @@
         <v>1</v>
       </c>
       <c r="C137" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="D137" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E137" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="F137" t="s">
         <v>128</v>
       </c>
       <c r="G137" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
@@ -6940,19 +6868,19 @@
         <v>2</v>
       </c>
       <c r="C138" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="D138" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E138" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="F138" t="s">
         <v>128</v>
       </c>
       <c r="G138" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
@@ -6963,19 +6891,19 @@
         <v>3</v>
       </c>
       <c r="C139" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="D139" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E139" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="F139" t="s">
         <v>128</v>
       </c>
       <c r="G139" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
@@ -6986,19 +6914,19 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="D140" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E140" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="F140" t="s">
         <v>128</v>
       </c>
       <c r="G140" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
@@ -7009,19 +6937,19 @@
         <v>5</v>
       </c>
       <c r="C141" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="D141" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E141" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="F141" t="s">
         <v>128</v>
       </c>
       <c r="G141" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
@@ -7032,19 +6960,19 @@
         <v>6</v>
       </c>
       <c r="C142" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="D142" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E142" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="F142" t="s">
         <v>128</v>
       </c>
       <c r="G142" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
@@ -7055,19 +6983,19 @@
         <v>7</v>
       </c>
       <c r="C143" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="D143" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E143" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="F143" t="s">
         <v>367</v>
       </c>
       <c r="G143" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
@@ -7078,19 +7006,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="D144" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E144" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="F144" t="s">
         <v>367</v>
       </c>
       <c r="G144" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
@@ -7101,19 +7029,19 @@
         <v>9</v>
       </c>
       <c r="C145" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="D145" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E145" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="F145" t="s">
         <v>367</v>
       </c>
       <c r="G145" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
@@ -7124,19 +7052,19 @@
         <v>10</v>
       </c>
       <c r="C146" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="D146" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E146" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="F146" t="s">
         <v>367</v>
       </c>
       <c r="G146" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
@@ -7147,19 +7075,19 @@
         <v>11</v>
       </c>
       <c r="C147" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="D147" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E147" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="F147" t="s">
         <v>367</v>
       </c>
       <c r="G147" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
@@ -7170,19 +7098,19 @@
         <v>12</v>
       </c>
       <c r="C148" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="D148" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E148" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="F148" t="s">
         <v>367</v>
       </c>
       <c r="G148" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
@@ -7193,19 +7121,19 @@
         <v>13</v>
       </c>
       <c r="C149" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="D149" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E149" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="F149" t="s">
         <v>367</v>
       </c>
       <c r="G149" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
@@ -7216,19 +7144,19 @@
         <v>14</v>
       </c>
       <c r="C150" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="D150" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E150" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="F150" t="s">
         <v>367</v>
       </c>
       <c r="G150" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
@@ -7239,13 +7167,14 @@
         <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="D151" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47CA2A5-5A50-1149-9B29-EEBFA797CD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F20C6D-95FF-BA47-A3C4-4F3EFB45FAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41960" yWindow="6500" windowWidth="33860" windowHeight="28300" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="34000" yWindow="2200" windowWidth="33860" windowHeight="28300" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="682">
   <si>
     <t>pFS2</t>
   </si>
@@ -2013,6 +2013,66 @@
   </si>
   <si>
     <t>Stems number of the alive cohorts</t>
+  </si>
+  <si>
+    <t>mortality_details</t>
+  </si>
+  <si>
+    <t>stems_loss_manag</t>
+  </si>
+  <si>
+    <t>biom_loss_stem_manag</t>
+  </si>
+  <si>
+    <t>biom_loss_root_manag</t>
+  </si>
+  <si>
+    <t>biom_loss_foliage_manag</t>
+  </si>
+  <si>
+    <t>var_11_6</t>
+  </si>
+  <si>
+    <t>var_11_7</t>
+  </si>
+  <si>
+    <t>var_11_8</t>
+  </si>
+  <si>
+    <t>var_11_9</t>
+  </si>
+  <si>
+    <t>var_11_10</t>
+  </si>
+  <si>
+    <t>var_11_11</t>
+  </si>
+  <si>
+    <t>var_11_12</t>
+  </si>
+  <si>
+    <t>var_11_13</t>
+  </si>
+  <si>
+    <t>var_11_14</t>
+  </si>
+  <si>
+    <t>var_11_15</t>
+  </si>
+  <si>
+    <t>var_11_5</t>
+  </si>
+  <si>
+    <t>Number of trees removed due to management</t>
+  </si>
+  <si>
+    <t>Stem biomass removed due to management</t>
+  </si>
+  <si>
+    <t>Root biomass removed due to management</t>
+  </si>
+  <si>
+    <t>Foliage biomass remoed due to management</t>
   </si>
 </sst>
 </file>
@@ -4079,7 +4139,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA3706E6-9BD2-3A49-A255-D2B55C8D9AB1}">
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="51.1640625" customWidth="1"/>
@@ -7173,6 +7233,240 @@
         <v>594</v>
       </c>
     </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>11</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="C152" t="s">
+        <v>663</v>
+      </c>
+      <c r="D152" t="s">
+        <v>662</v>
+      </c>
+      <c r="E152" t="s">
+        <v>678</v>
+      </c>
+      <c r="F152" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>11</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153" t="s">
+        <v>664</v>
+      </c>
+      <c r="D153" t="s">
+        <v>662</v>
+      </c>
+      <c r="E153" t="s">
+        <v>679</v>
+      </c>
+      <c r="F153" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>11</v>
+      </c>
+      <c r="B154">
+        <v>3</v>
+      </c>
+      <c r="C154" t="s">
+        <v>665</v>
+      </c>
+      <c r="D154" t="s">
+        <v>662</v>
+      </c>
+      <c r="E154" t="s">
+        <v>680</v>
+      </c>
+      <c r="F154" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>11</v>
+      </c>
+      <c r="B155">
+        <v>4</v>
+      </c>
+      <c r="C155" t="s">
+        <v>666</v>
+      </c>
+      <c r="D155" t="s">
+        <v>662</v>
+      </c>
+      <c r="E155" t="s">
+        <v>681</v>
+      </c>
+      <c r="F155" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>11</v>
+      </c>
+      <c r="B156">
+        <v>5</v>
+      </c>
+      <c r="C156" t="s">
+        <v>677</v>
+      </c>
+      <c r="D156" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>11</v>
+      </c>
+      <c r="B157">
+        <v>6</v>
+      </c>
+      <c r="C157" t="s">
+        <v>667</v>
+      </c>
+      <c r="D157" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>11</v>
+      </c>
+      <c r="B158">
+        <v>7</v>
+      </c>
+      <c r="C158" t="s">
+        <v>668</v>
+      </c>
+      <c r="D158" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>11</v>
+      </c>
+      <c r="B159">
+        <v>8</v>
+      </c>
+      <c r="C159" t="s">
+        <v>669</v>
+      </c>
+      <c r="D159" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>11</v>
+      </c>
+      <c r="B160">
+        <v>9</v>
+      </c>
+      <c r="C160" t="s">
+        <v>670</v>
+      </c>
+      <c r="D160" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>11</v>
+      </c>
+      <c r="B161">
+        <v>10</v>
+      </c>
+      <c r="C161" t="s">
+        <v>671</v>
+      </c>
+      <c r="D161" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>11</v>
+      </c>
+      <c r="B162">
+        <v>11</v>
+      </c>
+      <c r="C162" t="s">
+        <v>672</v>
+      </c>
+      <c r="D162" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>11</v>
+      </c>
+      <c r="B163">
+        <v>12</v>
+      </c>
+      <c r="C163" t="s">
+        <v>673</v>
+      </c>
+      <c r="D163" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>11</v>
+      </c>
+      <c r="B164">
+        <v>13</v>
+      </c>
+      <c r="C164" t="s">
+        <v>674</v>
+      </c>
+      <c r="D164" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>11</v>
+      </c>
+      <c r="B165">
+        <v>14</v>
+      </c>
+      <c r="C165" t="s">
+        <v>675</v>
+      </c>
+      <c r="D165" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>11</v>
+      </c>
+      <c r="B166">
+        <v>15</v>
+      </c>
+      <c r="C166" t="s">
+        <v>676</v>
+      </c>
+      <c r="D166" t="s">
+        <v>662</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F20C6D-95FF-BA47-A3C4-4F3EFB45FAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A696D98-0593-CB41-9451-677977712FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34000" yWindow="2200" windowWidth="33860" windowHeight="28300" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="686">
   <si>
     <t>pFS2</t>
   </si>
@@ -2030,15 +2030,6 @@
     <t>biom_loss_foliage_manag</t>
   </si>
   <si>
-    <t>var_11_6</t>
-  </si>
-  <si>
-    <t>var_11_7</t>
-  </si>
-  <si>
-    <t>var_11_8</t>
-  </si>
-  <si>
     <t>var_11_9</t>
   </si>
   <si>
@@ -2060,9 +2051,6 @@
     <t>var_11_15</t>
   </si>
   <si>
-    <t>var_11_5</t>
-  </si>
-  <si>
     <t>Number of trees removed due to management</t>
   </si>
   <si>
@@ -2073,6 +2061,30 @@
   </si>
   <si>
     <t>Foliage biomass remoed due to management</t>
+  </si>
+  <si>
+    <t>stems_loss_stress</t>
+  </si>
+  <si>
+    <t>biom_loss_stem_stress</t>
+  </si>
+  <si>
+    <t>biom_loss_root_stress</t>
+  </si>
+  <si>
+    <t>biom_loss_foliage_stress</t>
+  </si>
+  <si>
+    <t>Number of trees removed due to stress related mortality</t>
+  </si>
+  <si>
+    <t>Stem biomass removed due to stress related mortality</t>
+  </si>
+  <si>
+    <t>Root biomass removed due to stress related mortality</t>
+  </si>
+  <si>
+    <t>Foliage biomass remoed due to stress related mortality</t>
   </si>
 </sst>
 </file>
@@ -7247,7 +7259,7 @@
         <v>662</v>
       </c>
       <c r="E152" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="F152" t="s">
         <v>305</v>
@@ -7267,7 +7279,7 @@
         <v>662</v>
       </c>
       <c r="E153" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="F153" t="s">
         <v>391</v>
@@ -7287,7 +7299,7 @@
         <v>662</v>
       </c>
       <c r="E154" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="F154" t="s">
         <v>391</v>
@@ -7307,7 +7319,7 @@
         <v>662</v>
       </c>
       <c r="E155" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="F155" t="s">
         <v>391</v>
@@ -7321,10 +7333,16 @@
         <v>5</v>
       </c>
       <c r="C156" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D156" t="s">
         <v>662</v>
+      </c>
+      <c r="E156" t="s">
+        <v>682</v>
+      </c>
+      <c r="F156" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
@@ -7335,10 +7353,16 @@
         <v>6</v>
       </c>
       <c r="C157" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="D157" t="s">
         <v>662</v>
+      </c>
+      <c r="E157" t="s">
+        <v>683</v>
+      </c>
+      <c r="F157" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
@@ -7349,10 +7373,16 @@
         <v>7</v>
       </c>
       <c r="C158" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="D158" t="s">
         <v>662</v>
+      </c>
+      <c r="E158" t="s">
+        <v>684</v>
+      </c>
+      <c r="F158" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
@@ -7363,10 +7393,16 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="D159" t="s">
         <v>662</v>
+      </c>
+      <c r="E159" t="s">
+        <v>685</v>
+      </c>
+      <c r="F159" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
@@ -7377,7 +7413,7 @@
         <v>9</v>
       </c>
       <c r="C160" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D160" t="s">
         <v>662</v>
@@ -7391,7 +7427,7 @@
         <v>10</v>
       </c>
       <c r="C161" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D161" t="s">
         <v>662</v>
@@ -7405,7 +7441,7 @@
         <v>11</v>
       </c>
       <c r="C162" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D162" t="s">
         <v>662</v>
@@ -7419,7 +7455,7 @@
         <v>12</v>
       </c>
       <c r="C163" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D163" t="s">
         <v>662</v>
@@ -7433,7 +7469,7 @@
         <v>13</v>
       </c>
       <c r="C164" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D164" t="s">
         <v>662</v>
@@ -7447,7 +7483,7 @@
         <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D165" t="s">
         <v>662</v>
@@ -7461,7 +7497,7 @@
         <v>15</v>
       </c>
       <c r="C166" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D166" t="s">
         <v>662</v>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A696D98-0593-CB41-9451-677977712FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF03FDC-2B21-AC49-A84E-0B01CA2D4B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34000" yWindow="2200" windowWidth="33860" windowHeight="28300" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="17340" yWindow="500" windowWidth="33860" windowHeight="28300" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="688">
   <si>
     <t>pFS2</t>
   </si>
@@ -1712,18 +1712,12 @@
     <t>month-1</t>
   </si>
   <si>
-    <t>mort_thinn</t>
-  </si>
-  <si>
     <t>Number of trees that died due to density-dependent mortality</t>
   </si>
   <si>
     <t>Self thinning</t>
   </si>
   <si>
-    <t>mort_stress</t>
-  </si>
-  <si>
     <t>Number of trees that died due to stress-related mortality</t>
   </si>
   <si>
@@ -2030,18 +2024,6 @@
     <t>biom_loss_foliage_manag</t>
   </si>
   <si>
-    <t>var_11_9</t>
-  </si>
-  <si>
-    <t>var_11_10</t>
-  </si>
-  <si>
-    <t>var_11_11</t>
-  </si>
-  <si>
-    <t>var_11_12</t>
-  </si>
-  <si>
     <t>var_11_13</t>
   </si>
   <si>
@@ -2085,6 +2067,30 @@
   </si>
   <si>
     <t>Foliage biomass remoed due to stress related mortality</t>
+  </si>
+  <si>
+    <t>stems_loss_density</t>
+  </si>
+  <si>
+    <t>biom_loss_stem_density</t>
+  </si>
+  <si>
+    <t>biom_loss_root_density</t>
+  </si>
+  <si>
+    <t>biom_loss_foliage_density</t>
+  </si>
+  <si>
+    <t>Number of trees removed due to density dependet mortality</t>
+  </si>
+  <si>
+    <t>Stem biomass removed due to density dependet mortality</t>
+  </si>
+  <si>
+    <t>Root biomass removed due to density dependet mortality</t>
+  </si>
+  <si>
+    <t>Foliage biomass remoed due to density dependet mortality</t>
   </si>
 </sst>
 </file>
@@ -2930,10 +2936,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -2942,10 +2948,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -2954,10 +2960,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -2966,10 +2972,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -2978,10 +2984,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -2990,10 +2996,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -5796,7 +5802,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D79" t="s">
         <v>468</v>
@@ -6450,19 +6456,19 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>561</v>
+        <v>680</v>
       </c>
       <c r="D109" t="s">
         <v>554</v>
       </c>
       <c r="E109" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F109" t="s">
         <v>305</v>
       </c>
       <c r="G109" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
@@ -6473,19 +6479,19 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>564</v>
+        <v>672</v>
       </c>
       <c r="D110" t="s">
         <v>554</v>
       </c>
       <c r="E110" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F110" t="s">
         <v>305</v>
       </c>
       <c r="G110" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -6496,19 +6502,19 @@
         <v>5</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D111" t="s">
         <v>554</v>
       </c>
       <c r="E111" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F111" t="s">
         <v>305</v>
       </c>
       <c r="G111" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
@@ -6519,7 +6525,7 @@
         <v>6</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D112" t="s">
         <v>554</v>
@@ -6533,7 +6539,7 @@
         <v>7</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D113" t="s">
         <v>554</v>
@@ -6547,7 +6553,7 @@
         <v>8</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D114" t="s">
         <v>554</v>
@@ -6564,7 +6570,7 @@
         <v>9</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D115" t="s">
         <v>554</v>
@@ -6581,13 +6587,13 @@
         <v>10</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D116" t="s">
         <v>554</v>
       </c>
       <c r="E116" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
@@ -6598,7 +6604,7 @@
         <v>11</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D117" t="s">
         <v>554</v>
@@ -6612,7 +6618,7 @@
         <v>12</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D118" t="s">
         <v>554</v>
@@ -6626,7 +6632,7 @@
         <v>13</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D119" t="s">
         <v>554</v>
@@ -6640,7 +6646,7 @@
         <v>14</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D120" t="s">
         <v>554</v>
@@ -6654,7 +6660,7 @@
         <v>15</v>
       </c>
       <c r="C121" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D121" t="s">
         <v>554</v>
@@ -6668,19 +6674,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
+        <v>566</v>
+      </c>
+      <c r="D122" t="s">
+        <v>567</v>
+      </c>
+      <c r="E122" t="s">
         <v>568</v>
       </c>
-      <c r="D122" t="s">
+      <c r="F122" t="s">
         <v>569</v>
       </c>
-      <c r="E122" t="s">
+      <c r="G122" t="s">
         <v>570</v>
-      </c>
-      <c r="F122" t="s">
-        <v>571</v>
-      </c>
-      <c r="G122" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
@@ -6691,19 +6697,19 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
+        <v>571</v>
+      </c>
+      <c r="D123" t="s">
+        <v>567</v>
+      </c>
+      <c r="E123" t="s">
+        <v>572</v>
+      </c>
+      <c r="F123" t="s">
+        <v>569</v>
+      </c>
+      <c r="G123" t="s">
         <v>573</v>
-      </c>
-      <c r="D123" t="s">
-        <v>569</v>
-      </c>
-      <c r="E123" t="s">
-        <v>574</v>
-      </c>
-      <c r="F123" t="s">
-        <v>571</v>
-      </c>
-      <c r="G123" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
@@ -6714,16 +6720,16 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D124" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E124" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G124" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
@@ -6734,16 +6740,16 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D125" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E125" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="G125" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
@@ -6754,19 +6760,19 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D126" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E126" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F126" t="s">
         <v>288</v>
       </c>
       <c r="G126" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
@@ -6777,10 +6783,10 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D127" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
@@ -6791,10 +6797,10 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D128" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
@@ -6805,10 +6811,10 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D129" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
@@ -6819,10 +6825,10 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D130" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
@@ -6833,10 +6839,10 @@
         <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D131" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
@@ -6847,10 +6853,10 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D132" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
@@ -6861,10 +6867,10 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D133" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
@@ -6875,10 +6881,10 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D134" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
@@ -6889,10 +6895,10 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D135" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
@@ -6903,10 +6909,10 @@
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D136" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
@@ -6917,19 +6923,19 @@
         <v>1</v>
       </c>
       <c r="C137" t="s">
+        <v>591</v>
+      </c>
+      <c r="D137" t="s">
+        <v>592</v>
+      </c>
+      <c r="E137" t="s">
         <v>593</v>
       </c>
-      <c r="D137" t="s">
+      <c r="F137" t="s">
+        <v>128</v>
+      </c>
+      <c r="G137" t="s">
         <v>594</v>
-      </c>
-      <c r="E137" t="s">
-        <v>595</v>
-      </c>
-      <c r="F137" t="s">
-        <v>128</v>
-      </c>
-      <c r="G137" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
@@ -6940,19 +6946,19 @@
         <v>2</v>
       </c>
       <c r="C138" t="s">
+        <v>595</v>
+      </c>
+      <c r="D138" t="s">
+        <v>592</v>
+      </c>
+      <c r="E138" t="s">
+        <v>596</v>
+      </c>
+      <c r="F138" t="s">
+        <v>128</v>
+      </c>
+      <c r="G138" t="s">
         <v>597</v>
-      </c>
-      <c r="D138" t="s">
-        <v>594</v>
-      </c>
-      <c r="E138" t="s">
-        <v>598</v>
-      </c>
-      <c r="F138" t="s">
-        <v>128</v>
-      </c>
-      <c r="G138" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
@@ -6963,19 +6969,19 @@
         <v>3</v>
       </c>
       <c r="C139" t="s">
+        <v>598</v>
+      </c>
+      <c r="D139" t="s">
+        <v>592</v>
+      </c>
+      <c r="E139" t="s">
+        <v>599</v>
+      </c>
+      <c r="F139" t="s">
+        <v>128</v>
+      </c>
+      <c r="G139" t="s">
         <v>600</v>
-      </c>
-      <c r="D139" t="s">
-        <v>594</v>
-      </c>
-      <c r="E139" t="s">
-        <v>601</v>
-      </c>
-      <c r="F139" t="s">
-        <v>128</v>
-      </c>
-      <c r="G139" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
@@ -6986,19 +6992,19 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
+        <v>601</v>
+      </c>
+      <c r="D140" t="s">
+        <v>592</v>
+      </c>
+      <c r="E140" t="s">
+        <v>602</v>
+      </c>
+      <c r="F140" t="s">
+        <v>128</v>
+      </c>
+      <c r="G140" t="s">
         <v>603</v>
-      </c>
-      <c r="D140" t="s">
-        <v>594</v>
-      </c>
-      <c r="E140" t="s">
-        <v>604</v>
-      </c>
-      <c r="F140" t="s">
-        <v>128</v>
-      </c>
-      <c r="G140" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
@@ -7009,19 +7015,19 @@
         <v>5</v>
       </c>
       <c r="C141" t="s">
+        <v>604</v>
+      </c>
+      <c r="D141" t="s">
+        <v>592</v>
+      </c>
+      <c r="E141" t="s">
+        <v>605</v>
+      </c>
+      <c r="F141" t="s">
+        <v>128</v>
+      </c>
+      <c r="G141" t="s">
         <v>606</v>
-      </c>
-      <c r="D141" t="s">
-        <v>594</v>
-      </c>
-      <c r="E141" t="s">
-        <v>607</v>
-      </c>
-      <c r="F141" t="s">
-        <v>128</v>
-      </c>
-      <c r="G141" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
@@ -7032,19 +7038,19 @@
         <v>6</v>
       </c>
       <c r="C142" t="s">
+        <v>607</v>
+      </c>
+      <c r="D142" t="s">
+        <v>592</v>
+      </c>
+      <c r="E142" t="s">
+        <v>608</v>
+      </c>
+      <c r="F142" t="s">
+        <v>128</v>
+      </c>
+      <c r="G142" t="s">
         <v>609</v>
-      </c>
-      <c r="D142" t="s">
-        <v>594</v>
-      </c>
-      <c r="E142" t="s">
-        <v>610</v>
-      </c>
-      <c r="F142" t="s">
-        <v>128</v>
-      </c>
-      <c r="G142" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
@@ -7055,19 +7061,19 @@
         <v>7</v>
       </c>
       <c r="C143" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D143" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E143" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F143" t="s">
         <v>367</v>
       </c>
       <c r="G143" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
@@ -7078,19 +7084,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D144" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E144" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F144" t="s">
         <v>367</v>
       </c>
       <c r="G144" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
@@ -7101,19 +7107,19 @@
         <v>9</v>
       </c>
       <c r="C145" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D145" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E145" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="F145" t="s">
         <v>367</v>
       </c>
       <c r="G145" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
@@ -7124,19 +7130,19 @@
         <v>10</v>
       </c>
       <c r="C146" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D146" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E146" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="F146" t="s">
         <v>367</v>
       </c>
       <c r="G146" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
@@ -7147,19 +7153,19 @@
         <v>11</v>
       </c>
       <c r="C147" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D147" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E147" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F147" t="s">
         <v>367</v>
       </c>
       <c r="G147" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
@@ -7170,19 +7176,19 @@
         <v>12</v>
       </c>
       <c r="C148" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D148" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E148" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F148" t="s">
         <v>367</v>
       </c>
       <c r="G148" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
@@ -7193,19 +7199,19 @@
         <v>13</v>
       </c>
       <c r="C149" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D149" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E149" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F149" t="s">
         <v>367</v>
       </c>
       <c r="G149" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
@@ -7216,19 +7222,19 @@
         <v>14</v>
       </c>
       <c r="C150" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D150" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E150" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="F150" t="s">
         <v>367</v>
       </c>
       <c r="G150" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
@@ -7239,10 +7245,10 @@
         <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D151" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
@@ -7253,13 +7259,13 @@
         <v>1</v>
       </c>
       <c r="C152" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D152" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E152" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="F152" t="s">
         <v>305</v>
@@ -7273,13 +7279,13 @@
         <v>2</v>
       </c>
       <c r="C153" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D153" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E153" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="F153" t="s">
         <v>391</v>
@@ -7293,13 +7299,13 @@
         <v>3</v>
       </c>
       <c r="C154" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D154" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E154" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="F154" t="s">
         <v>391</v>
@@ -7313,13 +7319,13 @@
         <v>4</v>
       </c>
       <c r="C155" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D155" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E155" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="F155" t="s">
         <v>391</v>
@@ -7333,13 +7339,13 @@
         <v>5</v>
       </c>
       <c r="C156" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="D156" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E156" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="F156" t="s">
         <v>305</v>
@@ -7353,13 +7359,13 @@
         <v>6</v>
       </c>
       <c r="C157" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="D157" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E157" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="F157" t="s">
         <v>391</v>
@@ -7373,13 +7379,13 @@
         <v>7</v>
       </c>
       <c r="C158" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="D158" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E158" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="F158" t="s">
         <v>391</v>
@@ -7393,13 +7399,13 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="D159" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E159" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="F159" t="s">
         <v>391</v>
@@ -7413,13 +7419,19 @@
         <v>9</v>
       </c>
       <c r="C160" t="s">
-        <v>667</v>
+        <v>680</v>
       </c>
       <c r="D160" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660</v>
+      </c>
+      <c r="E160" t="s">
+        <v>684</v>
+      </c>
+      <c r="F160" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>11</v>
       </c>
@@ -7427,13 +7439,19 @@
         <v>10</v>
       </c>
       <c r="C161" t="s">
-        <v>668</v>
+        <v>681</v>
       </c>
       <c r="D161" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660</v>
+      </c>
+      <c r="E161" t="s">
+        <v>685</v>
+      </c>
+      <c r="F161" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>11</v>
       </c>
@@ -7441,13 +7459,19 @@
         <v>11</v>
       </c>
       <c r="C162" t="s">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="D162" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660</v>
+      </c>
+      <c r="E162" t="s">
+        <v>686</v>
+      </c>
+      <c r="F162" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>11</v>
       </c>
@@ -7455,13 +7479,19 @@
         <v>12</v>
       </c>
       <c r="C163" t="s">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="D163" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660</v>
+      </c>
+      <c r="E163" t="s">
+        <v>687</v>
+      </c>
+      <c r="F163" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>11</v>
       </c>
@@ -7469,13 +7499,13 @@
         <v>13</v>
       </c>
       <c r="C164" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="D164" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>11</v>
       </c>
@@ -7483,13 +7513,13 @@
         <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="D165" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>11</v>
       </c>
@@ -7497,10 +7527,10 @@
         <v>15</v>
       </c>
       <c r="C166" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D166" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF03FDC-2B21-AC49-A84E-0B01CA2D4B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F903BF-3827-1F46-9732-B29A8B79E7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17340" yWindow="500" windowWidth="33860" windowHeight="28300" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="1420" yWindow="500" windowWidth="32960" windowHeight="28300" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
     <sheet name="sizeDist" sheetId="9" r:id="rId2"/>
     <sheet name="output" sheetId="10" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="11" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">output!$A$1:$G$221</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="745">
   <si>
     <t>pFS2</t>
   </si>
@@ -2024,15 +2028,6 @@
     <t>biom_loss_foliage_manag</t>
   </si>
   <si>
-    <t>var_11_13</t>
-  </si>
-  <si>
-    <t>var_11_14</t>
-  </si>
-  <si>
-    <t>var_11_15</t>
-  </si>
-  <si>
     <t>Number of trees removed due to management</t>
   </si>
   <si>
@@ -2091,13 +2086,193 @@
   </si>
   <si>
     <t>Foliage biomass remoed due to density dependet mortality</t>
+  </si>
+  <si>
+    <t>var_1_16</t>
+  </si>
+  <si>
+    <t>var_1_17</t>
+  </si>
+  <si>
+    <t>var_1_18</t>
+  </si>
+  <si>
+    <t>var_1_19</t>
+  </si>
+  <si>
+    <t>var_1_20</t>
+  </si>
+  <si>
+    <t>var_2_16</t>
+  </si>
+  <si>
+    <t>var_2_17</t>
+  </si>
+  <si>
+    <t>var_2_18</t>
+  </si>
+  <si>
+    <t>var_2_19</t>
+  </si>
+  <si>
+    <t>var_2_20</t>
+  </si>
+  <si>
+    <t>var_3_16</t>
+  </si>
+  <si>
+    <t>var_3_17</t>
+  </si>
+  <si>
+    <t>var_3_18</t>
+  </si>
+  <si>
+    <t>var_3_19</t>
+  </si>
+  <si>
+    <t>var_3_20</t>
+  </si>
+  <si>
+    <t>var_4_16</t>
+  </si>
+  <si>
+    <t>var_4_17</t>
+  </si>
+  <si>
+    <t>var_4_18</t>
+  </si>
+  <si>
+    <t>var_4_19</t>
+  </si>
+  <si>
+    <t>var_4_20</t>
+  </si>
+  <si>
+    <t>var_5_16</t>
+  </si>
+  <si>
+    <t>var_5_17</t>
+  </si>
+  <si>
+    <t>var_5_18</t>
+  </si>
+  <si>
+    <t>var_5_19</t>
+  </si>
+  <si>
+    <t>var_5_20</t>
+  </si>
+  <si>
+    <t>var_6_16</t>
+  </si>
+  <si>
+    <t>var_6_17</t>
+  </si>
+  <si>
+    <t>var_6_18</t>
+  </si>
+  <si>
+    <t>var_6_19</t>
+  </si>
+  <si>
+    <t>var_6_20</t>
+  </si>
+  <si>
+    <t>var_7_16</t>
+  </si>
+  <si>
+    <t>var_7_17</t>
+  </si>
+  <si>
+    <t>var_7_18</t>
+  </si>
+  <si>
+    <t>var_7_19</t>
+  </si>
+  <si>
+    <t>var_7_20</t>
+  </si>
+  <si>
+    <t>var_8_16</t>
+  </si>
+  <si>
+    <t>var_8_17</t>
+  </si>
+  <si>
+    <t>var_8_18</t>
+  </si>
+  <si>
+    <t>var_8_19</t>
+  </si>
+  <si>
+    <t>var_8_20</t>
+  </si>
+  <si>
+    <t>var_9_16</t>
+  </si>
+  <si>
+    <t>var_9_17</t>
+  </si>
+  <si>
+    <t>var_9_18</t>
+  </si>
+  <si>
+    <t>var_9_19</t>
+  </si>
+  <si>
+    <t>var_9_20</t>
+  </si>
+  <si>
+    <t>var_10_16</t>
+  </si>
+  <si>
+    <t>var_10_17</t>
+  </si>
+  <si>
+    <t>var_10_18</t>
+  </si>
+  <si>
+    <t>var_10_19</t>
+  </si>
+  <si>
+    <t>var_10_20</t>
+  </si>
+  <si>
+    <t>var_11_16</t>
+  </si>
+  <si>
+    <t>var_11_17</t>
+  </si>
+  <si>
+    <t>var_11_18</t>
+  </si>
+  <si>
+    <t>var_11_19</t>
+  </si>
+  <si>
+    <t>var_11_20</t>
+  </si>
+  <si>
+    <t>Showing 1 to 37 of 55 entries, 4 total columns</t>
+  </si>
+  <si>
+    <t>stems_loss_def</t>
+  </si>
+  <si>
+    <t>biom_loss_stem_def</t>
+  </si>
+  <si>
+    <t>biom_loss_root_def</t>
+  </si>
+  <si>
+    <t>biom_loss_foliage_def</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2121,6 +2296,25 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Grande"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Lucida Grande"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Lucida Grande"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2150,10 +2344,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4157,7 +4354,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA3706E6-9BD2-3A49-A255-D2B55C8D9AB1}">
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G221"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="51.1640625" customWidth="1"/>
@@ -4495,118 +4692,73 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17">
+      <c r="A17" s="4">
         <v>1</v>
       </c>
-      <c r="C17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" t="s">
-        <v>300</v>
-      </c>
-      <c r="E17" t="s">
-        <v>301</v>
-      </c>
-      <c r="F17" t="s">
-        <v>156</v>
-      </c>
-      <c r="G17" t="s">
-        <v>302</v>
+      <c r="B17" s="4">
+        <v>16</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
-        <v>303</v>
-      </c>
-      <c r="D18" t="s">
-        <v>300</v>
-      </c>
-      <c r="E18" t="s">
-        <v>304</v>
-      </c>
-      <c r="F18" t="s">
-        <v>305</v>
-      </c>
-      <c r="G18" t="s">
-        <v>306</v>
+      <c r="A18" s="4">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4">
+        <v>17</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2</v>
-      </c>
-      <c r="B19">
-        <v>3</v>
-      </c>
-      <c r="C19" t="s">
-        <v>307</v>
-      </c>
-      <c r="D19" t="s">
-        <v>300</v>
-      </c>
-      <c r="E19" t="s">
-        <v>308</v>
-      </c>
-      <c r="F19" t="s">
-        <v>309</v>
-      </c>
-      <c r="G19" t="s">
-        <v>310</v>
+      <c r="A19" s="4">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4">
+        <v>18</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>2</v>
-      </c>
-      <c r="B20">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s">
-        <v>311</v>
-      </c>
-      <c r="D20" t="s">
-        <v>300</v>
-      </c>
-      <c r="E20" t="s">
-        <v>312</v>
-      </c>
-      <c r="F20" t="s">
-        <v>313</v>
-      </c>
-      <c r="G20" t="s">
-        <v>314</v>
+      <c r="A20" s="4">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4">
+        <v>19</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>2</v>
-      </c>
-      <c r="B21">
-        <v>5</v>
-      </c>
-      <c r="C21" t="s">
-        <v>315</v>
-      </c>
-      <c r="D21" t="s">
-        <v>300</v>
-      </c>
-      <c r="E21" t="s">
-        <v>316</v>
-      </c>
-      <c r="F21" t="s">
-        <v>317</v>
-      </c>
-      <c r="G21" t="s">
-        <v>316</v>
+      <c r="A21" s="4">
+        <v>1</v>
+      </c>
+      <c r="B21" s="4">
+        <v>20</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -4614,22 +4766,22 @@
         <v>2</v>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>318</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
         <v>300</v>
       </c>
       <c r="E22" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="F22" t="s">
-        <v>320</v>
+        <v>156</v>
       </c>
       <c r="G22" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -4637,22 +4789,22 @@
         <v>2</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="D23" t="s">
         <v>300</v>
       </c>
       <c r="E23" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="F23" t="s">
-        <v>128</v>
+        <v>305</v>
       </c>
       <c r="G23" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -4660,22 +4812,22 @@
         <v>2</v>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="D24" t="s">
         <v>300</v>
       </c>
       <c r="E24" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="F24" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="G24" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -4683,22 +4835,22 @@
         <v>2</v>
       </c>
       <c r="B25">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="D25" t="s">
         <v>300</v>
       </c>
       <c r="E25" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="F25" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="G25" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -4706,22 +4858,22 @@
         <v>2</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="D26" t="s">
         <v>300</v>
       </c>
       <c r="E26" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="F26" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="G26" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -4729,22 +4881,22 @@
         <v>2</v>
       </c>
       <c r="B27">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="D27" t="s">
         <v>300</v>
       </c>
       <c r="E27" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="F27" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="G27" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -4752,22 +4904,22 @@
         <v>2</v>
       </c>
       <c r="B28">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="D28" t="s">
         <v>300</v>
       </c>
       <c r="E28" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="F28" t="s">
-        <v>333</v>
+        <v>128</v>
       </c>
       <c r="G28" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -4775,22 +4927,22 @@
         <v>2</v>
       </c>
       <c r="B29">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="D29" t="s">
         <v>300</v>
       </c>
       <c r="E29" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="F29" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="G29" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -4798,13 +4950,22 @@
         <v>2</v>
       </c>
       <c r="B30">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="D30" t="s">
         <v>300</v>
+      </c>
+      <c r="E30" t="s">
+        <v>329</v>
+      </c>
+      <c r="F30" t="s">
+        <v>320</v>
+      </c>
+      <c r="G30" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -4812,240 +4973,189 @@
         <v>2</v>
       </c>
       <c r="B31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="D31" t="s">
         <v>300</v>
       </c>
+      <c r="E31" t="s">
+        <v>332</v>
+      </c>
+      <c r="F31" t="s">
+        <v>333</v>
+      </c>
+      <c r="G31" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="D32" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="E32" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="F32" t="s">
-        <v>128</v>
+        <v>337</v>
       </c>
       <c r="G32" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="D33" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="E33" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="F33" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="G33" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="D34" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="E34" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="F34" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="G34" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="D35" t="s">
-        <v>348</v>
-      </c>
-      <c r="E35" t="s">
-        <v>360</v>
-      </c>
-      <c r="F35" t="s">
-        <v>357</v>
-      </c>
-      <c r="G35" t="s">
-        <v>361</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="D36" t="s">
-        <v>348</v>
-      </c>
-      <c r="E36" t="s">
-        <v>363</v>
-      </c>
-      <c r="G36" t="s">
-        <v>364</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>3</v>
-      </c>
-      <c r="B37">
-        <v>6</v>
-      </c>
-      <c r="C37" t="s">
-        <v>365</v>
-      </c>
-      <c r="D37" t="s">
-        <v>348</v>
-      </c>
-      <c r="E37" t="s">
-        <v>366</v>
-      </c>
-      <c r="F37" t="s">
-        <v>367</v>
-      </c>
-      <c r="G37" t="s">
-        <v>368</v>
+      <c r="A37" s="4">
+        <v>2</v>
+      </c>
+      <c r="B37" s="4">
+        <v>16</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>3</v>
-      </c>
-      <c r="B38">
-        <v>7</v>
-      </c>
-      <c r="C38" t="s">
-        <v>369</v>
-      </c>
-      <c r="D38" t="s">
-        <v>348</v>
-      </c>
-      <c r="E38" t="s">
-        <v>370</v>
-      </c>
-      <c r="F38" t="s">
-        <v>128</v>
-      </c>
-      <c r="G38" t="s">
-        <v>371</v>
+      <c r="A38" s="4">
+        <v>2</v>
+      </c>
+      <c r="B38" s="4">
+        <v>17</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>3</v>
-      </c>
-      <c r="B39">
-        <v>8</v>
-      </c>
-      <c r="C39" t="s">
-        <v>372</v>
-      </c>
-      <c r="D39" t="s">
-        <v>348</v>
-      </c>
-      <c r="E39" t="s">
-        <v>373</v>
-      </c>
-      <c r="F39" t="s">
-        <v>128</v>
-      </c>
-      <c r="G39" t="s">
-        <v>374</v>
+      <c r="A39" s="4">
+        <v>2</v>
+      </c>
+      <c r="B39" s="4">
+        <v>18</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>3</v>
-      </c>
-      <c r="B40">
-        <v>9</v>
-      </c>
-      <c r="C40" t="s">
-        <v>375</v>
-      </c>
-      <c r="D40" t="s">
-        <v>348</v>
-      </c>
-      <c r="E40" t="s">
-        <v>376</v>
-      </c>
-      <c r="F40" t="s">
-        <v>128</v>
-      </c>
-      <c r="G40" t="s">
-        <v>377</v>
+      <c r="A40" s="4">
+        <v>2</v>
+      </c>
+      <c r="B40" s="4">
+        <v>19</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>3</v>
-      </c>
-      <c r="B41">
-        <v>10</v>
-      </c>
-      <c r="C41" t="s">
-        <v>378</v>
-      </c>
-      <c r="D41" t="s">
-        <v>348</v>
-      </c>
-      <c r="E41" t="s">
-        <v>379</v>
-      </c>
-      <c r="F41" t="s">
-        <v>380</v>
-      </c>
-      <c r="G41" t="s">
-        <v>381</v>
+      <c r="A41" s="4">
+        <v>2</v>
+      </c>
+      <c r="B41" s="4">
+        <v>20</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -5053,22 +5163,22 @@
         <v>3</v>
       </c>
       <c r="B42">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="D42" t="s">
         <v>348</v>
       </c>
       <c r="E42" t="s">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="F42" t="s">
-        <v>285</v>
+        <v>128</v>
       </c>
       <c r="G42" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -5076,13 +5186,22 @@
         <v>3</v>
       </c>
       <c r="B43">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="D43" t="s">
         <v>348</v>
+      </c>
+      <c r="E43" t="s">
+        <v>352</v>
+      </c>
+      <c r="F43" t="s">
+        <v>353</v>
+      </c>
+      <c r="G43" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -5090,13 +5209,22 @@
         <v>3</v>
       </c>
       <c r="B44">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="D44" t="s">
         <v>348</v>
+      </c>
+      <c r="E44" t="s">
+        <v>356</v>
+      </c>
+      <c r="F44" t="s">
+        <v>357</v>
+      </c>
+      <c r="G44" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
@@ -5104,13 +5232,22 @@
         <v>3</v>
       </c>
       <c r="B45">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="D45" t="s">
         <v>348</v>
+      </c>
+      <c r="E45" t="s">
+        <v>360</v>
+      </c>
+      <c r="F45" t="s">
+        <v>357</v>
+      </c>
+      <c r="G45" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -5118,2423 +5255,4230 @@
         <v>3</v>
       </c>
       <c r="B46">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="D46" t="s">
         <v>348</v>
       </c>
+      <c r="E46" t="s">
+        <v>363</v>
+      </c>
+      <c r="G46" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>365</v>
       </c>
       <c r="D47" t="s">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="E47" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="F47" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="G47" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>369</v>
       </c>
       <c r="D48" t="s">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="E48" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="F48" t="s">
-        <v>391</v>
+        <v>128</v>
       </c>
       <c r="G48" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>372</v>
       </c>
       <c r="D49" t="s">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="E49" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="F49" t="s">
-        <v>391</v>
+        <v>128</v>
       </c>
       <c r="G49" t="s">
-        <v>396</v>
+        <v>374</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
       <c r="D50" t="s">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="E50" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
       <c r="F50" t="s">
-        <v>399</v>
+        <v>128</v>
       </c>
       <c r="G50" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="D51" t="s">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="E51" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="F51" t="s">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="G51" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B52">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>405</v>
+        <v>382</v>
       </c>
       <c r="D52" t="s">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="E52" t="s">
-        <v>406</v>
+        <v>383</v>
+      </c>
+      <c r="F52" t="s">
+        <v>285</v>
       </c>
       <c r="G52" t="s">
-        <v>407</v>
+        <v>384</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="D53" t="s">
-        <v>389</v>
-      </c>
-      <c r="E53" t="s">
-        <v>409</v>
-      </c>
-      <c r="F53" t="s">
-        <v>391</v>
-      </c>
-      <c r="G53" t="s">
-        <v>410</v>
+        <v>348</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B54">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="D54" t="s">
-        <v>389</v>
-      </c>
-      <c r="E54" t="s">
-        <v>412</v>
-      </c>
-      <c r="F54" t="s">
-        <v>391</v>
-      </c>
-      <c r="G54" t="s">
-        <v>413</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B55">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>414</v>
+        <v>387</v>
       </c>
       <c r="D55" t="s">
-        <v>389</v>
-      </c>
-      <c r="E55" t="s">
-        <v>415</v>
-      </c>
-      <c r="F55" t="s">
-        <v>391</v>
-      </c>
-      <c r="G55" t="s">
-        <v>416</v>
+        <v>348</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B56">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>417</v>
+        <v>388</v>
       </c>
       <c r="D56" t="s">
-        <v>389</v>
-      </c>
-      <c r="E56" t="s">
-        <v>418</v>
-      </c>
-      <c r="F56" t="s">
-        <v>391</v>
-      </c>
-      <c r="G56" t="s">
-        <v>419</v>
+        <v>348</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57">
-        <v>11</v>
-      </c>
-      <c r="C57" t="s">
-        <v>420</v>
-      </c>
-      <c r="D57" t="s">
-        <v>389</v>
-      </c>
-      <c r="E57" t="s">
-        <v>421</v>
-      </c>
-      <c r="F57" t="s">
-        <v>391</v>
-      </c>
-      <c r="G57" t="s">
-        <v>422</v>
+      <c r="A57" s="4">
+        <v>3</v>
+      </c>
+      <c r="B57" s="4">
+        <v>16</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>4</v>
-      </c>
-      <c r="B58">
-        <v>12</v>
-      </c>
-      <c r="C58" t="s">
-        <v>423</v>
-      </c>
-      <c r="D58" t="s">
-        <v>389</v>
+      <c r="A58" s="4">
+        <v>3</v>
+      </c>
+      <c r="B58" s="4">
+        <v>17</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>4</v>
-      </c>
-      <c r="B59">
-        <v>13</v>
-      </c>
-      <c r="C59" t="s">
-        <v>424</v>
-      </c>
-      <c r="D59" t="s">
-        <v>389</v>
+      <c r="A59" s="4">
+        <v>3</v>
+      </c>
+      <c r="B59" s="4">
+        <v>18</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>4</v>
-      </c>
-      <c r="B60">
-        <v>14</v>
-      </c>
-      <c r="C60" t="s">
-        <v>425</v>
-      </c>
-      <c r="D60" t="s">
-        <v>389</v>
+      <c r="A60" s="4">
+        <v>3</v>
+      </c>
+      <c r="B60" s="4">
+        <v>19</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>4</v>
-      </c>
-      <c r="B61">
-        <v>15</v>
-      </c>
-      <c r="C61" t="s">
-        <v>426</v>
-      </c>
-      <c r="D61" t="s">
-        <v>389</v>
+      <c r="A61" s="4">
+        <v>3</v>
+      </c>
+      <c r="B61" s="4">
+        <v>20</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>427</v>
+        <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="E62" t="s">
-        <v>429</v>
+        <v>390</v>
       </c>
       <c r="F62" t="s">
-        <v>128</v>
+        <v>391</v>
       </c>
       <c r="G62" t="s">
-        <v>430</v>
+        <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>431</v>
+        <v>115</v>
       </c>
       <c r="D63" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="E63" t="s">
-        <v>432</v>
+        <v>393</v>
       </c>
       <c r="F63" t="s">
-        <v>128</v>
+        <v>391</v>
       </c>
       <c r="G63" t="s">
-        <v>433</v>
+        <v>394</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B64">
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>434</v>
+        <v>114</v>
       </c>
       <c r="D64" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="E64" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
       <c r="F64" t="s">
-        <v>128</v>
+        <v>391</v>
       </c>
       <c r="G64" t="s">
-        <v>436</v>
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B65">
         <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>437</v>
+        <v>397</v>
       </c>
       <c r="D65" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="E65" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="F65" t="s">
-        <v>128</v>
+        <v>399</v>
       </c>
       <c r="G65" t="s">
-        <v>439</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B66">
         <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>440</v>
+        <v>401</v>
       </c>
       <c r="D66" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="E66" t="s">
-        <v>441</v>
+        <v>402</v>
       </c>
       <c r="F66" t="s">
-        <v>128</v>
+        <v>403</v>
       </c>
       <c r="G66" t="s">
-        <v>442</v>
+        <v>404</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B67">
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>443</v>
+        <v>405</v>
       </c>
       <c r="D67" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="E67" t="s">
-        <v>444</v>
-      </c>
-      <c r="F67" t="s">
-        <v>128</v>
+        <v>406</v>
       </c>
       <c r="G67" t="s">
-        <v>445</v>
+        <v>407</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B68">
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="D68" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="E68" t="s">
-        <v>447</v>
+        <v>409</v>
       </c>
       <c r="F68" t="s">
-        <v>128</v>
+        <v>391</v>
       </c>
       <c r="G68" t="s">
-        <v>448</v>
+        <v>410</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B69">
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>449</v>
+        <v>411</v>
       </c>
       <c r="D69" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="E69" t="s">
-        <v>450</v>
+        <v>412</v>
       </c>
       <c r="F69" t="s">
-        <v>128</v>
+        <v>391</v>
       </c>
       <c r="G69" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B70">
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>452</v>
+        <v>414</v>
       </c>
       <c r="D70" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="E70" t="s">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="F70" t="s">
-        <v>128</v>
+        <v>391</v>
       </c>
       <c r="G70" t="s">
-        <v>454</v>
+        <v>416</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B71">
         <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>455</v>
+        <v>417</v>
       </c>
       <c r="D71" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="E71" t="s">
-        <v>456</v>
+        <v>418</v>
       </c>
       <c r="F71" t="s">
-        <v>128</v>
+        <v>391</v>
       </c>
       <c r="G71" t="s">
-        <v>457</v>
+        <v>419</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B72">
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>458</v>
+        <v>420</v>
       </c>
       <c r="D72" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
       <c r="E72" t="s">
-        <v>459</v>
+        <v>421</v>
       </c>
       <c r="F72" t="s">
-        <v>128</v>
+        <v>391</v>
       </c>
       <c r="G72" t="s">
-        <v>460</v>
+        <v>422</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B73">
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>461</v>
+        <v>423</v>
       </c>
       <c r="D73" t="s">
-        <v>428</v>
-      </c>
-      <c r="E73" t="s">
-        <v>462</v>
-      </c>
-      <c r="G73" t="s">
-        <v>463</v>
+        <v>389</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B74">
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="D74" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B75">
         <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>465</v>
+        <v>425</v>
       </c>
       <c r="D75" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B76">
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>466</v>
+        <v>426</v>
       </c>
       <c r="D76" t="s">
-        <v>428</v>
+        <v>389</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77">
-        <v>6</v>
-      </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="C77" t="s">
-        <v>467</v>
-      </c>
-      <c r="D77" t="s">
-        <v>468</v>
-      </c>
-      <c r="E77" t="s">
-        <v>469</v>
-      </c>
-      <c r="F77" t="s">
-        <v>391</v>
-      </c>
-      <c r="G77" t="s">
-        <v>470</v>
+      <c r="A77" s="4">
+        <v>4</v>
+      </c>
+      <c r="B77" s="4">
+        <v>16</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78">
-        <v>6</v>
-      </c>
-      <c r="B78">
-        <v>2</v>
-      </c>
-      <c r="C78" t="s">
-        <v>471</v>
-      </c>
-      <c r="D78" t="s">
-        <v>468</v>
-      </c>
-      <c r="E78" t="s">
-        <v>472</v>
-      </c>
-      <c r="F78" t="s">
-        <v>391</v>
-      </c>
-      <c r="G78" t="s">
-        <v>473</v>
+      <c r="A78" s="4">
+        <v>4</v>
+      </c>
+      <c r="B78" s="4">
+        <v>17</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>6</v>
-      </c>
-      <c r="B79">
-        <v>3</v>
-      </c>
-      <c r="C79" t="s">
-        <v>635</v>
-      </c>
-      <c r="D79" t="s">
-        <v>468</v>
-      </c>
-      <c r="E79" t="s">
-        <v>474</v>
-      </c>
-      <c r="F79" t="s">
-        <v>475</v>
-      </c>
-      <c r="G79" t="s">
-        <v>476</v>
+      <c r="A79" s="4">
+        <v>4</v>
+      </c>
+      <c r="B79" s="4">
+        <v>18</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80">
-        <v>6</v>
-      </c>
-      <c r="B80">
+      <c r="A80" s="4">
         <v>4</v>
       </c>
-      <c r="C80" t="s">
-        <v>477</v>
-      </c>
-      <c r="D80" t="s">
-        <v>468</v>
-      </c>
-      <c r="E80" t="s">
-        <v>478</v>
-      </c>
-      <c r="F80" t="s">
-        <v>128</v>
-      </c>
-      <c r="G80" t="s">
-        <v>477</v>
+      <c r="B80" s="4">
+        <v>19</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81">
-        <v>6</v>
-      </c>
-      <c r="B81">
-        <v>5</v>
-      </c>
-      <c r="C81" t="s">
-        <v>479</v>
-      </c>
-      <c r="D81" t="s">
-        <v>468</v>
-      </c>
-      <c r="E81" t="s">
-        <v>480</v>
-      </c>
-      <c r="F81" t="s">
-        <v>481</v>
-      </c>
-      <c r="G81" t="s">
-        <v>482</v>
+      <c r="A81" s="4">
+        <v>4</v>
+      </c>
+      <c r="B81" s="4">
+        <v>20</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B82">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>483</v>
+        <v>427</v>
       </c>
       <c r="D82" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="E82" t="s">
-        <v>484</v>
+        <v>429</v>
       </c>
       <c r="F82" t="s">
-        <v>485</v>
+        <v>128</v>
       </c>
       <c r="G82" t="s">
-        <v>486</v>
+        <v>430</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B83">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>487</v>
+        <v>431</v>
       </c>
       <c r="D83" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="E83" t="s">
-        <v>488</v>
+        <v>432</v>
       </c>
       <c r="F83" t="s">
-        <v>485</v>
+        <v>128</v>
       </c>
       <c r="G83" t="s">
-        <v>489</v>
+        <v>433</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B84">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>490</v>
+        <v>434</v>
       </c>
       <c r="D84" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="E84" t="s">
-        <v>491</v>
+        <v>435</v>
       </c>
       <c r="F84" t="s">
-        <v>485</v>
+        <v>128</v>
       </c>
       <c r="G84" t="s">
-        <v>492</v>
+        <v>436</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B85">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>493</v>
+        <v>437</v>
       </c>
       <c r="D85" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="E85" t="s">
-        <v>494</v>
+        <v>438</v>
       </c>
       <c r="F85" t="s">
         <v>128</v>
       </c>
       <c r="G85" t="s">
-        <v>495</v>
+        <v>439</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B86">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C86" t="s">
-        <v>496</v>
+        <v>440</v>
       </c>
       <c r="D86" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="E86" t="s">
-        <v>497</v>
+        <v>441</v>
       </c>
       <c r="F86" t="s">
         <v>128</v>
       </c>
       <c r="G86" t="s">
-        <v>498</v>
+        <v>442</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87">
+        <v>5</v>
+      </c>
+      <c r="B87">
         <v>6</v>
       </c>
-      <c r="B87">
-        <v>11</v>
-      </c>
       <c r="C87" t="s">
-        <v>499</v>
+        <v>443</v>
       </c>
       <c r="D87" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="E87" t="s">
-        <v>500</v>
+        <v>444</v>
       </c>
       <c r="F87" t="s">
         <v>128</v>
       </c>
       <c r="G87" t="s">
-        <v>501</v>
+        <v>445</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B88">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>502</v>
+        <v>446</v>
       </c>
       <c r="D88" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="E88" t="s">
-        <v>503</v>
+        <v>447</v>
       </c>
       <c r="F88" t="s">
         <v>128</v>
       </c>
       <c r="G88" t="s">
-        <v>502</v>
+        <v>448</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B89">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>504</v>
+        <v>449</v>
       </c>
       <c r="D89" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="E89" t="s">
-        <v>505</v>
+        <v>450</v>
       </c>
       <c r="F89" t="s">
-        <v>391</v>
+        <v>128</v>
       </c>
       <c r="G89" t="s">
-        <v>506</v>
+        <v>451</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B90">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>507</v>
+        <v>452</v>
       </c>
       <c r="D90" t="s">
-        <v>468</v>
+        <v>428</v>
+      </c>
+      <c r="E90" t="s">
+        <v>453</v>
+      </c>
+      <c r="F90" t="s">
+        <v>128</v>
+      </c>
+      <c r="G90" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B91">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>508</v>
+        <v>455</v>
       </c>
       <c r="D91" t="s">
-        <v>468</v>
+        <v>428</v>
+      </c>
+      <c r="E91" t="s">
+        <v>456</v>
+      </c>
+      <c r="F91" t="s">
+        <v>128</v>
+      </c>
+      <c r="G91" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>509</v>
+        <v>458</v>
       </c>
       <c r="D92" t="s">
-        <v>510</v>
+        <v>428</v>
       </c>
       <c r="E92" t="s">
-        <v>511</v>
+        <v>459</v>
       </c>
       <c r="F92" t="s">
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="G92" t="s">
-        <v>511</v>
+        <v>460</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>513</v>
+        <v>461</v>
       </c>
       <c r="D93" t="s">
-        <v>510</v>
+        <v>428</v>
       </c>
       <c r="E93" t="s">
-        <v>514</v>
-      </c>
-      <c r="F93" t="s">
-        <v>512</v>
+        <v>462</v>
       </c>
       <c r="G93" t="s">
-        <v>514</v>
+        <v>463</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>515</v>
+        <v>464</v>
       </c>
       <c r="D94" t="s">
-        <v>510</v>
-      </c>
-      <c r="E94" t="s">
-        <v>516</v>
-      </c>
-      <c r="F94" t="s">
-        <v>517</v>
-      </c>
-      <c r="G94" t="s">
-        <v>518</v>
+        <v>428</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B95">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C95" t="s">
-        <v>519</v>
+        <v>465</v>
       </c>
       <c r="D95" t="s">
-        <v>510</v>
-      </c>
-      <c r="E95" t="s">
-        <v>520</v>
-      </c>
-      <c r="F95" t="s">
-        <v>521</v>
-      </c>
-      <c r="G95" t="s">
-        <v>522</v>
+        <v>428</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B96">
+        <v>15</v>
+      </c>
+      <c r="C96" t="s">
+        <v>466</v>
+      </c>
+      <c r="D96" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" s="4">
         <v>5</v>
       </c>
-      <c r="C96" t="s">
-        <v>523</v>
-      </c>
-      <c r="D96" t="s">
-        <v>510</v>
-      </c>
-      <c r="E96" t="s">
-        <v>524</v>
-      </c>
-      <c r="F96" t="s">
-        <v>128</v>
-      </c>
-      <c r="G96" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A97">
-        <v>7</v>
-      </c>
-      <c r="B97">
-        <v>6</v>
-      </c>
-      <c r="C97" t="s">
-        <v>526</v>
-      </c>
-      <c r="D97" t="s">
-        <v>510</v>
-      </c>
-      <c r="E97" t="s">
-        <v>527</v>
-      </c>
-      <c r="F97" t="s">
-        <v>521</v>
-      </c>
-      <c r="G97" t="s">
-        <v>528</v>
+      <c r="B97" s="4">
+        <v>16</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A98">
-        <v>7</v>
-      </c>
-      <c r="B98">
-        <v>7</v>
-      </c>
-      <c r="C98" t="s">
-        <v>529</v>
-      </c>
-      <c r="D98" t="s">
-        <v>510</v>
-      </c>
-      <c r="E98" t="s">
-        <v>530</v>
-      </c>
-      <c r="F98" t="s">
-        <v>521</v>
-      </c>
-      <c r="G98" t="s">
-        <v>531</v>
+      <c r="A98" s="4">
+        <v>5</v>
+      </c>
+      <c r="B98" s="4">
+        <v>17</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A99">
-        <v>7</v>
-      </c>
-      <c r="B99">
-        <v>8</v>
-      </c>
-      <c r="C99" t="s">
-        <v>532</v>
-      </c>
-      <c r="D99" t="s">
-        <v>510</v>
-      </c>
-      <c r="E99" t="s">
-        <v>533</v>
-      </c>
-      <c r="F99" t="s">
-        <v>534</v>
-      </c>
-      <c r="G99" t="s">
-        <v>535</v>
+      <c r="A99" s="4">
+        <v>5</v>
+      </c>
+      <c r="B99" s="4">
+        <v>18</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A100">
-        <v>7</v>
-      </c>
-      <c r="B100">
-        <v>9</v>
-      </c>
-      <c r="C100" t="s">
-        <v>536</v>
-      </c>
-      <c r="D100" t="s">
-        <v>510</v>
-      </c>
-      <c r="E100" t="s">
-        <v>537</v>
-      </c>
-      <c r="F100" t="s">
-        <v>534</v>
-      </c>
-      <c r="G100" t="s">
-        <v>538</v>
+      <c r="A100" s="4">
+        <v>5</v>
+      </c>
+      <c r="B100" s="4">
+        <v>19</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A101">
-        <v>7</v>
-      </c>
-      <c r="B101">
-        <v>10</v>
-      </c>
-      <c r="C101" t="s">
-        <v>539</v>
-      </c>
-      <c r="D101" t="s">
-        <v>510</v>
-      </c>
-      <c r="E101" t="s">
-        <v>540</v>
-      </c>
-      <c r="F101" t="s">
-        <v>517</v>
-      </c>
-      <c r="G101" t="s">
-        <v>541</v>
+      <c r="A101" s="4">
+        <v>5</v>
+      </c>
+      <c r="B101" s="4">
+        <v>20</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B102">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>542</v>
+        <v>467</v>
       </c>
       <c r="D102" t="s">
-        <v>510</v>
+        <v>468</v>
       </c>
       <c r="E102" t="s">
-        <v>543</v>
+        <v>469</v>
       </c>
       <c r="F102" t="s">
-        <v>517</v>
+        <v>391</v>
       </c>
       <c r="G102" t="s">
-        <v>544</v>
+        <v>470</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B103">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>545</v>
+        <v>471</v>
       </c>
       <c r="D103" t="s">
-        <v>510</v>
+        <v>468</v>
       </c>
       <c r="E103" t="s">
-        <v>546</v>
+        <v>472</v>
       </c>
       <c r="F103" t="s">
-        <v>521</v>
+        <v>391</v>
       </c>
       <c r="G103" t="s">
-        <v>547</v>
+        <v>473</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B104">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>548</v>
+        <v>635</v>
       </c>
       <c r="D104" t="s">
-        <v>510</v>
+        <v>468</v>
       </c>
       <c r="E104" t="s">
-        <v>549</v>
+        <v>474</v>
       </c>
       <c r="F104" t="s">
-        <v>521</v>
+        <v>475</v>
       </c>
       <c r="G104" t="s">
-        <v>550</v>
+        <v>476</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B105">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>551</v>
+        <v>477</v>
       </c>
       <c r="D105" t="s">
-        <v>510</v>
+        <v>468</v>
+      </c>
+      <c r="E105" t="s">
+        <v>478</v>
+      </c>
+      <c r="F105" t="s">
+        <v>128</v>
+      </c>
+      <c r="G105" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B106">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>552</v>
+        <v>479</v>
       </c>
       <c r="D106" t="s">
-        <v>510</v>
+        <v>468</v>
+      </c>
+      <c r="E106" t="s">
+        <v>480</v>
+      </c>
+      <c r="F106" t="s">
+        <v>481</v>
+      </c>
+      <c r="G106" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C107" t="s">
-        <v>553</v>
+        <v>483</v>
       </c>
       <c r="D107" t="s">
-        <v>554</v>
+        <v>468</v>
       </c>
       <c r="E107" t="s">
-        <v>555</v>
+        <v>484</v>
       </c>
       <c r="F107" t="s">
-        <v>556</v>
+        <v>485</v>
       </c>
       <c r="G107" t="s">
-        <v>557</v>
+        <v>486</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>558</v>
+        <v>487</v>
       </c>
       <c r="D108" t="s">
-        <v>554</v>
+        <v>468</v>
       </c>
       <c r="E108" t="s">
-        <v>559</v>
+        <v>488</v>
       </c>
       <c r="F108" t="s">
-        <v>560</v>
+        <v>485</v>
       </c>
       <c r="G108" t="s">
-        <v>558</v>
+        <v>489</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109">
+        <v>6</v>
+      </c>
+      <c r="B109">
         <v>8</v>
       </c>
-      <c r="B109">
-        <v>3</v>
-      </c>
       <c r="C109" t="s">
-        <v>680</v>
+        <v>490</v>
       </c>
       <c r="D109" t="s">
-        <v>554</v>
+        <v>468</v>
       </c>
       <c r="E109" t="s">
-        <v>561</v>
+        <v>491</v>
       </c>
       <c r="F109" t="s">
-        <v>305</v>
+        <v>485</v>
       </c>
       <c r="G109" t="s">
-        <v>562</v>
+        <v>492</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B110">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C110" t="s">
-        <v>672</v>
+        <v>493</v>
       </c>
       <c r="D110" t="s">
-        <v>554</v>
+        <v>468</v>
       </c>
       <c r="E110" t="s">
-        <v>563</v>
+        <v>494</v>
       </c>
       <c r="F110" t="s">
-        <v>305</v>
+        <v>128</v>
       </c>
       <c r="G110" t="s">
-        <v>564</v>
+        <v>495</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="2">
-        <v>8</v>
-      </c>
-      <c r="B111" s="2">
-        <v>5</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>648</v>
+      <c r="A111">
+        <v>6</v>
+      </c>
+      <c r="B111">
+        <v>10</v>
+      </c>
+      <c r="C111" t="s">
+        <v>496</v>
       </c>
       <c r="D111" t="s">
-        <v>554</v>
+        <v>468</v>
       </c>
       <c r="E111" t="s">
-        <v>655</v>
+        <v>497</v>
       </c>
       <c r="F111" t="s">
-        <v>305</v>
+        <v>128</v>
       </c>
       <c r="G111" t="s">
-        <v>562</v>
+        <v>498</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B112">
-        <v>6</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>656</v>
+        <v>11</v>
+      </c>
+      <c r="C112" t="s">
+        <v>499</v>
       </c>
       <c r="D112" t="s">
-        <v>554</v>
+        <v>468</v>
+      </c>
+      <c r="E112" t="s">
+        <v>500</v>
+      </c>
+      <c r="F112" t="s">
+        <v>128</v>
+      </c>
+      <c r="G112" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B113">
-        <v>7</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>657</v>
+        <v>12</v>
+      </c>
+      <c r="C113" t="s">
+        <v>502</v>
       </c>
       <c r="D113" t="s">
-        <v>554</v>
+        <v>468</v>
+      </c>
+      <c r="E113" t="s">
+        <v>503</v>
+      </c>
+      <c r="F113" t="s">
+        <v>128</v>
+      </c>
+      <c r="G113" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B114">
-        <v>8</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>658</v>
+        <v>13</v>
+      </c>
+      <c r="C114" t="s">
+        <v>504</v>
       </c>
       <c r="D114" t="s">
-        <v>554</v>
+        <v>468</v>
       </c>
       <c r="E114" t="s">
-        <v>316</v>
+        <v>505</v>
+      </c>
+      <c r="F114" t="s">
+        <v>391</v>
+      </c>
+      <c r="G114" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B115">
-        <v>9</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>649</v>
+        <v>14</v>
+      </c>
+      <c r="C115" t="s">
+        <v>507</v>
       </c>
       <c r="D115" t="s">
-        <v>554</v>
-      </c>
-      <c r="E115" t="s">
-        <v>316</v>
+        <v>468</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B116">
-        <v>10</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>650</v>
+        <v>15</v>
+      </c>
+      <c r="C116" t="s">
+        <v>508</v>
       </c>
       <c r="D116" t="s">
-        <v>554</v>
-      </c>
-      <c r="E116" t="s">
-        <v>659</v>
+        <v>468</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A117">
-        <v>8</v>
-      </c>
-      <c r="B117">
-        <v>11</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="D117" t="s">
-        <v>554</v>
+      <c r="A117" s="4">
+        <v>6</v>
+      </c>
+      <c r="B117" s="4">
+        <v>16</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118">
-        <v>8</v>
-      </c>
-      <c r="B118">
-        <v>12</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="D118" t="s">
-        <v>554</v>
+      <c r="A118" s="4">
+        <v>6</v>
+      </c>
+      <c r="B118" s="4">
+        <v>17</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119">
-        <v>8</v>
-      </c>
-      <c r="B119">
-        <v>13</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="D119" t="s">
-        <v>554</v>
+      <c r="A119" s="4">
+        <v>6</v>
+      </c>
+      <c r="B119" s="4">
+        <v>18</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120">
-        <v>8</v>
-      </c>
-      <c r="B120">
-        <v>14</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="D120" t="s">
-        <v>554</v>
+      <c r="A120" s="4">
+        <v>6</v>
+      </c>
+      <c r="B120" s="4">
+        <v>19</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A121">
-        <v>8</v>
-      </c>
-      <c r="B121">
-        <v>15</v>
-      </c>
-      <c r="C121" t="s">
-        <v>565</v>
-      </c>
-      <c r="D121" t="s">
-        <v>554</v>
+      <c r="A121" s="4">
+        <v>6</v>
+      </c>
+      <c r="B121" s="4">
+        <v>20</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>566</v>
+        <v>509</v>
       </c>
       <c r="D122" t="s">
-        <v>567</v>
+        <v>510</v>
       </c>
       <c r="E122" t="s">
-        <v>568</v>
+        <v>511</v>
       </c>
       <c r="F122" t="s">
-        <v>569</v>
+        <v>512</v>
       </c>
       <c r="G122" t="s">
-        <v>570</v>
+        <v>511</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>571</v>
+        <v>513</v>
       </c>
       <c r="D123" t="s">
-        <v>567</v>
+        <v>510</v>
       </c>
       <c r="E123" t="s">
-        <v>572</v>
+        <v>514</v>
       </c>
       <c r="F123" t="s">
-        <v>569</v>
+        <v>512</v>
       </c>
       <c r="G123" t="s">
-        <v>573</v>
+        <v>514</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B124">
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>574</v>
+        <v>515</v>
       </c>
       <c r="D124" t="s">
-        <v>567</v>
+        <v>510</v>
       </c>
       <c r="E124" t="s">
-        <v>575</v>
+        <v>516</v>
+      </c>
+      <c r="F124" t="s">
+        <v>517</v>
       </c>
       <c r="G124" t="s">
-        <v>574</v>
+        <v>518</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B125">
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>576</v>
+        <v>519</v>
       </c>
       <c r="D125" t="s">
-        <v>567</v>
+        <v>510</v>
       </c>
       <c r="E125" t="s">
-        <v>577</v>
+        <v>520</v>
+      </c>
+      <c r="F125" t="s">
+        <v>521</v>
       </c>
       <c r="G125" t="s">
-        <v>576</v>
+        <v>522</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B126">
         <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>578</v>
+        <v>523</v>
       </c>
       <c r="D126" t="s">
-        <v>567</v>
+        <v>510</v>
       </c>
       <c r="E126" t="s">
-        <v>579</v>
+        <v>524</v>
       </c>
       <c r="F126" t="s">
-        <v>288</v>
+        <v>128</v>
       </c>
       <c r="G126" t="s">
-        <v>580</v>
+        <v>525</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B127">
         <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>581</v>
+        <v>526</v>
       </c>
       <c r="D127" t="s">
-        <v>567</v>
+        <v>510</v>
+      </c>
+      <c r="E127" t="s">
+        <v>527</v>
+      </c>
+      <c r="F127" t="s">
+        <v>521</v>
+      </c>
+      <c r="G127" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B128">
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>582</v>
+        <v>529</v>
       </c>
       <c r="D128" t="s">
-        <v>567</v>
+        <v>510</v>
+      </c>
+      <c r="E128" t="s">
+        <v>530</v>
+      </c>
+      <c r="F128" t="s">
+        <v>521</v>
+      </c>
+      <c r="G128" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B129">
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>583</v>
+        <v>532</v>
       </c>
       <c r="D129" t="s">
-        <v>567</v>
+        <v>510</v>
+      </c>
+      <c r="E129" t="s">
+        <v>533</v>
+      </c>
+      <c r="F129" t="s">
+        <v>534</v>
+      </c>
+      <c r="G129" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B130">
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>584</v>
+        <v>536</v>
       </c>
       <c r="D130" t="s">
-        <v>567</v>
+        <v>510</v>
+      </c>
+      <c r="E130" t="s">
+        <v>537</v>
+      </c>
+      <c r="F130" t="s">
+        <v>534</v>
+      </c>
+      <c r="G130" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B131">
         <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>585</v>
+        <v>539</v>
       </c>
       <c r="D131" t="s">
-        <v>567</v>
+        <v>510</v>
+      </c>
+      <c r="E131" t="s">
+        <v>540</v>
+      </c>
+      <c r="F131" t="s">
+        <v>517</v>
+      </c>
+      <c r="G131" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B132">
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>586</v>
+        <v>542</v>
       </c>
       <c r="D132" t="s">
-        <v>567</v>
+        <v>510</v>
+      </c>
+      <c r="E132" t="s">
+        <v>543</v>
+      </c>
+      <c r="F132" t="s">
+        <v>517</v>
+      </c>
+      <c r="G132" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B133">
         <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>587</v>
+        <v>545</v>
       </c>
       <c r="D133" t="s">
-        <v>567</v>
+        <v>510</v>
+      </c>
+      <c r="E133" t="s">
+        <v>546</v>
+      </c>
+      <c r="F133" t="s">
+        <v>521</v>
+      </c>
+      <c r="G133" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B134">
         <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>588</v>
+        <v>548</v>
       </c>
       <c r="D134" t="s">
-        <v>567</v>
+        <v>510</v>
+      </c>
+      <c r="E134" t="s">
+        <v>549</v>
+      </c>
+      <c r="F134" t="s">
+        <v>521</v>
+      </c>
+      <c r="G134" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B135">
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>589</v>
+        <v>551</v>
       </c>
       <c r="D135" t="s">
-        <v>567</v>
+        <v>510</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B136">
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>590</v>
+        <v>552</v>
       </c>
       <c r="D136" t="s">
-        <v>567</v>
+        <v>510</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A137">
-        <v>10</v>
-      </c>
-      <c r="B137">
-        <v>1</v>
-      </c>
-      <c r="C137" t="s">
-        <v>591</v>
-      </c>
-      <c r="D137" t="s">
-        <v>592</v>
-      </c>
-      <c r="E137" t="s">
-        <v>593</v>
-      </c>
-      <c r="F137" t="s">
-        <v>128</v>
-      </c>
-      <c r="G137" t="s">
-        <v>594</v>
+      <c r="A137" s="4">
+        <v>7</v>
+      </c>
+      <c r="B137" s="4">
+        <v>16</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A138">
-        <v>10</v>
-      </c>
-      <c r="B138">
-        <v>2</v>
-      </c>
-      <c r="C138" t="s">
-        <v>595</v>
-      </c>
-      <c r="D138" t="s">
-        <v>592</v>
-      </c>
-      <c r="E138" t="s">
-        <v>596</v>
-      </c>
-      <c r="F138" t="s">
-        <v>128</v>
-      </c>
-      <c r="G138" t="s">
-        <v>597</v>
+      <c r="A138" s="4">
+        <v>7</v>
+      </c>
+      <c r="B138" s="4">
+        <v>17</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A139">
-        <v>10</v>
-      </c>
-      <c r="B139">
-        <v>3</v>
-      </c>
-      <c r="C139" t="s">
-        <v>598</v>
-      </c>
-      <c r="D139" t="s">
-        <v>592</v>
-      </c>
-      <c r="E139" t="s">
-        <v>599</v>
-      </c>
-      <c r="F139" t="s">
-        <v>128</v>
-      </c>
-      <c r="G139" t="s">
-        <v>600</v>
+      <c r="A139" s="4">
+        <v>7</v>
+      </c>
+      <c r="B139" s="4">
+        <v>18</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A140">
-        <v>10</v>
-      </c>
-      <c r="B140">
-        <v>4</v>
-      </c>
-      <c r="C140" t="s">
-        <v>601</v>
-      </c>
-      <c r="D140" t="s">
-        <v>592</v>
-      </c>
-      <c r="E140" t="s">
-        <v>602</v>
-      </c>
-      <c r="F140" t="s">
-        <v>128</v>
-      </c>
-      <c r="G140" t="s">
-        <v>603</v>
+      <c r="A140" s="4">
+        <v>7</v>
+      </c>
+      <c r="B140" s="4">
+        <v>19</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A141">
-        <v>10</v>
-      </c>
-      <c r="B141">
-        <v>5</v>
-      </c>
-      <c r="C141" t="s">
-        <v>604</v>
-      </c>
-      <c r="D141" t="s">
-        <v>592</v>
-      </c>
-      <c r="E141" t="s">
-        <v>605</v>
-      </c>
-      <c r="F141" t="s">
-        <v>128</v>
-      </c>
-      <c r="G141" t="s">
-        <v>606</v>
+      <c r="A141" s="4">
+        <v>7</v>
+      </c>
+      <c r="B141" s="4">
+        <v>20</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="D141" s="4" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B142">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>607</v>
+        <v>553</v>
       </c>
       <c r="D142" t="s">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="E142" t="s">
-        <v>608</v>
+        <v>555</v>
       </c>
       <c r="F142" t="s">
-        <v>128</v>
+        <v>556</v>
       </c>
       <c r="G142" t="s">
-        <v>609</v>
+        <v>557</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B143">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C143" t="s">
-        <v>610</v>
+        <v>558</v>
       </c>
       <c r="D143" t="s">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="E143" t="s">
-        <v>611</v>
+        <v>559</v>
       </c>
       <c r="F143" t="s">
-        <v>367</v>
+        <v>560</v>
       </c>
       <c r="G143" t="s">
-        <v>612</v>
+        <v>558</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B144">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C144" t="s">
-        <v>613</v>
+        <v>677</v>
       </c>
       <c r="D144" t="s">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="E144" t="s">
-        <v>614</v>
+        <v>561</v>
       </c>
       <c r="F144" t="s">
-        <v>367</v>
+        <v>305</v>
       </c>
       <c r="G144" t="s">
-        <v>615</v>
+        <v>562</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B145">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>616</v>
+        <v>669</v>
       </c>
       <c r="D145" t="s">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="E145" t="s">
-        <v>617</v>
+        <v>563</v>
       </c>
       <c r="F145" t="s">
-        <v>367</v>
+        <v>305</v>
       </c>
       <c r="G145" t="s">
-        <v>618</v>
+        <v>564</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A146">
-        <v>10</v>
-      </c>
-      <c r="B146">
-        <v>10</v>
-      </c>
-      <c r="C146" t="s">
-        <v>619</v>
+      <c r="A146" s="2">
+        <v>8</v>
+      </c>
+      <c r="B146" s="2">
+        <v>5</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>648</v>
       </c>
       <c r="D146" t="s">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="E146" t="s">
-        <v>620</v>
+        <v>655</v>
       </c>
       <c r="F146" t="s">
-        <v>367</v>
+        <v>305</v>
       </c>
       <c r="G146" t="s">
-        <v>621</v>
+        <v>562</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B147">
-        <v>11</v>
-      </c>
-      <c r="C147" t="s">
-        <v>622</v>
+        <v>6</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>656</v>
       </c>
       <c r="D147" t="s">
-        <v>592</v>
-      </c>
-      <c r="E147" t="s">
-        <v>623</v>
-      </c>
-      <c r="F147" t="s">
-        <v>367</v>
-      </c>
-      <c r="G147" t="s">
-        <v>624</v>
+        <v>554</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B148">
-        <v>12</v>
-      </c>
-      <c r="C148" t="s">
-        <v>625</v>
+        <v>7</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>657</v>
       </c>
       <c r="D148" t="s">
-        <v>592</v>
-      </c>
-      <c r="E148" t="s">
-        <v>626</v>
-      </c>
-      <c r="F148" t="s">
-        <v>367</v>
-      </c>
-      <c r="G148" t="s">
-        <v>627</v>
+        <v>554</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B149">
-        <v>13</v>
-      </c>
-      <c r="C149" t="s">
-        <v>628</v>
+        <v>8</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>658</v>
       </c>
       <c r="D149" t="s">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="E149" t="s">
-        <v>629</v>
-      </c>
-      <c r="F149" t="s">
-        <v>367</v>
-      </c>
-      <c r="G149" t="s">
-        <v>630</v>
+        <v>316</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B150">
-        <v>14</v>
-      </c>
-      <c r="C150" t="s">
-        <v>631</v>
+        <v>9</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>649</v>
       </c>
       <c r="D150" t="s">
-        <v>592</v>
+        <v>554</v>
       </c>
       <c r="E150" t="s">
-        <v>632</v>
-      </c>
-      <c r="F150" t="s">
-        <v>367</v>
-      </c>
-      <c r="G150" t="s">
-        <v>633</v>
+        <v>316</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151">
+        <v>8</v>
+      </c>
+      <c r="B151">
         <v>10</v>
       </c>
-      <c r="B151">
-        <v>15</v>
-      </c>
-      <c r="C151" t="s">
-        <v>634</v>
+      <c r="C151" s="1" t="s">
+        <v>650</v>
       </c>
       <c r="D151" t="s">
-        <v>592</v>
+        <v>554</v>
+      </c>
+      <c r="E151" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152">
+        <v>8</v>
+      </c>
+      <c r="B152">
         <v>11</v>
       </c>
-      <c r="B152">
-        <v>1</v>
-      </c>
-      <c r="C152" t="s">
-        <v>661</v>
+      <c r="C152" s="1" t="s">
+        <v>651</v>
       </c>
       <c r="D152" t="s">
-        <v>660</v>
-      </c>
-      <c r="E152" t="s">
-        <v>668</v>
-      </c>
-      <c r="F152" t="s">
-        <v>305</v>
+        <v>554</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B153">
-        <v>2</v>
-      </c>
-      <c r="C153" t="s">
-        <v>662</v>
+        <v>12</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>652</v>
       </c>
       <c r="D153" t="s">
-        <v>660</v>
-      </c>
-      <c r="E153" t="s">
-        <v>669</v>
-      </c>
-      <c r="F153" t="s">
-        <v>391</v>
+        <v>554</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B154">
-        <v>3</v>
-      </c>
-      <c r="C154" t="s">
-        <v>663</v>
+        <v>13</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="D154" t="s">
-        <v>660</v>
-      </c>
-      <c r="E154" t="s">
-        <v>670</v>
-      </c>
-      <c r="F154" t="s">
-        <v>391</v>
+        <v>554</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B155">
-        <v>4</v>
-      </c>
-      <c r="C155" t="s">
-        <v>664</v>
+        <v>14</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>654</v>
       </c>
       <c r="D155" t="s">
-        <v>660</v>
-      </c>
-      <c r="E155" t="s">
-        <v>671</v>
-      </c>
-      <c r="F155" t="s">
-        <v>391</v>
+        <v>554</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156">
+        <v>8</v>
+      </c>
+      <c r="B156">
+        <v>15</v>
+      </c>
+      <c r="C156" t="s">
+        <v>565</v>
+      </c>
+      <c r="D156" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" s="4">
+        <v>8</v>
+      </c>
+      <c r="B157" s="4">
+        <v>16</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" s="4">
+        <v>8</v>
+      </c>
+      <c r="B158" s="4">
+        <v>17</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" s="4">
+        <v>8</v>
+      </c>
+      <c r="B159" s="4">
+        <v>18</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" s="4">
+        <v>8</v>
+      </c>
+      <c r="B160" s="4">
+        <v>19</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="4">
+        <v>8</v>
+      </c>
+      <c r="B161" s="4">
+        <v>20</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>9</v>
+      </c>
+      <c r="B162">
+        <v>1</v>
+      </c>
+      <c r="C162" t="s">
+        <v>566</v>
+      </c>
+      <c r="D162" t="s">
+        <v>567</v>
+      </c>
+      <c r="E162" t="s">
+        <v>568</v>
+      </c>
+      <c r="F162" t="s">
+        <v>569</v>
+      </c>
+      <c r="G162" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>9</v>
+      </c>
+      <c r="B163">
+        <v>2</v>
+      </c>
+      <c r="C163" t="s">
+        <v>571</v>
+      </c>
+      <c r="D163" t="s">
+        <v>567</v>
+      </c>
+      <c r="E163" t="s">
+        <v>572</v>
+      </c>
+      <c r="F163" t="s">
+        <v>569</v>
+      </c>
+      <c r="G163" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>9</v>
+      </c>
+      <c r="B164">
+        <v>3</v>
+      </c>
+      <c r="C164" t="s">
+        <v>574</v>
+      </c>
+      <c r="D164" t="s">
+        <v>567</v>
+      </c>
+      <c r="E164" t="s">
+        <v>575</v>
+      </c>
+      <c r="G164" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>9</v>
+      </c>
+      <c r="B165">
+        <v>4</v>
+      </c>
+      <c r="C165" t="s">
+        <v>576</v>
+      </c>
+      <c r="D165" t="s">
+        <v>567</v>
+      </c>
+      <c r="E165" t="s">
+        <v>577</v>
+      </c>
+      <c r="G165" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>9</v>
+      </c>
+      <c r="B166">
+        <v>5</v>
+      </c>
+      <c r="C166" t="s">
+        <v>578</v>
+      </c>
+      <c r="D166" t="s">
+        <v>567</v>
+      </c>
+      <c r="E166" t="s">
+        <v>579</v>
+      </c>
+      <c r="F166" t="s">
+        <v>288</v>
+      </c>
+      <c r="G166" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>9</v>
+      </c>
+      <c r="B167">
+        <v>6</v>
+      </c>
+      <c r="C167" t="s">
+        <v>581</v>
+      </c>
+      <c r="D167" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>9</v>
+      </c>
+      <c r="B168">
+        <v>7</v>
+      </c>
+      <c r="C168" t="s">
+        <v>582</v>
+      </c>
+      <c r="D168" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>9</v>
+      </c>
+      <c r="B169">
+        <v>8</v>
+      </c>
+      <c r="C169" t="s">
+        <v>583</v>
+      </c>
+      <c r="D169" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>9</v>
+      </c>
+      <c r="B170">
+        <v>9</v>
+      </c>
+      <c r="C170" t="s">
+        <v>584</v>
+      </c>
+      <c r="D170" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>9</v>
+      </c>
+      <c r="B171">
+        <v>10</v>
+      </c>
+      <c r="C171" t="s">
+        <v>585</v>
+      </c>
+      <c r="D171" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>9</v>
+      </c>
+      <c r="B172">
         <v>11</v>
       </c>
-      <c r="B156">
+      <c r="C172" t="s">
+        <v>586</v>
+      </c>
+      <c r="D172" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>9</v>
+      </c>
+      <c r="B173">
+        <v>12</v>
+      </c>
+      <c r="C173" t="s">
+        <v>587</v>
+      </c>
+      <c r="D173" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>9</v>
+      </c>
+      <c r="B174">
+        <v>13</v>
+      </c>
+      <c r="C174" t="s">
+        <v>588</v>
+      </c>
+      <c r="D174" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>9</v>
+      </c>
+      <c r="B175">
+        <v>14</v>
+      </c>
+      <c r="C175" t="s">
+        <v>589</v>
+      </c>
+      <c r="D175" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>9</v>
+      </c>
+      <c r="B176">
+        <v>15</v>
+      </c>
+      <c r="C176" t="s">
+        <v>590</v>
+      </c>
+      <c r="D176" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="4">
+        <v>9</v>
+      </c>
+      <c r="B177" s="4">
+        <v>16</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="4">
+        <v>9</v>
+      </c>
+      <c r="B178" s="4">
+        <v>17</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="4">
+        <v>9</v>
+      </c>
+      <c r="B179" s="4">
+        <v>18</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A180" s="4">
+        <v>9</v>
+      </c>
+      <c r="B180" s="4">
+        <v>19</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A181" s="4">
+        <v>9</v>
+      </c>
+      <c r="B181" s="4">
+        <v>20</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>10</v>
+      </c>
+      <c r="B182">
+        <v>1</v>
+      </c>
+      <c r="C182" t="s">
+        <v>591</v>
+      </c>
+      <c r="D182" t="s">
+        <v>592</v>
+      </c>
+      <c r="E182" t="s">
+        <v>593</v>
+      </c>
+      <c r="F182" t="s">
+        <v>128</v>
+      </c>
+      <c r="G182" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>10</v>
+      </c>
+      <c r="B183">
+        <v>2</v>
+      </c>
+      <c r="C183" t="s">
+        <v>595</v>
+      </c>
+      <c r="D183" t="s">
+        <v>592</v>
+      </c>
+      <c r="E183" t="s">
+        <v>596</v>
+      </c>
+      <c r="F183" t="s">
+        <v>128</v>
+      </c>
+      <c r="G183" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>10</v>
+      </c>
+      <c r="B184">
+        <v>3</v>
+      </c>
+      <c r="C184" t="s">
+        <v>598</v>
+      </c>
+      <c r="D184" t="s">
+        <v>592</v>
+      </c>
+      <c r="E184" t="s">
+        <v>599</v>
+      </c>
+      <c r="F184" t="s">
+        <v>128</v>
+      </c>
+      <c r="G184" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>10</v>
+      </c>
+      <c r="B185">
+        <v>4</v>
+      </c>
+      <c r="C185" t="s">
+        <v>601</v>
+      </c>
+      <c r="D185" t="s">
+        <v>592</v>
+      </c>
+      <c r="E185" t="s">
+        <v>602</v>
+      </c>
+      <c r="F185" t="s">
+        <v>128</v>
+      </c>
+      <c r="G185" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>10</v>
+      </c>
+      <c r="B186">
         <v>5</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C186" t="s">
+        <v>604</v>
+      </c>
+      <c r="D186" t="s">
+        <v>592</v>
+      </c>
+      <c r="E186" t="s">
+        <v>605</v>
+      </c>
+      <c r="F186" t="s">
+        <v>128</v>
+      </c>
+      <c r="G186" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>10</v>
+      </c>
+      <c r="B187">
+        <v>6</v>
+      </c>
+      <c r="C187" t="s">
+        <v>607</v>
+      </c>
+      <c r="D187" t="s">
+        <v>592</v>
+      </c>
+      <c r="E187" t="s">
+        <v>608</v>
+      </c>
+      <c r="F187" t="s">
+        <v>128</v>
+      </c>
+      <c r="G187" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>10</v>
+      </c>
+      <c r="B188">
+        <v>7</v>
+      </c>
+      <c r="C188" t="s">
+        <v>610</v>
+      </c>
+      <c r="D188" t="s">
+        <v>592</v>
+      </c>
+      <c r="E188" t="s">
+        <v>611</v>
+      </c>
+      <c r="F188" t="s">
+        <v>367</v>
+      </c>
+      <c r="G188" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>10</v>
+      </c>
+      <c r="B189">
+        <v>8</v>
+      </c>
+      <c r="C189" t="s">
+        <v>613</v>
+      </c>
+      <c r="D189" t="s">
+        <v>592</v>
+      </c>
+      <c r="E189" t="s">
+        <v>614</v>
+      </c>
+      <c r="F189" t="s">
+        <v>367</v>
+      </c>
+      <c r="G189" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>10</v>
+      </c>
+      <c r="B190">
+        <v>9</v>
+      </c>
+      <c r="C190" t="s">
+        <v>616</v>
+      </c>
+      <c r="D190" t="s">
+        <v>592</v>
+      </c>
+      <c r="E190" t="s">
+        <v>617</v>
+      </c>
+      <c r="F190" t="s">
+        <v>367</v>
+      </c>
+      <c r="G190" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>10</v>
+      </c>
+      <c r="B191">
+        <v>10</v>
+      </c>
+      <c r="C191" t="s">
+        <v>619</v>
+      </c>
+      <c r="D191" t="s">
+        <v>592</v>
+      </c>
+      <c r="E191" t="s">
+        <v>620</v>
+      </c>
+      <c r="F191" t="s">
+        <v>367</v>
+      </c>
+      <c r="G191" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>10</v>
+      </c>
+      <c r="B192">
+        <v>11</v>
+      </c>
+      <c r="C192" t="s">
+        <v>622</v>
+      </c>
+      <c r="D192" t="s">
+        <v>592</v>
+      </c>
+      <c r="E192" t="s">
+        <v>623</v>
+      </c>
+      <c r="F192" t="s">
+        <v>367</v>
+      </c>
+      <c r="G192" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>10</v>
+      </c>
+      <c r="B193">
+        <v>12</v>
+      </c>
+      <c r="C193" t="s">
+        <v>625</v>
+      </c>
+      <c r="D193" t="s">
+        <v>592</v>
+      </c>
+      <c r="E193" t="s">
+        <v>626</v>
+      </c>
+      <c r="F193" t="s">
+        <v>367</v>
+      </c>
+      <c r="G193" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>10</v>
+      </c>
+      <c r="B194">
+        <v>13</v>
+      </c>
+      <c r="C194" t="s">
+        <v>628</v>
+      </c>
+      <c r="D194" t="s">
+        <v>592</v>
+      </c>
+      <c r="E194" t="s">
+        <v>629</v>
+      </c>
+      <c r="F194" t="s">
+        <v>367</v>
+      </c>
+      <c r="G194" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>10</v>
+      </c>
+      <c r="B195">
+        <v>14</v>
+      </c>
+      <c r="C195" t="s">
+        <v>631</v>
+      </c>
+      <c r="D195" t="s">
+        <v>592</v>
+      </c>
+      <c r="E195" t="s">
+        <v>632</v>
+      </c>
+      <c r="F195" t="s">
+        <v>367</v>
+      </c>
+      <c r="G195" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>10</v>
+      </c>
+      <c r="B196">
+        <v>15</v>
+      </c>
+      <c r="C196" t="s">
+        <v>634</v>
+      </c>
+      <c r="D196" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A197" s="4">
+        <v>10</v>
+      </c>
+      <c r="B197" s="4">
+        <v>16</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A198" s="4">
+        <v>10</v>
+      </c>
+      <c r="B198" s="4">
+        <v>17</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D198" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A199" s="4">
+        <v>10</v>
+      </c>
+      <c r="B199" s="4">
+        <v>18</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="D199" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A200" s="4">
+        <v>10</v>
+      </c>
+      <c r="B200" s="4">
+        <v>19</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A201" s="4">
+        <v>10</v>
+      </c>
+      <c r="B201" s="4">
+        <v>20</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>11</v>
+      </c>
+      <c r="B202">
+        <v>1</v>
+      </c>
+      <c r="C202" t="s">
+        <v>661</v>
+      </c>
+      <c r="D202" t="s">
+        <v>660</v>
+      </c>
+      <c r="E202" t="s">
+        <v>665</v>
+      </c>
+      <c r="F202" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>11</v>
+      </c>
+      <c r="B203">
+        <v>2</v>
+      </c>
+      <c r="C203" t="s">
+        <v>662</v>
+      </c>
+      <c r="D203" t="s">
+        <v>660</v>
+      </c>
+      <c r="E203" t="s">
+        <v>666</v>
+      </c>
+      <c r="F203" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>11</v>
+      </c>
+      <c r="B204">
+        <v>3</v>
+      </c>
+      <c r="C204" t="s">
+        <v>663</v>
+      </c>
+      <c r="D204" t="s">
+        <v>660</v>
+      </c>
+      <c r="E204" t="s">
+        <v>667</v>
+      </c>
+      <c r="F204" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <v>11</v>
+      </c>
+      <c r="B205">
+        <v>4</v>
+      </c>
+      <c r="C205" t="s">
+        <v>664</v>
+      </c>
+      <c r="D205" t="s">
+        <v>660</v>
+      </c>
+      <c r="E205" t="s">
+        <v>668</v>
+      </c>
+      <c r="F205" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>11</v>
+      </c>
+      <c r="B206">
+        <v>5</v>
+      </c>
+      <c r="C206" t="s">
+        <v>669</v>
+      </c>
+      <c r="D206" t="s">
+        <v>660</v>
+      </c>
+      <c r="E206" t="s">
+        <v>673</v>
+      </c>
+      <c r="F206" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>11</v>
+      </c>
+      <c r="B207">
+        <v>6</v>
+      </c>
+      <c r="C207" t="s">
+        <v>670</v>
+      </c>
+      <c r="D207" t="s">
+        <v>660</v>
+      </c>
+      <c r="E207" t="s">
+        <v>674</v>
+      </c>
+      <c r="F207" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <v>11</v>
+      </c>
+      <c r="B208">
+        <v>7</v>
+      </c>
+      <c r="C208" t="s">
+        <v>671</v>
+      </c>
+      <c r="D208" t="s">
+        <v>660</v>
+      </c>
+      <c r="E208" t="s">
+        <v>675</v>
+      </c>
+      <c r="F208" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <v>11</v>
+      </c>
+      <c r="B209">
+        <v>8</v>
+      </c>
+      <c r="C209" t="s">
         <v>672</v>
       </c>
-      <c r="D156" t="s">
+      <c r="D209" t="s">
         <v>660</v>
       </c>
-      <c r="E156" t="s">
+      <c r="E209" t="s">
         <v>676</v>
       </c>
-      <c r="F156" t="s">
+      <c r="F209" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>11</v>
+      </c>
+      <c r="B210">
+        <v>9</v>
+      </c>
+      <c r="C210" t="s">
+        <v>677</v>
+      </c>
+      <c r="D210" t="s">
+        <v>660</v>
+      </c>
+      <c r="E210" t="s">
+        <v>681</v>
+      </c>
+      <c r="F210" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A157">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A211">
         <v>11</v>
       </c>
-      <c r="B157">
-        <v>6</v>
-      </c>
-      <c r="C157" t="s">
-        <v>673</v>
-      </c>
-      <c r="D157" t="s">
+      <c r="B211">
+        <v>10</v>
+      </c>
+      <c r="C211" t="s">
+        <v>678</v>
+      </c>
+      <c r="D211" t="s">
         <v>660</v>
       </c>
-      <c r="E157" t="s">
-        <v>677</v>
-      </c>
-      <c r="F157" t="s">
+      <c r="E211" t="s">
+        <v>682</v>
+      </c>
+      <c r="F211" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A158">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A212">
         <v>11</v>
       </c>
-      <c r="B158">
-        <v>7</v>
-      </c>
-      <c r="C158" t="s">
-        <v>674</v>
-      </c>
-      <c r="D158" t="s">
+      <c r="B212">
+        <v>11</v>
+      </c>
+      <c r="C212" t="s">
+        <v>679</v>
+      </c>
+      <c r="D212" t="s">
         <v>660</v>
       </c>
-      <c r="E158" t="s">
-        <v>678</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="E212" t="s">
+        <v>683</v>
+      </c>
+      <c r="F212" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A159">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A213">
         <v>11</v>
       </c>
-      <c r="B159">
-        <v>8</v>
-      </c>
-      <c r="C159" t="s">
-        <v>675</v>
-      </c>
-      <c r="D159" t="s">
+      <c r="B213">
+        <v>12</v>
+      </c>
+      <c r="C213" t="s">
+        <v>680</v>
+      </c>
+      <c r="D213" t="s">
         <v>660</v>
       </c>
-      <c r="E159" t="s">
-        <v>679</v>
-      </c>
-      <c r="F159" t="s">
+      <c r="E213" t="s">
+        <v>684</v>
+      </c>
+      <c r="F213" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A160">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A214">
         <v>11</v>
       </c>
-      <c r="B160">
-        <v>9</v>
-      </c>
-      <c r="C160" t="s">
-        <v>680</v>
-      </c>
-      <c r="D160" t="s">
+      <c r="B214">
+        <v>13</v>
+      </c>
+      <c r="C214" t="s">
+        <v>741</v>
+      </c>
+      <c r="D214" t="s">
         <v>660</v>
       </c>
-      <c r="E160" t="s">
-        <v>684</v>
-      </c>
-      <c r="F160" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A161">
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A215">
         <v>11</v>
       </c>
-      <c r="B161">
-        <v>10</v>
-      </c>
-      <c r="C161" t="s">
-        <v>681</v>
-      </c>
-      <c r="D161" t="s">
+      <c r="B215">
+        <v>14</v>
+      </c>
+      <c r="C215" t="s">
+        <v>742</v>
+      </c>
+      <c r="D215" t="s">
         <v>660</v>
       </c>
-      <c r="E161" t="s">
-        <v>685</v>
-      </c>
-      <c r="F161" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162">
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A216">
         <v>11</v>
       </c>
-      <c r="B162">
+      <c r="B216">
+        <v>15</v>
+      </c>
+      <c r="C216" t="s">
+        <v>743</v>
+      </c>
+      <c r="D216" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A217" s="4">
         <v>11</v>
       </c>
-      <c r="C162" t="s">
-        <v>682</v>
-      </c>
-      <c r="D162" t="s">
+      <c r="B217" s="4">
+        <v>16</v>
+      </c>
+      <c r="C217" t="s">
+        <v>744</v>
+      </c>
+      <c r="D217" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="E162" t="s">
-        <v>686</v>
-      </c>
-      <c r="F162" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163">
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A218" s="4">
         <v>11</v>
       </c>
-      <c r="B163">
-        <v>12</v>
-      </c>
-      <c r="C163" t="s">
-        <v>683</v>
-      </c>
-      <c r="D163" t="s">
+      <c r="B218" s="4">
+        <v>17</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="D218" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="E163" t="s">
-        <v>687</v>
-      </c>
-      <c r="F163" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A164">
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A219" s="4">
         <v>11</v>
       </c>
-      <c r="B164">
-        <v>13</v>
-      </c>
-      <c r="C164" t="s">
-        <v>665</v>
-      </c>
-      <c r="D164" t="s">
+      <c r="B219" s="4">
+        <v>18</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="D219" s="4" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A165">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A220" s="4">
         <v>11</v>
       </c>
-      <c r="B165">
-        <v>14</v>
-      </c>
-      <c r="C165" t="s">
-        <v>666</v>
-      </c>
-      <c r="D165" t="s">
+      <c r="B220" s="4">
+        <v>19</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="D220" s="4" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A166">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A221" s="4">
         <v>11</v>
       </c>
-      <c r="B166">
-        <v>15</v>
-      </c>
-      <c r="C166" t="s">
-        <v>667</v>
-      </c>
-      <c r="D166" t="s">
+      <c r="B221" s="4">
+        <v>20</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="D221" s="4" t="s">
         <v>660</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G221" xr:uid="{DA3706E6-9BD2-3A49-A255-D2B55C8D9AB1}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G221">
+      <sortCondition ref="A1:A221"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C146B8-AED1-D84E-BB27-CA28C1D97E3C}">
+  <dimension ref="A1:E58"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4">
+        <v>16</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4">
+        <v>20</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4">
+        <v>16</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4">
+        <v>17</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4">
+        <v>18</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
+        <v>19</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4">
+        <v>16</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4">
+        <v>17</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4">
+        <v>3</v>
+      </c>
+      <c r="C15" s="4">
+        <v>18</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4">
+        <v>3</v>
+      </c>
+      <c r="C16" s="4">
+        <v>19</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4">
+        <v>3</v>
+      </c>
+      <c r="C17" s="4">
+        <v>20</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4">
+        <v>4</v>
+      </c>
+      <c r="C18" s="4">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4">
+        <v>4</v>
+      </c>
+      <c r="C19" s="4">
+        <v>17</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4">
+        <v>4</v>
+      </c>
+      <c r="C20" s="4">
+        <v>18</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4">
+        <v>4</v>
+      </c>
+      <c r="C21" s="4">
+        <v>19</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4">
+        <v>4</v>
+      </c>
+      <c r="C22" s="4">
+        <v>20</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4">
+        <v>16</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4">
+        <v>5</v>
+      </c>
+      <c r="C24" s="4">
+        <v>17</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4">
+        <v>18</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4">
+        <v>5</v>
+      </c>
+      <c r="C26" s="4">
+        <v>19</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
+        <v>25</v>
+      </c>
+      <c r="B27" s="4">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4">
+        <v>20</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4">
+        <v>16</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4">
+        <v>6</v>
+      </c>
+      <c r="C29" s="4">
+        <v>17</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>28</v>
+      </c>
+      <c r="B30" s="4">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4">
+        <v>18</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4">
+        <v>6</v>
+      </c>
+      <c r="C31" s="4">
+        <v>19</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4">
+        <v>6</v>
+      </c>
+      <c r="C32" s="4">
+        <v>20</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4">
+        <v>7</v>
+      </c>
+      <c r="C33" s="4">
+        <v>16</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4">
+        <v>7</v>
+      </c>
+      <c r="C34" s="4">
+        <v>17</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4">
+        <v>7</v>
+      </c>
+      <c r="C35" s="4">
+        <v>18</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4">
+        <v>7</v>
+      </c>
+      <c r="C36" s="4">
+        <v>19</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4">
+        <v>7</v>
+      </c>
+      <c r="C37" s="4">
+        <v>20</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4">
+        <v>8</v>
+      </c>
+      <c r="C38" s="4">
+        <v>16</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4">
+        <v>8</v>
+      </c>
+      <c r="C39" s="4">
+        <v>17</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4">
+        <v>8</v>
+      </c>
+      <c r="C40" s="4">
+        <v>18</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4">
+        <v>8</v>
+      </c>
+      <c r="C41" s="4">
+        <v>19</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4">
+        <v>8</v>
+      </c>
+      <c r="C42" s="4">
+        <v>20</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4">
+        <v>9</v>
+      </c>
+      <c r="C43" s="4">
+        <v>16</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4">
+        <v>9</v>
+      </c>
+      <c r="C44" s="4">
+        <v>17</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4">
+        <v>9</v>
+      </c>
+      <c r="C45" s="4">
+        <v>18</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4">
+        <v>9</v>
+      </c>
+      <c r="C46" s="4">
+        <v>19</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4">
+        <v>9</v>
+      </c>
+      <c r="C47" s="4">
+        <v>20</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4">
+        <v>10</v>
+      </c>
+      <c r="C48" s="4">
+        <v>16</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4">
+        <v>10</v>
+      </c>
+      <c r="C49" s="4">
+        <v>17</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4">
+        <v>10</v>
+      </c>
+      <c r="C50" s="4">
+        <v>18</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4">
+        <v>10</v>
+      </c>
+      <c r="C51" s="4">
+        <v>19</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <v>50</v>
+      </c>
+      <c r="B52" s="4">
+        <v>10</v>
+      </c>
+      <c r="C52" s="4">
+        <v>20</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4">
+        <v>11</v>
+      </c>
+      <c r="C53" s="4">
+        <v>16</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
+        <v>52</v>
+      </c>
+      <c r="B54" s="4">
+        <v>11</v>
+      </c>
+      <c r="C54" s="4">
+        <v>17</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
+        <v>53</v>
+      </c>
+      <c r="B55" s="4">
+        <v>11</v>
+      </c>
+      <c r="C55" s="4">
+        <v>18</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="3">
+        <v>54</v>
+      </c>
+      <c r="B56" s="4">
+        <v>11</v>
+      </c>
+      <c r="C56" s="4">
+        <v>19</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="3">
+        <v>55</v>
+      </c>
+      <c r="B57" s="4">
+        <v>11</v>
+      </c>
+      <c r="C57" s="4">
+        <v>20</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="5" t="s">
+        <v>740</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trotsiuk/Documents/Research/software/r3PG/data-raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F903BF-3827-1F46-9732-B29A8B79E7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391A5BF4-4965-477B-B28F-85BC38AF9E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="500" windowWidth="32960" windowHeight="28300" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="747">
   <si>
     <t>pFS2</t>
   </si>
@@ -1986,12 +1986,6 @@
     <t>stems_n_total</t>
   </si>
   <si>
-    <t>var_8_11</t>
-  </si>
-  <si>
-    <t>var_8_12</t>
-  </si>
-  <si>
     <t>var_8_13</t>
   </si>
   <si>
@@ -2266,13 +2260,25 @@
   </si>
   <si>
     <t>biom_loss_foliage_def</t>
+  </si>
+  <si>
+    <t>lt_fT</t>
+  </si>
+  <si>
+    <t>lt_fPhys</t>
+  </si>
+  <si>
+    <t>10-year average fT</t>
+  </si>
+  <si>
+    <t>10-year average fPhys</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2667,9 +2673,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E287297-02C0-BF44-BF0C-8FADE2A87F8F}">
   <dimension ref="A1:D89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -2683,7 +2689,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2697,7 +2703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2711,7 +2717,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -2725,7 +2731,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2739,7 +2745,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -2753,7 +2759,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2767,7 +2773,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -2781,7 +2787,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -2795,7 +2801,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2809,7 +2815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2823,7 +2829,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2837,7 +2843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2851,7 +2857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2865,7 +2871,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2879,7 +2885,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2893,7 +2899,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2907,7 +2913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2921,7 +2927,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2935,7 +2941,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2949,7 +2955,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -2963,7 +2969,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2977,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2991,7 +2997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -3005,7 +3011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -3019,7 +3025,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -3033,7 +3039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -3047,7 +3053,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -3061,7 +3067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -3075,7 +3081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -3089,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -3103,7 +3109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -3117,7 +3123,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -3131,7 +3137,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
         <v>636</v>
       </c>
@@ -3143,7 +3149,7 @@
         <v>-20.399999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
         <v>637</v>
       </c>
@@ -3155,7 +3161,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
         <v>638</v>
       </c>
@@ -3167,7 +3173,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
         <v>639</v>
       </c>
@@ -3179,7 +3185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
         <v>640</v>
       </c>
@@ -3191,7 +3197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
         <v>641</v>
       </c>
@@ -3203,7 +3209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>33</v>
       </c>
@@ -3217,7 +3223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>34</v>
       </c>
@@ -3231,7 +3237,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>35</v>
       </c>
@@ -3245,7 +3251,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>36</v>
       </c>
@@ -3259,7 +3265,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>37</v>
       </c>
@@ -3273,7 +3279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>38</v>
       </c>
@@ -3287,7 +3293,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -3301,7 +3307,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>40</v>
       </c>
@@ -3315,7 +3321,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
         <v>41</v>
       </c>
@@ -3329,7 +3335,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -3343,7 +3349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>43</v>
       </c>
@@ -3357,7 +3363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -3371,7 +3377,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>45</v>
       </c>
@@ -3385,7 +3391,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>46</v>
       </c>
@@ -3399,7 +3405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -3413,7 +3419,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>48</v>
       </c>
@@ -3427,7 +3433,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>49</v>
       </c>
@@ -3441,7 +3447,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>50</v>
       </c>
@@ -3455,7 +3461,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>51</v>
       </c>
@@ -3469,7 +3475,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -3483,7 +3489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>53</v>
       </c>
@@ -3497,7 +3503,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>54</v>
       </c>
@@ -3511,7 +3517,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -3525,7 +3531,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>56</v>
       </c>
@@ -3539,7 +3545,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>57</v>
       </c>
@@ -3553,7 +3559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>58</v>
       </c>
@@ -3567,7 +3573,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>59</v>
       </c>
@@ -3581,7 +3587,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>60</v>
       </c>
@@ -3595,7 +3601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -3609,7 +3615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>61</v>
       </c>
@@ -3623,7 +3629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
         <v>62</v>
       </c>
@@ -3637,7 +3643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
         <v>63</v>
       </c>
@@ -3651,7 +3657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>64</v>
       </c>
@@ -3665,7 +3671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>65</v>
       </c>
@@ -3679,7 +3685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>66</v>
       </c>
@@ -3693,7 +3699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>67</v>
       </c>
@@ -3707,7 +3713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>69</v>
       </c>
@@ -3721,7 +3727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>70</v>
       </c>
@@ -3735,7 +3741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>71</v>
       </c>
@@ -3749,7 +3755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
         <v>72</v>
       </c>
@@ -3763,7 +3769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
         <v>73</v>
       </c>
@@ -3777,7 +3783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
         <v>74</v>
       </c>
@@ -3791,7 +3797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
         <v>75</v>
       </c>
@@ -3805,7 +3811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>76</v>
       </c>
@@ -3819,7 +3825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
         <v>77</v>
       </c>
@@ -3833,7 +3839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
         <v>78</v>
       </c>
@@ -3847,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
         <v>109</v>
       </c>
@@ -3861,7 +3867,7 @@
         <v>-90</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
         <v>110</v>
       </c>
@@ -3875,7 +3881,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
         <v>111</v>
       </c>
@@ -3889,7 +3895,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>112</v>
       </c>
@@ -3905,15 +3911,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF000D6-A72C-6444-9177-22D437B8361A}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -3927,7 +3937,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -3941,7 +3951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -3955,7 +3965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -3969,7 +3979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -3983,7 +3993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>83</v>
       </c>
@@ -3997,7 +4007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>84</v>
       </c>
@@ -4011,7 +4021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -4025,7 +4035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>86</v>
       </c>
@@ -4039,7 +4049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -4053,7 +4063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -4067,7 +4077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -4081,7 +4091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -4095,7 +4105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -4109,7 +4119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -4123,7 +4133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>93</v>
       </c>
@@ -4137,7 +4147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -4151,7 +4161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -4165,7 +4175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -4179,7 +4189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>97</v>
       </c>
@@ -4193,7 +4203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -4207,7 +4217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>99</v>
       </c>
@@ -4221,7 +4231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>100</v>
       </c>
@@ -4235,7 +4245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -4249,7 +4259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -4263,7 +4273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>103</v>
       </c>
@@ -4277,7 +4287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -4291,7 +4301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>105</v>
       </c>
@@ -4305,7 +4315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -4319,7 +4329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>107</v>
       </c>
@@ -4333,7 +4343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>108</v>
       </c>
@@ -4349,20 +4359,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA3706E6-9BD2-3A49-A255-D2B55C8D9AB1}">
   <dimension ref="A1:G221"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="3" max="3" width="51.1640625" customWidth="1"/>
+    <col min="3" max="3" width="51.125" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="179" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>256</v>
       </c>
@@ -4385,7 +4399,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4408,7 +4422,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4431,7 +4445,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4454,7 +4468,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4477,7 +4491,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4500,7 +4514,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4523,7 +4537,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4546,7 +4560,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>1</v>
       </c>
@@ -4569,7 +4583,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>1</v>
       </c>
@@ -4592,7 +4606,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>1</v>
       </c>
@@ -4612,7 +4626,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>1</v>
       </c>
@@ -4635,7 +4649,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>1</v>
       </c>
@@ -4649,7 +4663,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>1</v>
       </c>
@@ -4663,7 +4677,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>1</v>
       </c>
@@ -4677,7 +4691,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>1</v>
       </c>
@@ -4691,7 +4705,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="4">
         <v>1</v>
       </c>
@@ -4699,13 +4713,13 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="4">
         <v>1</v>
       </c>
@@ -4713,13 +4727,13 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="4">
         <v>1</v>
       </c>
@@ -4727,13 +4741,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="4">
         <v>1</v>
       </c>
@@ -4741,13 +4755,13 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="4">
         <v>1</v>
       </c>
@@ -4755,13 +4769,13 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4784,7 +4798,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>2</v>
       </c>
@@ -4807,7 +4821,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>2</v>
       </c>
@@ -4830,7 +4844,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>2</v>
       </c>
@@ -4853,7 +4867,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>2</v>
       </c>
@@ -4876,7 +4890,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>2</v>
       </c>
@@ -4899,7 +4913,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>2</v>
       </c>
@@ -4922,7 +4936,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>2</v>
       </c>
@@ -4945,7 +4959,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>2</v>
       </c>
@@ -4968,7 +4982,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>2</v>
       </c>
@@ -4991,7 +5005,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>2</v>
       </c>
@@ -5014,7 +5028,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>2</v>
       </c>
@@ -5037,7 +5051,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>2</v>
       </c>
@@ -5060,7 +5074,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>2</v>
       </c>
@@ -5074,7 +5088,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>2</v>
       </c>
@@ -5088,7 +5102,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="4">
         <v>2</v>
       </c>
@@ -5096,13 +5110,13 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="4">
         <v>2</v>
       </c>
@@ -5110,13 +5124,13 @@
         <v>17</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="4">
         <v>2</v>
       </c>
@@ -5124,13 +5138,13 @@
         <v>18</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7">
       <c r="A40" s="4">
         <v>2</v>
       </c>
@@ -5138,13 +5152,13 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7">
       <c r="A41" s="4">
         <v>2</v>
       </c>
@@ -5152,13 +5166,13 @@
         <v>20</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>3</v>
       </c>
@@ -5181,7 +5195,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>3</v>
       </c>
@@ -5204,7 +5218,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>3</v>
       </c>
@@ -5227,7 +5241,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>3</v>
       </c>
@@ -5250,7 +5264,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>3</v>
       </c>
@@ -5270,7 +5284,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>3</v>
       </c>
@@ -5293,7 +5307,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>3</v>
       </c>
@@ -5316,7 +5330,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>3</v>
       </c>
@@ -5339,7 +5353,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>3</v>
       </c>
@@ -5362,7 +5376,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>3</v>
       </c>
@@ -5385,7 +5399,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>3</v>
       </c>
@@ -5408,7 +5422,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>3</v>
       </c>
@@ -5422,7 +5436,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>3</v>
       </c>
@@ -5436,7 +5450,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>3</v>
       </c>
@@ -5450,7 +5464,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>3</v>
       </c>
@@ -5464,7 +5478,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7">
       <c r="A57" s="4">
         <v>3</v>
       </c>
@@ -5472,13 +5486,13 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7">
       <c r="A58" s="4">
         <v>3</v>
       </c>
@@ -5486,13 +5500,13 @@
         <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7">
       <c r="A59" s="4">
         <v>3</v>
       </c>
@@ -5500,13 +5514,13 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7">
       <c r="A60" s="4">
         <v>3</v>
       </c>
@@ -5514,13 +5528,13 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7">
       <c r="A61" s="4">
         <v>3</v>
       </c>
@@ -5528,13 +5542,13 @@
         <v>20</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7">
       <c r="A62">
         <v>4</v>
       </c>
@@ -5557,7 +5571,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7">
       <c r="A63">
         <v>4</v>
       </c>
@@ -5580,7 +5594,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7">
       <c r="A64">
         <v>4</v>
       </c>
@@ -5603,7 +5617,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>4</v>
       </c>
@@ -5626,7 +5640,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>4</v>
       </c>
@@ -5649,7 +5663,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>4</v>
       </c>
@@ -5669,7 +5683,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>4</v>
       </c>
@@ -5692,7 +5706,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>4</v>
       </c>
@@ -5715,7 +5729,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>4</v>
       </c>
@@ -5738,7 +5752,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>4</v>
       </c>
@@ -5761,7 +5775,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>4</v>
       </c>
@@ -5784,7 +5798,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>4</v>
       </c>
@@ -5798,7 +5812,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>4</v>
       </c>
@@ -5812,7 +5826,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>4</v>
       </c>
@@ -5826,7 +5840,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>4</v>
       </c>
@@ -5840,7 +5854,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7">
       <c r="A77" s="4">
         <v>4</v>
       </c>
@@ -5848,13 +5862,13 @@
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7">
       <c r="A78" s="4">
         <v>4</v>
       </c>
@@ -5862,13 +5876,13 @@
         <v>17</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7">
       <c r="A79" s="4">
         <v>4</v>
       </c>
@@ -5876,13 +5890,13 @@
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7">
       <c r="A80" s="4">
         <v>4</v>
       </c>
@@ -5890,13 +5904,13 @@
         <v>19</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7">
       <c r="A81" s="4">
         <v>4</v>
       </c>
@@ -5904,13 +5918,13 @@
         <v>20</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7">
       <c r="A82">
         <v>5</v>
       </c>
@@ -5933,7 +5947,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7">
       <c r="A83">
         <v>5</v>
       </c>
@@ -5956,7 +5970,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7">
       <c r="A84">
         <v>5</v>
       </c>
@@ -5979,7 +5993,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7">
       <c r="A85">
         <v>5</v>
       </c>
@@ -6002,7 +6016,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7">
       <c r="A86">
         <v>5</v>
       </c>
@@ -6025,7 +6039,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7">
       <c r="A87">
         <v>5</v>
       </c>
@@ -6048,7 +6062,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7">
       <c r="A88">
         <v>5</v>
       </c>
@@ -6071,7 +6085,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7">
       <c r="A89">
         <v>5</v>
       </c>
@@ -6094,7 +6108,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7">
       <c r="A90">
         <v>5</v>
       </c>
@@ -6117,7 +6131,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7">
       <c r="A91">
         <v>5</v>
       </c>
@@ -6140,7 +6154,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7">
       <c r="A92">
         <v>5</v>
       </c>
@@ -6163,7 +6177,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7">
       <c r="A93">
         <v>5</v>
       </c>
@@ -6183,7 +6197,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7">
       <c r="A94">
         <v>5</v>
       </c>
@@ -6197,7 +6211,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7">
       <c r="A95">
         <v>5</v>
       </c>
@@ -6211,7 +6225,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7">
       <c r="A96">
         <v>5</v>
       </c>
@@ -6225,7 +6239,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7">
       <c r="A97" s="4">
         <v>5</v>
       </c>
@@ -6233,13 +6247,13 @@
         <v>16</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7">
       <c r="A98" s="4">
         <v>5</v>
       </c>
@@ -6247,13 +6261,13 @@
         <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7">
       <c r="A99" s="4">
         <v>5</v>
       </c>
@@ -6261,13 +6275,13 @@
         <v>18</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7">
       <c r="A100" s="4">
         <v>5</v>
       </c>
@@ -6275,13 +6289,13 @@
         <v>19</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7">
       <c r="A101" s="4">
         <v>5</v>
       </c>
@@ -6289,13 +6303,13 @@
         <v>20</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7">
       <c r="A102">
         <v>6</v>
       </c>
@@ -6318,7 +6332,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7">
       <c r="A103">
         <v>6</v>
       </c>
@@ -6341,7 +6355,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7">
       <c r="A104">
         <v>6</v>
       </c>
@@ -6364,7 +6378,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7">
       <c r="A105">
         <v>6</v>
       </c>
@@ -6387,7 +6401,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7">
       <c r="A106">
         <v>6</v>
       </c>
@@ -6410,7 +6424,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7">
       <c r="A107">
         <v>6</v>
       </c>
@@ -6433,7 +6447,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7">
       <c r="A108">
         <v>6</v>
       </c>
@@ -6456,7 +6470,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7">
       <c r="A109">
         <v>6</v>
       </c>
@@ -6479,7 +6493,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7">
       <c r="A110">
         <v>6</v>
       </c>
@@ -6502,7 +6516,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" s="2" customFormat="1">
       <c r="A111">
         <v>6</v>
       </c>
@@ -6525,7 +6539,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7">
       <c r="A112">
         <v>6</v>
       </c>
@@ -6548,7 +6562,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7">
       <c r="A113">
         <v>6</v>
       </c>
@@ -6571,7 +6585,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7">
       <c r="A114">
         <v>6</v>
       </c>
@@ -6594,7 +6608,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7">
       <c r="A115">
         <v>6</v>
       </c>
@@ -6608,7 +6622,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7">
       <c r="A116">
         <v>6</v>
       </c>
@@ -6622,7 +6636,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7">
       <c r="A117" s="4">
         <v>6</v>
       </c>
@@ -6630,13 +6644,13 @@
         <v>16</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7">
       <c r="A118" s="4">
         <v>6</v>
       </c>
@@ -6644,13 +6658,13 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7">
       <c r="A119" s="4">
         <v>6</v>
       </c>
@@ -6658,13 +6672,13 @@
         <v>18</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7">
       <c r="A120" s="4">
         <v>6</v>
       </c>
@@ -6672,13 +6686,13 @@
         <v>19</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7">
       <c r="A121" s="4">
         <v>6</v>
       </c>
@@ -6686,13 +6700,13 @@
         <v>20</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7">
       <c r="A122">
         <v>7</v>
       </c>
@@ -6715,7 +6729,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7">
       <c r="A123">
         <v>7</v>
       </c>
@@ -6738,7 +6752,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7">
       <c r="A124">
         <v>7</v>
       </c>
@@ -6761,7 +6775,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7">
       <c r="A125">
         <v>7</v>
       </c>
@@ -6784,7 +6798,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7">
       <c r="A126">
         <v>7</v>
       </c>
@@ -6807,7 +6821,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7">
       <c r="A127">
         <v>7</v>
       </c>
@@ -6830,7 +6844,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7">
       <c r="A128">
         <v>7</v>
       </c>
@@ -6853,7 +6867,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7">
       <c r="A129">
         <v>7</v>
       </c>
@@ -6876,7 +6890,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7">
       <c r="A130">
         <v>7</v>
       </c>
@@ -6899,7 +6913,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7">
       <c r="A131">
         <v>7</v>
       </c>
@@ -6922,7 +6936,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7">
       <c r="A132">
         <v>7</v>
       </c>
@@ -6945,7 +6959,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7">
       <c r="A133">
         <v>7</v>
       </c>
@@ -6968,7 +6982,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7">
       <c r="A134">
         <v>7</v>
       </c>
@@ -6991,7 +7005,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7">
       <c r="A135">
         <v>7</v>
       </c>
@@ -7005,7 +7019,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7">
       <c r="A136">
         <v>7</v>
       </c>
@@ -7019,7 +7033,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7">
       <c r="A137" s="4">
         <v>7</v>
       </c>
@@ -7027,13 +7041,13 @@
         <v>16</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7">
       <c r="A138" s="4">
         <v>7</v>
       </c>
@@ -7041,13 +7055,13 @@
         <v>17</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7">
       <c r="A139" s="4">
         <v>7</v>
       </c>
@@ -7055,13 +7069,13 @@
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7">
       <c r="A140" s="4">
         <v>7</v>
       </c>
@@ -7069,13 +7083,13 @@
         <v>19</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7">
       <c r="A141" s="4">
         <v>7</v>
       </c>
@@ -7083,13 +7097,13 @@
         <v>20</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7">
       <c r="A142">
         <v>8</v>
       </c>
@@ -7112,7 +7126,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7">
       <c r="A143">
         <v>8</v>
       </c>
@@ -7135,7 +7149,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7">
       <c r="A144">
         <v>8</v>
       </c>
@@ -7143,7 +7157,7 @@
         <v>3</v>
       </c>
       <c r="C144" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D144" t="s">
         <v>554</v>
@@ -7158,7 +7172,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7">
       <c r="A145">
         <v>8</v>
       </c>
@@ -7166,7 +7180,7 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D145" t="s">
         <v>554</v>
@@ -7181,7 +7195,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7">
       <c r="A146" s="2">
         <v>8</v>
       </c>
@@ -7195,7 +7209,7 @@
         <v>554</v>
       </c>
       <c r="E146" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F146" t="s">
         <v>305</v>
@@ -7204,7 +7218,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7">
       <c r="A147">
         <v>8</v>
       </c>
@@ -7212,13 +7226,13 @@
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D147" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7">
       <c r="A148">
         <v>8</v>
       </c>
@@ -7226,13 +7240,13 @@
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D148" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7">
       <c r="A149">
         <v>8</v>
       </c>
@@ -7240,16 +7254,13 @@
         <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D149" t="s">
         <v>554</v>
       </c>
-      <c r="E149" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="150" spans="1:7">
       <c r="A150">
         <v>8</v>
       </c>
@@ -7257,16 +7268,16 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>649</v>
+        <v>743</v>
       </c>
       <c r="D150" t="s">
         <v>554</v>
       </c>
       <c r="E150" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
       <c r="A151">
         <v>8</v>
       </c>
@@ -7274,16 +7285,16 @@
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>650</v>
+        <v>744</v>
       </c>
       <c r="D151" t="s">
         <v>554</v>
       </c>
       <c r="E151" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
       <c r="A152">
         <v>8</v>
       </c>
@@ -7291,13 +7302,16 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D152" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E152" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
       <c r="A153">
         <v>8</v>
       </c>
@@ -7305,13 +7319,16 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D153" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E153" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
       <c r="A154">
         <v>8</v>
       </c>
@@ -7319,13 +7336,13 @@
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D154" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7">
       <c r="A155">
         <v>8</v>
       </c>
@@ -7333,13 +7350,13 @@
         <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D155" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7">
       <c r="A156">
         <v>8</v>
       </c>
@@ -7353,7 +7370,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7">
       <c r="A157" s="4">
         <v>8</v>
       </c>
@@ -7361,13 +7378,13 @@
         <v>16</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7">
       <c r="A158" s="4">
         <v>8</v>
       </c>
@@ -7375,13 +7392,13 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7">
       <c r="A159" s="4">
         <v>8</v>
       </c>
@@ -7389,13 +7406,13 @@
         <v>18</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7">
       <c r="A160" s="4">
         <v>8</v>
       </c>
@@ -7403,13 +7420,13 @@
         <v>19</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7">
       <c r="A161" s="4">
         <v>8</v>
       </c>
@@ -7417,13 +7434,13 @@
         <v>20</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7">
       <c r="A162">
         <v>9</v>
       </c>
@@ -7446,7 +7463,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7">
       <c r="A163">
         <v>9</v>
       </c>
@@ -7469,7 +7486,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7">
       <c r="A164">
         <v>9</v>
       </c>
@@ -7489,7 +7506,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7">
       <c r="A165">
         <v>9</v>
       </c>
@@ -7509,7 +7526,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7">
       <c r="A166">
         <v>9</v>
       </c>
@@ -7532,7 +7549,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7">
       <c r="A167">
         <v>9</v>
       </c>
@@ -7546,7 +7563,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7">
       <c r="A168">
         <v>9</v>
       </c>
@@ -7560,7 +7577,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7">
       <c r="A169">
         <v>9</v>
       </c>
@@ -7574,7 +7591,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7">
       <c r="A170">
         <v>9</v>
       </c>
@@ -7588,7 +7605,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7">
       <c r="A171">
         <v>9</v>
       </c>
@@ -7602,7 +7619,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7">
       <c r="A172">
         <v>9</v>
       </c>
@@ -7616,7 +7633,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7">
       <c r="A173">
         <v>9</v>
       </c>
@@ -7630,7 +7647,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7">
       <c r="A174">
         <v>9</v>
       </c>
@@ -7644,7 +7661,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7">
       <c r="A175">
         <v>9</v>
       </c>
@@ -7658,7 +7675,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7">
       <c r="A176">
         <v>9</v>
       </c>
@@ -7672,7 +7689,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7">
       <c r="A177" s="4">
         <v>9</v>
       </c>
@@ -7680,13 +7697,13 @@
         <v>16</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7">
       <c r="A178" s="4">
         <v>9</v>
       </c>
@@ -7694,13 +7711,13 @@
         <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7">
       <c r="A179" s="4">
         <v>9</v>
       </c>
@@ -7708,13 +7725,13 @@
         <v>18</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7">
       <c r="A180" s="4">
         <v>9</v>
       </c>
@@ -7722,13 +7739,13 @@
         <v>19</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7">
       <c r="A181" s="4">
         <v>9</v>
       </c>
@@ -7736,13 +7753,13 @@
         <v>20</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7">
       <c r="A182">
         <v>10</v>
       </c>
@@ -7765,7 +7782,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7">
       <c r="A183">
         <v>10</v>
       </c>
@@ -7788,7 +7805,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7">
       <c r="A184">
         <v>10</v>
       </c>
@@ -7811,7 +7828,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7">
       <c r="A185">
         <v>10</v>
       </c>
@@ -7834,7 +7851,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7">
       <c r="A186">
         <v>10</v>
       </c>
@@ -7857,7 +7874,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7">
       <c r="A187">
         <v>10</v>
       </c>
@@ -7880,7 +7897,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7">
       <c r="A188">
         <v>10</v>
       </c>
@@ -7903,7 +7920,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7">
       <c r="A189">
         <v>10</v>
       </c>
@@ -7926,7 +7943,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7">
       <c r="A190">
         <v>10</v>
       </c>
@@ -7949,7 +7966,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7">
       <c r="A191">
         <v>10</v>
       </c>
@@ -7972,7 +7989,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7">
       <c r="A192">
         <v>10</v>
       </c>
@@ -7995,7 +8012,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7">
       <c r="A193">
         <v>10</v>
       </c>
@@ -8018,7 +8035,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7">
       <c r="A194">
         <v>10</v>
       </c>
@@ -8041,7 +8058,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7">
       <c r="A195">
         <v>10</v>
       </c>
@@ -8064,7 +8081,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7">
       <c r="A196">
         <v>10</v>
       </c>
@@ -8078,7 +8095,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7">
       <c r="A197" s="4">
         <v>10</v>
       </c>
@@ -8086,13 +8103,13 @@
         <v>16</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7">
       <c r="A198" s="4">
         <v>10</v>
       </c>
@@ -8100,13 +8117,13 @@
         <v>17</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7">
       <c r="A199" s="4">
         <v>10</v>
       </c>
@@ -8114,13 +8131,13 @@
         <v>18</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7">
       <c r="A200" s="4">
         <v>10</v>
       </c>
@@ -8128,13 +8145,13 @@
         <v>19</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7">
       <c r="A201" s="4">
         <v>10</v>
       </c>
@@ -8142,13 +8159,13 @@
         <v>20</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7">
       <c r="A202">
         <v>11</v>
       </c>
@@ -8156,19 +8173,19 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D202" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E202" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F202" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7">
       <c r="A203">
         <v>11</v>
       </c>
@@ -8176,19 +8193,19 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D203" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E203" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F203" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7">
       <c r="A204">
         <v>11</v>
       </c>
@@ -8196,19 +8213,19 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D204" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E204" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F204" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7">
       <c r="A205">
         <v>11</v>
       </c>
@@ -8216,19 +8233,19 @@
         <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D205" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E205" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F205" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7">
       <c r="A206">
         <v>11</v>
       </c>
@@ -8236,19 +8253,19 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D206" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E206" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F206" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7">
       <c r="A207">
         <v>11</v>
       </c>
@@ -8256,19 +8273,19 @@
         <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D207" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E207" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F207" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7">
       <c r="A208">
         <v>11</v>
       </c>
@@ -8276,19 +8293,19 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D208" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E208" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F208" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:6">
       <c r="A209">
         <v>11</v>
       </c>
@@ -8296,19 +8313,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D209" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E209" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F209" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:6">
       <c r="A210">
         <v>11</v>
       </c>
@@ -8316,19 +8333,19 @@
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D210" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E210" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F210" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:6">
       <c r="A211">
         <v>11</v>
       </c>
@@ -8336,19 +8353,19 @@
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D211" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E211" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F211" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:6">
       <c r="A212">
         <v>11</v>
       </c>
@@ -8356,19 +8373,19 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D212" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E212" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="F212" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:6">
       <c r="A213">
         <v>11</v>
       </c>
@@ -8376,19 +8393,19 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D213" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E213" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F213" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:6">
       <c r="A214">
         <v>11</v>
       </c>
@@ -8396,13 +8413,13 @@
         <v>13</v>
       </c>
       <c r="C214" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D214" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
       <c r="A215">
         <v>11</v>
       </c>
@@ -8410,13 +8427,13 @@
         <v>14</v>
       </c>
       <c r="C215" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D215" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
       <c r="A216">
         <v>11</v>
       </c>
@@ -8424,13 +8441,13 @@
         <v>15</v>
       </c>
       <c r="C216" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D216" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
       <c r="A217" s="4">
         <v>11</v>
       </c>
@@ -8438,13 +8455,13 @@
         <v>16</v>
       </c>
       <c r="C217" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
       <c r="A218" s="4">
         <v>11</v>
       </c>
@@ -8452,13 +8469,13 @@
         <v>17</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
       <c r="A219" s="4">
         <v>11</v>
       </c>
@@ -8466,13 +8483,13 @@
         <v>18</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
       <c r="A220" s="4">
         <v>11</v>
       </c>
@@ -8480,13 +8497,13 @@
         <v>19</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
       <c r="A221" s="4">
         <v>11</v>
       </c>
@@ -8494,10 +8511,10 @@
         <v>20</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
@@ -8508,15 +8525,19 @@
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C146B8-AED1-D84E-BB27-CA28C1D97E3C}">
   <dimension ref="A1:E58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
         <v>256</v>
@@ -8531,14 +8552,14 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -8549,13 +8570,13 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -8566,13 +8587,13 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -8583,13 +8604,13 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -8600,13 +8621,13 @@
         <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -8617,13 +8638,13 @@
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -8634,13 +8655,13 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -8651,13 +8672,13 @@
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -8668,13 +8689,13 @@
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -8685,13 +8706,13 @@
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -8702,13 +8723,13 @@
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -8719,13 +8740,13 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -8736,13 +8757,13 @@
         <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -8753,13 +8774,13 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -8770,13 +8791,13 @@
         <v>19</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -8787,13 +8808,13 @@
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -8804,13 +8825,13 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -8821,13 +8842,13 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -8838,13 +8859,13 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -8855,13 +8876,13 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -8872,13 +8893,13 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -8889,13 +8910,13 @@
         <v>16</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -8906,13 +8927,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -8923,13 +8944,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -8940,13 +8961,13 @@
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -8957,13 +8978,13 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -8974,13 +8995,13 @@
         <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -8991,13 +9012,13 @@
         <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -9008,13 +9029,13 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -9025,13 +9046,13 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5">
       <c r="A32" s="3">
         <v>30</v>
       </c>
@@ -9042,13 +9063,13 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5">
       <c r="A33" s="3">
         <v>31</v>
       </c>
@@ -9059,13 +9080,13 @@
         <v>16</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5">
       <c r="A34" s="3">
         <v>32</v>
       </c>
@@ -9076,13 +9097,13 @@
         <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5">
       <c r="A35" s="3">
         <v>33</v>
       </c>
@@ -9093,13 +9114,13 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5">
       <c r="A36" s="3">
         <v>34</v>
       </c>
@@ -9110,13 +9131,13 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5">
       <c r="A37" s="3">
         <v>35</v>
       </c>
@@ -9127,13 +9148,13 @@
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5">
       <c r="A38" s="3">
         <v>36</v>
       </c>
@@ -9144,13 +9165,13 @@
         <v>16</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5">
       <c r="A39" s="3">
         <v>37</v>
       </c>
@@ -9161,13 +9182,13 @@
         <v>17</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5">
       <c r="A40" s="3">
         <v>38</v>
       </c>
@@ -9178,13 +9199,13 @@
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5">
       <c r="A41" s="3">
         <v>39</v>
       </c>
@@ -9195,13 +9216,13 @@
         <v>19</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5">
       <c r="A42" s="3">
         <v>40</v>
       </c>
@@ -9212,13 +9233,13 @@
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5">
       <c r="A43" s="3">
         <v>41</v>
       </c>
@@ -9229,13 +9250,13 @@
         <v>16</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5">
       <c r="A44" s="3">
         <v>42</v>
       </c>
@@ -9246,13 +9267,13 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5">
       <c r="A45" s="3">
         <v>43</v>
       </c>
@@ -9263,13 +9284,13 @@
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5">
       <c r="A46" s="3">
         <v>44</v>
       </c>
@@ -9280,13 +9301,13 @@
         <v>19</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5">
       <c r="A47" s="3">
         <v>45</v>
       </c>
@@ -9297,13 +9318,13 @@
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5">
       <c r="A48" s="3">
         <v>46</v>
       </c>
@@ -9314,13 +9335,13 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5">
       <c r="A49" s="3">
         <v>47</v>
       </c>
@@ -9331,13 +9352,13 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5">
       <c r="A50" s="3">
         <v>48</v>
       </c>
@@ -9348,13 +9369,13 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5">
       <c r="A51" s="3">
         <v>49</v>
       </c>
@@ -9365,13 +9386,13 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5">
       <c r="A52" s="3">
         <v>50</v>
       </c>
@@ -9382,13 +9403,13 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5">
       <c r="A53" s="3">
         <v>51</v>
       </c>
@@ -9399,13 +9420,13 @@
         <v>16</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" s="3">
         <v>52</v>
       </c>
@@ -9416,13 +9437,13 @@
         <v>17</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" s="3">
         <v>53</v>
       </c>
@@ -9433,13 +9454,13 @@
         <v>18</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" s="3">
         <v>54</v>
       </c>
@@ -9450,13 +9471,13 @@
         <v>19</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" s="3">
         <v>55</v>
       </c>
@@ -9467,18 +9488,22 @@
         <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391A5BF4-4965-477B-B28F-85BC38AF9E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1508449C-9AC6-4417-AD96-1EAC476E3481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="749">
   <si>
     <t>pFS2</t>
   </si>
@@ -2272,6 +2272,12 @@
   </si>
   <si>
     <t>10-year average fPhys</t>
+  </si>
+  <si>
+    <t>Hd</t>
+  </si>
+  <si>
+    <t>Height (m) at which diameter was measured for background mortality and allometric equations</t>
   </si>
 </sst>
 </file>
@@ -2672,7 +2678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E287297-02C0-BF44-BF0C-8FADE2A87F8F}">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3616,25 +3622,25 @@
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" t="s">
-        <v>202</v>
-      </c>
-      <c r="C69" t="s">
-        <v>128</v>
-      </c>
-      <c r="D69">
-        <v>0</v>
+      <c r="A69" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1.3</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B70" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C70" t="s">
         <v>128</v>
@@ -3645,10 +3651,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B71" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C71" t="s">
         <v>128</v>
@@ -3659,10 +3665,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B72" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C72" t="s">
         <v>128</v>
@@ -3673,10 +3679,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B73" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C73" t="s">
         <v>128</v>
@@ -3687,10 +3693,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C74" t="s">
         <v>128</v>
@@ -3701,10 +3707,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B75" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C75" t="s">
         <v>128</v>
@@ -3715,10 +3721,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B76" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C76" t="s">
         <v>128</v>
@@ -3729,10 +3735,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B77" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C77" t="s">
         <v>128</v>
@@ -3743,10 +3749,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B78" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C78" t="s">
         <v>128</v>
@@ -3757,10 +3763,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B79" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C79" t="s">
         <v>128</v>
@@ -3771,10 +3777,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B80" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C80" t="s">
         <v>128</v>
@@ -3785,10 +3791,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B81" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C81" t="s">
         <v>128</v>
@@ -3799,10 +3805,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B82" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C82" t="s">
         <v>128</v>
@@ -3813,10 +3819,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B83" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C83" t="s">
         <v>128</v>
@@ -3827,10 +3833,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B84" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C84" t="s">
         <v>128</v>
@@ -3841,10 +3847,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C85" t="s">
         <v>128</v>
@@ -3855,57 +3861,71 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="B86" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C86" t="s">
-        <v>220</v>
+        <v>128</v>
       </c>
       <c r="D86">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B87" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C87" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="D87">
-        <v>0.8</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B88" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C88" t="s">
-        <v>223</v>
+        <v>128</v>
       </c>
       <c r="D88">
-        <v>24</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
+        <v>111</v>
+      </c>
+      <c r="B89" t="s">
+        <v>222</v>
+      </c>
+      <c r="C89" t="s">
+        <v>223</v>
+      </c>
+      <c r="D89">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
         <v>112</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B90" t="s">
         <v>224</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C90" t="s">
         <v>225</v>
       </c>
-      <c r="D89">
+      <c r="D90">
         <v>2.2999999999999998</v>
       </c>
     </row>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1508449C-9AC6-4417-AD96-1EAC476E3481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D5C1D8-5565-4D0B-A00D-BC5432543F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="751">
   <si>
     <t>pFS2</t>
   </si>
@@ -2278,6 +2278,12 @@
   </si>
   <si>
     <t>Height (m) at which diameter was measured for background mortality and allometric equations</t>
+  </si>
+  <si>
+    <t>gammaAPAR</t>
+  </si>
+  <si>
+    <t>Determines light benefit to shorter cohorts</t>
   </si>
 </sst>
 </file>
@@ -2678,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E287297-02C0-BF44-BF0C-8FADE2A87F8F}">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -3314,277 +3320,275 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" t="s">
-        <v>175</v>
-      </c>
-      <c r="C47" t="s">
-        <v>156</v>
-      </c>
-      <c r="D47">
-        <v>3</v>
+      <c r="A47" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C48" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D48">
-        <v>0.15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C49" t="s">
         <v>128</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C50" t="s">
         <v>128</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C51" t="s">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="D51">
-        <v>0.06</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B52" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C52" t="s">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="D52">
-        <v>0.47</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C53" t="s">
-        <v>183</v>
+        <v>128</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C54" t="s">
         <v>183</v>
       </c>
       <c r="D54">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
+        <v>183</v>
       </c>
       <c r="D55">
-        <v>3.33</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C56" t="s">
-        <v>187</v>
+        <v>128</v>
       </c>
       <c r="D56">
-        <v>0.05</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B57" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C57" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D57">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C58" t="s">
-        <v>128</v>
+        <v>183</v>
       </c>
       <c r="D58">
-        <v>0.66</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C59" t="s">
-        <v>191</v>
+        <v>128</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B60" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C60" t="s">
         <v>191</v>
       </c>
       <c r="D60">
-        <v>4.4000000000000004</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B61" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C61" t="s">
         <v>191</v>
       </c>
       <c r="D61">
-        <v>27</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C62" t="s">
-        <v>128</v>
+        <v>191</v>
       </c>
       <c r="D62">
-        <v>0.75</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B63" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" t="s">
         <v>128</v>
       </c>
       <c r="D63">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B64" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C64" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B65" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C65" t="s">
-        <v>198</v>
+        <v>156</v>
       </c>
       <c r="D65">
-        <v>0.45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B66" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C66" t="s">
         <v>198</v>
@@ -3595,66 +3599,66 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B67" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C67" t="s">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="D67">
-        <v>4</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
+        <v>60</v>
+      </c>
+      <c r="B68" t="s">
+        <v>200</v>
+      </c>
+      <c r="C68" t="s">
+        <v>156</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
         <v>68</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B69" t="s">
         <v>201</v>
       </c>
-      <c r="C68" t="s">
-        <v>128</v>
-      </c>
-      <c r="D68">
+      <c r="C69" t="s">
+        <v>128</v>
+      </c>
+      <c r="D69">
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="1" t="s">
+    <row r="70" spans="1:4">
+      <c r="A70" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D70" s="1">
         <v>1.3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" t="s">
-        <v>61</v>
-      </c>
-      <c r="B70" t="s">
-        <v>202</v>
-      </c>
-      <c r="C70" t="s">
-        <v>128</v>
-      </c>
-      <c r="D70">
-        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B71" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C71" t="s">
         <v>128</v>
@@ -3665,10 +3669,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B72" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C72" t="s">
         <v>128</v>
@@ -3679,10 +3683,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B73" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C73" t="s">
         <v>128</v>
@@ -3693,10 +3697,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C74" t="s">
         <v>128</v>
@@ -3707,10 +3711,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B75" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C75" t="s">
         <v>128</v>
@@ -3721,10 +3725,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B76" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C76" t="s">
         <v>128</v>
@@ -3735,10 +3739,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B77" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C77" t="s">
         <v>128</v>
@@ -3749,10 +3753,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B78" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C78" t="s">
         <v>128</v>
@@ -3763,10 +3767,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C79" t="s">
         <v>128</v>
@@ -3777,10 +3781,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B80" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C80" t="s">
         <v>128</v>
@@ -3791,10 +3795,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B81" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C81" t="s">
         <v>128</v>
@@ -3805,10 +3809,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B82" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C82" t="s">
         <v>128</v>
@@ -3819,10 +3823,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B83" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C83" t="s">
         <v>128</v>
@@ -3833,10 +3837,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B84" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C84" t="s">
         <v>128</v>
@@ -3847,10 +3851,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B85" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C85" t="s">
         <v>128</v>
@@ -3861,10 +3865,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B86" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C86" t="s">
         <v>128</v>
@@ -3875,57 +3879,71 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="B87" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C87" t="s">
-        <v>220</v>
+        <v>128</v>
       </c>
       <c r="D87">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B88" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C88" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="D88">
-        <v>0.8</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B89" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C89" t="s">
-        <v>223</v>
+        <v>128</v>
       </c>
       <c r="D89">
-        <v>24</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
+        <v>111</v>
+      </c>
+      <c r="B90" t="s">
+        <v>222</v>
+      </c>
+      <c r="C90" t="s">
+        <v>223</v>
+      </c>
+      <c r="D90">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
         <v>112</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B91" t="s">
         <v>224</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C91" t="s">
         <v>225</v>
       </c>
-      <c r="D90">
+      <c r="D91">
         <v>2.2999999999999998</v>
       </c>
     </row>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D5C1D8-5565-4D0B-A00D-BC5432543F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB0120A-085C-483A-BAD9-E0792B62A0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:4">

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB0120A-085C-483A-BAD9-E0792B62A0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4E0500-B472-4C42-A9F9-4C08329D08B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="752">
   <si>
     <t>pFS2</t>
   </si>
@@ -1188,9 +1188,6 @@
     <t>VPDspecies</t>
   </si>
   <si>
-    <t>var_3_12</t>
-  </si>
-  <si>
     <t>var_3_13</t>
   </si>
   <si>
@@ -2284,6 +2281,12 @@
   </si>
   <si>
     <t>Determines light benefit to shorter cohorts</t>
+  </si>
+  <si>
+    <t>m_apar</t>
+  </si>
+  <si>
+    <t>Modifier to amplify light benefit to shorter cohorts</t>
   </si>
 </sst>
 </file>
@@ -3151,10 +3154,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -3163,10 +3166,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -3175,10 +3178,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -3187,10 +3190,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -3199,10 +3202,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -3211,10 +3214,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -3321,10 +3324,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>749</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>750</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -3641,10 +3644,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>748</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>320</v>
@@ -4751,7 +4754,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>261</v>
@@ -4765,7 +4768,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>261</v>
@@ -4779,7 +4782,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>261</v>
@@ -4793,7 +4796,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>261</v>
@@ -4807,7 +4810,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>261</v>
@@ -5148,7 +5151,7 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>300</v>
@@ -5162,7 +5165,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>300</v>
@@ -5176,7 +5179,7 @@
         <v>18</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>300</v>
@@ -5190,7 +5193,7 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>300</v>
@@ -5204,7 +5207,7 @@
         <v>20</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>300</v>
@@ -5467,11 +5470,14 @@
       <c r="B53">
         <v>12</v>
       </c>
-      <c r="C53" t="s">
-        <v>385</v>
+      <c r="C53" s="1" t="s">
+        <v>750</v>
       </c>
       <c r="D53" t="s">
         <v>348</v>
+      </c>
+      <c r="E53" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5482,7 +5488,7 @@
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D54" t="s">
         <v>348</v>
@@ -5496,7 +5502,7 @@
         <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D55" t="s">
         <v>348</v>
@@ -5510,7 +5516,7 @@
         <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D56" t="s">
         <v>348</v>
@@ -5524,7 +5530,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>348</v>
@@ -5538,7 +5544,7 @@
         <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>348</v>
@@ -5552,7 +5558,7 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>348</v>
@@ -5566,7 +5572,7 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>348</v>
@@ -5580,7 +5586,7 @@
         <v>20</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>348</v>
@@ -5597,16 +5603,16 @@
         <v>116</v>
       </c>
       <c r="D62" t="s">
+        <v>388</v>
+      </c>
+      <c r="E62" t="s">
         <v>389</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>390</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>391</v>
-      </c>
-      <c r="G62" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5620,16 +5626,16 @@
         <v>115</v>
       </c>
       <c r="D63" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E63" t="s">
+        <v>392</v>
+      </c>
+      <c r="F63" t="s">
+        <v>390</v>
+      </c>
+      <c r="G63" t="s">
         <v>393</v>
-      </c>
-      <c r="F63" t="s">
-        <v>391</v>
-      </c>
-      <c r="G63" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5643,16 +5649,16 @@
         <v>114</v>
       </c>
       <c r="D64" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E64" t="s">
+        <v>394</v>
+      </c>
+      <c r="F64" t="s">
+        <v>390</v>
+      </c>
+      <c r="G64" t="s">
         <v>395</v>
-      </c>
-      <c r="F64" t="s">
-        <v>391</v>
-      </c>
-      <c r="G64" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -5663,19 +5669,19 @@
         <v>4</v>
       </c>
       <c r="C65" t="s">
+        <v>396</v>
+      </c>
+      <c r="D65" t="s">
+        <v>388</v>
+      </c>
+      <c r="E65" t="s">
         <v>397</v>
       </c>
-      <c r="D65" t="s">
-        <v>389</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>398</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>399</v>
-      </c>
-      <c r="G65" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -5686,19 +5692,19 @@
         <v>5</v>
       </c>
       <c r="C66" t="s">
+        <v>400</v>
+      </c>
+      <c r="D66" t="s">
+        <v>388</v>
+      </c>
+      <c r="E66" t="s">
         <v>401</v>
       </c>
-      <c r="D66" t="s">
-        <v>389</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>402</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>403</v>
-      </c>
-      <c r="G66" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5709,16 +5715,16 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
+        <v>404</v>
+      </c>
+      <c r="D67" t="s">
+        <v>388</v>
+      </c>
+      <c r="E67" t="s">
         <v>405</v>
       </c>
-      <c r="D67" t="s">
-        <v>389</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="G67" t="s">
         <v>406</v>
-      </c>
-      <c r="G67" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -5729,19 +5735,19 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
+        <v>407</v>
+      </c>
+      <c r="D68" t="s">
+        <v>388</v>
+      </c>
+      <c r="E68" t="s">
         <v>408</v>
       </c>
-      <c r="D68" t="s">
-        <v>389</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
+        <v>390</v>
+      </c>
+      <c r="G68" t="s">
         <v>409</v>
-      </c>
-      <c r="F68" t="s">
-        <v>391</v>
-      </c>
-      <c r="G68" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5752,19 +5758,19 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
+        <v>410</v>
+      </c>
+      <c r="D69" t="s">
+        <v>388</v>
+      </c>
+      <c r="E69" t="s">
         <v>411</v>
       </c>
-      <c r="D69" t="s">
-        <v>389</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
+        <v>390</v>
+      </c>
+      <c r="G69" t="s">
         <v>412</v>
-      </c>
-      <c r="F69" t="s">
-        <v>391</v>
-      </c>
-      <c r="G69" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -5775,19 +5781,19 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
+        <v>413</v>
+      </c>
+      <c r="D70" t="s">
+        <v>388</v>
+      </c>
+      <c r="E70" t="s">
         <v>414</v>
       </c>
-      <c r="D70" t="s">
-        <v>389</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
+        <v>390</v>
+      </c>
+      <c r="G70" t="s">
         <v>415</v>
-      </c>
-      <c r="F70" t="s">
-        <v>391</v>
-      </c>
-      <c r="G70" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -5798,19 +5804,19 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
+        <v>416</v>
+      </c>
+      <c r="D71" t="s">
+        <v>388</v>
+      </c>
+      <c r="E71" t="s">
         <v>417</v>
       </c>
-      <c r="D71" t="s">
-        <v>389</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
+        <v>390</v>
+      </c>
+      <c r="G71" t="s">
         <v>418</v>
-      </c>
-      <c r="F71" t="s">
-        <v>391</v>
-      </c>
-      <c r="G71" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -5821,19 +5827,19 @@
         <v>11</v>
       </c>
       <c r="C72" t="s">
+        <v>419</v>
+      </c>
+      <c r="D72" t="s">
+        <v>388</v>
+      </c>
+      <c r="E72" t="s">
         <v>420</v>
       </c>
-      <c r="D72" t="s">
-        <v>389</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
+        <v>390</v>
+      </c>
+      <c r="G72" t="s">
         <v>421</v>
-      </c>
-      <c r="F72" t="s">
-        <v>391</v>
-      </c>
-      <c r="G72" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -5844,10 +5850,10 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D73" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5858,10 +5864,10 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D74" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -5872,10 +5878,10 @@
         <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D75" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -5886,10 +5892,10 @@
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D76" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -5900,10 +5906,10 @@
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -5914,10 +5920,10 @@
         <v>17</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5928,10 +5934,10 @@
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -5942,10 +5948,10 @@
         <v>19</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5956,10 +5962,10 @@
         <v>20</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -5970,19 +5976,19 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
+        <v>426</v>
+      </c>
+      <c r="D82" t="s">
         <v>427</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>428</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
+        <v>128</v>
+      </c>
+      <c r="G82" t="s">
         <v>429</v>
-      </c>
-      <c r="F82" t="s">
-        <v>128</v>
-      </c>
-      <c r="G82" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -5993,19 +5999,19 @@
         <v>2</v>
       </c>
       <c r="C83" t="s">
+        <v>430</v>
+      </c>
+      <c r="D83" t="s">
+        <v>427</v>
+      </c>
+      <c r="E83" t="s">
         <v>431</v>
       </c>
-      <c r="D83" t="s">
-        <v>428</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
+        <v>128</v>
+      </c>
+      <c r="G83" t="s">
         <v>432</v>
-      </c>
-      <c r="F83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G83" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -6016,19 +6022,19 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
+        <v>433</v>
+      </c>
+      <c r="D84" t="s">
+        <v>427</v>
+      </c>
+      <c r="E84" t="s">
         <v>434</v>
       </c>
-      <c r="D84" t="s">
-        <v>428</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
+        <v>128</v>
+      </c>
+      <c r="G84" t="s">
         <v>435</v>
-      </c>
-      <c r="F84" t="s">
-        <v>128</v>
-      </c>
-      <c r="G84" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -6039,19 +6045,19 @@
         <v>4</v>
       </c>
       <c r="C85" t="s">
+        <v>436</v>
+      </c>
+      <c r="D85" t="s">
+        <v>427</v>
+      </c>
+      <c r="E85" t="s">
         <v>437</v>
       </c>
-      <c r="D85" t="s">
-        <v>428</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
+        <v>128</v>
+      </c>
+      <c r="G85" t="s">
         <v>438</v>
-      </c>
-      <c r="F85" t="s">
-        <v>128</v>
-      </c>
-      <c r="G85" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -6062,19 +6068,19 @@
         <v>5</v>
       </c>
       <c r="C86" t="s">
+        <v>439</v>
+      </c>
+      <c r="D86" t="s">
+        <v>427</v>
+      </c>
+      <c r="E86" t="s">
         <v>440</v>
       </c>
-      <c r="D86" t="s">
-        <v>428</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
+        <v>128</v>
+      </c>
+      <c r="G86" t="s">
         <v>441</v>
-      </c>
-      <c r="F86" t="s">
-        <v>128</v>
-      </c>
-      <c r="G86" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -6085,19 +6091,19 @@
         <v>6</v>
       </c>
       <c r="C87" t="s">
+        <v>442</v>
+      </c>
+      <c r="D87" t="s">
+        <v>427</v>
+      </c>
+      <c r="E87" t="s">
         <v>443</v>
       </c>
-      <c r="D87" t="s">
-        <v>428</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
+        <v>128</v>
+      </c>
+      <c r="G87" t="s">
         <v>444</v>
-      </c>
-      <c r="F87" t="s">
-        <v>128</v>
-      </c>
-      <c r="G87" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -6108,19 +6114,19 @@
         <v>7</v>
       </c>
       <c r="C88" t="s">
+        <v>445</v>
+      </c>
+      <c r="D88" t="s">
+        <v>427</v>
+      </c>
+      <c r="E88" t="s">
         <v>446</v>
       </c>
-      <c r="D88" t="s">
-        <v>428</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
+        <v>128</v>
+      </c>
+      <c r="G88" t="s">
         <v>447</v>
-      </c>
-      <c r="F88" t="s">
-        <v>128</v>
-      </c>
-      <c r="G88" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -6131,19 +6137,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
+        <v>448</v>
+      </c>
+      <c r="D89" t="s">
+        <v>427</v>
+      </c>
+      <c r="E89" t="s">
         <v>449</v>
       </c>
-      <c r="D89" t="s">
-        <v>428</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
+        <v>128</v>
+      </c>
+      <c r="G89" t="s">
         <v>450</v>
-      </c>
-      <c r="F89" t="s">
-        <v>128</v>
-      </c>
-      <c r="G89" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -6154,19 +6160,19 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
+        <v>451</v>
+      </c>
+      <c r="D90" t="s">
+        <v>427</v>
+      </c>
+      <c r="E90" t="s">
         <v>452</v>
       </c>
-      <c r="D90" t="s">
-        <v>428</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
+        <v>128</v>
+      </c>
+      <c r="G90" t="s">
         <v>453</v>
-      </c>
-      <c r="F90" t="s">
-        <v>128</v>
-      </c>
-      <c r="G90" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6177,19 +6183,19 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
+        <v>454</v>
+      </c>
+      <c r="D91" t="s">
+        <v>427</v>
+      </c>
+      <c r="E91" t="s">
         <v>455</v>
       </c>
-      <c r="D91" t="s">
-        <v>428</v>
-      </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
+        <v>128</v>
+      </c>
+      <c r="G91" t="s">
         <v>456</v>
-      </c>
-      <c r="F91" t="s">
-        <v>128</v>
-      </c>
-      <c r="G91" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6200,19 +6206,19 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
+        <v>457</v>
+      </c>
+      <c r="D92" t="s">
+        <v>427</v>
+      </c>
+      <c r="E92" t="s">
         <v>458</v>
       </c>
-      <c r="D92" t="s">
-        <v>428</v>
-      </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
+        <v>128</v>
+      </c>
+      <c r="G92" t="s">
         <v>459</v>
-      </c>
-      <c r="F92" t="s">
-        <v>128</v>
-      </c>
-      <c r="G92" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6223,16 +6229,16 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
+        <v>460</v>
+      </c>
+      <c r="D93" t="s">
+        <v>427</v>
+      </c>
+      <c r="E93" t="s">
         <v>461</v>
       </c>
-      <c r="D93" t="s">
-        <v>428</v>
-      </c>
-      <c r="E93" t="s">
+      <c r="G93" t="s">
         <v>462</v>
-      </c>
-      <c r="G93" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6243,10 +6249,10 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D94" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6257,10 +6263,10 @@
         <v>14</v>
       </c>
       <c r="C95" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D95" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6271,10 +6277,10 @@
         <v>15</v>
       </c>
       <c r="C96" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D96" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6285,10 +6291,10 @@
         <v>16</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6299,10 +6305,10 @@
         <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -6313,10 +6319,10 @@
         <v>18</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -6327,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -6341,10 +6347,10 @@
         <v>20</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -6355,19 +6361,19 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
+        <v>466</v>
+      </c>
+      <c r="D102" t="s">
         <v>467</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>468</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
+        <v>390</v>
+      </c>
+      <c r="G102" t="s">
         <v>469</v>
-      </c>
-      <c r="F102" t="s">
-        <v>391</v>
-      </c>
-      <c r="G102" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -6378,19 +6384,19 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
+        <v>470</v>
+      </c>
+      <c r="D103" t="s">
+        <v>467</v>
+      </c>
+      <c r="E103" t="s">
         <v>471</v>
       </c>
-      <c r="D103" t="s">
-        <v>468</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
+        <v>390</v>
+      </c>
+      <c r="G103" t="s">
         <v>472</v>
-      </c>
-      <c r="F103" t="s">
-        <v>391</v>
-      </c>
-      <c r="G103" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -6401,19 +6407,19 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D104" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E104" t="s">
+        <v>473</v>
+      </c>
+      <c r="F104" t="s">
         <v>474</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>475</v>
-      </c>
-      <c r="G104" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6424,19 +6430,19 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
+        <v>476</v>
+      </c>
+      <c r="D105" t="s">
+        <v>467</v>
+      </c>
+      <c r="E105" t="s">
         <v>477</v>
       </c>
-      <c r="D105" t="s">
-        <v>468</v>
-      </c>
-      <c r="E105" t="s">
-        <v>478</v>
-      </c>
       <c r="F105" t="s">
         <v>128</v>
       </c>
       <c r="G105" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6447,19 +6453,19 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
+        <v>478</v>
+      </c>
+      <c r="D106" t="s">
+        <v>467</v>
+      </c>
+      <c r="E106" t="s">
         <v>479</v>
       </c>
-      <c r="D106" t="s">
-        <v>468</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>480</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>481</v>
-      </c>
-      <c r="G106" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6470,19 +6476,19 @@
         <v>6</v>
       </c>
       <c r="C107" t="s">
+        <v>482</v>
+      </c>
+      <c r="D107" t="s">
+        <v>467</v>
+      </c>
+      <c r="E107" t="s">
         <v>483</v>
       </c>
-      <c r="D107" t="s">
-        <v>468</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>484</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>485</v>
-      </c>
-      <c r="G107" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6493,19 +6499,19 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
+        <v>486</v>
+      </c>
+      <c r="D108" t="s">
+        <v>467</v>
+      </c>
+      <c r="E108" t="s">
         <v>487</v>
       </c>
-      <c r="D108" t="s">
-        <v>468</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
+        <v>484</v>
+      </c>
+      <c r="G108" t="s">
         <v>488</v>
-      </c>
-      <c r="F108" t="s">
-        <v>485</v>
-      </c>
-      <c r="G108" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6516,19 +6522,19 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
+        <v>489</v>
+      </c>
+      <c r="D109" t="s">
+        <v>467</v>
+      </c>
+      <c r="E109" t="s">
         <v>490</v>
       </c>
-      <c r="D109" t="s">
-        <v>468</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
+        <v>484</v>
+      </c>
+      <c r="G109" t="s">
         <v>491</v>
-      </c>
-      <c r="F109" t="s">
-        <v>485</v>
-      </c>
-      <c r="G109" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6539,19 +6545,19 @@
         <v>9</v>
       </c>
       <c r="C110" t="s">
+        <v>492</v>
+      </c>
+      <c r="D110" t="s">
+        <v>467</v>
+      </c>
+      <c r="E110" t="s">
         <v>493</v>
       </c>
-      <c r="D110" t="s">
-        <v>468</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
+        <v>128</v>
+      </c>
+      <c r="G110" t="s">
         <v>494</v>
-      </c>
-      <c r="F110" t="s">
-        <v>128</v>
-      </c>
-      <c r="G110" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1">
@@ -6562,19 +6568,19 @@
         <v>10</v>
       </c>
       <c r="C111" t="s">
+        <v>495</v>
+      </c>
+      <c r="D111" t="s">
+        <v>467</v>
+      </c>
+      <c r="E111" t="s">
         <v>496</v>
       </c>
-      <c r="D111" t="s">
-        <v>468</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
+        <v>128</v>
+      </c>
+      <c r="G111" t="s">
         <v>497</v>
-      </c>
-      <c r="F111" t="s">
-        <v>128</v>
-      </c>
-      <c r="G111" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6585,19 +6591,19 @@
         <v>11</v>
       </c>
       <c r="C112" t="s">
+        <v>498</v>
+      </c>
+      <c r="D112" t="s">
+        <v>467</v>
+      </c>
+      <c r="E112" t="s">
         <v>499</v>
       </c>
-      <c r="D112" t="s">
-        <v>468</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
+        <v>128</v>
+      </c>
+      <c r="G112" t="s">
         <v>500</v>
-      </c>
-      <c r="F112" t="s">
-        <v>128</v>
-      </c>
-      <c r="G112" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6608,19 +6614,19 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
+        <v>501</v>
+      </c>
+      <c r="D113" t="s">
+        <v>467</v>
+      </c>
+      <c r="E113" t="s">
         <v>502</v>
       </c>
-      <c r="D113" t="s">
-        <v>468</v>
-      </c>
-      <c r="E113" t="s">
-        <v>503</v>
-      </c>
       <c r="F113" t="s">
         <v>128</v>
       </c>
       <c r="G113" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6631,19 +6637,19 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
+        <v>503</v>
+      </c>
+      <c r="D114" t="s">
+        <v>467</v>
+      </c>
+      <c r="E114" t="s">
         <v>504</v>
       </c>
-      <c r="D114" t="s">
-        <v>468</v>
-      </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
+        <v>390</v>
+      </c>
+      <c r="G114" t="s">
         <v>505</v>
-      </c>
-      <c r="F114" t="s">
-        <v>391</v>
-      </c>
-      <c r="G114" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -6654,10 +6660,10 @@
         <v>14</v>
       </c>
       <c r="C115" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D115" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6668,10 +6674,10 @@
         <v>15</v>
       </c>
       <c r="C116" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D116" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -6682,10 +6688,10 @@
         <v>16</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -6696,10 +6702,10 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -6710,10 +6716,10 @@
         <v>18</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -6724,10 +6730,10 @@
         <v>19</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6738,10 +6744,10 @@
         <v>20</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6752,19 +6758,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
+        <v>508</v>
+      </c>
+      <c r="D122" t="s">
         <v>509</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>510</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>511</v>
       </c>
-      <c r="F122" t="s">
-        <v>512</v>
-      </c>
       <c r="G122" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6775,19 +6781,19 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
+        <v>512</v>
+      </c>
+      <c r="D123" t="s">
+        <v>509</v>
+      </c>
+      <c r="E123" t="s">
         <v>513</v>
       </c>
-      <c r="D123" t="s">
-        <v>510</v>
-      </c>
-      <c r="E123" t="s">
-        <v>514</v>
-      </c>
       <c r="F123" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G123" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6798,19 +6804,19 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
+        <v>514</v>
+      </c>
+      <c r="D124" t="s">
+        <v>509</v>
+      </c>
+      <c r="E124" t="s">
         <v>515</v>
       </c>
-      <c r="D124" t="s">
-        <v>510</v>
-      </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>516</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>517</v>
-      </c>
-      <c r="G124" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -6821,19 +6827,19 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
+        <v>518</v>
+      </c>
+      <c r="D125" t="s">
+        <v>509</v>
+      </c>
+      <c r="E125" t="s">
         <v>519</v>
       </c>
-      <c r="D125" t="s">
-        <v>510</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>520</v>
       </c>
-      <c r="F125" t="s">
+      <c r="G125" t="s">
         <v>521</v>
-      </c>
-      <c r="G125" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6844,19 +6850,19 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
+        <v>522</v>
+      </c>
+      <c r="D126" t="s">
+        <v>509</v>
+      </c>
+      <c r="E126" t="s">
         <v>523</v>
       </c>
-      <c r="D126" t="s">
-        <v>510</v>
-      </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
+        <v>128</v>
+      </c>
+      <c r="G126" t="s">
         <v>524</v>
-      </c>
-      <c r="F126" t="s">
-        <v>128</v>
-      </c>
-      <c r="G126" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -6867,19 +6873,19 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
+        <v>525</v>
+      </c>
+      <c r="D127" t="s">
+        <v>509</v>
+      </c>
+      <c r="E127" t="s">
         <v>526</v>
       </c>
-      <c r="D127" t="s">
-        <v>510</v>
-      </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
+        <v>520</v>
+      </c>
+      <c r="G127" t="s">
         <v>527</v>
-      </c>
-      <c r="F127" t="s">
-        <v>521</v>
-      </c>
-      <c r="G127" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -6890,19 +6896,19 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
+        <v>528</v>
+      </c>
+      <c r="D128" t="s">
+        <v>509</v>
+      </c>
+      <c r="E128" t="s">
         <v>529</v>
       </c>
-      <c r="D128" t="s">
-        <v>510</v>
-      </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
+        <v>520</v>
+      </c>
+      <c r="G128" t="s">
         <v>530</v>
-      </c>
-      <c r="F128" t="s">
-        <v>521</v>
-      </c>
-      <c r="G128" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -6913,19 +6919,19 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>531</v>
+      </c>
+      <c r="D129" t="s">
+        <v>509</v>
+      </c>
+      <c r="E129" t="s">
         <v>532</v>
       </c>
-      <c r="D129" t="s">
-        <v>510</v>
-      </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>533</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
         <v>534</v>
-      </c>
-      <c r="G129" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6936,19 +6942,19 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
+        <v>535</v>
+      </c>
+      <c r="D130" t="s">
+        <v>509</v>
+      </c>
+      <c r="E130" t="s">
         <v>536</v>
       </c>
-      <c r="D130" t="s">
-        <v>510</v>
-      </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
+        <v>533</v>
+      </c>
+      <c r="G130" t="s">
         <v>537</v>
-      </c>
-      <c r="F130" t="s">
-        <v>534</v>
-      </c>
-      <c r="G130" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6959,19 +6965,19 @@
         <v>10</v>
       </c>
       <c r="C131" t="s">
+        <v>538</v>
+      </c>
+      <c r="D131" t="s">
+        <v>509</v>
+      </c>
+      <c r="E131" t="s">
         <v>539</v>
       </c>
-      <c r="D131" t="s">
-        <v>510</v>
-      </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
+        <v>516</v>
+      </c>
+      <c r="G131" t="s">
         <v>540</v>
-      </c>
-      <c r="F131" t="s">
-        <v>517</v>
-      </c>
-      <c r="G131" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -6982,19 +6988,19 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
+        <v>541</v>
+      </c>
+      <c r="D132" t="s">
+        <v>509</v>
+      </c>
+      <c r="E132" t="s">
         <v>542</v>
       </c>
-      <c r="D132" t="s">
-        <v>510</v>
-      </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
+        <v>516</v>
+      </c>
+      <c r="G132" t="s">
         <v>543</v>
-      </c>
-      <c r="F132" t="s">
-        <v>517</v>
-      </c>
-      <c r="G132" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -7005,19 +7011,19 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
+        <v>544</v>
+      </c>
+      <c r="D133" t="s">
+        <v>509</v>
+      </c>
+      <c r="E133" t="s">
         <v>545</v>
       </c>
-      <c r="D133" t="s">
-        <v>510</v>
-      </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
+        <v>520</v>
+      </c>
+      <c r="G133" t="s">
         <v>546</v>
-      </c>
-      <c r="F133" t="s">
-        <v>521</v>
-      </c>
-      <c r="G133" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -7028,19 +7034,19 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
+        <v>547</v>
+      </c>
+      <c r="D134" t="s">
+        <v>509</v>
+      </c>
+      <c r="E134" t="s">
         <v>548</v>
       </c>
-      <c r="D134" t="s">
-        <v>510</v>
-      </c>
-      <c r="E134" t="s">
+      <c r="F134" t="s">
+        <v>520</v>
+      </c>
+      <c r="G134" t="s">
         <v>549</v>
-      </c>
-      <c r="F134" t="s">
-        <v>521</v>
-      </c>
-      <c r="G134" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -7051,10 +7057,10 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D135" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -7065,10 +7071,10 @@
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D136" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7079,10 +7085,10 @@
         <v>16</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7093,10 +7099,10 @@
         <v>17</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -7107,10 +7113,10 @@
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -7121,10 +7127,10 @@
         <v>19</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -7135,10 +7141,10 @@
         <v>20</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -7149,19 +7155,19 @@
         <v>1</v>
       </c>
       <c r="C142" t="s">
+        <v>552</v>
+      </c>
+      <c r="D142" t="s">
         <v>553</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>554</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>555</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>556</v>
-      </c>
-      <c r="G142" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7172,19 +7178,19 @@
         <v>2</v>
       </c>
       <c r="C143" t="s">
+        <v>557</v>
+      </c>
+      <c r="D143" t="s">
+        <v>553</v>
+      </c>
+      <c r="E143" t="s">
         <v>558</v>
       </c>
-      <c r="D143" t="s">
-        <v>554</v>
-      </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>559</v>
       </c>
-      <c r="F143" t="s">
-        <v>560</v>
-      </c>
       <c r="G143" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7195,19 +7201,19 @@
         <v>3</v>
       </c>
       <c r="C144" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D144" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E144" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F144" t="s">
         <v>305</v>
       </c>
       <c r="G144" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -7218,19 +7224,19 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D145" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E145" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="F145" t="s">
         <v>305</v>
       </c>
       <c r="G145" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -7241,19 +7247,19 @@
         <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D146" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E146" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F146" t="s">
         <v>305</v>
       </c>
       <c r="G146" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -7264,10 +7270,10 @@
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D147" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -7278,10 +7284,10 @@
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D148" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -7292,10 +7298,10 @@
         <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D149" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -7306,13 +7312,13 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D150" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E150" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -7323,13 +7329,13 @@
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D151" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E151" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -7340,10 +7346,10 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D152" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E152" t="s">
         <v>316</v>
@@ -7357,13 +7363,13 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D153" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E153" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -7374,10 +7380,10 @@
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D154" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -7388,10 +7394,10 @@
         <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D155" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -7402,10 +7408,10 @@
         <v>15</v>
       </c>
       <c r="C156" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D156" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -7416,10 +7422,10 @@
         <v>16</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -7430,10 +7436,10 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -7444,10 +7450,10 @@
         <v>18</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -7458,10 +7464,10 @@
         <v>19</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -7472,10 +7478,10 @@
         <v>20</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7486,19 +7492,19 @@
         <v>1</v>
       </c>
       <c r="C162" t="s">
+        <v>565</v>
+      </c>
+      <c r="D162" t="s">
         <v>566</v>
       </c>
-      <c r="D162" t="s">
+      <c r="E162" t="s">
         <v>567</v>
       </c>
-      <c r="E162" t="s">
+      <c r="F162" t="s">
         <v>568</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>569</v>
-      </c>
-      <c r="G162" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7509,19 +7515,19 @@
         <v>2</v>
       </c>
       <c r="C163" t="s">
+        <v>570</v>
+      </c>
+      <c r="D163" t="s">
+        <v>566</v>
+      </c>
+      <c r="E163" t="s">
         <v>571</v>
       </c>
-      <c r="D163" t="s">
-        <v>567</v>
-      </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
+        <v>568</v>
+      </c>
+      <c r="G163" t="s">
         <v>572</v>
-      </c>
-      <c r="F163" t="s">
-        <v>569</v>
-      </c>
-      <c r="G163" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7532,16 +7538,16 @@
         <v>3</v>
       </c>
       <c r="C164" t="s">
+        <v>573</v>
+      </c>
+      <c r="D164" t="s">
+        <v>566</v>
+      </c>
+      <c r="E164" t="s">
         <v>574</v>
       </c>
-      <c r="D164" t="s">
-        <v>567</v>
-      </c>
-      <c r="E164" t="s">
-        <v>575</v>
-      </c>
       <c r="G164" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7552,16 +7558,16 @@
         <v>4</v>
       </c>
       <c r="C165" t="s">
+        <v>575</v>
+      </c>
+      <c r="D165" t="s">
+        <v>566</v>
+      </c>
+      <c r="E165" t="s">
         <v>576</v>
       </c>
-      <c r="D165" t="s">
-        <v>567</v>
-      </c>
-      <c r="E165" t="s">
-        <v>577</v>
-      </c>
       <c r="G165" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7572,19 +7578,19 @@
         <v>5</v>
       </c>
       <c r="C166" t="s">
+        <v>577</v>
+      </c>
+      <c r="D166" t="s">
+        <v>566</v>
+      </c>
+      <c r="E166" t="s">
         <v>578</v>
-      </c>
-      <c r="D166" t="s">
-        <v>567</v>
-      </c>
-      <c r="E166" t="s">
-        <v>579</v>
       </c>
       <c r="F166" t="s">
         <v>288</v>
       </c>
       <c r="G166" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7595,10 +7601,10 @@
         <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D167" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7609,10 +7615,10 @@
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D168" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7623,10 +7629,10 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D169" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7637,10 +7643,10 @@
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D170" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7651,10 +7657,10 @@
         <v>10</v>
       </c>
       <c r="C171" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D171" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7665,10 +7671,10 @@
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D172" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7679,10 +7685,10 @@
         <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D173" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7693,10 +7699,10 @@
         <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D174" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7707,10 +7713,10 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D175" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7721,10 +7727,10 @@
         <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D176" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7735,10 +7741,10 @@
         <v>16</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -7749,10 +7755,10 @@
         <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -7763,10 +7769,10 @@
         <v>18</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -7777,10 +7783,10 @@
         <v>19</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -7791,10 +7797,10 @@
         <v>20</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -7805,19 +7811,19 @@
         <v>1</v>
       </c>
       <c r="C182" t="s">
+        <v>590</v>
+      </c>
+      <c r="D182" t="s">
         <v>591</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>592</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" t="s">
+        <v>128</v>
+      </c>
+      <c r="G182" t="s">
         <v>593</v>
-      </c>
-      <c r="F182" t="s">
-        <v>128</v>
-      </c>
-      <c r="G182" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -7828,19 +7834,19 @@
         <v>2</v>
       </c>
       <c r="C183" t="s">
+        <v>594</v>
+      </c>
+      <c r="D183" t="s">
+        <v>591</v>
+      </c>
+      <c r="E183" t="s">
         <v>595</v>
       </c>
-      <c r="D183" t="s">
-        <v>592</v>
-      </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
+        <v>128</v>
+      </c>
+      <c r="G183" t="s">
         <v>596</v>
-      </c>
-      <c r="F183" t="s">
-        <v>128</v>
-      </c>
-      <c r="G183" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -7851,19 +7857,19 @@
         <v>3</v>
       </c>
       <c r="C184" t="s">
+        <v>597</v>
+      </c>
+      <c r="D184" t="s">
+        <v>591</v>
+      </c>
+      <c r="E184" t="s">
         <v>598</v>
       </c>
-      <c r="D184" t="s">
-        <v>592</v>
-      </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
+        <v>128</v>
+      </c>
+      <c r="G184" t="s">
         <v>599</v>
-      </c>
-      <c r="F184" t="s">
-        <v>128</v>
-      </c>
-      <c r="G184" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -7874,19 +7880,19 @@
         <v>4</v>
       </c>
       <c r="C185" t="s">
+        <v>600</v>
+      </c>
+      <c r="D185" t="s">
+        <v>591</v>
+      </c>
+      <c r="E185" t="s">
         <v>601</v>
       </c>
-      <c r="D185" t="s">
-        <v>592</v>
-      </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
+        <v>128</v>
+      </c>
+      <c r="G185" t="s">
         <v>602</v>
-      </c>
-      <c r="F185" t="s">
-        <v>128</v>
-      </c>
-      <c r="G185" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -7897,19 +7903,19 @@
         <v>5</v>
       </c>
       <c r="C186" t="s">
+        <v>603</v>
+      </c>
+      <c r="D186" t="s">
+        <v>591</v>
+      </c>
+      <c r="E186" t="s">
         <v>604</v>
       </c>
-      <c r="D186" t="s">
-        <v>592</v>
-      </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
+        <v>128</v>
+      </c>
+      <c r="G186" t="s">
         <v>605</v>
-      </c>
-      <c r="F186" t="s">
-        <v>128</v>
-      </c>
-      <c r="G186" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -7920,19 +7926,19 @@
         <v>6</v>
       </c>
       <c r="C187" t="s">
+        <v>606</v>
+      </c>
+      <c r="D187" t="s">
+        <v>591</v>
+      </c>
+      <c r="E187" t="s">
         <v>607</v>
       </c>
-      <c r="D187" t="s">
-        <v>592</v>
-      </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
+        <v>128</v>
+      </c>
+      <c r="G187" t="s">
         <v>608</v>
-      </c>
-      <c r="F187" t="s">
-        <v>128</v>
-      </c>
-      <c r="G187" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7943,19 +7949,19 @@
         <v>7</v>
       </c>
       <c r="C188" t="s">
+        <v>609</v>
+      </c>
+      <c r="D188" t="s">
+        <v>591</v>
+      </c>
+      <c r="E188" t="s">
         <v>610</v>
-      </c>
-      <c r="D188" t="s">
-        <v>592</v>
-      </c>
-      <c r="E188" t="s">
-        <v>611</v>
       </c>
       <c r="F188" t="s">
         <v>367</v>
       </c>
       <c r="G188" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7966,19 +7972,19 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
+        <v>612</v>
+      </c>
+      <c r="D189" t="s">
+        <v>591</v>
+      </c>
+      <c r="E189" t="s">
         <v>613</v>
-      </c>
-      <c r="D189" t="s">
-        <v>592</v>
-      </c>
-      <c r="E189" t="s">
-        <v>614</v>
       </c>
       <c r="F189" t="s">
         <v>367</v>
       </c>
       <c r="G189" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -7989,19 +7995,19 @@
         <v>9</v>
       </c>
       <c r="C190" t="s">
+        <v>615</v>
+      </c>
+      <c r="D190" t="s">
+        <v>591</v>
+      </c>
+      <c r="E190" t="s">
         <v>616</v>
-      </c>
-      <c r="D190" t="s">
-        <v>592</v>
-      </c>
-      <c r="E190" t="s">
-        <v>617</v>
       </c>
       <c r="F190" t="s">
         <v>367</v>
       </c>
       <c r="G190" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -8012,19 +8018,19 @@
         <v>10</v>
       </c>
       <c r="C191" t="s">
+        <v>618</v>
+      </c>
+      <c r="D191" t="s">
+        <v>591</v>
+      </c>
+      <c r="E191" t="s">
         <v>619</v>
-      </c>
-      <c r="D191" t="s">
-        <v>592</v>
-      </c>
-      <c r="E191" t="s">
-        <v>620</v>
       </c>
       <c r="F191" t="s">
         <v>367</v>
       </c>
       <c r="G191" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -8035,19 +8041,19 @@
         <v>11</v>
       </c>
       <c r="C192" t="s">
+        <v>621</v>
+      </c>
+      <c r="D192" t="s">
+        <v>591</v>
+      </c>
+      <c r="E192" t="s">
         <v>622</v>
-      </c>
-      <c r="D192" t="s">
-        <v>592</v>
-      </c>
-      <c r="E192" t="s">
-        <v>623</v>
       </c>
       <c r="F192" t="s">
         <v>367</v>
       </c>
       <c r="G192" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -8058,19 +8064,19 @@
         <v>12</v>
       </c>
       <c r="C193" t="s">
+        <v>624</v>
+      </c>
+      <c r="D193" t="s">
+        <v>591</v>
+      </c>
+      <c r="E193" t="s">
         <v>625</v>
-      </c>
-      <c r="D193" t="s">
-        <v>592</v>
-      </c>
-      <c r="E193" t="s">
-        <v>626</v>
       </c>
       <c r="F193" t="s">
         <v>367</v>
       </c>
       <c r="G193" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -8081,19 +8087,19 @@
         <v>13</v>
       </c>
       <c r="C194" t="s">
+        <v>627</v>
+      </c>
+      <c r="D194" t="s">
+        <v>591</v>
+      </c>
+      <c r="E194" t="s">
         <v>628</v>
-      </c>
-      <c r="D194" t="s">
-        <v>592</v>
-      </c>
-      <c r="E194" t="s">
-        <v>629</v>
       </c>
       <c r="F194" t="s">
         <v>367</v>
       </c>
       <c r="G194" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -8104,19 +8110,19 @@
         <v>14</v>
       </c>
       <c r="C195" t="s">
+        <v>630</v>
+      </c>
+      <c r="D195" t="s">
+        <v>591</v>
+      </c>
+      <c r="E195" t="s">
         <v>631</v>
-      </c>
-      <c r="D195" t="s">
-        <v>592</v>
-      </c>
-      <c r="E195" t="s">
-        <v>632</v>
       </c>
       <c r="F195" t="s">
         <v>367</v>
       </c>
       <c r="G195" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -8127,10 +8133,10 @@
         <v>15</v>
       </c>
       <c r="C196" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D196" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -8141,10 +8147,10 @@
         <v>16</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -8155,10 +8161,10 @@
         <v>17</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -8169,10 +8175,10 @@
         <v>18</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -8183,10 +8189,10 @@
         <v>19</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -8197,10 +8203,10 @@
         <v>20</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -8211,13 +8217,13 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D202" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E202" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F202" t="s">
         <v>305</v>
@@ -8231,16 +8237,16 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D203" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E203" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F203" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -8251,16 +8257,16 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D204" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E204" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F204" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -8271,16 +8277,16 @@
         <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D205" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E205" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F205" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -8291,13 +8297,13 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D206" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E206" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F206" t="s">
         <v>305</v>
@@ -8311,16 +8317,16 @@
         <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D207" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E207" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F207" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -8331,16 +8337,16 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D208" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E208" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F208" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -8351,16 +8357,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D209" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E209" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F209" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -8371,13 +8377,13 @@
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D210" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E210" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F210" t="s">
         <v>305</v>
@@ -8391,16 +8397,16 @@
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D211" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E211" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F211" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -8411,16 +8417,16 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D212" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E212" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F212" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -8431,16 +8437,16 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D213" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E213" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F213" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -8451,10 +8457,10 @@
         <v>13</v>
       </c>
       <c r="C214" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D214" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -8465,10 +8471,10 @@
         <v>14</v>
       </c>
       <c r="C215" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D215" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8479,10 +8485,10 @@
         <v>15</v>
       </c>
       <c r="C216" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D216" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -8493,10 +8499,10 @@
         <v>16</v>
       </c>
       <c r="C217" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -8507,10 +8513,10 @@
         <v>17</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8521,10 +8527,10 @@
         <v>18</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -8535,10 +8541,10 @@
         <v>19</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8549,10 +8555,10 @@
         <v>20</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
@@ -8608,7 +8614,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>261</v>
@@ -8625,7 +8631,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>261</v>
@@ -8642,7 +8648,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>261</v>
@@ -8659,7 +8665,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>261</v>
@@ -8676,7 +8682,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>261</v>
@@ -8693,7 +8699,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>300</v>
@@ -8710,7 +8716,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>300</v>
@@ -8727,7 +8733,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>300</v>
@@ -8744,7 +8750,7 @@
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>300</v>
@@ -8761,7 +8767,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>300</v>
@@ -8778,7 +8784,7 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>348</v>
@@ -8795,7 +8801,7 @@
         <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>348</v>
@@ -8812,7 +8818,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>348</v>
@@ -8829,7 +8835,7 @@
         <v>19</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>348</v>
@@ -8846,7 +8852,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>348</v>
@@ -8863,10 +8869,10 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8880,10 +8886,10 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8897,10 +8903,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8914,10 +8920,10 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8931,10 +8937,10 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8948,10 +8954,10 @@
         <v>16</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8965,10 +8971,10 @@
         <v>17</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8982,10 +8988,10 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8999,10 +9005,10 @@
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -9016,10 +9022,10 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9033,10 +9039,10 @@
         <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9050,10 +9056,10 @@
         <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9067,10 +9073,10 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9084,10 +9090,10 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9101,10 +9107,10 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9118,10 +9124,10 @@
         <v>16</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9135,10 +9141,10 @@
         <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9152,10 +9158,10 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9169,10 +9175,10 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9186,10 +9192,10 @@
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9203,10 +9209,10 @@
         <v>16</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9220,10 +9226,10 @@
         <v>17</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -9237,10 +9243,10 @@
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -9254,10 +9260,10 @@
         <v>19</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -9271,10 +9277,10 @@
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -9288,10 +9294,10 @@
         <v>16</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9305,10 +9311,10 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9322,10 +9328,10 @@
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9339,10 +9345,10 @@
         <v>19</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -9356,10 +9362,10 @@
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -9373,10 +9379,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -9390,10 +9396,10 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -9407,10 +9413,10 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -9424,10 +9430,10 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -9441,10 +9447,10 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -9458,10 +9464,10 @@
         <v>16</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9475,10 +9481,10 @@
         <v>17</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9492,10 +9498,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9509,10 +9515,10 @@
         <v>19</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9526,15 +9532,15 @@
         <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4E0500-B472-4C42-A9F9-4C08329D08B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FF79BD-6090-42A3-80BF-86A66EB5E907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="760">
   <si>
     <t>pFS2</t>
   </si>
@@ -2287,6 +2287,30 @@
   </si>
   <si>
     <t>Modifier to amplify light benefit to shorter cohorts</t>
+  </si>
+  <si>
+    <t>def_type</t>
+  </si>
+  <si>
+    <t>def_recover_t</t>
+  </si>
+  <si>
+    <t>Number of trees removed due to defoliation</t>
+  </si>
+  <si>
+    <t>Stem biomass removed due to defoliation</t>
+  </si>
+  <si>
+    <t>Root biomass removed due to defoliation</t>
+  </si>
+  <si>
+    <t>Foliage biomass remoed due to defoliation</t>
+  </si>
+  <si>
+    <t>Defoliation type (1 = Pruning; 2 = Epicormic; 3 = Coppice; 4 = Stand-replacing)</t>
+  </si>
+  <si>
+    <t>Maximum number of months required to recover the pre-defoliation foliage biomass (pruning or epicormic responses) or foliage + stem mass (coppice responses) of the trees that survived the defoliation event.</t>
   </si>
 </sst>
 </file>
@@ -2365,13 +2389,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8462,6 +8487,12 @@
       <c r="D214" t="s">
         <v>657</v>
       </c>
+      <c r="E214" t="s">
+        <v>754</v>
+      </c>
+      <c r="F214" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215">
@@ -8470,11 +8501,17 @@
       <c r="B215">
         <v>14</v>
       </c>
-      <c r="C215" t="s">
+      <c r="C215" s="1" t="s">
         <v>739</v>
       </c>
       <c r="D215" t="s">
         <v>657</v>
+      </c>
+      <c r="E215" t="s">
+        <v>755</v>
+      </c>
+      <c r="F215" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8484,11 +8521,17 @@
       <c r="B216">
         <v>15</v>
       </c>
-      <c r="C216" t="s">
+      <c r="C216" s="1" t="s">
         <v>740</v>
       </c>
       <c r="D216" t="s">
         <v>657</v>
+      </c>
+      <c r="E216" t="s">
+        <v>756</v>
+      </c>
+      <c r="F216" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -8498,11 +8541,17 @@
       <c r="B217" s="4">
         <v>16</v>
       </c>
-      <c r="C217" t="s">
+      <c r="C217" s="1" t="s">
         <v>741</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>657</v>
+      </c>
+      <c r="E217" t="s">
+        <v>757</v>
+      </c>
+      <c r="F217" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -8512,11 +8561,14 @@
       <c r="B218" s="4">
         <v>17</v>
       </c>
-      <c r="C218" s="4" t="s">
-        <v>733</v>
+      <c r="C218" s="6" t="s">
+        <v>752</v>
       </c>
       <c r="D218" s="4" t="s">
         <v>657</v>
+      </c>
+      <c r="E218" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8526,11 +8578,17 @@
       <c r="B219" s="4">
         <v>18</v>
       </c>
-      <c r="C219" s="4" t="s">
-        <v>734</v>
+      <c r="C219" s="6" t="s">
+        <v>753</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>657</v>
+      </c>
+      <c r="E219" t="s">
+        <v>759</v>
+      </c>
+      <c r="F219" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="220" spans="1:6">

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FF79BD-6090-42A3-80BF-86A66EB5E907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F7C97A-0B8B-437E-A7F3-6C5A7420771B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="20940" windowHeight="21015" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -8481,7 +8481,7 @@
       <c r="B214">
         <v>13</v>
       </c>
-      <c r="C214" t="s">
+      <c r="C214" s="1" t="s">
         <v>738</v>
       </c>
       <c r="D214" t="s">

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F7C97A-0B8B-437E-A7F3-6C5A7420771B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E43DBBA-826E-4163-B061-5852093B1EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="20940" windowHeight="21015" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -2304,13 +2304,13 @@
     <t>Root biomass removed due to defoliation</t>
   </si>
   <si>
-    <t>Foliage biomass remoed due to defoliation</t>
-  </si>
-  <si>
     <t>Defoliation type (1 = Pruning; 2 = Epicormic; 3 = Coppice; 4 = Stand-replacing)</t>
   </si>
   <si>
     <t>Maximum number of months required to recover the pre-defoliation foliage biomass (pruning or epicormic responses) or foliage + stem mass (coppice responses) of the trees that survived the defoliation event.</t>
+  </si>
+  <si>
+    <t>Foliage biomass removed due to defoliation</t>
   </si>
 </sst>
 </file>
@@ -8548,7 +8548,7 @@
         <v>657</v>
       </c>
       <c r="E217" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F217" t="s">
         <v>390</v>
@@ -8568,7 +8568,7 @@
         <v>657</v>
       </c>
       <c r="E218" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8585,7 +8585,7 @@
         <v>657</v>
       </c>
       <c r="E219" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>138</v>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E43DBBA-826E-4163-B061-5852093B1EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012E5397-90E6-48BB-8F7B-234485784936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="759">
   <si>
     <t>pFS2</t>
   </si>
@@ -1713,18 +1713,9 @@
     <t>month-1</t>
   </si>
   <si>
-    <t>Number of trees that died due to density-dependent mortality</t>
-  </si>
-  <si>
     <t>Self thinning</t>
   </si>
   <si>
-    <t>Number of trees that died due to stress-related mortality</t>
-  </si>
-  <si>
-    <t>Stem mortality</t>
-  </si>
-  <si>
     <t>var_8_15</t>
   </si>
   <si>
@@ -2311,6 +2302,12 @@
   </si>
   <si>
     <t>Foliage biomass removed due to defoliation</t>
+  </si>
+  <si>
+    <t>var_8_11</t>
+  </si>
+  <si>
+    <t>var_8_12</t>
   </si>
 </sst>
 </file>
@@ -3179,10 +3176,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -3191,10 +3188,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -3203,10 +3200,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -3215,10 +3212,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -3227,10 +3224,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -3239,10 +3236,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -3349,10 +3346,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -3669,10 +3666,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>320</v>
@@ -4779,7 +4776,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>261</v>
@@ -4793,7 +4790,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>261</v>
@@ -4807,7 +4804,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>261</v>
@@ -4821,7 +4818,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>261</v>
@@ -4835,7 +4832,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>261</v>
@@ -5176,7 +5173,7 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>300</v>
@@ -5190,7 +5187,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>300</v>
@@ -5204,7 +5201,7 @@
         <v>18</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>300</v>
@@ -5218,7 +5215,7 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>300</v>
@@ -5232,7 +5229,7 @@
         <v>20</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>300</v>
@@ -5496,13 +5493,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D53" t="s">
         <v>348</v>
       </c>
       <c r="E53" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5555,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>348</v>
@@ -5569,7 +5566,7 @@
         <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>348</v>
@@ -5583,7 +5580,7 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>348</v>
@@ -5597,7 +5594,7 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>348</v>
@@ -5611,7 +5608,7 @@
         <v>20</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>348</v>
@@ -5931,7 +5928,7 @@
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>388</v>
@@ -5945,7 +5942,7 @@
         <v>17</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>388</v>
@@ -5959,7 +5956,7 @@
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>388</v>
@@ -5973,7 +5970,7 @@
         <v>19</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>388</v>
@@ -5987,7 +5984,7 @@
         <v>20</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>388</v>
@@ -6316,7 +6313,7 @@
         <v>16</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>427</v>
@@ -6330,7 +6327,7 @@
         <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>427</v>
@@ -6344,7 +6341,7 @@
         <v>18</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>427</v>
@@ -6358,7 +6355,7 @@
         <v>19</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>427</v>
@@ -6372,7 +6369,7 @@
         <v>20</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>427</v>
@@ -6432,7 +6429,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D104" t="s">
         <v>467</v>
@@ -6713,7 +6710,7 @@
         <v>16</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>467</v>
@@ -6727,7 +6724,7 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>467</v>
@@ -6741,7 +6738,7 @@
         <v>18</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>467</v>
@@ -6755,7 +6752,7 @@
         <v>19</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>467</v>
@@ -6769,7 +6766,7 @@
         <v>20</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>467</v>
@@ -7110,7 +7107,7 @@
         <v>16</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>509</v>
@@ -7124,7 +7121,7 @@
         <v>17</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>509</v>
@@ -7138,7 +7135,7 @@
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>509</v>
@@ -7152,7 +7149,7 @@
         <v>19</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>509</v>
@@ -7166,7 +7163,7 @@
         <v>20</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>509</v>
@@ -7225,46 +7222,37 @@
       <c r="B144">
         <v>3</v>
       </c>
-      <c r="C144" t="s">
-        <v>674</v>
+      <c r="C144" s="1" t="s">
+        <v>644</v>
       </c>
       <c r="D144" t="s">
         <v>553</v>
       </c>
       <c r="E144" t="s">
-        <v>560</v>
+        <v>649</v>
       </c>
       <c r="F144" t="s">
         <v>305</v>
       </c>
       <c r="G144" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
       <c r="A145">
         <v>8</v>
       </c>
       <c r="B145">
         <v>4</v>
       </c>
-      <c r="C145" t="s">
-        <v>666</v>
+      <c r="C145" s="1" t="s">
+        <v>650</v>
       </c>
       <c r="D145" t="s">
         <v>553</v>
       </c>
-      <c r="E145" t="s">
-        <v>562</v>
-      </c>
-      <c r="F145" t="s">
-        <v>305</v>
-      </c>
-      <c r="G145" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
+    </row>
+    <row r="146" spans="1:5">
       <c r="A146" s="2">
         <v>8</v>
       </c>
@@ -7272,22 +7260,13 @@
         <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="D146" t="s">
         <v>553</v>
       </c>
-      <c r="E146" t="s">
-        <v>652</v>
-      </c>
-      <c r="F146" t="s">
-        <v>305</v>
-      </c>
-      <c r="G146" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
+    </row>
+    <row r="147" spans="1:5">
       <c r="A147">
         <v>8</v>
       </c>
@@ -7295,13 +7274,13 @@
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D147" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:5">
       <c r="A148">
         <v>8</v>
       </c>
@@ -7309,13 +7288,16 @@
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>654</v>
+        <v>739</v>
       </c>
       <c r="D148" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="149" spans="1:7">
+      <c r="E148" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
       <c r="A149">
         <v>8</v>
       </c>
@@ -7323,13 +7305,16 @@
         <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>655</v>
+        <v>740</v>
       </c>
       <c r="D149" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="150" spans="1:7">
+      <c r="E149" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
       <c r="A150">
         <v>8</v>
       </c>
@@ -7337,16 +7322,16 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>742</v>
+        <v>645</v>
       </c>
       <c r="D150" t="s">
         <v>553</v>
       </c>
       <c r="E150" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
       <c r="A151">
         <v>8</v>
       </c>
@@ -7354,16 +7339,16 @@
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>743</v>
+        <v>646</v>
       </c>
       <c r="D151" t="s">
         <v>553</v>
       </c>
       <c r="E151" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
       <c r="A152">
         <v>8</v>
       </c>
@@ -7371,16 +7356,13 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>648</v>
+        <v>757</v>
       </c>
       <c r="D152" t="s">
         <v>553</v>
       </c>
-      <c r="E152" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
+    </row>
+    <row r="153" spans="1:5">
       <c r="A153">
         <v>8</v>
       </c>
@@ -7388,16 +7370,13 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>649</v>
+        <v>758</v>
       </c>
       <c r="D153" t="s">
         <v>553</v>
       </c>
-      <c r="E153" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
+    </row>
+    <row r="154" spans="1:5">
       <c r="A154">
         <v>8</v>
       </c>
@@ -7405,13 +7384,13 @@
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D154" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:5">
       <c r="A155">
         <v>8</v>
       </c>
@@ -7419,13 +7398,13 @@
         <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D155" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:5">
       <c r="A156">
         <v>8</v>
       </c>
@@ -7433,13 +7412,13 @@
         <v>15</v>
       </c>
       <c r="C156" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D156" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:5">
       <c r="A157" s="4">
         <v>8</v>
       </c>
@@ -7447,13 +7426,13 @@
         <v>16</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:5">
       <c r="A158" s="4">
         <v>8</v>
       </c>
@@ -7461,13 +7440,13 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:5">
       <c r="A159" s="4">
         <v>8</v>
       </c>
@@ -7475,13 +7454,13 @@
         <v>18</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:5">
       <c r="A160" s="4">
         <v>8</v>
       </c>
@@ -7489,7 +7468,7 @@
         <v>19</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>553</v>
@@ -7503,7 +7482,7 @@
         <v>20</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>553</v>
@@ -7517,19 +7496,19 @@
         <v>1</v>
       </c>
       <c r="C162" t="s">
+        <v>562</v>
+      </c>
+      <c r="D162" t="s">
+        <v>563</v>
+      </c>
+      <c r="E162" t="s">
+        <v>564</v>
+      </c>
+      <c r="F162" t="s">
         <v>565</v>
       </c>
-      <c r="D162" t="s">
+      <c r="G162" t="s">
         <v>566</v>
-      </c>
-      <c r="E162" t="s">
-        <v>567</v>
-      </c>
-      <c r="F162" t="s">
-        <v>568</v>
-      </c>
-      <c r="G162" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7540,19 +7519,19 @@
         <v>2</v>
       </c>
       <c r="C163" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D163" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E163" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="F163" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="G163" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7563,16 +7542,16 @@
         <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D164" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E164" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="G164" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7583,16 +7562,16 @@
         <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="D165" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E165" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="G165" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7603,19 +7582,19 @@
         <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D166" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E166" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="F166" t="s">
         <v>288</v>
       </c>
       <c r="G166" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7626,10 +7605,10 @@
         <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D167" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7640,10 +7619,10 @@
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D168" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7654,10 +7633,10 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D169" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7668,10 +7647,10 @@
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D170" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7682,10 +7661,10 @@
         <v>10</v>
       </c>
       <c r="C171" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D171" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7696,10 +7675,10 @@
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D172" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7710,10 +7689,10 @@
         <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D173" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7724,10 +7703,10 @@
         <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D174" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7738,10 +7717,10 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D175" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7752,10 +7731,10 @@
         <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D176" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7766,10 +7745,10 @@
         <v>16</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -7780,10 +7759,10 @@
         <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -7794,10 +7773,10 @@
         <v>18</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -7808,10 +7787,10 @@
         <v>19</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -7822,10 +7801,10 @@
         <v>20</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -7836,19 +7815,19 @@
         <v>1</v>
       </c>
       <c r="C182" t="s">
+        <v>587</v>
+      </c>
+      <c r="D182" t="s">
+        <v>588</v>
+      </c>
+      <c r="E182" t="s">
+        <v>589</v>
+      </c>
+      <c r="F182" t="s">
+        <v>128</v>
+      </c>
+      <c r="G182" t="s">
         <v>590</v>
-      </c>
-      <c r="D182" t="s">
-        <v>591</v>
-      </c>
-      <c r="E182" t="s">
-        <v>592</v>
-      </c>
-      <c r="F182" t="s">
-        <v>128</v>
-      </c>
-      <c r="G182" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -7859,19 +7838,19 @@
         <v>2</v>
       </c>
       <c r="C183" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D183" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E183" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F183" t="s">
         <v>128</v>
       </c>
       <c r="G183" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -7882,19 +7861,19 @@
         <v>3</v>
       </c>
       <c r="C184" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D184" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E184" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="F184" t="s">
         <v>128</v>
       </c>
       <c r="G184" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -7905,19 +7884,19 @@
         <v>4</v>
       </c>
       <c r="C185" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D185" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E185" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="F185" t="s">
         <v>128</v>
       </c>
       <c r="G185" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -7928,19 +7907,19 @@
         <v>5</v>
       </c>
       <c r="C186" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D186" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E186" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F186" t="s">
         <v>128</v>
       </c>
       <c r="G186" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -7951,19 +7930,19 @@
         <v>6</v>
       </c>
       <c r="C187" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D187" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E187" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F187" t="s">
         <v>128</v>
       </c>
       <c r="G187" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7974,19 +7953,19 @@
         <v>7</v>
       </c>
       <c r="C188" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D188" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E188" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F188" t="s">
         <v>367</v>
       </c>
       <c r="G188" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7997,19 +7976,19 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D189" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E189" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F189" t="s">
         <v>367</v>
       </c>
       <c r="G189" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -8020,19 +7999,19 @@
         <v>9</v>
       </c>
       <c r="C190" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D190" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E190" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="F190" t="s">
         <v>367</v>
       </c>
       <c r="G190" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -8043,19 +8022,19 @@
         <v>10</v>
       </c>
       <c r="C191" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D191" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E191" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F191" t="s">
         <v>367</v>
       </c>
       <c r="G191" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -8066,19 +8045,19 @@
         <v>11</v>
       </c>
       <c r="C192" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D192" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E192" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F192" t="s">
         <v>367</v>
       </c>
       <c r="G192" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -8089,19 +8068,19 @@
         <v>12</v>
       </c>
       <c r="C193" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D193" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E193" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F193" t="s">
         <v>367</v>
       </c>
       <c r="G193" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -8112,19 +8091,19 @@
         <v>13</v>
       </c>
       <c r="C194" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D194" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E194" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F194" t="s">
         <v>367</v>
       </c>
       <c r="G194" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -8135,19 +8114,19 @@
         <v>14</v>
       </c>
       <c r="C195" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D195" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="E195" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="F195" t="s">
         <v>367</v>
       </c>
       <c r="G195" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -8158,10 +8137,10 @@
         <v>15</v>
       </c>
       <c r="C196" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="D196" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -8172,10 +8151,10 @@
         <v>16</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -8186,10 +8165,10 @@
         <v>17</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -8200,10 +8179,10 @@
         <v>18</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -8214,10 +8193,10 @@
         <v>19</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -8228,10 +8207,10 @@
         <v>20</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -8242,13 +8221,13 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D202" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E202" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="F202" t="s">
         <v>305</v>
@@ -8262,13 +8241,13 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D203" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E203" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="F203" t="s">
         <v>390</v>
@@ -8282,13 +8261,13 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D204" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E204" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="F204" t="s">
         <v>390</v>
@@ -8302,13 +8281,13 @@
         <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D205" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E205" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="F205" t="s">
         <v>390</v>
@@ -8322,13 +8301,13 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D206" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E206" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F206" t="s">
         <v>305</v>
@@ -8342,13 +8321,13 @@
         <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D207" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E207" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="F207" t="s">
         <v>390</v>
@@ -8362,13 +8341,13 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D208" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E208" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="F208" t="s">
         <v>390</v>
@@ -8382,13 +8361,13 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D209" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E209" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="F209" t="s">
         <v>390</v>
@@ -8402,13 +8381,13 @@
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D210" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E210" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F210" t="s">
         <v>305</v>
@@ -8422,13 +8401,13 @@
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D211" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E211" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="F211" t="s">
         <v>390</v>
@@ -8442,13 +8421,13 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D212" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E212" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="F212" t="s">
         <v>390</v>
@@ -8462,13 +8441,13 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D213" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E213" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="F213" t="s">
         <v>390</v>
@@ -8482,13 +8461,13 @@
         <v>13</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D214" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E214" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="F214" t="s">
         <v>305</v>
@@ -8502,13 +8481,13 @@
         <v>14</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D215" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E215" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="F215" t="s">
         <v>390</v>
@@ -8522,13 +8501,13 @@
         <v>15</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D216" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E216" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="F216" t="s">
         <v>390</v>
@@ -8542,13 +8521,13 @@
         <v>16</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E217" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="F217" t="s">
         <v>390</v>
@@ -8562,13 +8541,13 @@
         <v>17</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E218" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8579,13 +8558,13 @@
         <v>18</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E219" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>138</v>
@@ -8599,10 +8578,10 @@
         <v>19</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8613,10 +8592,10 @@
         <v>20</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -8672,7 +8651,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>261</v>
@@ -8689,7 +8668,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>261</v>
@@ -8706,7 +8685,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>261</v>
@@ -8723,7 +8702,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>261</v>
@@ -8740,7 +8719,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>261</v>
@@ -8757,7 +8736,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>300</v>
@@ -8774,7 +8753,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>300</v>
@@ -8791,7 +8770,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>300</v>
@@ -8808,7 +8787,7 @@
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>300</v>
@@ -8825,7 +8804,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>300</v>
@@ -8842,7 +8821,7 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>348</v>
@@ -8859,7 +8838,7 @@
         <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>348</v>
@@ -8876,7 +8855,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>348</v>
@@ -8893,7 +8872,7 @@
         <v>19</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>348</v>
@@ -8910,7 +8889,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>348</v>
@@ -8927,7 +8906,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>388</v>
@@ -8944,7 +8923,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>388</v>
@@ -8961,7 +8940,7 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>388</v>
@@ -8978,7 +8957,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>388</v>
@@ -8995,7 +8974,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>388</v>
@@ -9012,7 +8991,7 @@
         <v>16</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>427</v>
@@ -9029,7 +9008,7 @@
         <v>17</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>427</v>
@@ -9046,7 +9025,7 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>427</v>
@@ -9063,7 +9042,7 @@
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>427</v>
@@ -9080,7 +9059,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>427</v>
@@ -9097,7 +9076,7 @@
         <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>467</v>
@@ -9114,7 +9093,7 @@
         <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>467</v>
@@ -9131,7 +9110,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>467</v>
@@ -9148,7 +9127,7 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>467</v>
@@ -9165,7 +9144,7 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>467</v>
@@ -9182,7 +9161,7 @@
         <v>16</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>509</v>
@@ -9199,7 +9178,7 @@
         <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>509</v>
@@ -9216,7 +9195,7 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>509</v>
@@ -9233,7 +9212,7 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>509</v>
@@ -9250,7 +9229,7 @@
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>509</v>
@@ -9267,7 +9246,7 @@
         <v>16</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>553</v>
@@ -9284,7 +9263,7 @@
         <v>17</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>553</v>
@@ -9301,7 +9280,7 @@
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>553</v>
@@ -9318,7 +9297,7 @@
         <v>19</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>553</v>
@@ -9335,7 +9314,7 @@
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>553</v>
@@ -9352,10 +9331,10 @@
         <v>16</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9369,10 +9348,10 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9386,10 +9365,10 @@
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9403,10 +9382,10 @@
         <v>19</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -9420,10 +9399,10 @@
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -9437,10 +9416,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -9454,10 +9433,10 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -9471,10 +9450,10 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -9488,10 +9467,10 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -9505,10 +9484,10 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -9522,10 +9501,10 @@
         <v>16</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9539,10 +9518,10 @@
         <v>17</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9556,10 +9535,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9573,10 +9552,10 @@
         <v>19</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9590,15 +9569,15 @@
         <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012E5397-90E6-48BB-8F7B-234485784936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E6E07D-6DC8-4E59-A391-D457F44847EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -2711,6 +2711,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E287297-02C0-BF44-BF0C-8FADE2A87F8F}">
   <dimension ref="A1:D91"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="2" max="2" width="80" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E6E07D-6DC8-4E59-A391-D457F44847EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2941141-42E1-412B-9197-175FE96C2BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="57510" yWindow="75" windowWidth="19350" windowHeight="20880" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -477,9 +477,6 @@
     <t>days</t>
   </si>
   <si>
-    <t xml:space="preserve">Moisture ratio deficit for fq = 0.5 </t>
-  </si>
-  <si>
     <t>Power of moisture ratio deficit</t>
   </si>
   <si>
@@ -2308,6 +2305,9 @@
   </si>
   <si>
     <t>var_8_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moisture ratio deficit for fsw = 0.5 </t>
   </si>
 </sst>
 </file>
@@ -2958,7 +2958,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>758</v>
       </c>
       <c r="C18" t="s">
         <v>128</v>
@@ -2972,7 +2972,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s">
         <v>128</v>
@@ -2986,7 +2986,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" t="s">
         <v>128</v>
@@ -3000,7 +3000,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" t="s">
         <v>128</v>
@@ -3014,7 +3014,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
         <v>128</v>
@@ -3028,7 +3028,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
         <v>128</v>
@@ -3042,7 +3042,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C24" t="s">
         <v>128</v>
@@ -3056,10 +3056,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" t="s">
         <v>155</v>
-      </c>
-      <c r="C25" t="s">
-        <v>156</v>
       </c>
       <c r="D25">
         <v>50</v>
@@ -3070,7 +3070,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C26" t="s">
         <v>128</v>
@@ -3084,7 +3084,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C27" t="s">
         <v>128</v>
@@ -3098,10 +3098,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C28" t="s">
         <v>159</v>
-      </c>
-      <c r="C28" t="s">
-        <v>160</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -3112,10 +3112,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -3126,10 +3126,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C31" t="s">
         <v>128</v>
@@ -3154,10 +3154,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" t="s">
         <v>164</v>
-      </c>
-      <c r="C32" t="s">
-        <v>165</v>
       </c>
       <c r="D32">
         <v>300</v>
@@ -3168,7 +3168,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C33" t="s">
         <v>128</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -3191,10 +3191,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -3203,10 +3203,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -3215,10 +3215,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -3239,10 +3239,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -3254,7 +3254,7 @@
         <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C40" t="s">
         <v>128</v>
@@ -3268,7 +3268,7 @@
         <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C41" t="s">
         <v>128</v>
@@ -3282,7 +3282,7 @@
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C42" t="s">
         <v>128</v>
@@ -3296,10 +3296,10 @@
         <v>36</v>
       </c>
       <c r="B43" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" t="s">
         <v>170</v>
-      </c>
-      <c r="C43" t="s">
-        <v>171</v>
       </c>
       <c r="D43">
         <v>11</v>
@@ -3310,10 +3310,10 @@
         <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -3324,10 +3324,10 @@
         <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D45">
         <v>2.5</v>
@@ -3338,7 +3338,7 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C46" t="s">
         <v>128</v>
@@ -3349,10 +3349,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>746</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -3364,10 +3364,10 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -3378,7 +3378,7 @@
         <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s">
         <v>128</v>
@@ -3392,7 +3392,7 @@
         <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C50" t="s">
         <v>128</v>
@@ -3406,7 +3406,7 @@
         <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C51" t="s">
         <v>128</v>
@@ -3420,10 +3420,10 @@
         <v>44</v>
       </c>
       <c r="B52" t="s">
+        <v>178</v>
+      </c>
+      <c r="C52" t="s">
         <v>179</v>
-      </c>
-      <c r="C52" t="s">
-        <v>180</v>
       </c>
       <c r="D52">
         <v>0.06</v>
@@ -3434,7 +3434,7 @@
         <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C53" t="s">
         <v>128</v>
@@ -3448,10 +3448,10 @@
         <v>46</v>
       </c>
       <c r="B54" t="s">
+        <v>181</v>
+      </c>
+      <c r="C54" t="s">
         <v>182</v>
-      </c>
-      <c r="C54" t="s">
-        <v>183</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3462,10 +3462,10 @@
         <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D55">
         <v>0.02</v>
@@ -3476,7 +3476,7 @@
         <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C56" t="s">
         <v>128</v>
@@ -3490,10 +3490,10 @@
         <v>49</v>
       </c>
       <c r="B57" t="s">
+        <v>185</v>
+      </c>
+      <c r="C57" t="s">
         <v>186</v>
-      </c>
-      <c r="C57" t="s">
-        <v>187</v>
       </c>
       <c r="D57">
         <v>0.05</v>
@@ -3504,10 +3504,10 @@
         <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D58">
         <v>0.2</v>
@@ -3518,7 +3518,7 @@
         <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C59" t="s">
         <v>128</v>
@@ -3532,10 +3532,10 @@
         <v>52</v>
       </c>
       <c r="B60" t="s">
+        <v>189</v>
+      </c>
+      <c r="C60" t="s">
         <v>190</v>
-      </c>
-      <c r="C60" t="s">
-        <v>191</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -3546,10 +3546,10 @@
         <v>53</v>
       </c>
       <c r="B61" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D61">
         <v>4.4000000000000004</v>
@@ -3560,10 +3560,10 @@
         <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C62" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D62">
         <v>27</v>
@@ -3574,7 +3574,7 @@
         <v>55</v>
       </c>
       <c r="B63" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C63" t="s">
         <v>128</v>
@@ -3588,7 +3588,7 @@
         <v>56</v>
       </c>
       <c r="B64" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C64" t="s">
         <v>128</v>
@@ -3602,10 +3602,10 @@
         <v>57</v>
       </c>
       <c r="B65" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C65" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3616,10 +3616,10 @@
         <v>58</v>
       </c>
       <c r="B66" t="s">
+        <v>196</v>
+      </c>
+      <c r="C66" t="s">
         <v>197</v>
-      </c>
-      <c r="C66" t="s">
-        <v>198</v>
       </c>
       <c r="D66">
         <v>0.45</v>
@@ -3630,10 +3630,10 @@
         <v>59</v>
       </c>
       <c r="B67" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C67" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D67">
         <v>0.45</v>
@@ -3644,10 +3644,10 @@
         <v>60</v>
       </c>
       <c r="B68" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C68" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -3658,7 +3658,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C69" t="s">
         <v>128</v>
@@ -3669,13 +3669,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>744</v>
-      </c>
       <c r="C70" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D70" s="1">
         <v>1.3</v>
@@ -3686,7 +3686,7 @@
         <v>61</v>
       </c>
       <c r="B71" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C71" t="s">
         <v>128</v>
@@ -3700,7 +3700,7 @@
         <v>62</v>
       </c>
       <c r="B72" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C72" t="s">
         <v>128</v>
@@ -3714,7 +3714,7 @@
         <v>63</v>
       </c>
       <c r="B73" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C73" t="s">
         <v>128</v>
@@ -3728,7 +3728,7 @@
         <v>64</v>
       </c>
       <c r="B74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C74" t="s">
         <v>128</v>
@@ -3742,7 +3742,7 @@
         <v>65</v>
       </c>
       <c r="B75" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C75" t="s">
         <v>128</v>
@@ -3756,7 +3756,7 @@
         <v>66</v>
       </c>
       <c r="B76" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C76" t="s">
         <v>128</v>
@@ -3770,7 +3770,7 @@
         <v>67</v>
       </c>
       <c r="B77" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C77" t="s">
         <v>128</v>
@@ -3784,7 +3784,7 @@
         <v>69</v>
       </c>
       <c r="B78" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C78" t="s">
         <v>128</v>
@@ -3798,7 +3798,7 @@
         <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C79" t="s">
         <v>128</v>
@@ -3812,7 +3812,7 @@
         <v>71</v>
       </c>
       <c r="B80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C80" t="s">
         <v>128</v>
@@ -3826,7 +3826,7 @@
         <v>72</v>
       </c>
       <c r="B81" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C81" t="s">
         <v>128</v>
@@ -3840,7 +3840,7 @@
         <v>73</v>
       </c>
       <c r="B82" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C82" t="s">
         <v>128</v>
@@ -3854,7 +3854,7 @@
         <v>74</v>
       </c>
       <c r="B83" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C83" t="s">
         <v>128</v>
@@ -3868,7 +3868,7 @@
         <v>75</v>
       </c>
       <c r="B84" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C84" t="s">
         <v>128</v>
@@ -3882,7 +3882,7 @@
         <v>76</v>
       </c>
       <c r="B85" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C85" t="s">
         <v>128</v>
@@ -3896,7 +3896,7 @@
         <v>77</v>
       </c>
       <c r="B86" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C86" t="s">
         <v>128</v>
@@ -3910,7 +3910,7 @@
         <v>78</v>
       </c>
       <c r="B87" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C87" t="s">
         <v>128</v>
@@ -3924,10 +3924,10 @@
         <v>109</v>
       </c>
       <c r="B88" t="s">
+        <v>218</v>
+      </c>
+      <c r="C88" t="s">
         <v>219</v>
-      </c>
-      <c r="C88" t="s">
-        <v>220</v>
       </c>
       <c r="D88">
         <v>-90</v>
@@ -3938,7 +3938,7 @@
         <v>110</v>
       </c>
       <c r="B89" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C89" t="s">
         <v>128</v>
@@ -3952,10 +3952,10 @@
         <v>111</v>
       </c>
       <c r="B90" t="s">
+        <v>221</v>
+      </c>
+      <c r="C90" t="s">
         <v>222</v>
-      </c>
-      <c r="C90" t="s">
-        <v>223</v>
       </c>
       <c r="D90">
         <v>24</v>
@@ -3966,10 +3966,10 @@
         <v>112</v>
       </c>
       <c r="B91" t="s">
+        <v>223</v>
+      </c>
+      <c r="C91" t="s">
         <v>224</v>
-      </c>
-      <c r="C91" t="s">
-        <v>225</v>
       </c>
       <c r="D91">
         <v>2.2999999999999998</v>
@@ -4008,7 +4008,7 @@
         <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
         <v>128</v>
@@ -4022,7 +4022,7 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C3" t="s">
         <v>128</v>
@@ -4036,7 +4036,7 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
         <v>128</v>
@@ -4050,7 +4050,7 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C5" t="s">
         <v>128</v>
@@ -4064,7 +4064,7 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" t="s">
         <v>128</v>
@@ -4078,7 +4078,7 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C7" t="s">
         <v>128</v>
@@ -4092,7 +4092,7 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C8" t="s">
         <v>128</v>
@@ -4106,7 +4106,7 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C9" t="s">
         <v>128</v>
@@ -4120,7 +4120,7 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C10" t="s">
         <v>128</v>
@@ -4134,7 +4134,7 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C11" t="s">
         <v>128</v>
@@ -4148,7 +4148,7 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C12" t="s">
         <v>128</v>
@@ -4162,7 +4162,7 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C13" t="s">
         <v>128</v>
@@ -4176,7 +4176,7 @@
         <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C14" t="s">
         <v>128</v>
@@ -4190,7 +4190,7 @@
         <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C15" t="s">
         <v>128</v>
@@ -4204,7 +4204,7 @@
         <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C16" t="s">
         <v>128</v>
@@ -4218,7 +4218,7 @@
         <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C17" t="s">
         <v>128</v>
@@ -4232,7 +4232,7 @@
         <v>95</v>
       </c>
       <c r="B18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C18" t="s">
         <v>128</v>
@@ -4246,7 +4246,7 @@
         <v>96</v>
       </c>
       <c r="B19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C19" t="s">
         <v>128</v>
@@ -4260,7 +4260,7 @@
         <v>97</v>
       </c>
       <c r="B20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
         <v>128</v>
@@ -4274,7 +4274,7 @@
         <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C21" t="s">
         <v>128</v>
@@ -4288,7 +4288,7 @@
         <v>99</v>
       </c>
       <c r="B22" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C22" t="s">
         <v>128</v>
@@ -4302,7 +4302,7 @@
         <v>100</v>
       </c>
       <c r="B23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C23" t="s">
         <v>128</v>
@@ -4316,7 +4316,7 @@
         <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C24" t="s">
         <v>128</v>
@@ -4330,7 +4330,7 @@
         <v>102</v>
       </c>
       <c r="B25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C25" t="s">
         <v>128</v>
@@ -4344,7 +4344,7 @@
         <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C26" t="s">
         <v>128</v>
@@ -4358,7 +4358,7 @@
         <v>104</v>
       </c>
       <c r="B27" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C27" t="s">
         <v>128</v>
@@ -4372,7 +4372,7 @@
         <v>105</v>
       </c>
       <c r="B28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C28" t="s">
         <v>128</v>
@@ -4386,7 +4386,7 @@
         <v>106</v>
       </c>
       <c r="B29" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C29" t="s">
         <v>128</v>
@@ -4400,7 +4400,7 @@
         <v>107</v>
       </c>
       <c r="B30" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C30" t="s">
         <v>128</v>
@@ -4414,7 +4414,7 @@
         <v>108</v>
       </c>
       <c r="B31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C31" t="s">
         <v>128</v>
@@ -4444,16 +4444,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" t="s">
         <v>256</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>257</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>258</v>
-      </c>
-      <c r="D1" t="s">
-        <v>259</v>
       </c>
       <c r="E1" t="s">
         <v>124</v>
@@ -4462,7 +4462,7 @@
         <v>125</v>
       </c>
       <c r="G1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4476,16 +4476,16 @@
         <v>118</v>
       </c>
       <c r="D2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E2" t="s">
         <v>261</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>262</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>263</v>
-      </c>
-      <c r="G2" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4499,16 +4499,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G3" t="s">
         <v>265</v>
-      </c>
-      <c r="F3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G3" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4522,16 +4522,16 @@
         <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E4" t="s">
+        <v>266</v>
+      </c>
+      <c r="F4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G4" t="s">
         <v>267</v>
-      </c>
-      <c r="F4" t="s">
-        <v>263</v>
-      </c>
-      <c r="G4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4545,16 +4545,16 @@
         <v>122</v>
       </c>
       <c r="D5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E5" t="s">
+        <v>268</v>
+      </c>
+      <c r="F5" t="s">
         <v>269</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>270</v>
-      </c>
-      <c r="G5" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4565,19 +4565,19 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E6" t="s">
         <v>272</v>
       </c>
-      <c r="D6" t="s">
-        <v>261</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>273</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>274</v>
-      </c>
-      <c r="G6" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4588,19 +4588,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E7" t="s">
         <v>276</v>
       </c>
-      <c r="D7" t="s">
-        <v>261</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>277</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>278</v>
-      </c>
-      <c r="G7" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4614,16 +4614,16 @@
         <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E8" t="s">
+        <v>279</v>
+      </c>
+      <c r="F8" t="s">
         <v>280</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>281</v>
-      </c>
-      <c r="G8" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4634,19 +4634,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
+        <v>282</v>
+      </c>
+      <c r="D9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E9" t="s">
         <v>283</v>
       </c>
-      <c r="D9" t="s">
-        <v>261</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>284</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>285</v>
-      </c>
-      <c r="G9" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4660,16 +4660,16 @@
         <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E10" t="s">
+        <v>286</v>
+      </c>
+      <c r="F10" t="s">
         <v>287</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>288</v>
-      </c>
-      <c r="G10" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -4680,16 +4680,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D11" t="s">
+        <v>260</v>
+      </c>
+      <c r="E11" t="s">
         <v>290</v>
       </c>
-      <c r="D11" t="s">
-        <v>261</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>291</v>
-      </c>
-      <c r="G11" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -4700,19 +4700,19 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E12" t="s">
         <v>293</v>
       </c>
-      <c r="D12" t="s">
-        <v>261</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>280</v>
+      </c>
+      <c r="G12" t="s">
         <v>294</v>
-      </c>
-      <c r="F12" t="s">
-        <v>281</v>
-      </c>
-      <c r="G12" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4723,10 +4723,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4737,10 +4737,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4751,10 +4751,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4765,10 +4765,10 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -4779,10 +4779,10 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -4793,10 +4793,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4807,10 +4807,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4821,10 +4821,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -4835,10 +4835,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -4852,16 +4852,16 @@
         <v>113</v>
       </c>
       <c r="D22" t="s">
+        <v>299</v>
+      </c>
+      <c r="E22" t="s">
         <v>300</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
+        <v>155</v>
+      </c>
+      <c r="G22" t="s">
         <v>301</v>
-      </c>
-      <c r="F22" t="s">
-        <v>156</v>
-      </c>
-      <c r="G22" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4872,19 +4872,19 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
+        <v>302</v>
+      </c>
+      <c r="D23" t="s">
+        <v>299</v>
+      </c>
+      <c r="E23" t="s">
         <v>303</v>
       </c>
-      <c r="D23" t="s">
-        <v>300</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>304</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>305</v>
-      </c>
-      <c r="G23" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4895,19 +4895,19 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
+        <v>306</v>
+      </c>
+      <c r="D24" t="s">
+        <v>299</v>
+      </c>
+      <c r="E24" t="s">
         <v>307</v>
       </c>
-      <c r="D24" t="s">
-        <v>300</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>308</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>309</v>
-      </c>
-      <c r="G24" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4918,19 +4918,19 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
+        <v>310</v>
+      </c>
+      <c r="D25" t="s">
+        <v>299</v>
+      </c>
+      <c r="E25" t="s">
         <v>311</v>
       </c>
-      <c r="D25" t="s">
-        <v>300</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>312</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>313</v>
-      </c>
-      <c r="G25" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4941,19 +4941,19 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
+        <v>314</v>
+      </c>
+      <c r="D26" t="s">
+        <v>299</v>
+      </c>
+      <c r="E26" t="s">
         <v>315</v>
       </c>
-      <c r="D26" t="s">
-        <v>300</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>316</v>
       </c>
-      <c r="F26" t="s">
-        <v>317</v>
-      </c>
       <c r="G26" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -4964,19 +4964,19 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
+        <v>317</v>
+      </c>
+      <c r="D27" t="s">
+        <v>299</v>
+      </c>
+      <c r="E27" t="s">
         <v>318</v>
       </c>
-      <c r="D27" t="s">
-        <v>300</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>319</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>320</v>
-      </c>
-      <c r="G27" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -4987,19 +4987,19 @@
         <v>7</v>
       </c>
       <c r="C28" t="s">
+        <v>321</v>
+      </c>
+      <c r="D28" t="s">
+        <v>299</v>
+      </c>
+      <c r="E28" t="s">
         <v>322</v>
       </c>
-      <c r="D28" t="s">
-        <v>300</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" t="s">
         <v>323</v>
-      </c>
-      <c r="F28" t="s">
-        <v>128</v>
-      </c>
-      <c r="G28" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5010,19 +5010,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>324</v>
+      </c>
+      <c r="D29" t="s">
+        <v>299</v>
+      </c>
+      <c r="E29" t="s">
         <v>325</v>
       </c>
-      <c r="D29" t="s">
-        <v>300</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
+        <v>319</v>
+      </c>
+      <c r="G29" t="s">
         <v>326</v>
-      </c>
-      <c r="F29" t="s">
-        <v>320</v>
-      </c>
-      <c r="G29" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5033,19 +5033,19 @@
         <v>9</v>
       </c>
       <c r="C30" t="s">
+        <v>327</v>
+      </c>
+      <c r="D30" t="s">
+        <v>299</v>
+      </c>
+      <c r="E30" t="s">
         <v>328</v>
       </c>
-      <c r="D30" t="s">
-        <v>300</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
+        <v>319</v>
+      </c>
+      <c r="G30" t="s">
         <v>329</v>
-      </c>
-      <c r="F30" t="s">
-        <v>320</v>
-      </c>
-      <c r="G30" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5056,19 +5056,19 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
+        <v>330</v>
+      </c>
+      <c r="D31" t="s">
+        <v>299</v>
+      </c>
+      <c r="E31" t="s">
         <v>331</v>
       </c>
-      <c r="D31" t="s">
-        <v>300</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>332</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>333</v>
-      </c>
-      <c r="G31" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -5079,19 +5079,19 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
+        <v>334</v>
+      </c>
+      <c r="D32" t="s">
+        <v>299</v>
+      </c>
+      <c r="E32" t="s">
         <v>335</v>
       </c>
-      <c r="D32" t="s">
-        <v>300</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>336</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>337</v>
-      </c>
-      <c r="G32" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -5102,19 +5102,19 @@
         <v>12</v>
       </c>
       <c r="C33" t="s">
+        <v>338</v>
+      </c>
+      <c r="D33" t="s">
+        <v>299</v>
+      </c>
+      <c r="E33" t="s">
         <v>339</v>
       </c>
-      <c r="D33" t="s">
-        <v>300</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
+        <v>332</v>
+      </c>
+      <c r="G33" t="s">
         <v>340</v>
-      </c>
-      <c r="F33" t="s">
-        <v>333</v>
-      </c>
-      <c r="G33" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5125,19 +5125,19 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
+        <v>341</v>
+      </c>
+      <c r="D34" t="s">
+        <v>299</v>
+      </c>
+      <c r="E34" t="s">
         <v>342</v>
       </c>
-      <c r="D34" t="s">
-        <v>300</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>332</v>
+      </c>
+      <c r="G34" t="s">
         <v>343</v>
-      </c>
-      <c r="F34" t="s">
-        <v>333</v>
-      </c>
-      <c r="G34" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -5148,10 +5148,10 @@
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D35" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -5162,10 +5162,10 @@
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -5176,10 +5176,10 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -5190,10 +5190,10 @@
         <v>17</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -5204,10 +5204,10 @@
         <v>18</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -5218,10 +5218,10 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -5232,10 +5232,10 @@
         <v>20</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -5246,19 +5246,19 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
+        <v>346</v>
+      </c>
+      <c r="D42" t="s">
         <v>347</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>348</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
+        <v>128</v>
+      </c>
+      <c r="G42" t="s">
         <v>349</v>
-      </c>
-      <c r="F42" t="s">
-        <v>128</v>
-      </c>
-      <c r="G42" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -5269,19 +5269,19 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
+        <v>350</v>
+      </c>
+      <c r="D43" t="s">
+        <v>347</v>
+      </c>
+      <c r="E43" t="s">
         <v>351</v>
       </c>
-      <c r="D43" t="s">
-        <v>348</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>352</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>353</v>
-      </c>
-      <c r="G43" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -5292,19 +5292,19 @@
         <v>3</v>
       </c>
       <c r="C44" t="s">
+        <v>354</v>
+      </c>
+      <c r="D44" t="s">
+        <v>347</v>
+      </c>
+      <c r="E44" t="s">
         <v>355</v>
       </c>
-      <c r="D44" t="s">
-        <v>348</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>356</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>357</v>
-      </c>
-      <c r="G44" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -5315,19 +5315,19 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
+        <v>358</v>
+      </c>
+      <c r="D45" t="s">
+        <v>347</v>
+      </c>
+      <c r="E45" t="s">
         <v>359</v>
       </c>
-      <c r="D45" t="s">
-        <v>348</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
+        <v>356</v>
+      </c>
+      <c r="G45" t="s">
         <v>360</v>
-      </c>
-      <c r="F45" t="s">
-        <v>357</v>
-      </c>
-      <c r="G45" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -5338,16 +5338,16 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
+        <v>361</v>
+      </c>
+      <c r="D46" t="s">
+        <v>347</v>
+      </c>
+      <c r="E46" t="s">
         <v>362</v>
       </c>
-      <c r="D46" t="s">
-        <v>348</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="G46" t="s">
         <v>363</v>
-      </c>
-      <c r="G46" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -5358,19 +5358,19 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
+        <v>364</v>
+      </c>
+      <c r="D47" t="s">
+        <v>347</v>
+      </c>
+      <c r="E47" t="s">
         <v>365</v>
       </c>
-      <c r="D47" t="s">
-        <v>348</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>366</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>367</v>
-      </c>
-      <c r="G47" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -5381,19 +5381,19 @@
         <v>7</v>
       </c>
       <c r="C48" t="s">
+        <v>368</v>
+      </c>
+      <c r="D48" t="s">
+        <v>347</v>
+      </c>
+      <c r="E48" t="s">
         <v>369</v>
       </c>
-      <c r="D48" t="s">
-        <v>348</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
+        <v>128</v>
+      </c>
+      <c r="G48" t="s">
         <v>370</v>
-      </c>
-      <c r="F48" t="s">
-        <v>128</v>
-      </c>
-      <c r="G48" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5404,19 +5404,19 @@
         <v>8</v>
       </c>
       <c r="C49" t="s">
+        <v>371</v>
+      </c>
+      <c r="D49" t="s">
+        <v>347</v>
+      </c>
+      <c r="E49" t="s">
         <v>372</v>
       </c>
-      <c r="D49" t="s">
-        <v>348</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
+        <v>128</v>
+      </c>
+      <c r="G49" t="s">
         <v>373</v>
-      </c>
-      <c r="F49" t="s">
-        <v>128</v>
-      </c>
-      <c r="G49" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -5427,19 +5427,19 @@
         <v>9</v>
       </c>
       <c r="C50" t="s">
+        <v>374</v>
+      </c>
+      <c r="D50" t="s">
+        <v>347</v>
+      </c>
+      <c r="E50" t="s">
         <v>375</v>
       </c>
-      <c r="D50" t="s">
-        <v>348</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
+        <v>128</v>
+      </c>
+      <c r="G50" t="s">
         <v>376</v>
-      </c>
-      <c r="F50" t="s">
-        <v>128</v>
-      </c>
-      <c r="G50" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -5450,19 +5450,19 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
+        <v>377</v>
+      </c>
+      <c r="D51" t="s">
+        <v>347</v>
+      </c>
+      <c r="E51" t="s">
         <v>378</v>
       </c>
-      <c r="D51" t="s">
-        <v>348</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>379</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>380</v>
-      </c>
-      <c r="G51" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -5473,19 +5473,19 @@
         <v>11</v>
       </c>
       <c r="C52" t="s">
+        <v>381</v>
+      </c>
+      <c r="D52" t="s">
+        <v>347</v>
+      </c>
+      <c r="E52" t="s">
         <v>382</v>
       </c>
-      <c r="D52" t="s">
-        <v>348</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
+        <v>284</v>
+      </c>
+      <c r="G52" t="s">
         <v>383</v>
-      </c>
-      <c r="F52" t="s">
-        <v>285</v>
-      </c>
-      <c r="G52" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -5496,13 +5496,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D53" t="s">
+        <v>347</v>
+      </c>
+      <c r="E53" t="s">
         <v>747</v>
-      </c>
-      <c r="D53" t="s">
-        <v>348</v>
-      </c>
-      <c r="E53" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5513,10 +5513,10 @@
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D54" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -5527,10 +5527,10 @@
         <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D55" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -5541,10 +5541,10 @@
         <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D56" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -5555,10 +5555,10 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -5569,10 +5569,10 @@
         <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -5583,10 +5583,10 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -5597,10 +5597,10 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -5611,10 +5611,10 @@
         <v>20</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -5628,16 +5628,16 @@
         <v>116</v>
       </c>
       <c r="D62" t="s">
+        <v>387</v>
+      </c>
+      <c r="E62" t="s">
         <v>388</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>389</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>390</v>
-      </c>
-      <c r="G62" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5651,16 +5651,16 @@
         <v>115</v>
       </c>
       <c r="D63" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E63" t="s">
+        <v>391</v>
+      </c>
+      <c r="F63" t="s">
+        <v>389</v>
+      </c>
+      <c r="G63" t="s">
         <v>392</v>
-      </c>
-      <c r="F63" t="s">
-        <v>390</v>
-      </c>
-      <c r="G63" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5674,16 +5674,16 @@
         <v>114</v>
       </c>
       <c r="D64" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E64" t="s">
+        <v>393</v>
+      </c>
+      <c r="F64" t="s">
+        <v>389</v>
+      </c>
+      <c r="G64" t="s">
         <v>394</v>
-      </c>
-      <c r="F64" t="s">
-        <v>390</v>
-      </c>
-      <c r="G64" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -5694,19 +5694,19 @@
         <v>4</v>
       </c>
       <c r="C65" t="s">
+        <v>395</v>
+      </c>
+      <c r="D65" t="s">
+        <v>387</v>
+      </c>
+      <c r="E65" t="s">
         <v>396</v>
       </c>
-      <c r="D65" t="s">
-        <v>388</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>397</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>398</v>
-      </c>
-      <c r="G65" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -5717,19 +5717,19 @@
         <v>5</v>
       </c>
       <c r="C66" t="s">
+        <v>399</v>
+      </c>
+      <c r="D66" t="s">
+        <v>387</v>
+      </c>
+      <c r="E66" t="s">
         <v>400</v>
       </c>
-      <c r="D66" t="s">
-        <v>388</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>401</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>402</v>
-      </c>
-      <c r="G66" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5740,16 +5740,16 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
+        <v>403</v>
+      </c>
+      <c r="D67" t="s">
+        <v>387</v>
+      </c>
+      <c r="E67" t="s">
         <v>404</v>
       </c>
-      <c r="D67" t="s">
-        <v>388</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="G67" t="s">
         <v>405</v>
-      </c>
-      <c r="G67" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -5760,19 +5760,19 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
+        <v>406</v>
+      </c>
+      <c r="D68" t="s">
+        <v>387</v>
+      </c>
+      <c r="E68" t="s">
         <v>407</v>
       </c>
-      <c r="D68" t="s">
-        <v>388</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
+        <v>389</v>
+      </c>
+      <c r="G68" t="s">
         <v>408</v>
-      </c>
-      <c r="F68" t="s">
-        <v>390</v>
-      </c>
-      <c r="G68" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5783,19 +5783,19 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
+        <v>409</v>
+      </c>
+      <c r="D69" t="s">
+        <v>387</v>
+      </c>
+      <c r="E69" t="s">
         <v>410</v>
       </c>
-      <c r="D69" t="s">
-        <v>388</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
+        <v>389</v>
+      </c>
+      <c r="G69" t="s">
         <v>411</v>
-      </c>
-      <c r="F69" t="s">
-        <v>390</v>
-      </c>
-      <c r="G69" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -5806,19 +5806,19 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
+        <v>412</v>
+      </c>
+      <c r="D70" t="s">
+        <v>387</v>
+      </c>
+      <c r="E70" t="s">
         <v>413</v>
       </c>
-      <c r="D70" t="s">
-        <v>388</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
+        <v>389</v>
+      </c>
+      <c r="G70" t="s">
         <v>414</v>
-      </c>
-      <c r="F70" t="s">
-        <v>390</v>
-      </c>
-      <c r="G70" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -5829,19 +5829,19 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
+        <v>415</v>
+      </c>
+      <c r="D71" t="s">
+        <v>387</v>
+      </c>
+      <c r="E71" t="s">
         <v>416</v>
       </c>
-      <c r="D71" t="s">
-        <v>388</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
+        <v>389</v>
+      </c>
+      <c r="G71" t="s">
         <v>417</v>
-      </c>
-      <c r="F71" t="s">
-        <v>390</v>
-      </c>
-      <c r="G71" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -5852,19 +5852,19 @@
         <v>11</v>
       </c>
       <c r="C72" t="s">
+        <v>418</v>
+      </c>
+      <c r="D72" t="s">
+        <v>387</v>
+      </c>
+      <c r="E72" t="s">
         <v>419</v>
       </c>
-      <c r="D72" t="s">
-        <v>388</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
+        <v>389</v>
+      </c>
+      <c r="G72" t="s">
         <v>420</v>
-      </c>
-      <c r="F72" t="s">
-        <v>390</v>
-      </c>
-      <c r="G72" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -5875,10 +5875,10 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D73" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5889,10 +5889,10 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D74" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -5903,10 +5903,10 @@
         <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D75" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -5917,10 +5917,10 @@
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D76" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -5931,10 +5931,10 @@
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -5945,10 +5945,10 @@
         <v>17</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5959,10 +5959,10 @@
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -5973,10 +5973,10 @@
         <v>19</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5987,10 +5987,10 @@
         <v>20</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -6001,19 +6001,19 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
+        <v>425</v>
+      </c>
+      <c r="D82" t="s">
         <v>426</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>427</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
+        <v>128</v>
+      </c>
+      <c r="G82" t="s">
         <v>428</v>
-      </c>
-      <c r="F82" t="s">
-        <v>128</v>
-      </c>
-      <c r="G82" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -6024,19 +6024,19 @@
         <v>2</v>
       </c>
       <c r="C83" t="s">
+        <v>429</v>
+      </c>
+      <c r="D83" t="s">
+        <v>426</v>
+      </c>
+      <c r="E83" t="s">
         <v>430</v>
       </c>
-      <c r="D83" t="s">
-        <v>427</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
+        <v>128</v>
+      </c>
+      <c r="G83" t="s">
         <v>431</v>
-      </c>
-      <c r="F83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G83" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -6047,19 +6047,19 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
+        <v>432</v>
+      </c>
+      <c r="D84" t="s">
+        <v>426</v>
+      </c>
+      <c r="E84" t="s">
         <v>433</v>
       </c>
-      <c r="D84" t="s">
-        <v>427</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
+        <v>128</v>
+      </c>
+      <c r="G84" t="s">
         <v>434</v>
-      </c>
-      <c r="F84" t="s">
-        <v>128</v>
-      </c>
-      <c r="G84" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -6070,19 +6070,19 @@
         <v>4</v>
       </c>
       <c r="C85" t="s">
+        <v>435</v>
+      </c>
+      <c r="D85" t="s">
+        <v>426</v>
+      </c>
+      <c r="E85" t="s">
         <v>436</v>
       </c>
-      <c r="D85" t="s">
-        <v>427</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
+        <v>128</v>
+      </c>
+      <c r="G85" t="s">
         <v>437</v>
-      </c>
-      <c r="F85" t="s">
-        <v>128</v>
-      </c>
-      <c r="G85" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -6093,19 +6093,19 @@
         <v>5</v>
       </c>
       <c r="C86" t="s">
+        <v>438</v>
+      </c>
+      <c r="D86" t="s">
+        <v>426</v>
+      </c>
+      <c r="E86" t="s">
         <v>439</v>
       </c>
-      <c r="D86" t="s">
-        <v>427</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
+        <v>128</v>
+      </c>
+      <c r="G86" t="s">
         <v>440</v>
-      </c>
-      <c r="F86" t="s">
-        <v>128</v>
-      </c>
-      <c r="G86" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -6116,19 +6116,19 @@
         <v>6</v>
       </c>
       <c r="C87" t="s">
+        <v>441</v>
+      </c>
+      <c r="D87" t="s">
+        <v>426</v>
+      </c>
+      <c r="E87" t="s">
         <v>442</v>
       </c>
-      <c r="D87" t="s">
-        <v>427</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
+        <v>128</v>
+      </c>
+      <c r="G87" t="s">
         <v>443</v>
-      </c>
-      <c r="F87" t="s">
-        <v>128</v>
-      </c>
-      <c r="G87" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -6139,19 +6139,19 @@
         <v>7</v>
       </c>
       <c r="C88" t="s">
+        <v>444</v>
+      </c>
+      <c r="D88" t="s">
+        <v>426</v>
+      </c>
+      <c r="E88" t="s">
         <v>445</v>
       </c>
-      <c r="D88" t="s">
-        <v>427</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
+        <v>128</v>
+      </c>
+      <c r="G88" t="s">
         <v>446</v>
-      </c>
-      <c r="F88" t="s">
-        <v>128</v>
-      </c>
-      <c r="G88" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -6162,19 +6162,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
+        <v>447</v>
+      </c>
+      <c r="D89" t="s">
+        <v>426</v>
+      </c>
+      <c r="E89" t="s">
         <v>448</v>
       </c>
-      <c r="D89" t="s">
-        <v>427</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
+        <v>128</v>
+      </c>
+      <c r="G89" t="s">
         <v>449</v>
-      </c>
-      <c r="F89" t="s">
-        <v>128</v>
-      </c>
-      <c r="G89" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -6185,19 +6185,19 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
+        <v>450</v>
+      </c>
+      <c r="D90" t="s">
+        <v>426</v>
+      </c>
+      <c r="E90" t="s">
         <v>451</v>
       </c>
-      <c r="D90" t="s">
-        <v>427</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
+        <v>128</v>
+      </c>
+      <c r="G90" t="s">
         <v>452</v>
-      </c>
-      <c r="F90" t="s">
-        <v>128</v>
-      </c>
-      <c r="G90" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6208,19 +6208,19 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
+        <v>453</v>
+      </c>
+      <c r="D91" t="s">
+        <v>426</v>
+      </c>
+      <c r="E91" t="s">
         <v>454</v>
       </c>
-      <c r="D91" t="s">
-        <v>427</v>
-      </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
+        <v>128</v>
+      </c>
+      <c r="G91" t="s">
         <v>455</v>
-      </c>
-      <c r="F91" t="s">
-        <v>128</v>
-      </c>
-      <c r="G91" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6231,19 +6231,19 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
+        <v>456</v>
+      </c>
+      <c r="D92" t="s">
+        <v>426</v>
+      </c>
+      <c r="E92" t="s">
         <v>457</v>
       </c>
-      <c r="D92" t="s">
-        <v>427</v>
-      </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
+        <v>128</v>
+      </c>
+      <c r="G92" t="s">
         <v>458</v>
-      </c>
-      <c r="F92" t="s">
-        <v>128</v>
-      </c>
-      <c r="G92" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6254,16 +6254,16 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
+        <v>459</v>
+      </c>
+      <c r="D93" t="s">
+        <v>426</v>
+      </c>
+      <c r="E93" t="s">
         <v>460</v>
       </c>
-      <c r="D93" t="s">
-        <v>427</v>
-      </c>
-      <c r="E93" t="s">
+      <c r="G93" t="s">
         <v>461</v>
-      </c>
-      <c r="G93" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6274,10 +6274,10 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D94" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6288,10 +6288,10 @@
         <v>14</v>
       </c>
       <c r="C95" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D95" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6302,10 +6302,10 @@
         <v>15</v>
       </c>
       <c r="C96" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D96" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6316,10 +6316,10 @@
         <v>16</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6330,10 +6330,10 @@
         <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -6344,10 +6344,10 @@
         <v>18</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -6358,10 +6358,10 @@
         <v>19</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -6372,10 +6372,10 @@
         <v>20</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -6386,19 +6386,19 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
+        <v>465</v>
+      </c>
+      <c r="D102" t="s">
         <v>466</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>467</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
+        <v>389</v>
+      </c>
+      <c r="G102" t="s">
         <v>468</v>
-      </c>
-      <c r="F102" t="s">
-        <v>390</v>
-      </c>
-      <c r="G102" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -6409,19 +6409,19 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
+        <v>469</v>
+      </c>
+      <c r="D103" t="s">
+        <v>466</v>
+      </c>
+      <c r="E103" t="s">
         <v>470</v>
       </c>
-      <c r="D103" t="s">
-        <v>467</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
+        <v>389</v>
+      </c>
+      <c r="G103" t="s">
         <v>471</v>
-      </c>
-      <c r="F103" t="s">
-        <v>390</v>
-      </c>
-      <c r="G103" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -6432,19 +6432,19 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D104" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E104" t="s">
+        <v>472</v>
+      </c>
+      <c r="F104" t="s">
         <v>473</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>474</v>
-      </c>
-      <c r="G104" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6455,19 +6455,19 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
+        <v>475</v>
+      </c>
+      <c r="D105" t="s">
+        <v>466</v>
+      </c>
+      <c r="E105" t="s">
         <v>476</v>
       </c>
-      <c r="D105" t="s">
-        <v>467</v>
-      </c>
-      <c r="E105" t="s">
-        <v>477</v>
-      </c>
       <c r="F105" t="s">
         <v>128</v>
       </c>
       <c r="G105" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6478,19 +6478,19 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
+        <v>477</v>
+      </c>
+      <c r="D106" t="s">
+        <v>466</v>
+      </c>
+      <c r="E106" t="s">
         <v>478</v>
       </c>
-      <c r="D106" t="s">
-        <v>467</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>479</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>480</v>
-      </c>
-      <c r="G106" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6501,19 +6501,19 @@
         <v>6</v>
       </c>
       <c r="C107" t="s">
+        <v>481</v>
+      </c>
+      <c r="D107" t="s">
+        <v>466</v>
+      </c>
+      <c r="E107" t="s">
         <v>482</v>
       </c>
-      <c r="D107" t="s">
-        <v>467</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>483</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>484</v>
-      </c>
-      <c r="G107" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6524,19 +6524,19 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
+        <v>485</v>
+      </c>
+      <c r="D108" t="s">
+        <v>466</v>
+      </c>
+      <c r="E108" t="s">
         <v>486</v>
       </c>
-      <c r="D108" t="s">
-        <v>467</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
+        <v>483</v>
+      </c>
+      <c r="G108" t="s">
         <v>487</v>
-      </c>
-      <c r="F108" t="s">
-        <v>484</v>
-      </c>
-      <c r="G108" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6547,19 +6547,19 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
+        <v>488</v>
+      </c>
+      <c r="D109" t="s">
+        <v>466</v>
+      </c>
+      <c r="E109" t="s">
         <v>489</v>
       </c>
-      <c r="D109" t="s">
-        <v>467</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
+        <v>483</v>
+      </c>
+      <c r="G109" t="s">
         <v>490</v>
-      </c>
-      <c r="F109" t="s">
-        <v>484</v>
-      </c>
-      <c r="G109" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6570,19 +6570,19 @@
         <v>9</v>
       </c>
       <c r="C110" t="s">
+        <v>491</v>
+      </c>
+      <c r="D110" t="s">
+        <v>466</v>
+      </c>
+      <c r="E110" t="s">
         <v>492</v>
       </c>
-      <c r="D110" t="s">
-        <v>467</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
+        <v>128</v>
+      </c>
+      <c r="G110" t="s">
         <v>493</v>
-      </c>
-      <c r="F110" t="s">
-        <v>128</v>
-      </c>
-      <c r="G110" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1">
@@ -6593,19 +6593,19 @@
         <v>10</v>
       </c>
       <c r="C111" t="s">
+        <v>494</v>
+      </c>
+      <c r="D111" t="s">
+        <v>466</v>
+      </c>
+      <c r="E111" t="s">
         <v>495</v>
       </c>
-      <c r="D111" t="s">
-        <v>467</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
+        <v>128</v>
+      </c>
+      <c r="G111" t="s">
         <v>496</v>
-      </c>
-      <c r="F111" t="s">
-        <v>128</v>
-      </c>
-      <c r="G111" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6616,19 +6616,19 @@
         <v>11</v>
       </c>
       <c r="C112" t="s">
+        <v>497</v>
+      </c>
+      <c r="D112" t="s">
+        <v>466</v>
+      </c>
+      <c r="E112" t="s">
         <v>498</v>
       </c>
-      <c r="D112" t="s">
-        <v>467</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
+        <v>128</v>
+      </c>
+      <c r="G112" t="s">
         <v>499</v>
-      </c>
-      <c r="F112" t="s">
-        <v>128</v>
-      </c>
-      <c r="G112" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6639,19 +6639,19 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
+        <v>500</v>
+      </c>
+      <c r="D113" t="s">
+        <v>466</v>
+      </c>
+      <c r="E113" t="s">
         <v>501</v>
       </c>
-      <c r="D113" t="s">
-        <v>467</v>
-      </c>
-      <c r="E113" t="s">
-        <v>502</v>
-      </c>
       <c r="F113" t="s">
         <v>128</v>
       </c>
       <c r="G113" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6662,19 +6662,19 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
+        <v>502</v>
+      </c>
+      <c r="D114" t="s">
+        <v>466</v>
+      </c>
+      <c r="E114" t="s">
         <v>503</v>
       </c>
-      <c r="D114" t="s">
-        <v>467</v>
-      </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
+        <v>389</v>
+      </c>
+      <c r="G114" t="s">
         <v>504</v>
-      </c>
-      <c r="F114" t="s">
-        <v>390</v>
-      </c>
-      <c r="G114" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -6685,10 +6685,10 @@
         <v>14</v>
       </c>
       <c r="C115" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D115" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6699,10 +6699,10 @@
         <v>15</v>
       </c>
       <c r="C116" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D116" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -6713,10 +6713,10 @@
         <v>16</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -6727,10 +6727,10 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -6741,10 +6741,10 @@
         <v>18</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -6755,10 +6755,10 @@
         <v>19</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>20</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6783,19 +6783,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
+        <v>507</v>
+      </c>
+      <c r="D122" t="s">
         <v>508</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>509</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>510</v>
       </c>
-      <c r="F122" t="s">
-        <v>511</v>
-      </c>
       <c r="G122" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6806,19 +6806,19 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
+        <v>511</v>
+      </c>
+      <c r="D123" t="s">
+        <v>508</v>
+      </c>
+      <c r="E123" t="s">
         <v>512</v>
       </c>
-      <c r="D123" t="s">
-        <v>509</v>
-      </c>
-      <c r="E123" t="s">
-        <v>513</v>
-      </c>
       <c r="F123" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G123" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6829,19 +6829,19 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
+        <v>513</v>
+      </c>
+      <c r="D124" t="s">
+        <v>508</v>
+      </c>
+      <c r="E124" t="s">
         <v>514</v>
       </c>
-      <c r="D124" t="s">
-        <v>509</v>
-      </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>515</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>516</v>
-      </c>
-      <c r="G124" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -6852,19 +6852,19 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
+        <v>517</v>
+      </c>
+      <c r="D125" t="s">
+        <v>508</v>
+      </c>
+      <c r="E125" t="s">
         <v>518</v>
       </c>
-      <c r="D125" t="s">
-        <v>509</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>519</v>
       </c>
-      <c r="F125" t="s">
+      <c r="G125" t="s">
         <v>520</v>
-      </c>
-      <c r="G125" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6875,19 +6875,19 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
+        <v>521</v>
+      </c>
+      <c r="D126" t="s">
+        <v>508</v>
+      </c>
+      <c r="E126" t="s">
         <v>522</v>
       </c>
-      <c r="D126" t="s">
-        <v>509</v>
-      </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
+        <v>128</v>
+      </c>
+      <c r="G126" t="s">
         <v>523</v>
-      </c>
-      <c r="F126" t="s">
-        <v>128</v>
-      </c>
-      <c r="G126" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -6898,19 +6898,19 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
+        <v>524</v>
+      </c>
+      <c r="D127" t="s">
+        <v>508</v>
+      </c>
+      <c r="E127" t="s">
         <v>525</v>
       </c>
-      <c r="D127" t="s">
-        <v>509</v>
-      </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
+        <v>519</v>
+      </c>
+      <c r="G127" t="s">
         <v>526</v>
-      </c>
-      <c r="F127" t="s">
-        <v>520</v>
-      </c>
-      <c r="G127" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -6921,19 +6921,19 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
+        <v>527</v>
+      </c>
+      <c r="D128" t="s">
+        <v>508</v>
+      </c>
+      <c r="E128" t="s">
         <v>528</v>
       </c>
-      <c r="D128" t="s">
-        <v>509</v>
-      </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
+        <v>519</v>
+      </c>
+      <c r="G128" t="s">
         <v>529</v>
-      </c>
-      <c r="F128" t="s">
-        <v>520</v>
-      </c>
-      <c r="G128" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -6944,19 +6944,19 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>530</v>
+      </c>
+      <c r="D129" t="s">
+        <v>508</v>
+      </c>
+      <c r="E129" t="s">
         <v>531</v>
       </c>
-      <c r="D129" t="s">
-        <v>509</v>
-      </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>532</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
         <v>533</v>
-      </c>
-      <c r="G129" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6967,19 +6967,19 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
+        <v>534</v>
+      </c>
+      <c r="D130" t="s">
+        <v>508</v>
+      </c>
+      <c r="E130" t="s">
         <v>535</v>
       </c>
-      <c r="D130" t="s">
-        <v>509</v>
-      </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
+        <v>532</v>
+      </c>
+      <c r="G130" t="s">
         <v>536</v>
-      </c>
-      <c r="F130" t="s">
-        <v>533</v>
-      </c>
-      <c r="G130" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6990,19 +6990,19 @@
         <v>10</v>
       </c>
       <c r="C131" t="s">
+        <v>537</v>
+      </c>
+      <c r="D131" t="s">
+        <v>508</v>
+      </c>
+      <c r="E131" t="s">
         <v>538</v>
       </c>
-      <c r="D131" t="s">
-        <v>509</v>
-      </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
+        <v>515</v>
+      </c>
+      <c r="G131" t="s">
         <v>539</v>
-      </c>
-      <c r="F131" t="s">
-        <v>516</v>
-      </c>
-      <c r="G131" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -7013,19 +7013,19 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
+        <v>540</v>
+      </c>
+      <c r="D132" t="s">
+        <v>508</v>
+      </c>
+      <c r="E132" t="s">
         <v>541</v>
       </c>
-      <c r="D132" t="s">
-        <v>509</v>
-      </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
+        <v>515</v>
+      </c>
+      <c r="G132" t="s">
         <v>542</v>
-      </c>
-      <c r="F132" t="s">
-        <v>516</v>
-      </c>
-      <c r="G132" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -7036,19 +7036,19 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
+        <v>543</v>
+      </c>
+      <c r="D133" t="s">
+        <v>508</v>
+      </c>
+      <c r="E133" t="s">
         <v>544</v>
       </c>
-      <c r="D133" t="s">
-        <v>509</v>
-      </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
+        <v>519</v>
+      </c>
+      <c r="G133" t="s">
         <v>545</v>
-      </c>
-      <c r="F133" t="s">
-        <v>520</v>
-      </c>
-      <c r="G133" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -7059,19 +7059,19 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
+        <v>546</v>
+      </c>
+      <c r="D134" t="s">
+        <v>508</v>
+      </c>
+      <c r="E134" t="s">
         <v>547</v>
       </c>
-      <c r="D134" t="s">
-        <v>509</v>
-      </c>
-      <c r="E134" t="s">
+      <c r="F134" t="s">
+        <v>519</v>
+      </c>
+      <c r="G134" t="s">
         <v>548</v>
-      </c>
-      <c r="F134" t="s">
-        <v>520</v>
-      </c>
-      <c r="G134" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -7082,10 +7082,10 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D135" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -7096,10 +7096,10 @@
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D136" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7110,10 +7110,10 @@
         <v>16</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7124,10 +7124,10 @@
         <v>17</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -7138,10 +7138,10 @@
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -7152,10 +7152,10 @@
         <v>19</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -7166,10 +7166,10 @@
         <v>20</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -7180,19 +7180,19 @@
         <v>1</v>
       </c>
       <c r="C142" t="s">
+        <v>551</v>
+      </c>
+      <c r="D142" t="s">
         <v>552</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>553</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>554</v>
       </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>555</v>
-      </c>
-      <c r="G142" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7203,19 +7203,19 @@
         <v>2</v>
       </c>
       <c r="C143" t="s">
+        <v>556</v>
+      </c>
+      <c r="D143" t="s">
+        <v>552</v>
+      </c>
+      <c r="E143" t="s">
         <v>557</v>
       </c>
-      <c r="D143" t="s">
-        <v>553</v>
-      </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>558</v>
       </c>
-      <c r="F143" t="s">
-        <v>559</v>
-      </c>
       <c r="G143" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7226,19 +7226,19 @@
         <v>3</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D144" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E144" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F144" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G144" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -7249,10 +7249,10 @@
         <v>4</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D145" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -7263,10 +7263,10 @@
         <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D146" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -7277,10 +7277,10 @@
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D147" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -7291,13 +7291,13 @@
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D148" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E148" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -7308,13 +7308,13 @@
         <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D149" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E149" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -7325,13 +7325,13 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D150" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E150" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -7342,13 +7342,13 @@
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D151" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E151" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -7359,10 +7359,10 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D152" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -7373,10 +7373,10 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D153" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -7387,10 +7387,10 @@
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D154" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -7401,10 +7401,10 @@
         <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D155" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -7415,10 +7415,10 @@
         <v>15</v>
       </c>
       <c r="C156" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D156" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -7429,10 +7429,10 @@
         <v>16</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -7443,10 +7443,10 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -7457,10 +7457,10 @@
         <v>18</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -7471,10 +7471,10 @@
         <v>19</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -7485,10 +7485,10 @@
         <v>20</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7499,19 +7499,19 @@
         <v>1</v>
       </c>
       <c r="C162" t="s">
+        <v>561</v>
+      </c>
+      <c r="D162" t="s">
         <v>562</v>
       </c>
-      <c r="D162" t="s">
+      <c r="E162" t="s">
         <v>563</v>
       </c>
-      <c r="E162" t="s">
+      <c r="F162" t="s">
         <v>564</v>
       </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>565</v>
-      </c>
-      <c r="G162" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7522,19 +7522,19 @@
         <v>2</v>
       </c>
       <c r="C163" t="s">
+        <v>566</v>
+      </c>
+      <c r="D163" t="s">
+        <v>562</v>
+      </c>
+      <c r="E163" t="s">
         <v>567</v>
       </c>
-      <c r="D163" t="s">
-        <v>563</v>
-      </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
+        <v>564</v>
+      </c>
+      <c r="G163" t="s">
         <v>568</v>
-      </c>
-      <c r="F163" t="s">
-        <v>565</v>
-      </c>
-      <c r="G163" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7545,16 +7545,16 @@
         <v>3</v>
       </c>
       <c r="C164" t="s">
+        <v>569</v>
+      </c>
+      <c r="D164" t="s">
+        <v>562</v>
+      </c>
+      <c r="E164" t="s">
         <v>570</v>
       </c>
-      <c r="D164" t="s">
-        <v>563</v>
-      </c>
-      <c r="E164" t="s">
-        <v>571</v>
-      </c>
       <c r="G164" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7565,16 +7565,16 @@
         <v>4</v>
       </c>
       <c r="C165" t="s">
+        <v>571</v>
+      </c>
+      <c r="D165" t="s">
+        <v>562</v>
+      </c>
+      <c r="E165" t="s">
         <v>572</v>
       </c>
-      <c r="D165" t="s">
-        <v>563</v>
-      </c>
-      <c r="E165" t="s">
-        <v>573</v>
-      </c>
       <c r="G165" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7585,19 +7585,19 @@
         <v>5</v>
       </c>
       <c r="C166" t="s">
+        <v>573</v>
+      </c>
+      <c r="D166" t="s">
+        <v>562</v>
+      </c>
+      <c r="E166" t="s">
         <v>574</v>
       </c>
-      <c r="D166" t="s">
-        <v>563</v>
-      </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
+        <v>287</v>
+      </c>
+      <c r="G166" t="s">
         <v>575</v>
-      </c>
-      <c r="F166" t="s">
-        <v>288</v>
-      </c>
-      <c r="G166" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7608,10 +7608,10 @@
         <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D167" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7622,10 +7622,10 @@
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D168" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7636,10 +7636,10 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D169" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7650,10 +7650,10 @@
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D170" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7664,10 +7664,10 @@
         <v>10</v>
       </c>
       <c r="C171" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D171" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7678,10 +7678,10 @@
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D172" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7692,10 +7692,10 @@
         <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D173" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7706,10 +7706,10 @@
         <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D174" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7720,10 +7720,10 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D175" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7734,10 +7734,10 @@
         <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D176" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7748,10 +7748,10 @@
         <v>16</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -7762,10 +7762,10 @@
         <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -7776,10 +7776,10 @@
         <v>18</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -7790,10 +7790,10 @@
         <v>19</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -7804,10 +7804,10 @@
         <v>20</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -7818,19 +7818,19 @@
         <v>1</v>
       </c>
       <c r="C182" t="s">
+        <v>586</v>
+      </c>
+      <c r="D182" t="s">
         <v>587</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>588</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" t="s">
+        <v>128</v>
+      </c>
+      <c r="G182" t="s">
         <v>589</v>
-      </c>
-      <c r="F182" t="s">
-        <v>128</v>
-      </c>
-      <c r="G182" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -7841,19 +7841,19 @@
         <v>2</v>
       </c>
       <c r="C183" t="s">
+        <v>590</v>
+      </c>
+      <c r="D183" t="s">
+        <v>587</v>
+      </c>
+      <c r="E183" t="s">
         <v>591</v>
       </c>
-      <c r="D183" t="s">
-        <v>588</v>
-      </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
+        <v>128</v>
+      </c>
+      <c r="G183" t="s">
         <v>592</v>
-      </c>
-      <c r="F183" t="s">
-        <v>128</v>
-      </c>
-      <c r="G183" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -7864,19 +7864,19 @@
         <v>3</v>
       </c>
       <c r="C184" t="s">
+        <v>593</v>
+      </c>
+      <c r="D184" t="s">
+        <v>587</v>
+      </c>
+      <c r="E184" t="s">
         <v>594</v>
       </c>
-      <c r="D184" t="s">
-        <v>588</v>
-      </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
+        <v>128</v>
+      </c>
+      <c r="G184" t="s">
         <v>595</v>
-      </c>
-      <c r="F184" t="s">
-        <v>128</v>
-      </c>
-      <c r="G184" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -7887,19 +7887,19 @@
         <v>4</v>
       </c>
       <c r="C185" t="s">
+        <v>596</v>
+      </c>
+      <c r="D185" t="s">
+        <v>587</v>
+      </c>
+      <c r="E185" t="s">
         <v>597</v>
       </c>
-      <c r="D185" t="s">
-        <v>588</v>
-      </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
+        <v>128</v>
+      </c>
+      <c r="G185" t="s">
         <v>598</v>
-      </c>
-      <c r="F185" t="s">
-        <v>128</v>
-      </c>
-      <c r="G185" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -7910,19 +7910,19 @@
         <v>5</v>
       </c>
       <c r="C186" t="s">
+        <v>599</v>
+      </c>
+      <c r="D186" t="s">
+        <v>587</v>
+      </c>
+      <c r="E186" t="s">
         <v>600</v>
       </c>
-      <c r="D186" t="s">
-        <v>588</v>
-      </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
+        <v>128</v>
+      </c>
+      <c r="G186" t="s">
         <v>601</v>
-      </c>
-      <c r="F186" t="s">
-        <v>128</v>
-      </c>
-      <c r="G186" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -7933,19 +7933,19 @@
         <v>6</v>
       </c>
       <c r="C187" t="s">
+        <v>602</v>
+      </c>
+      <c r="D187" t="s">
+        <v>587</v>
+      </c>
+      <c r="E187" t="s">
         <v>603</v>
       </c>
-      <c r="D187" t="s">
-        <v>588</v>
-      </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
+        <v>128</v>
+      </c>
+      <c r="G187" t="s">
         <v>604</v>
-      </c>
-      <c r="F187" t="s">
-        <v>128</v>
-      </c>
-      <c r="G187" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7956,19 +7956,19 @@
         <v>7</v>
       </c>
       <c r="C188" t="s">
+        <v>605</v>
+      </c>
+      <c r="D188" t="s">
+        <v>587</v>
+      </c>
+      <c r="E188" t="s">
         <v>606</v>
       </c>
-      <c r="D188" t="s">
-        <v>588</v>
-      </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
+        <v>366</v>
+      </c>
+      <c r="G188" t="s">
         <v>607</v>
-      </c>
-      <c r="F188" t="s">
-        <v>367</v>
-      </c>
-      <c r="G188" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7979,19 +7979,19 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
+        <v>608</v>
+      </c>
+      <c r="D189" t="s">
+        <v>587</v>
+      </c>
+      <c r="E189" t="s">
         <v>609</v>
       </c>
-      <c r="D189" t="s">
-        <v>588</v>
-      </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
+        <v>366</v>
+      </c>
+      <c r="G189" t="s">
         <v>610</v>
-      </c>
-      <c r="F189" t="s">
-        <v>367</v>
-      </c>
-      <c r="G189" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -8002,19 +8002,19 @@
         <v>9</v>
       </c>
       <c r="C190" t="s">
+        <v>611</v>
+      </c>
+      <c r="D190" t="s">
+        <v>587</v>
+      </c>
+      <c r="E190" t="s">
         <v>612</v>
       </c>
-      <c r="D190" t="s">
-        <v>588</v>
-      </c>
-      <c r="E190" t="s">
+      <c r="F190" t="s">
+        <v>366</v>
+      </c>
+      <c r="G190" t="s">
         <v>613</v>
-      </c>
-      <c r="F190" t="s">
-        <v>367</v>
-      </c>
-      <c r="G190" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -8025,19 +8025,19 @@
         <v>10</v>
       </c>
       <c r="C191" t="s">
+        <v>614</v>
+      </c>
+      <c r="D191" t="s">
+        <v>587</v>
+      </c>
+      <c r="E191" t="s">
         <v>615</v>
       </c>
-      <c r="D191" t="s">
-        <v>588</v>
-      </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
+        <v>366</v>
+      </c>
+      <c r="G191" t="s">
         <v>616</v>
-      </c>
-      <c r="F191" t="s">
-        <v>367</v>
-      </c>
-      <c r="G191" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -8048,19 +8048,19 @@
         <v>11</v>
       </c>
       <c r="C192" t="s">
+        <v>617</v>
+      </c>
+      <c r="D192" t="s">
+        <v>587</v>
+      </c>
+      <c r="E192" t="s">
         <v>618</v>
       </c>
-      <c r="D192" t="s">
-        <v>588</v>
-      </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
+        <v>366</v>
+      </c>
+      <c r="G192" t="s">
         <v>619</v>
-      </c>
-      <c r="F192" t="s">
-        <v>367</v>
-      </c>
-      <c r="G192" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -8071,19 +8071,19 @@
         <v>12</v>
       </c>
       <c r="C193" t="s">
+        <v>620</v>
+      </c>
+      <c r="D193" t="s">
+        <v>587</v>
+      </c>
+      <c r="E193" t="s">
         <v>621</v>
       </c>
-      <c r="D193" t="s">
-        <v>588</v>
-      </c>
-      <c r="E193" t="s">
+      <c r="F193" t="s">
+        <v>366</v>
+      </c>
+      <c r="G193" t="s">
         <v>622</v>
-      </c>
-      <c r="F193" t="s">
-        <v>367</v>
-      </c>
-      <c r="G193" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -8094,19 +8094,19 @@
         <v>13</v>
       </c>
       <c r="C194" t="s">
+        <v>623</v>
+      </c>
+      <c r="D194" t="s">
+        <v>587</v>
+      </c>
+      <c r="E194" t="s">
         <v>624</v>
       </c>
-      <c r="D194" t="s">
-        <v>588</v>
-      </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
+        <v>366</v>
+      </c>
+      <c r="G194" t="s">
         <v>625</v>
-      </c>
-      <c r="F194" t="s">
-        <v>367</v>
-      </c>
-      <c r="G194" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -8117,19 +8117,19 @@
         <v>14</v>
       </c>
       <c r="C195" t="s">
+        <v>626</v>
+      </c>
+      <c r="D195" t="s">
+        <v>587</v>
+      </c>
+      <c r="E195" t="s">
         <v>627</v>
       </c>
-      <c r="D195" t="s">
-        <v>588</v>
-      </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
+        <v>366</v>
+      </c>
+      <c r="G195" t="s">
         <v>628</v>
-      </c>
-      <c r="F195" t="s">
-        <v>367</v>
-      </c>
-      <c r="G195" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -8140,10 +8140,10 @@
         <v>15</v>
       </c>
       <c r="C196" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D196" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -8154,10 +8154,10 @@
         <v>16</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -8168,10 +8168,10 @@
         <v>17</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -8182,10 +8182,10 @@
         <v>18</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -8196,10 +8196,10 @@
         <v>19</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -8210,10 +8210,10 @@
         <v>20</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -8224,16 +8224,16 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D202" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E202" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F202" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -8244,16 +8244,16 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D203" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E203" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F203" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -8264,16 +8264,16 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D204" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E204" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="F204" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -8284,16 +8284,16 @@
         <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D205" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E205" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F205" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -8304,16 +8304,16 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D206" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E206" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F206" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -8324,16 +8324,16 @@
         <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D207" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E207" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F207" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -8344,16 +8344,16 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D208" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E208" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F208" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -8364,16 +8364,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D209" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E209" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F209" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -8384,16 +8384,16 @@
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D210" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E210" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F210" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -8404,16 +8404,16 @@
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D211" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E211" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="F211" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -8424,16 +8424,16 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D212" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E212" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F212" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -8444,16 +8444,16 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D213" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E213" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F213" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -8464,16 +8464,16 @@
         <v>13</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D214" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E214" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F214" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -8484,16 +8484,16 @@
         <v>14</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D215" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E215" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F215" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8504,16 +8504,16 @@
         <v>15</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D216" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E216" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F216" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -8524,16 +8524,16 @@
         <v>16</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E217" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F217" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -8544,13 +8544,13 @@
         <v>17</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E218" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8561,13 +8561,13 @@
         <v>18</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E219" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>138</v>
@@ -8581,10 +8581,10 @@
         <v>19</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8595,10 +8595,10 @@
         <v>20</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -8624,16 +8624,16 @@
     <row r="1" spans="1:5">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8654,10 +8654,10 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8671,10 +8671,10 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8688,10 +8688,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8705,10 +8705,10 @@
         <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8722,10 +8722,10 @@
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8739,10 +8739,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8756,10 +8756,10 @@
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8773,10 +8773,10 @@
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8790,10 +8790,10 @@
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8807,10 +8807,10 @@
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8824,10 +8824,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8841,10 +8841,10 @@
         <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8858,10 +8858,10 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8875,10 +8875,10 @@
         <v>19</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8892,10 +8892,10 @@
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8909,10 +8909,10 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8926,10 +8926,10 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8943,10 +8943,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8960,10 +8960,10 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8977,10 +8977,10 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8994,10 +8994,10 @@
         <v>16</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9011,10 +9011,10 @@
         <v>17</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9028,10 +9028,10 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9045,10 +9045,10 @@
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -9062,10 +9062,10 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9079,10 +9079,10 @@
         <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9096,10 +9096,10 @@
         <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9113,10 +9113,10 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9130,10 +9130,10 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9147,10 +9147,10 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9164,10 +9164,10 @@
         <v>16</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9181,10 +9181,10 @@
         <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9198,10 +9198,10 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9215,10 +9215,10 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9232,10 +9232,10 @@
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9249,10 +9249,10 @@
         <v>16</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9266,10 +9266,10 @@
         <v>17</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -9283,10 +9283,10 @@
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -9300,10 +9300,10 @@
         <v>19</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -9317,10 +9317,10 @@
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -9334,10 +9334,10 @@
         <v>16</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9351,10 +9351,10 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9368,10 +9368,10 @@
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9385,10 +9385,10 @@
         <v>19</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -9402,10 +9402,10 @@
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -9419,10 +9419,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -9436,10 +9436,10 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -9453,10 +9453,10 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -9470,10 +9470,10 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -9487,10 +9487,10 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -9504,10 +9504,10 @@
         <v>16</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9521,10 +9521,10 @@
         <v>17</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9538,10 +9538,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9555,10 +9555,10 @@
         <v>19</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9572,15 +9572,15 @@
         <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2941141-42E1-412B-9197-175FE96C2BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9693BDE3-8A05-461A-A01B-9F66E5E1E7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57510" yWindow="75" windowWidth="19350" windowHeight="20880" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -219,12 +219,6 @@
     <t>aH</t>
   </si>
   <si>
-    <t>nHB</t>
-  </si>
-  <si>
-    <t>nHC</t>
-  </si>
-  <si>
     <t>aV</t>
   </si>
   <si>
@@ -243,33 +237,9 @@
     <t>aK</t>
   </si>
   <si>
-    <t>nKB</t>
-  </si>
-  <si>
-    <t>nKH</t>
-  </si>
-  <si>
-    <t>nKC</t>
-  </si>
-  <si>
-    <t>nKrh</t>
-  </si>
-  <si>
     <t>aHL</t>
   </si>
   <si>
-    <t>nHLB</t>
-  </si>
-  <si>
-    <t>nHLL</t>
-  </si>
-  <si>
-    <t>nHLC</t>
-  </si>
-  <si>
-    <t>nHLrh</t>
-  </si>
-  <si>
     <t>Dscale0</t>
   </si>
   <si>
@@ -2308,6 +2278,36 @@
   </si>
   <si>
     <t xml:space="preserve">Moisture ratio deficit for fsw = 0.5 </t>
+  </si>
+  <si>
+    <t>nH1</t>
+  </si>
+  <si>
+    <t>nH2</t>
+  </si>
+  <si>
+    <t>nK1</t>
+  </si>
+  <si>
+    <t>nK2</t>
+  </si>
+  <si>
+    <t>nK3</t>
+  </si>
+  <si>
+    <t>nK4</t>
+  </si>
+  <si>
+    <t>nHL1</t>
+  </si>
+  <si>
+    <t>nHL2</t>
+  </si>
+  <si>
+    <t>nHL3</t>
+  </si>
+  <si>
+    <t>nHL4</t>
   </si>
 </sst>
 </file>
@@ -2717,16 +2717,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2748,10 +2748,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D3">
         <v>0.15</v>
@@ -2762,10 +2762,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D4">
         <v>9.5000000000000001E-2</v>
@@ -2776,10 +2776,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D5">
         <v>2.4</v>
@@ -2790,10 +2790,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D6">
         <v>0.8</v>
@@ -2804,10 +2804,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D7">
         <v>0.25</v>
@@ -2818,10 +2818,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D8">
         <v>2.7E-2</v>
@@ -2832,10 +2832,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D9">
         <v>1E-3</v>
@@ -2846,10 +2846,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C10" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D10">
         <v>12</v>
@@ -2860,10 +2860,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D11">
         <v>1.4999999999999999E-2</v>
@@ -2874,7 +2874,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -2888,7 +2888,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -2902,10 +2902,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D14">
         <v>8.5</v>
@@ -2916,10 +2916,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D15">
         <v>16</v>
@@ -2930,10 +2930,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D16">
         <v>40</v>
@@ -2944,10 +2944,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C17" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -2958,10 +2958,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D18">
         <v>0.7</v>
@@ -2972,10 +2972,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D19">
         <v>9</v>
@@ -2986,10 +2986,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D20">
         <v>1.4</v>
@@ -3000,10 +3000,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D21">
         <v>0.7</v>
@@ -3014,10 +3014,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -3028,10 +3028,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3042,10 +3042,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -3056,10 +3056,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C25" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D25">
         <v>50</v>
@@ -3070,10 +3070,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -3084,10 +3084,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D27">
         <v>0.95</v>
@@ -3098,10 +3098,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -3112,10 +3112,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C29" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -3126,10 +3126,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="C30" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -3140,10 +3140,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -3154,10 +3154,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C32" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D32">
         <v>300</v>
@@ -3168,10 +3168,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D33">
         <v>1.5</v>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -3191,10 +3191,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -3203,10 +3203,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -3215,10 +3215,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -3239,10 +3239,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -3254,10 +3254,10 @@
         <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -3268,10 +3268,10 @@
         <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D41">
         <v>0.2</v>
@@ -3282,10 +3282,10 @@
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D42">
         <v>0.2</v>
@@ -3296,10 +3296,10 @@
         <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C43" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D43">
         <v>11</v>
@@ -3310,10 +3310,10 @@
         <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C44" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -3324,10 +3324,10 @@
         <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D45">
         <v>2.5</v>
@@ -3338,10 +3338,10 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C46" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D46">
         <v>0.5</v>
@@ -3349,10 +3349,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -3364,10 +3364,10 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C48" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -3378,10 +3378,10 @@
         <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C49" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D49">
         <v>0.15</v>
@@ -3392,10 +3392,10 @@
         <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C50" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -3406,10 +3406,10 @@
         <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D51">
         <v>5</v>
@@ -3420,10 +3420,10 @@
         <v>44</v>
       </c>
       <c r="B52" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C52" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D52">
         <v>0.06</v>
@@ -3434,10 +3434,10 @@
         <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D53">
         <v>0.47</v>
@@ -3448,10 +3448,10 @@
         <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C54" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3462,10 +3462,10 @@
         <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C55" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D55">
         <v>0.02</v>
@@ -3476,10 +3476,10 @@
         <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C56" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D56">
         <v>3.33</v>
@@ -3490,10 +3490,10 @@
         <v>49</v>
       </c>
       <c r="B57" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C57" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D57">
         <v>0.05</v>
@@ -3504,10 +3504,10 @@
         <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C58" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D58">
         <v>0.2</v>
@@ -3518,10 +3518,10 @@
         <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C59" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D59">
         <v>0.66</v>
@@ -3532,10 +3532,10 @@
         <v>52</v>
       </c>
       <c r="B60" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C60" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -3546,10 +3546,10 @@
         <v>53</v>
       </c>
       <c r="B61" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C61" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D61">
         <v>4.4000000000000004</v>
@@ -3560,10 +3560,10 @@
         <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C62" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D62">
         <v>27</v>
@@ -3574,10 +3574,10 @@
         <v>55</v>
       </c>
       <c r="B63" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C63" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D63">
         <v>0.75</v>
@@ -3588,10 +3588,10 @@
         <v>56</v>
       </c>
       <c r="B64" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="C64" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D64">
         <v>0.15</v>
@@ -3602,10 +3602,10 @@
         <v>57</v>
       </c>
       <c r="B65" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C65" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3616,10 +3616,10 @@
         <v>58</v>
       </c>
       <c r="B66" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C66" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D66">
         <v>0.45</v>
@@ -3630,10 +3630,10 @@
         <v>59</v>
       </c>
       <c r="B67" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C67" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D67">
         <v>0.45</v>
@@ -3644,10 +3644,10 @@
         <v>60</v>
       </c>
       <c r="B68" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C68" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -3655,13 +3655,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C69" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D69">
         <v>3</v>
@@ -3669,13 +3669,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="D70" s="1">
         <v>1.3</v>
@@ -3686,10 +3686,10 @@
         <v>61</v>
       </c>
       <c r="B71" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C71" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3697,13 +3697,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>749</v>
       </c>
       <c r="B72" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C72" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3711,13 +3711,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>750</v>
       </c>
       <c r="B73" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3725,13 +3725,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B74" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C74" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3739,13 +3739,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B75" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C75" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3753,13 +3753,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B76" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C76" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3767,13 +3767,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C77" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3781,13 +3781,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B78" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C78" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3795,13 +3795,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>70</v>
+        <v>751</v>
       </c>
       <c r="B79" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C79" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3809,13 +3809,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>71</v>
+        <v>752</v>
       </c>
       <c r="B80" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C80" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3823,13 +3823,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>72</v>
+        <v>753</v>
       </c>
       <c r="B81" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C81" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3837,13 +3837,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>73</v>
+        <v>754</v>
       </c>
       <c r="B82" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C82" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3851,13 +3851,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B83" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C83" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3865,13 +3865,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>75</v>
+        <v>755</v>
       </c>
       <c r="B84" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C84" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3879,13 +3879,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>76</v>
+        <v>756</v>
       </c>
       <c r="B85" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C85" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3893,13 +3893,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>77</v>
+        <v>757</v>
       </c>
       <c r="B86" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C86" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3907,13 +3907,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>78</v>
+        <v>758</v>
       </c>
       <c r="B87" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C87" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3921,13 +3921,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B88" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C88" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D88">
         <v>-90</v>
@@ -3935,13 +3935,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B89" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C89" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D89">
         <v>0.8</v>
@@ -3949,13 +3949,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B90" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C90" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D90">
         <v>24</v>
@@ -3963,13 +3963,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B91" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C91" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D91">
         <v>2.2999999999999998</v>
@@ -3991,27 +3991,27 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -4019,13 +4019,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -4033,13 +4033,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -4047,13 +4047,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -4061,13 +4061,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -4075,13 +4075,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -4089,13 +4089,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -4103,13 +4103,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -4117,13 +4117,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -4131,13 +4131,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -4145,13 +4145,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C12" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -4159,13 +4159,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4173,13 +4173,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C14" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -4187,13 +4187,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -4201,13 +4201,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C16" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -4215,13 +4215,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -4229,13 +4229,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C18" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -4243,13 +4243,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -4257,13 +4257,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -4271,13 +4271,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -4285,13 +4285,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -4299,13 +4299,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -4313,13 +4313,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -4327,13 +4327,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -4341,13 +4341,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -4355,13 +4355,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -4369,13 +4369,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -4383,13 +4383,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -4397,13 +4397,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -4411,13 +4411,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -4444,25 +4444,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C1" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="E1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G1" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4473,19 +4473,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E2" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="F2" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="G2" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4496,19 +4496,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E3" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="G3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4519,19 +4519,19 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E4" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="F4" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="G4" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4542,19 +4542,19 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G5" t="s">
         <v>260</v>
-      </c>
-      <c r="E5" t="s">
-        <v>268</v>
-      </c>
-      <c r="F5" t="s">
-        <v>269</v>
-      </c>
-      <c r="G5" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4565,19 +4565,19 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D6" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E6" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="F6" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="G6" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4588,19 +4588,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D7" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E7" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="F7" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="G7" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4611,19 +4611,19 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E8" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F8" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G8" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4634,19 +4634,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D9" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E9" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="F9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="G9" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4657,19 +4657,19 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E10" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="F10" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="G10" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -4680,16 +4680,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D11" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G11" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -4700,19 +4700,19 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D12" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E12" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="F12" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G12" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4723,10 +4723,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D13" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4737,10 +4737,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D14" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4751,10 +4751,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D15" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4765,10 +4765,10 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D16" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -4779,10 +4779,10 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -4793,10 +4793,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4807,10 +4807,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4821,10 +4821,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -4835,10 +4835,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -4849,19 +4849,19 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E22" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="F22" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G22" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4872,19 +4872,19 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="D23" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E23" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="F23" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="G23" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4895,19 +4895,19 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D24" t="s">
+        <v>289</v>
+      </c>
+      <c r="E24" t="s">
+        <v>297</v>
+      </c>
+      <c r="F24" t="s">
+        <v>298</v>
+      </c>
+      <c r="G24" t="s">
         <v>299</v>
-      </c>
-      <c r="E24" t="s">
-        <v>307</v>
-      </c>
-      <c r="F24" t="s">
-        <v>308</v>
-      </c>
-      <c r="G24" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4918,19 +4918,19 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D25" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E25" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="F25" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="G25" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4941,19 +4941,19 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D26" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E26" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F26" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="G26" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -4964,19 +4964,19 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D27" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E27" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="F27" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="G27" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -4987,19 +4987,19 @@
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D28" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E28" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F28" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G28" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5010,19 +5010,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D29" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E29" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="F29" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="G29" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5033,19 +5033,19 @@
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D30" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E30" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F30" t="s">
+        <v>309</v>
+      </c>
+      <c r="G30" t="s">
         <v>319</v>
-      </c>
-      <c r="G30" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5056,19 +5056,19 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E31" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="F31" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="G31" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -5079,19 +5079,19 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E32" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="F32" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="G32" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -5102,19 +5102,19 @@
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D33" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E33" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="F33" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="G33" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5125,19 +5125,19 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D34" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="E34" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="F34" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="G34" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -5148,10 +5148,10 @@
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -5162,10 +5162,10 @@
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -5176,10 +5176,10 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -5190,10 +5190,10 @@
         <v>17</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -5204,10 +5204,10 @@
         <v>18</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -5218,10 +5218,10 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -5232,10 +5232,10 @@
         <v>20</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -5246,19 +5246,19 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D42" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E42" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="F42" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G42" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -5269,19 +5269,19 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D43" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E43" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="F43" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="G43" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -5292,19 +5292,19 @@
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D44" t="s">
+        <v>337</v>
+      </c>
+      <c r="E44" t="s">
+        <v>345</v>
+      </c>
+      <c r="F44" t="s">
+        <v>346</v>
+      </c>
+      <c r="G44" t="s">
         <v>347</v>
-      </c>
-      <c r="E44" t="s">
-        <v>355</v>
-      </c>
-      <c r="F44" t="s">
-        <v>356</v>
-      </c>
-      <c r="G44" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -5315,19 +5315,19 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="D45" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E45" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="F45" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="G45" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -5338,16 +5338,16 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D46" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E46" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="G46" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -5358,19 +5358,19 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D47" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E47" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="F47" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G47" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -5381,19 +5381,19 @@
         <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D48" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E48" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F48" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G48" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5404,19 +5404,19 @@
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D49" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E49" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="F49" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G49" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -5427,19 +5427,19 @@
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D50" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E50" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F50" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G50" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -5450,19 +5450,19 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D51" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E51" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="F51" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="G51" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -5473,19 +5473,19 @@
         <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D52" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E52" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="F52" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="G52" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -5496,13 +5496,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="D53" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E53" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5513,10 +5513,10 @@
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="D54" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -5527,10 +5527,10 @@
         <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D55" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -5541,10 +5541,10 @@
         <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="D56" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -5555,10 +5555,10 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -5569,10 +5569,10 @@
         <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -5583,10 +5583,10 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -5597,10 +5597,10 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -5611,10 +5611,10 @@
         <v>20</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -5625,19 +5625,19 @@
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D62" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E62" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="F62" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G62" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5648,19 +5648,19 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D63" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E63" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="F63" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G63" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5671,19 +5671,19 @@
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E64" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="F64" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G64" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -5694,19 +5694,19 @@
         <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D65" t="s">
+        <v>377</v>
+      </c>
+      <c r="E65" t="s">
+        <v>386</v>
+      </c>
+      <c r="F65" t="s">
         <v>387</v>
       </c>
-      <c r="E65" t="s">
-        <v>396</v>
-      </c>
-      <c r="F65" t="s">
-        <v>397</v>
-      </c>
       <c r="G65" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -5717,19 +5717,19 @@
         <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D66" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E66" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="F66" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="G66" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5740,16 +5740,16 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="D67" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E67" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="G67" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -5760,19 +5760,19 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="D68" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E68" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="F68" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G68" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5783,19 +5783,19 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="D69" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E69" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="F69" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G69" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -5806,19 +5806,19 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="D70" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E70" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="F70" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G70" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -5829,19 +5829,19 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="D71" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E71" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="F71" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G71" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -5852,19 +5852,19 @@
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="D72" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E72" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="F72" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G72" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -5875,10 +5875,10 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="D73" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5889,10 +5889,10 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="D74" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -5903,10 +5903,10 @@
         <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="D75" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -5917,10 +5917,10 @@
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="D76" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -5931,10 +5931,10 @@
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -5945,10 +5945,10 @@
         <v>17</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5959,10 +5959,10 @@
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -5973,10 +5973,10 @@
         <v>19</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5987,10 +5987,10 @@
         <v>20</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -6001,19 +6001,19 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D82" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E82" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="F82" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G82" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -6024,19 +6024,19 @@
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D83" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E83" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="F83" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G83" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -6047,19 +6047,19 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="D84" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E84" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="F84" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G84" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -6070,19 +6070,19 @@
         <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="D85" t="s">
+        <v>416</v>
+      </c>
+      <c r="E85" t="s">
         <v>426</v>
       </c>
-      <c r="E85" t="s">
-        <v>436</v>
-      </c>
       <c r="F85" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G85" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -6093,19 +6093,19 @@
         <v>5</v>
       </c>
       <c r="C86" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D86" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E86" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="F86" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G86" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -6116,19 +6116,19 @@
         <v>6</v>
       </c>
       <c r="C87" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="D87" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E87" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="F87" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G87" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -6139,19 +6139,19 @@
         <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="D88" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E88" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="F88" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G88" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -6162,19 +6162,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="D89" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E89" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="F89" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G89" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -6185,19 +6185,19 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="D90" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E90" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="F90" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G90" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6208,19 +6208,19 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="D91" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E91" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F91" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G91" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6231,19 +6231,19 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="D92" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E92" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="F92" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G92" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6254,16 +6254,16 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="D93" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E93" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G93" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6274,10 +6274,10 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="D94" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6288,10 +6288,10 @@
         <v>14</v>
       </c>
       <c r="C95" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="D95" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6302,10 +6302,10 @@
         <v>15</v>
       </c>
       <c r="C96" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="D96" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6316,10 +6316,10 @@
         <v>16</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6330,10 +6330,10 @@
         <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -6344,10 +6344,10 @@
         <v>18</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -6358,10 +6358,10 @@
         <v>19</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -6372,10 +6372,10 @@
         <v>20</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -6386,19 +6386,19 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="D102" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E102" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="F102" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G102" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -6409,19 +6409,19 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="D103" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E103" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="F103" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G103" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -6432,19 +6432,19 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="D104" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E104" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="F104" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="G104" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6455,19 +6455,19 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="D105" t="s">
+        <v>456</v>
+      </c>
+      <c r="E105" t="s">
         <v>466</v>
       </c>
-      <c r="E105" t="s">
-        <v>476</v>
-      </c>
       <c r="F105" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G105" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6478,19 +6478,19 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="D106" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E106" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="F106" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="G106" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6501,19 +6501,19 @@
         <v>6</v>
       </c>
       <c r="C107" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="D107" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E107" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="F107" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="G107" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6524,19 +6524,19 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="D108" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E108" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="F108" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="G108" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6547,19 +6547,19 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D109" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E109" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="F109" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="G109" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6570,19 +6570,19 @@
         <v>9</v>
       </c>
       <c r="C110" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="D110" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E110" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="F110" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G110" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1">
@@ -6593,19 +6593,19 @@
         <v>10</v>
       </c>
       <c r="C111" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="D111" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E111" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="F111" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G111" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6616,19 +6616,19 @@
         <v>11</v>
       </c>
       <c r="C112" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="D112" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E112" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="F112" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G112" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6639,19 +6639,19 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="D113" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E113" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="F113" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G113" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6662,19 +6662,19 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="D114" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="E114" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="F114" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G114" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -6685,10 +6685,10 @@
         <v>14</v>
       </c>
       <c r="C115" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="D115" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6699,10 +6699,10 @@
         <v>15</v>
       </c>
       <c r="C116" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D116" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -6713,10 +6713,10 @@
         <v>16</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -6727,10 +6727,10 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -6741,10 +6741,10 @@
         <v>18</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -6755,10 +6755,10 @@
         <v>19</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6769,10 +6769,10 @@
         <v>20</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6783,19 +6783,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="D122" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E122" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="F122" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G122" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6806,19 +6806,19 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D123" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E123" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="F123" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G123" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6829,19 +6829,19 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="D124" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E124" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="F124" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="G124" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -6852,19 +6852,19 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="D125" t="s">
+        <v>498</v>
+      </c>
+      <c r="E125" t="s">
         <v>508</v>
       </c>
-      <c r="E125" t="s">
-        <v>518</v>
-      </c>
       <c r="F125" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="G125" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6875,19 +6875,19 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="D126" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E126" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="F126" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G126" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -6898,19 +6898,19 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="D127" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E127" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="F127" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="G127" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -6921,19 +6921,19 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D128" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E128" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="F128" t="s">
+        <v>509</v>
+      </c>
+      <c r="G128" t="s">
         <v>519</v>
-      </c>
-      <c r="G128" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -6944,19 +6944,19 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="D129" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E129" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="F129" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="G129" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6967,19 +6967,19 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="D130" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E130" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="F130" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="G130" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6990,19 +6990,19 @@
         <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="D131" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E131" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="F131" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="G131" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -7013,19 +7013,19 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="D132" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E132" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="F132" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="G132" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -7036,19 +7036,19 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="D133" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E133" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="F133" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="G133" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -7059,19 +7059,19 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="D134" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E134" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="F134" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="G134" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -7082,10 +7082,10 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="D135" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -7096,10 +7096,10 @@
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="D136" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7110,10 +7110,10 @@
         <v>16</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7124,10 +7124,10 @@
         <v>17</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -7138,10 +7138,10 @@
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -7152,10 +7152,10 @@
         <v>19</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -7166,10 +7166,10 @@
         <v>20</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -7180,19 +7180,19 @@
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="D142" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="E142" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="F142" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="G142" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7203,19 +7203,19 @@
         <v>2</v>
       </c>
       <c r="C143" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="D143" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="E143" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="F143" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="G143" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7226,19 +7226,19 @@
         <v>3</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="D144" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="E144" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="F144" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="G144" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -7249,10 +7249,10 @@
         <v>4</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="D145" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -7263,10 +7263,10 @@
         <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="D146" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -7277,10 +7277,10 @@
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="D147" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -7291,13 +7291,13 @@
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="D148" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="E148" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -7308,13 +7308,13 @@
         <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="D149" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="E149" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -7325,13 +7325,13 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="D150" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="E150" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -7342,13 +7342,13 @@
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="D151" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="E151" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -7359,10 +7359,10 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="D152" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -7373,10 +7373,10 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
       <c r="D153" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -7387,10 +7387,10 @@
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="D154" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -7401,10 +7401,10 @@
         <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="D155" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -7415,10 +7415,10 @@
         <v>15</v>
       </c>
       <c r="C156" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="D156" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -7429,10 +7429,10 @@
         <v>16</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -7443,10 +7443,10 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -7457,10 +7457,10 @@
         <v>18</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -7471,10 +7471,10 @@
         <v>19</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -7485,10 +7485,10 @@
         <v>20</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7499,19 +7499,19 @@
         <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="D162" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="E162" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="F162" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="G162" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7522,19 +7522,19 @@
         <v>2</v>
       </c>
       <c r="C163" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="D163" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="E163" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="F163" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="G163" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7545,16 +7545,16 @@
         <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="D164" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="E164" t="s">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="G164" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7565,16 +7565,16 @@
         <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="D165" t="s">
+        <v>552</v>
+      </c>
+      <c r="E165" t="s">
         <v>562</v>
       </c>
-      <c r="E165" t="s">
-        <v>572</v>
-      </c>
       <c r="G165" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7585,19 +7585,19 @@
         <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="D166" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="E166" t="s">
-        <v>574</v>
+        <v>564</v>
       </c>
       <c r="F166" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="G166" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7608,10 +7608,10 @@
         <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="D167" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7622,10 +7622,10 @@
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="D168" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7636,10 +7636,10 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="D169" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7650,10 +7650,10 @@
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="D170" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7664,10 +7664,10 @@
         <v>10</v>
       </c>
       <c r="C171" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="D171" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7678,10 +7678,10 @@
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="D172" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7692,10 +7692,10 @@
         <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D173" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7706,10 +7706,10 @@
         <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="D174" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7720,10 +7720,10 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="D175" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7734,10 +7734,10 @@
         <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="D176" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7748,10 +7748,10 @@
         <v>16</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -7762,10 +7762,10 @@
         <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -7776,10 +7776,10 @@
         <v>18</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -7790,10 +7790,10 @@
         <v>19</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -7804,10 +7804,10 @@
         <v>20</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -7818,19 +7818,19 @@
         <v>1</v>
       </c>
       <c r="C182" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="D182" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E182" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="F182" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G182" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -7841,19 +7841,19 @@
         <v>2</v>
       </c>
       <c r="C183" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="D183" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E183" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="F183" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G183" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -7864,19 +7864,19 @@
         <v>3</v>
       </c>
       <c r="C184" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="D184" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E184" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="F184" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G184" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -7887,19 +7887,19 @@
         <v>4</v>
       </c>
       <c r="C185" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="D185" t="s">
+        <v>577</v>
+      </c>
+      <c r="E185" t="s">
         <v>587</v>
       </c>
-      <c r="E185" t="s">
-        <v>597</v>
-      </c>
       <c r="F185" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G185" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -7910,19 +7910,19 @@
         <v>5</v>
       </c>
       <c r="C186" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="D186" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E186" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="F186" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G186" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -7933,19 +7933,19 @@
         <v>6</v>
       </c>
       <c r="C187" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="D187" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E187" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="F187" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G187" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7956,19 +7956,19 @@
         <v>7</v>
       </c>
       <c r="C188" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="D188" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E188" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="F188" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G188" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7979,19 +7979,19 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="D189" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E189" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="F189" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G189" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -8002,19 +8002,19 @@
         <v>9</v>
       </c>
       <c r="C190" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="D190" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E190" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="F190" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G190" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -8025,19 +8025,19 @@
         <v>10</v>
       </c>
       <c r="C191" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="D191" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E191" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="F191" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G191" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -8048,19 +8048,19 @@
         <v>11</v>
       </c>
       <c r="C192" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="D192" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E192" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="F192" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G192" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -8071,19 +8071,19 @@
         <v>12</v>
       </c>
       <c r="C193" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="D193" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E193" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="F193" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G193" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -8094,19 +8094,19 @@
         <v>13</v>
       </c>
       <c r="C194" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="D194" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E194" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="F194" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G194" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -8117,19 +8117,19 @@
         <v>14</v>
       </c>
       <c r="C195" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="D195" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E195" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="F195" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G195" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -8140,10 +8140,10 @@
         <v>15</v>
       </c>
       <c r="C196" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="D196" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -8154,10 +8154,10 @@
         <v>16</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -8168,10 +8168,10 @@
         <v>17</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -8182,10 +8182,10 @@
         <v>18</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -8196,10 +8196,10 @@
         <v>19</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -8210,10 +8210,10 @@
         <v>20</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -8224,16 +8224,16 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="D202" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E202" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="F202" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -8244,16 +8244,16 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="D203" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E203" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="F203" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -8264,16 +8264,16 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="D204" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E204" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="F204" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -8284,16 +8284,16 @@
         <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="D205" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E205" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="F205" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -8304,16 +8304,16 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="D206" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E206" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="F206" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -8324,16 +8324,16 @@
         <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="D207" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E207" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="F207" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -8344,16 +8344,16 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="D208" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E208" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="F208" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -8364,16 +8364,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="D209" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E209" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="F209" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -8384,16 +8384,16 @@
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="D210" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E210" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="F210" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -8404,16 +8404,16 @@
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="D211" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E211" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="F211" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -8424,16 +8424,16 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="D212" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E212" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F212" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -8444,16 +8444,16 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="D213" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E213" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="F213" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -8464,16 +8464,16 @@
         <v>13</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="D214" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E214" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="F214" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -8484,16 +8484,16 @@
         <v>14</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="D215" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E215" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="F215" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8504,16 +8504,16 @@
         <v>15</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
       <c r="D216" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E216" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="F216" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -8524,16 +8524,16 @@
         <v>16</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E217" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="F217" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -8544,13 +8544,13 @@
         <v>17</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E218" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8561,16 +8561,16 @@
         <v>18</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="E219" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -8581,10 +8581,10 @@
         <v>19</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8595,10 +8595,10 @@
         <v>20</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -8624,16 +8624,16 @@
     <row r="1" spans="1:5">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8654,10 +8654,10 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8671,10 +8671,10 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8688,10 +8688,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8705,10 +8705,10 @@
         <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8722,10 +8722,10 @@
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8739,10 +8739,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8756,10 +8756,10 @@
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8773,10 +8773,10 @@
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8790,10 +8790,10 @@
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8807,10 +8807,10 @@
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8824,10 +8824,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8841,10 +8841,10 @@
         <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8858,10 +8858,10 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8875,10 +8875,10 @@
         <v>19</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8892,10 +8892,10 @@
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8909,10 +8909,10 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8926,10 +8926,10 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8943,10 +8943,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8960,10 +8960,10 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8977,10 +8977,10 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8994,10 +8994,10 @@
         <v>16</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9011,10 +9011,10 @@
         <v>17</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9028,10 +9028,10 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9045,10 +9045,10 @@
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -9062,10 +9062,10 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9079,10 +9079,10 @@
         <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9096,10 +9096,10 @@
         <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9113,10 +9113,10 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9130,10 +9130,10 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9147,10 +9147,10 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9164,10 +9164,10 @@
         <v>16</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9181,10 +9181,10 @@
         <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9198,10 +9198,10 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9215,10 +9215,10 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9232,10 +9232,10 @@
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9249,10 +9249,10 @@
         <v>16</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9266,10 +9266,10 @@
         <v>17</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -9283,10 +9283,10 @@
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -9300,10 +9300,10 @@
         <v>19</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -9317,10 +9317,10 @@
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -9334,10 +9334,10 @@
         <v>16</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9351,10 +9351,10 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9368,10 +9368,10 @@
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9385,10 +9385,10 @@
         <v>19</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -9402,10 +9402,10 @@
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -9419,10 +9419,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -9436,10 +9436,10 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -9453,10 +9453,10 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -9470,10 +9470,10 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -9487,10 +9487,10 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -9504,10 +9504,10 @@
         <v>16</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9521,10 +9521,10 @@
         <v>17</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9538,10 +9538,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9555,10 +9555,10 @@
         <v>19</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9572,15 +9572,15 @@
         <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9693BDE3-8A05-461A-A01B-9F66E5E1E7C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A073BA2D-C924-40F2-8E67-416E65DDE160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="751">
   <si>
     <t>pFS2</t>
   </si>
@@ -606,15 +606,6 @@
     <t>Crown shape (1=cone, 2=ellipsoid, 3=half-ellipsoid, 4=rectangular)</t>
   </si>
   <si>
-    <t>Constant in the stem height relationship</t>
-  </si>
-  <si>
-    <t>Power of DBH in the stem height relationship</t>
-  </si>
-  <si>
-    <t>Power of competition in the stem height relationship</t>
-  </si>
-  <si>
     <t>Constant in the stem volume relationship</t>
   </si>
   <si>
@@ -627,36 +618,6 @@
     <t>Power of DBH^2 x height in the stem volume relationship</t>
   </si>
   <si>
-    <t>Constant in the crown diameter relationship</t>
-  </si>
-  <si>
-    <t>Power of DBH in the crown diameter relationship</t>
-  </si>
-  <si>
-    <t>Power of height in the crown diameter relationship</t>
-  </si>
-  <si>
-    <t>Power of competition in the crown diameter relationship</t>
-  </si>
-  <si>
-    <t>Power of relative height in the crown diameter relationship</t>
-  </si>
-  <si>
-    <t>Constant in the LCL relationship</t>
-  </si>
-  <si>
-    <t>Power of DBH in the LCL relationship</t>
-  </si>
-  <si>
-    <t>Power of LAI in the LCL relationship</t>
-  </si>
-  <si>
-    <t>Power of competition in the LCL relationship</t>
-  </si>
-  <si>
-    <t>Power of relative height in the LCL relationship</t>
-  </si>
-  <si>
     <t>Intercept of net v. solar radiation relationship</t>
   </si>
   <si>
@@ -2308,6 +2269,21 @@
   </si>
   <si>
     <t>nHL4</t>
+  </si>
+  <si>
+    <t>nH3</t>
+  </si>
+  <si>
+    <t>nH4</t>
+  </si>
+  <si>
+    <t>Parameter of height equation</t>
+  </si>
+  <si>
+    <t>Parameter of crown diameter equation</t>
+  </si>
+  <si>
+    <t>Parameter of crown length equation</t>
   </si>
 </sst>
 </file>
@@ -2709,7 +2685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E287297-02C0-BF44-BF0C-8FADE2A87F8F}">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="2" max="2" width="80" bestFit="1" customWidth="1"/>
@@ -2958,7 +2934,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="C18" t="s">
         <v>118</v>
@@ -3179,10 +3155,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -3191,10 +3167,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -3203,10 +3179,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -3215,10 +3191,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -3227,10 +3203,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -3239,10 +3215,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -3349,10 +3325,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -3669,13 +3645,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="D70" s="1">
         <v>1.3</v>
@@ -3686,7 +3662,7 @@
         <v>61</v>
       </c>
       <c r="B71" t="s">
-        <v>191</v>
+        <v>748</v>
       </c>
       <c r="C71" t="s">
         <v>118</v>
@@ -3697,10 +3673,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="B72" t="s">
-        <v>192</v>
+        <v>748</v>
       </c>
       <c r="C72" t="s">
         <v>118</v>
@@ -3711,10 +3687,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="B73" t="s">
-        <v>193</v>
+        <v>748</v>
       </c>
       <c r="C73" t="s">
         <v>118</v>
@@ -3725,38 +3701,26 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>62</v>
+        <v>746</v>
       </c>
       <c r="B74" t="s">
-        <v>194</v>
-      </c>
-      <c r="C74" t="s">
-        <v>118</v>
-      </c>
-      <c r="D74">
-        <v>0</v>
+        <v>748</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>63</v>
+        <v>747</v>
       </c>
       <c r="B75" t="s">
-        <v>195</v>
-      </c>
-      <c r="C75" t="s">
-        <v>118</v>
-      </c>
-      <c r="D75">
-        <v>0</v>
+        <v>748</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B76" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C76" t="s">
         <v>118</v>
@@ -3767,10 +3731,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B77" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C77" t="s">
         <v>118</v>
@@ -3781,10 +3745,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B78" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C78" t="s">
         <v>118</v>
@@ -3795,10 +3759,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>751</v>
+        <v>65</v>
       </c>
       <c r="B79" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C79" t="s">
         <v>118</v>
@@ -3809,10 +3773,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>752</v>
+        <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>200</v>
+        <v>749</v>
       </c>
       <c r="C80" t="s">
         <v>118</v>
@@ -3823,10 +3787,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>753</v>
+        <v>738</v>
       </c>
       <c r="B81" t="s">
-        <v>201</v>
+        <v>749</v>
       </c>
       <c r="C81" t="s">
         <v>118</v>
@@ -3837,10 +3801,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>754</v>
+        <v>739</v>
       </c>
       <c r="B82" t="s">
-        <v>202</v>
+        <v>749</v>
       </c>
       <c r="C82" t="s">
         <v>118</v>
@@ -3851,10 +3815,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>68</v>
+        <v>740</v>
       </c>
       <c r="B83" t="s">
-        <v>203</v>
+        <v>749</v>
       </c>
       <c r="C83" t="s">
         <v>118</v>
@@ -3865,10 +3829,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>755</v>
+        <v>741</v>
       </c>
       <c r="B84" t="s">
-        <v>204</v>
+        <v>749</v>
       </c>
       <c r="C84" t="s">
         <v>118</v>
@@ -3879,10 +3843,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>756</v>
+        <v>68</v>
       </c>
       <c r="B85" t="s">
-        <v>205</v>
+        <v>750</v>
       </c>
       <c r="C85" t="s">
         <v>118</v>
@@ -3893,10 +3857,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="B86" t="s">
-        <v>206</v>
+        <v>750</v>
       </c>
       <c r="C86" t="s">
         <v>118</v>
@@ -3907,10 +3871,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>758</v>
+        <v>743</v>
       </c>
       <c r="B87" t="s">
-        <v>207</v>
+        <v>750</v>
       </c>
       <c r="C87" t="s">
         <v>118</v>
@@ -3921,61 +3885,90 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>99</v>
+        <v>744</v>
       </c>
       <c r="B88" t="s">
-        <v>208</v>
+        <v>750</v>
       </c>
       <c r="C88" t="s">
-        <v>209</v>
+        <v>118</v>
       </c>
       <c r="D88">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>100</v>
+        <v>745</v>
       </c>
       <c r="B89" t="s">
-        <v>210</v>
+        <v>750</v>
       </c>
       <c r="C89" t="s">
         <v>118</v>
       </c>
       <c r="D89">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B90" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="C90" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="D90">
-        <v>24</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
+        <v>100</v>
+      </c>
+      <c r="B91" t="s">
+        <v>197</v>
+      </c>
+      <c r="C91" t="s">
+        <v>118</v>
+      </c>
+      <c r="D91">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>101</v>
+      </c>
+      <c r="B92" t="s">
+        <v>198</v>
+      </c>
+      <c r="C92" t="s">
+        <v>199</v>
+      </c>
+      <c r="D92">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
         <v>102</v>
       </c>
-      <c r="B91" t="s">
-        <v>213</v>
-      </c>
-      <c r="C91" t="s">
-        <v>214</v>
-      </c>
-      <c r="D91">
+      <c r="B93" t="s">
+        <v>200</v>
+      </c>
+      <c r="C93" t="s">
+        <v>201</v>
+      </c>
+      <c r="D93">
         <v>2.2999999999999998</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Aptos"&amp;12&amp;KFF0000 OFFICIAL&amp;1#_x000D_</oddHeader>
@@ -4008,7 +4001,7 @@
         <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C2" t="s">
         <v>118</v>
@@ -4022,7 +4015,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
         <v>118</v>
@@ -4036,7 +4029,7 @@
         <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
         <v>118</v>
@@ -4050,7 +4043,7 @@
         <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C5" t="s">
         <v>118</v>
@@ -4064,7 +4057,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C6" t="s">
         <v>118</v>
@@ -4078,7 +4071,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C7" t="s">
         <v>118</v>
@@ -4092,7 +4085,7 @@
         <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C8" t="s">
         <v>118</v>
@@ -4106,7 +4099,7 @@
         <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C9" t="s">
         <v>118</v>
@@ -4120,7 +4113,7 @@
         <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C10" t="s">
         <v>118</v>
@@ -4134,7 +4127,7 @@
         <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C11" t="s">
         <v>118</v>
@@ -4148,7 +4141,7 @@
         <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C12" t="s">
         <v>118</v>
@@ -4162,7 +4155,7 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C13" t="s">
         <v>118</v>
@@ -4176,7 +4169,7 @@
         <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C14" t="s">
         <v>118</v>
@@ -4190,7 +4183,7 @@
         <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
         <v>118</v>
@@ -4204,7 +4197,7 @@
         <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C16" t="s">
         <v>118</v>
@@ -4218,7 +4211,7 @@
         <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="C17" t="s">
         <v>118</v>
@@ -4232,7 +4225,7 @@
         <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C18" t="s">
         <v>118</v>
@@ -4246,7 +4239,7 @@
         <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C19" t="s">
         <v>118</v>
@@ -4260,7 +4253,7 @@
         <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="C20" t="s">
         <v>118</v>
@@ -4274,7 +4267,7 @@
         <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="C21" t="s">
         <v>118</v>
@@ -4288,7 +4281,7 @@
         <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="C22" t="s">
         <v>118</v>
@@ -4302,7 +4295,7 @@
         <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C23" t="s">
         <v>118</v>
@@ -4316,7 +4309,7 @@
         <v>91</v>
       </c>
       <c r="B24" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C24" t="s">
         <v>118</v>
@@ -4330,7 +4323,7 @@
         <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="C25" t="s">
         <v>118</v>
@@ -4344,7 +4337,7 @@
         <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C26" t="s">
         <v>118</v>
@@ -4358,7 +4351,7 @@
         <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C27" t="s">
         <v>118</v>
@@ -4372,7 +4365,7 @@
         <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="C28" t="s">
         <v>118</v>
@@ -4386,7 +4379,7 @@
         <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="C29" t="s">
         <v>118</v>
@@ -4400,7 +4393,7 @@
         <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="C30" t="s">
         <v>118</v>
@@ -4414,7 +4407,7 @@
         <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C31" t="s">
         <v>118</v>
@@ -4444,16 +4437,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B1" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="C1" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="D1" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="E1" t="s">
         <v>114</v>
@@ -4462,7 +4455,7 @@
         <v>115</v>
       </c>
       <c r="G1" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4476,16 +4469,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E2" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="F2" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="G2" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4499,16 +4492,16 @@
         <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E3" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F3" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="G3" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4522,16 +4515,16 @@
         <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="F4" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="G4" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4545,16 +4538,16 @@
         <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="F5" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="G5" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4565,19 +4558,19 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="D6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F6" t="s">
         <v>250</v>
       </c>
-      <c r="E6" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" t="s">
-        <v>263</v>
-      </c>
       <c r="G6" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4588,19 +4581,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="D7" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E7" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="F7" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="G7" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4614,16 +4607,16 @@
         <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E8" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="F8" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="G8" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4634,19 +4627,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E9" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="F9" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="G9" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4660,16 +4653,16 @@
         <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E10" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="F10" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="G10" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -4680,16 +4673,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="D11" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E11" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="G11" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -4700,19 +4693,19 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="D12" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E12" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="F12" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="G12" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4723,10 +4716,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="D13" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4737,10 +4730,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="D14" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4751,10 +4744,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D15" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4765,10 +4758,10 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="D16" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -4779,10 +4772,10 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -4793,10 +4786,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4807,10 +4800,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4821,10 +4814,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -4835,10 +4828,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -4852,16 +4845,16 @@
         <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E22" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="F22" t="s">
         <v>145</v>
       </c>
       <c r="G22" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4872,19 +4865,19 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="D23" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E23" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="F23" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="G23" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4895,19 +4888,19 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="D24" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E24" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="F24" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="G24" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4918,19 +4911,19 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="D25" t="s">
+        <v>276</v>
+      </c>
+      <c r="E25" t="s">
+        <v>288</v>
+      </c>
+      <c r="F25" t="s">
         <v>289</v>
       </c>
-      <c r="E25" t="s">
-        <v>301</v>
-      </c>
-      <c r="F25" t="s">
-        <v>302</v>
-      </c>
       <c r="G25" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4941,19 +4934,19 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E26" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="F26" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="G26" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -4964,19 +4957,19 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E27" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="F27" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="G27" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -4987,19 +4980,19 @@
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E28" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="F28" t="s">
         <v>118</v>
       </c>
       <c r="G28" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5010,19 +5003,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E29" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="F29" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="G29" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5033,19 +5026,19 @@
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E30" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="F30" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="G30" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5056,19 +5049,19 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="D31" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E31" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="F31" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="G31" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -5079,19 +5072,19 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="D32" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E32" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="F32" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="G32" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -5102,19 +5095,19 @@
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="D33" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E33" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="F33" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="G33" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5125,19 +5118,19 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="D34" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E34" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="F34" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="G34" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -5148,10 +5141,10 @@
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="D35" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -5162,10 +5155,10 @@
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="D36" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -5176,10 +5169,10 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -5190,10 +5183,10 @@
         <v>17</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -5204,10 +5197,10 @@
         <v>18</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -5218,10 +5211,10 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -5232,10 +5225,10 @@
         <v>20</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -5246,19 +5239,19 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="D42" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E42" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="F42" t="s">
         <v>118</v>
       </c>
       <c r="G42" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -5269,19 +5262,19 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="D43" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E43" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="F43" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="G43" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -5292,19 +5285,19 @@
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="D44" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E44" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="F44" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="G44" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -5315,19 +5308,19 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="D45" t="s">
+        <v>324</v>
+      </c>
+      <c r="E45" t="s">
+        <v>336</v>
+      </c>
+      <c r="F45" t="s">
+        <v>333</v>
+      </c>
+      <c r="G45" t="s">
         <v>337</v>
-      </c>
-      <c r="E45" t="s">
-        <v>349</v>
-      </c>
-      <c r="F45" t="s">
-        <v>346</v>
-      </c>
-      <c r="G45" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -5338,16 +5331,16 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="D46" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E46" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="G46" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -5358,19 +5351,19 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="D47" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E47" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="F47" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="G47" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -5381,19 +5374,19 @@
         <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="D48" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E48" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="F48" t="s">
         <v>118</v>
       </c>
       <c r="G48" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5404,19 +5397,19 @@
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="D49" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E49" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="F49" t="s">
         <v>118</v>
       </c>
       <c r="G49" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -5427,19 +5420,19 @@
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="D50" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E50" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="F50" t="s">
         <v>118</v>
       </c>
       <c r="G50" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -5450,19 +5443,19 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="D51" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E51" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="F51" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="G51" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -5473,19 +5466,19 @@
         <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="D52" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E52" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="F52" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="G52" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -5496,13 +5489,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="D53" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E53" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5513,10 +5506,10 @@
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="D54" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -5527,10 +5520,10 @@
         <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="D55" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -5541,10 +5534,10 @@
         <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="D56" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -5555,10 +5548,10 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -5569,10 +5562,10 @@
         <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -5583,10 +5576,10 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -5597,10 +5590,10 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -5611,10 +5604,10 @@
         <v>20</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -5628,16 +5621,16 @@
         <v>106</v>
       </c>
       <c r="D62" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E62" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="F62" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="G62" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5651,16 +5644,16 @@
         <v>105</v>
       </c>
       <c r="D63" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E63" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="F63" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="G63" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5674,16 +5667,16 @@
         <v>104</v>
       </c>
       <c r="D64" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E64" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="F64" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="G64" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -5694,19 +5687,19 @@
         <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="D65" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E65" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="F65" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="G65" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -5717,19 +5710,19 @@
         <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="D66" t="s">
+        <v>364</v>
+      </c>
+      <c r="E66" t="s">
         <v>377</v>
       </c>
-      <c r="E66" t="s">
-        <v>390</v>
-      </c>
       <c r="F66" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="G66" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5740,16 +5733,16 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="D67" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E67" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="G67" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -5760,19 +5753,19 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="D68" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E68" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="F68" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="G68" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5783,19 +5776,19 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="D69" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E69" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="F69" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="G69" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -5806,19 +5799,19 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="D70" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E70" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="F70" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="G70" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -5829,19 +5822,19 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="D71" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E71" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="F71" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="G71" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -5852,19 +5845,19 @@
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="D72" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E72" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="F72" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="G72" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -5875,10 +5868,10 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="D73" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5889,10 +5882,10 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="D74" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -5903,10 +5896,10 @@
         <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="D75" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -5917,10 +5910,10 @@
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="D76" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -5931,10 +5924,10 @@
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -5945,10 +5938,10 @@
         <v>17</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5959,10 +5952,10 @@
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -5973,10 +5966,10 @@
         <v>19</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5987,10 +5980,10 @@
         <v>20</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -6001,19 +5994,19 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="D82" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E82" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="F82" t="s">
         <v>118</v>
       </c>
       <c r="G82" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -6024,19 +6017,19 @@
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="D83" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E83" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="F83" t="s">
         <v>118</v>
       </c>
       <c r="G83" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -6047,19 +6040,19 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="D84" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E84" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="F84" t="s">
         <v>118</v>
       </c>
       <c r="G84" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -6070,19 +6063,19 @@
         <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="D85" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E85" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="F85" t="s">
         <v>118</v>
       </c>
       <c r="G85" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -6093,19 +6086,19 @@
         <v>5</v>
       </c>
       <c r="C86" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="D86" t="s">
+        <v>403</v>
+      </c>
+      <c r="E86" t="s">
         <v>416</v>
       </c>
-      <c r="E86" t="s">
-        <v>429</v>
-      </c>
       <c r="F86" t="s">
         <v>118</v>
       </c>
       <c r="G86" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -6116,19 +6109,19 @@
         <v>6</v>
       </c>
       <c r="C87" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="D87" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E87" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="F87" t="s">
         <v>118</v>
       </c>
       <c r="G87" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -6139,19 +6132,19 @@
         <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="D88" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E88" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="F88" t="s">
         <v>118</v>
       </c>
       <c r="G88" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -6162,19 +6155,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="D89" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E89" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="F89" t="s">
         <v>118</v>
       </c>
       <c r="G89" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -6185,19 +6178,19 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="D90" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E90" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="F90" t="s">
         <v>118</v>
       </c>
       <c r="G90" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6208,19 +6201,19 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="D91" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E91" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="F91" t="s">
         <v>118</v>
       </c>
       <c r="G91" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6231,19 +6224,19 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="D92" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E92" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="F92" t="s">
         <v>118</v>
       </c>
       <c r="G92" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6254,16 +6247,16 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="D93" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E93" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="G93" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6274,10 +6267,10 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="D94" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6288,10 +6281,10 @@
         <v>14</v>
       </c>
       <c r="C95" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="D95" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6302,10 +6295,10 @@
         <v>15</v>
       </c>
       <c r="C96" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="D96" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6316,10 +6309,10 @@
         <v>16</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6330,10 +6323,10 @@
         <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -6344,10 +6337,10 @@
         <v>18</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -6358,10 +6351,10 @@
         <v>19</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -6372,10 +6365,10 @@
         <v>20</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -6386,19 +6379,19 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="D102" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E102" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="F102" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="G102" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -6409,19 +6402,19 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="D103" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E103" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="F103" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="G103" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -6432,19 +6425,19 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="D104" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E104" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="F104" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="G104" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6455,19 +6448,19 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="D105" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E105" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="F105" t="s">
         <v>118</v>
       </c>
       <c r="G105" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6478,19 +6471,19 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="D106" t="s">
+        <v>443</v>
+      </c>
+      <c r="E106" t="s">
+        <v>455</v>
+      </c>
+      <c r="F106" t="s">
         <v>456</v>
       </c>
-      <c r="E106" t="s">
-        <v>468</v>
-      </c>
-      <c r="F106" t="s">
-        <v>469</v>
-      </c>
       <c r="G106" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6501,19 +6494,19 @@
         <v>6</v>
       </c>
       <c r="C107" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="D107" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E107" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="F107" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="G107" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6524,19 +6517,19 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="D108" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E108" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="F108" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="G108" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6547,19 +6540,19 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="D109" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E109" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="F109" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="G109" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6570,19 +6563,19 @@
         <v>9</v>
       </c>
       <c r="C110" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="D110" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E110" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="F110" t="s">
         <v>118</v>
       </c>
       <c r="G110" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1">
@@ -6593,19 +6586,19 @@
         <v>10</v>
       </c>
       <c r="C111" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="D111" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E111" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="F111" t="s">
         <v>118</v>
       </c>
       <c r="G111" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6616,19 +6609,19 @@
         <v>11</v>
       </c>
       <c r="C112" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="D112" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E112" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="F112" t="s">
         <v>118</v>
       </c>
       <c r="G112" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6639,19 +6632,19 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="D113" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E113" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="F113" t="s">
         <v>118</v>
       </c>
       <c r="G113" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6662,19 +6655,19 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="D114" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="E114" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="F114" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="G114" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -6685,10 +6678,10 @@
         <v>14</v>
       </c>
       <c r="C115" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="D115" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6699,10 +6692,10 @@
         <v>15</v>
       </c>
       <c r="C116" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="D116" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -6713,10 +6706,10 @@
         <v>16</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -6727,10 +6720,10 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -6741,10 +6734,10 @@
         <v>18</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -6755,10 +6748,10 @@
         <v>19</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6769,10 +6762,10 @@
         <v>20</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6783,19 +6776,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="D122" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E122" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="F122" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="G122" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6806,19 +6799,19 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="D123" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E123" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="F123" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="G123" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6829,19 +6822,19 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="D124" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E124" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="F124" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="G124" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -6852,19 +6845,19 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="D125" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E125" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="F125" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G125" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6875,19 +6868,19 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="D126" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E126" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="F126" t="s">
         <v>118</v>
       </c>
       <c r="G126" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -6898,19 +6891,19 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="D127" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E127" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="F127" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G127" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -6921,19 +6914,19 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="D128" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E128" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="F128" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G128" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -6944,19 +6937,19 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="D129" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E129" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="F129" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="G129" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6967,19 +6960,19 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="D130" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E130" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="F130" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="G130" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6990,19 +6983,19 @@
         <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="D131" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E131" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="F131" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="G131" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -7013,19 +7006,19 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="D132" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E132" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="F132" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="G132" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -7036,19 +7029,19 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="D133" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E133" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="F133" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G133" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -7059,19 +7052,19 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="D134" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="E134" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="F134" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="G134" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -7082,10 +7075,10 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="D135" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -7096,10 +7089,10 @@
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="D136" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7110,10 +7103,10 @@
         <v>16</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7124,10 +7117,10 @@
         <v>17</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -7138,10 +7131,10 @@
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -7152,10 +7145,10 @@
         <v>19</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -7166,10 +7159,10 @@
         <v>20</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -7180,19 +7173,19 @@
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="D142" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="E142" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="F142" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="G142" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7203,19 +7196,19 @@
         <v>2</v>
       </c>
       <c r="C143" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="D143" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="E143" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="F143" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="G143" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7226,19 +7219,19 @@
         <v>3</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="D144" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="E144" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="F144" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="G144" t="s">
-        <v>549</v>
+        <v>536</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -7249,10 +7242,10 @@
         <v>4</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="D145" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -7263,10 +7256,10 @@
         <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="D146" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -7277,10 +7270,10 @@
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="D147" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -7291,13 +7284,13 @@
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="D148" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="E148" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -7308,13 +7301,13 @@
         <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="D149" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="E149" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -7325,13 +7318,13 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="D150" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="E150" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -7342,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="D151" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="E151" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -7359,10 +7352,10 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="D152" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -7373,10 +7366,10 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="D153" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -7387,10 +7380,10 @@
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="D154" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -7401,10 +7394,10 @@
         <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="D155" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -7415,10 +7408,10 @@
         <v>15</v>
       </c>
       <c r="C156" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="D156" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -7429,10 +7422,10 @@
         <v>16</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -7443,10 +7436,10 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -7457,10 +7450,10 @@
         <v>18</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -7471,10 +7464,10 @@
         <v>19</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -7485,10 +7478,10 @@
         <v>20</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7499,19 +7492,19 @@
         <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="D162" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="E162" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="F162" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="G162" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7522,19 +7515,19 @@
         <v>2</v>
       </c>
       <c r="C163" t="s">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="D163" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="E163" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="F163" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="G163" t="s">
-        <v>558</v>
+        <v>545</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7545,16 +7538,16 @@
         <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="D164" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="E164" t="s">
-        <v>560</v>
+        <v>547</v>
       </c>
       <c r="G164" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7565,16 +7558,16 @@
         <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="D165" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="E165" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="G165" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7585,19 +7578,19 @@
         <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="D166" t="s">
+        <v>539</v>
+      </c>
+      <c r="E166" t="s">
+        <v>551</v>
+      </c>
+      <c r="F166" t="s">
+        <v>264</v>
+      </c>
+      <c r="G166" t="s">
         <v>552</v>
-      </c>
-      <c r="E166" t="s">
-        <v>564</v>
-      </c>
-      <c r="F166" t="s">
-        <v>277</v>
-      </c>
-      <c r="G166" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7608,10 +7601,10 @@
         <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="D167" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7622,10 +7615,10 @@
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="D168" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7636,10 +7629,10 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="D169" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7650,10 +7643,10 @@
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="D170" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7664,10 +7657,10 @@
         <v>10</v>
       </c>
       <c r="C171" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="D171" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7678,10 +7671,10 @@
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="D172" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7692,10 +7685,10 @@
         <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="D173" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7706,10 +7699,10 @@
         <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="D174" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7720,10 +7713,10 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="D175" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7734,10 +7727,10 @@
         <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="D176" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7748,10 +7741,10 @@
         <v>16</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -7762,10 +7755,10 @@
         <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -7776,10 +7769,10 @@
         <v>18</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -7790,10 +7783,10 @@
         <v>19</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -7804,10 +7797,10 @@
         <v>20</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -7818,19 +7811,19 @@
         <v>1</v>
       </c>
       <c r="C182" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="D182" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E182" t="s">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="F182" t="s">
         <v>118</v>
       </c>
       <c r="G182" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -7841,19 +7834,19 @@
         <v>2</v>
       </c>
       <c r="C183" t="s">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="D183" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E183" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="F183" t="s">
         <v>118</v>
       </c>
       <c r="G183" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -7864,19 +7857,19 @@
         <v>3</v>
       </c>
       <c r="C184" t="s">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="D184" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E184" t="s">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="F184" t="s">
         <v>118</v>
       </c>
       <c r="G184" t="s">
-        <v>585</v>
+        <v>572</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -7887,19 +7880,19 @@
         <v>4</v>
       </c>
       <c r="C185" t="s">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="D185" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E185" t="s">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="F185" t="s">
         <v>118</v>
       </c>
       <c r="G185" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -7910,19 +7903,19 @@
         <v>5</v>
       </c>
       <c r="C186" t="s">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="D186" t="s">
+        <v>564</v>
+      </c>
+      <c r="E186" t="s">
         <v>577</v>
       </c>
-      <c r="E186" t="s">
-        <v>590</v>
-      </c>
       <c r="F186" t="s">
         <v>118</v>
       </c>
       <c r="G186" t="s">
-        <v>591</v>
+        <v>578</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -7933,19 +7926,19 @@
         <v>6</v>
       </c>
       <c r="C187" t="s">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="D187" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E187" t="s">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="F187" t="s">
         <v>118</v>
       </c>
       <c r="G187" t="s">
-        <v>594</v>
+        <v>581</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7956,19 +7949,19 @@
         <v>7</v>
       </c>
       <c r="C188" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="D188" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E188" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="F188" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="G188" t="s">
-        <v>597</v>
+        <v>584</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7979,19 +7972,19 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="D189" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E189" t="s">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="F189" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="G189" t="s">
-        <v>600</v>
+        <v>587</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -8002,19 +7995,19 @@
         <v>9</v>
       </c>
       <c r="C190" t="s">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="D190" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E190" t="s">
-        <v>602</v>
+        <v>589</v>
       </c>
       <c r="F190" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="G190" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -8025,19 +8018,19 @@
         <v>10</v>
       </c>
       <c r="C191" t="s">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="D191" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E191" t="s">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="F191" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="G191" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -8048,19 +8041,19 @@
         <v>11</v>
       </c>
       <c r="C192" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="D192" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E192" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="F192" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="G192" t="s">
-        <v>609</v>
+        <v>596</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -8071,19 +8064,19 @@
         <v>12</v>
       </c>
       <c r="C193" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="D193" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E193" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="F193" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="G193" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -8094,19 +8087,19 @@
         <v>13</v>
       </c>
       <c r="C194" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="D194" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E194" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="F194" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="G194" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -8117,19 +8110,19 @@
         <v>14</v>
       </c>
       <c r="C195" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="D195" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="E195" t="s">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="F195" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="G195" t="s">
-        <v>618</v>
+        <v>605</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -8140,10 +8133,10 @@
         <v>15</v>
       </c>
       <c r="C196" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="D196" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -8154,10 +8147,10 @@
         <v>16</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -8168,10 +8161,10 @@
         <v>17</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -8182,10 +8175,10 @@
         <v>18</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -8196,10 +8189,10 @@
         <v>19</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -8210,10 +8203,10 @@
         <v>20</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -8224,16 +8217,16 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="D202" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E202" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="F202" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -8244,16 +8237,16 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="D203" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E203" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="F203" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -8264,16 +8257,16 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="D204" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E204" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="F204" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -8284,16 +8277,16 @@
         <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="D205" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E205" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="F205" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -8304,16 +8297,16 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="D206" t="s">
+        <v>630</v>
+      </c>
+      <c r="E206" t="s">
         <v>643</v>
       </c>
-      <c r="E206" t="s">
-        <v>656</v>
-      </c>
       <c r="F206" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -8324,16 +8317,16 @@
         <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="D207" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E207" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="F207" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -8344,16 +8337,16 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="D208" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E208" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="F208" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -8364,16 +8357,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="D209" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E209" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="F209" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -8384,16 +8377,16 @@
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="D210" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E210" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="F210" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -8404,16 +8397,16 @@
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="D211" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E211" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="F211" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -8424,16 +8417,16 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="D212" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E212" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="F212" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -8444,16 +8437,16 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="D213" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E213" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="F213" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -8464,16 +8457,16 @@
         <v>13</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="D214" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E214" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="F214" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -8484,16 +8477,16 @@
         <v>14</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="D215" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E215" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="F215" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8504,16 +8497,16 @@
         <v>15</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="D216" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E216" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="F216" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -8524,16 +8517,16 @@
         <v>16</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E217" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="F217" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -8544,13 +8537,13 @@
         <v>17</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E218" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8561,13 +8554,13 @@
         <v>18</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="E219" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>128</v>
@@ -8581,10 +8574,10 @@
         <v>19</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8595,10 +8588,10 @@
         <v>20</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -8624,16 +8617,16 @@
     <row r="1" spans="1:5">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8654,10 +8647,10 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8671,10 +8664,10 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8688,10 +8681,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8705,10 +8698,10 @@
         <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8722,10 +8715,10 @@
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8739,10 +8732,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8756,10 +8749,10 @@
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8773,10 +8766,10 @@
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8790,10 +8783,10 @@
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8807,10 +8800,10 @@
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8824,10 +8817,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8841,10 +8834,10 @@
         <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8858,10 +8851,10 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8875,10 +8868,10 @@
         <v>19</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8892,10 +8885,10 @@
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8909,10 +8902,10 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8926,10 +8919,10 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8943,10 +8936,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8960,10 +8953,10 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8977,10 +8970,10 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8994,10 +8987,10 @@
         <v>16</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9011,10 +9004,10 @@
         <v>17</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9028,10 +9021,10 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9045,10 +9038,10 @@
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -9062,10 +9055,10 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9079,10 +9072,10 @@
         <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9096,10 +9089,10 @@
         <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9113,10 +9106,10 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9130,10 +9123,10 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9147,10 +9140,10 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9164,10 +9157,10 @@
         <v>16</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9181,10 +9174,10 @@
         <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9198,10 +9191,10 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9215,10 +9208,10 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9232,10 +9225,10 @@
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9249,10 +9242,10 @@
         <v>16</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9266,10 +9259,10 @@
         <v>17</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -9283,10 +9276,10 @@
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -9300,10 +9293,10 @@
         <v>19</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -9317,10 +9310,10 @@
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -9334,10 +9327,10 @@
         <v>16</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9351,10 +9344,10 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9368,10 +9361,10 @@
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9385,10 +9378,10 @@
         <v>19</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -9402,10 +9395,10 @@
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -9419,10 +9412,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -9436,10 +9429,10 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -9453,10 +9446,10 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -9470,10 +9463,10 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -9487,10 +9480,10 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -9504,10 +9497,10 @@
         <v>16</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9521,10 +9514,10 @@
         <v>17</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9538,10 +9531,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9555,10 +9548,10 @@
         <v>19</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9572,15 +9565,15 @@
         <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A073BA2D-C924-40F2-8E67-416E65DDE160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4794D4DA-529C-4ADA-815D-660F68455283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="4425" yWindow="1260" windowWidth="28800" windowHeight="15225" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -1752,99 +1752,66 @@
     <t>DWeibullLocation</t>
   </si>
   <si>
-    <t>wsweibullscale</t>
-  </si>
-  <si>
     <t>Weibull scale parameter of stem biomass distribution</t>
   </si>
   <si>
     <t>wsWeibullScale</t>
   </si>
   <si>
-    <t>wsweibullshape</t>
-  </si>
-  <si>
     <t>Weibull shape parameter of stem biomass distribution</t>
   </si>
   <si>
     <t>wsWeibullShape</t>
   </si>
   <si>
-    <t>wsweibulllocation</t>
-  </si>
-  <si>
     <t>Weibull location parameter of stem biomass distribution</t>
   </si>
   <si>
     <t>wsWeibullLocation</t>
   </si>
   <si>
-    <t>CVdbhDistribution</t>
-  </si>
-  <si>
     <t>Slope of CV of avDBH distribution vs age relationship</t>
   </si>
   <si>
     <t>CV of dbh Distribution</t>
   </si>
   <si>
-    <t>CVwsDistribution</t>
-  </si>
-  <si>
     <t>Coefficient of variation of stem biomass distribution</t>
   </si>
   <si>
     <t>CV of ws Distribution</t>
   </si>
   <si>
-    <t>wsrelBias</t>
-  </si>
-  <si>
     <t xml:space="preserve">Relative bias of calculating avDBH from mean stem biomass </t>
   </si>
   <si>
     <t>Relative bias in dbh from using mean ws</t>
   </si>
   <si>
-    <t>DrelBiaspFS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Relative bias of calculating pFS from avDBH </t>
   </si>
   <si>
     <t>Relative bias in pFS from using mean dbh</t>
   </si>
   <si>
-    <t>DrelBiasheight</t>
-  </si>
-  <si>
     <t xml:space="preserve">Relative bias of calculating mean Height from avDBH </t>
   </si>
   <si>
     <t>Relative bias in height from using mean dbh</t>
   </si>
   <si>
-    <t>DrelBiasBasArea</t>
-  </si>
-  <si>
     <t xml:space="preserve">Relative bias of calculating mean tree basal area from avDBH </t>
   </si>
   <si>
     <t>Relative bias in basal area from using mean dbh</t>
   </si>
   <si>
-    <t>DrelBiasLCL</t>
-  </si>
-  <si>
     <t xml:space="preserve">Relative bias of calculating mean live-crown length from avDBH </t>
   </si>
   <si>
     <t>Relative bias in LCL from using mean dbh</t>
   </si>
   <si>
-    <t>DrelBiasCrowndiameter</t>
-  </si>
-  <si>
     <t xml:space="preserve">Relative bias of calculating mean crown diameter from avDBH </t>
   </si>
   <si>
@@ -2284,6 +2251,39 @@
   </si>
   <si>
     <t>Parameter of crown length equation</t>
+  </si>
+  <si>
+    <t>var_10_4</t>
+  </si>
+  <si>
+    <t>var_10_5</t>
+  </si>
+  <si>
+    <t>var_10_6</t>
+  </si>
+  <si>
+    <t>var_10_7</t>
+  </si>
+  <si>
+    <t>var_10_8</t>
+  </si>
+  <si>
+    <t>var_10_9</t>
+  </si>
+  <si>
+    <t>var_10_10</t>
+  </si>
+  <si>
+    <t>var_10_11</t>
+  </si>
+  <si>
+    <t>var_10_12</t>
+  </si>
+  <si>
+    <t>var_10_13</t>
+  </si>
+  <si>
+    <t>var_10_14</t>
   </si>
 </sst>
 </file>
@@ -2934,7 +2934,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="C18" t="s">
         <v>118</v>
@@ -3155,10 +3155,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -3167,10 +3167,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -3191,10 +3191,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -3203,10 +3203,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -3215,10 +3215,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -3325,10 +3325,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -3645,10 +3645,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>296</v>
@@ -3662,7 +3662,7 @@
         <v>61</v>
       </c>
       <c r="B71" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="C71" t="s">
         <v>118</v>
@@ -3673,10 +3673,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="B72" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="C72" t="s">
         <v>118</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
+        <v>726</v>
+      </c>
+      <c r="B73" t="s">
         <v>737</v>
-      </c>
-      <c r="B73" t="s">
-        <v>748</v>
       </c>
       <c r="C73" t="s">
         <v>118</v>
@@ -3701,18 +3701,18 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="B74" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="B75" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3776,7 +3776,7 @@
         <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="C80" t="s">
         <v>118</v>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
+        <v>727</v>
+      </c>
+      <c r="B81" t="s">
         <v>738</v>
-      </c>
-      <c r="B81" t="s">
-        <v>749</v>
       </c>
       <c r="C81" t="s">
         <v>118</v>
@@ -3801,10 +3801,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="B82" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="C82" t="s">
         <v>118</v>
@@ -3815,10 +3815,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="B83" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="C83" t="s">
         <v>118</v>
@@ -3829,10 +3829,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="B84" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="C84" t="s">
         <v>118</v>
@@ -3846,7 +3846,7 @@
         <v>68</v>
       </c>
       <c r="B85" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="C85" t="s">
         <v>118</v>
@@ -3857,10 +3857,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="B86" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="C86" t="s">
         <v>118</v>
@@ -3871,10 +3871,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="B87" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="C87" t="s">
         <v>118</v>
@@ -3885,10 +3885,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="B88" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="C88" t="s">
         <v>118</v>
@@ -3899,10 +3899,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="B89" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="C89" t="s">
         <v>118</v>
@@ -4772,7 +4772,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>237</v>
@@ -4786,7 +4786,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>237</v>
@@ -4800,7 +4800,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>237</v>
@@ -4814,7 +4814,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>237</v>
@@ -4828,7 +4828,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>237</v>
@@ -5169,7 +5169,7 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>276</v>
@@ -5183,7 +5183,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>276</v>
@@ -5197,7 +5197,7 @@
         <v>18</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>276</v>
@@ -5211,7 +5211,7 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>276</v>
@@ -5225,7 +5225,7 @@
         <v>20</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>276</v>
@@ -5489,13 +5489,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="D53" t="s">
         <v>324</v>
       </c>
       <c r="E53" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5548,7 +5548,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>324</v>
@@ -5562,7 +5562,7 @@
         <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>324</v>
@@ -5576,7 +5576,7 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>324</v>
@@ -5590,7 +5590,7 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>324</v>
@@ -5604,7 +5604,7 @@
         <v>20</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>324</v>
@@ -5924,7 +5924,7 @@
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>364</v>
@@ -5938,7 +5938,7 @@
         <v>17</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>364</v>
@@ -5952,7 +5952,7 @@
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>364</v>
@@ -5966,7 +5966,7 @@
         <v>19</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>364</v>
@@ -5980,7 +5980,7 @@
         <v>20</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>364</v>
@@ -6309,7 +6309,7 @@
         <v>16</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>403</v>
@@ -6323,7 +6323,7 @@
         <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>403</v>
@@ -6337,7 +6337,7 @@
         <v>18</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>403</v>
@@ -6351,7 +6351,7 @@
         <v>19</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>403</v>
@@ -6365,7 +6365,7 @@
         <v>20</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>403</v>
@@ -6425,7 +6425,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="D104" t="s">
         <v>443</v>
@@ -6706,7 +6706,7 @@
         <v>16</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>443</v>
@@ -6720,7 +6720,7 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>443</v>
@@ -6734,7 +6734,7 @@
         <v>18</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>443</v>
@@ -6748,7 +6748,7 @@
         <v>19</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>443</v>
@@ -6762,7 +6762,7 @@
         <v>20</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>443</v>
@@ -7103,7 +7103,7 @@
         <v>16</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>485</v>
@@ -7117,7 +7117,7 @@
         <v>17</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>485</v>
@@ -7131,7 +7131,7 @@
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>485</v>
@@ -7145,7 +7145,7 @@
         <v>19</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>485</v>
@@ -7159,7 +7159,7 @@
         <v>20</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>485</v>
@@ -7219,13 +7219,13 @@
         <v>3</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="D144" t="s">
         <v>529</v>
       </c>
       <c r="E144" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F144" t="s">
         <v>281</v>
@@ -7242,7 +7242,7 @@
         <v>4</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="D145" t="s">
         <v>529</v>
@@ -7256,7 +7256,7 @@
         <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="D146" t="s">
         <v>529</v>
@@ -7270,7 +7270,7 @@
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="D147" t="s">
         <v>529</v>
@@ -7284,13 +7284,13 @@
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="D148" t="s">
         <v>529</v>
       </c>
       <c r="E148" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -7301,13 +7301,13 @@
         <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="D149" t="s">
         <v>529</v>
       </c>
       <c r="E149" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -7318,7 +7318,7 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="D150" t="s">
         <v>529</v>
@@ -7335,13 +7335,13 @@
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="D151" t="s">
         <v>529</v>
       </c>
       <c r="E151" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -7352,7 +7352,7 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="D152" t="s">
         <v>529</v>
@@ -7366,7 +7366,7 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D153" t="s">
         <v>529</v>
@@ -7380,7 +7380,7 @@
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="D154" t="s">
         <v>529</v>
@@ -7394,7 +7394,7 @@
         <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="D155" t="s">
         <v>529</v>
@@ -7422,7 +7422,7 @@
         <v>16</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>529</v>
@@ -7436,7 +7436,7 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>529</v>
@@ -7450,7 +7450,7 @@
         <v>18</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>529</v>
@@ -7464,7 +7464,7 @@
         <v>19</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>529</v>
@@ -7478,7 +7478,7 @@
         <v>20</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>529</v>
@@ -7741,7 +7741,7 @@
         <v>16</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>539</v>
@@ -7755,7 +7755,7 @@
         <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>539</v>
@@ -7769,7 +7769,7 @@
         <v>18</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>539</v>
@@ -7783,7 +7783,7 @@
         <v>19</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>539</v>
@@ -7797,7 +7797,7 @@
         <v>20</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>539</v>
@@ -7879,20 +7879,20 @@
       <c r="B185">
         <v>4</v>
       </c>
-      <c r="C185" t="s">
-        <v>573</v>
+      <c r="C185" s="1" t="s">
+        <v>740</v>
       </c>
       <c r="D185" t="s">
         <v>564</v>
       </c>
       <c r="E185" t="s">
+        <v>573</v>
+      </c>
+      <c r="F185" t="s">
+        <v>118</v>
+      </c>
+      <c r="G185" t="s">
         <v>574</v>
-      </c>
-      <c r="F185" t="s">
-        <v>118</v>
-      </c>
-      <c r="G185" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -7902,20 +7902,20 @@
       <c r="B186">
         <v>5</v>
       </c>
-      <c r="C186" t="s">
-        <v>576</v>
+      <c r="C186" s="1" t="s">
+        <v>741</v>
       </c>
       <c r="D186" t="s">
         <v>564</v>
       </c>
       <c r="E186" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F186" t="s">
         <v>118</v>
       </c>
       <c r="G186" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -7925,20 +7925,20 @@
       <c r="B187">
         <v>6</v>
       </c>
-      <c r="C187" t="s">
-        <v>579</v>
+      <c r="C187" s="1" t="s">
+        <v>742</v>
       </c>
       <c r="D187" t="s">
         <v>564</v>
       </c>
       <c r="E187" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F187" t="s">
         <v>118</v>
       </c>
       <c r="G187" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7948,20 +7948,20 @@
       <c r="B188">
         <v>7</v>
       </c>
-      <c r="C188" t="s">
-        <v>582</v>
+      <c r="C188" s="1" t="s">
+        <v>743</v>
       </c>
       <c r="D188" t="s">
         <v>564</v>
       </c>
       <c r="E188" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F188" t="s">
         <v>343</v>
       </c>
       <c r="G188" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7971,20 +7971,20 @@
       <c r="B189">
         <v>8</v>
       </c>
-      <c r="C189" t="s">
-        <v>585</v>
+      <c r="C189" s="1" t="s">
+        <v>744</v>
       </c>
       <c r="D189" t="s">
         <v>564</v>
       </c>
       <c r="E189" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="F189" t="s">
         <v>343</v>
       </c>
       <c r="G189" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -7994,20 +7994,20 @@
       <c r="B190">
         <v>9</v>
       </c>
-      <c r="C190" t="s">
-        <v>588</v>
+      <c r="C190" s="1" t="s">
+        <v>745</v>
       </c>
       <c r="D190" t="s">
         <v>564</v>
       </c>
       <c r="E190" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="F190" t="s">
         <v>343</v>
       </c>
       <c r="G190" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -8017,20 +8017,20 @@
       <c r="B191">
         <v>10</v>
       </c>
-      <c r="C191" t="s">
-        <v>591</v>
+      <c r="C191" s="1" t="s">
+        <v>746</v>
       </c>
       <c r="D191" t="s">
         <v>564</v>
       </c>
       <c r="E191" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="F191" t="s">
         <v>343</v>
       </c>
       <c r="G191" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -8040,20 +8040,20 @@
       <c r="B192">
         <v>11</v>
       </c>
-      <c r="C192" t="s">
-        <v>594</v>
+      <c r="C192" s="1" t="s">
+        <v>747</v>
       </c>
       <c r="D192" t="s">
         <v>564</v>
       </c>
       <c r="E192" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="F192" t="s">
         <v>343</v>
       </c>
       <c r="G192" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -8063,20 +8063,20 @@
       <c r="B193">
         <v>12</v>
       </c>
-      <c r="C193" t="s">
-        <v>597</v>
+      <c r="C193" s="1" t="s">
+        <v>748</v>
       </c>
       <c r="D193" t="s">
         <v>564</v>
       </c>
       <c r="E193" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="F193" t="s">
         <v>343</v>
       </c>
       <c r="G193" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -8086,20 +8086,20 @@
       <c r="B194">
         <v>13</v>
       </c>
-      <c r="C194" t="s">
-        <v>600</v>
+      <c r="C194" s="1" t="s">
+        <v>749</v>
       </c>
       <c r="D194" t="s">
         <v>564</v>
       </c>
       <c r="E194" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="F194" t="s">
         <v>343</v>
       </c>
       <c r="G194" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -8109,20 +8109,20 @@
       <c r="B195">
         <v>14</v>
       </c>
-      <c r="C195" t="s">
-        <v>603</v>
+      <c r="C195" s="1" t="s">
+        <v>750</v>
       </c>
       <c r="D195" t="s">
         <v>564</v>
       </c>
       <c r="E195" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="F195" t="s">
         <v>343</v>
       </c>
       <c r="G195" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -8132,8 +8132,8 @@
       <c r="B196">
         <v>15</v>
       </c>
-      <c r="C196" t="s">
-        <v>606</v>
+      <c r="C196" s="1" t="s">
+        <v>595</v>
       </c>
       <c r="D196" t="s">
         <v>564</v>
@@ -8147,7 +8147,7 @@
         <v>16</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>564</v>
@@ -8161,7 +8161,7 @@
         <v>17</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>564</v>
@@ -8175,7 +8175,7 @@
         <v>18</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>564</v>
@@ -8189,7 +8189,7 @@
         <v>19</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>564</v>
@@ -8203,7 +8203,7 @@
         <v>20</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>564</v>
@@ -8217,13 +8217,13 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="D202" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E202" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="F202" t="s">
         <v>281</v>
@@ -8237,13 +8237,13 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="D203" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E203" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="F203" t="s">
         <v>366</v>
@@ -8257,13 +8257,13 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="D204" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E204" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="F204" t="s">
         <v>366</v>
@@ -8277,13 +8277,13 @@
         <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="D205" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E205" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="F205" t="s">
         <v>366</v>
@@ -8297,13 +8297,13 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="D206" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E206" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="F206" t="s">
         <v>281</v>
@@ -8317,13 +8317,13 @@
         <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="D207" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E207" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="F207" t="s">
         <v>366</v>
@@ -8337,13 +8337,13 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="D208" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E208" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="F208" t="s">
         <v>366</v>
@@ -8357,13 +8357,13 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="D209" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E209" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="F209" t="s">
         <v>366</v>
@@ -8377,13 +8377,13 @@
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="D210" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E210" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="F210" t="s">
         <v>281</v>
@@ -8397,13 +8397,13 @@
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="D211" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E211" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="F211" t="s">
         <v>366</v>
@@ -8417,13 +8417,13 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="D212" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E212" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="F212" t="s">
         <v>366</v>
@@ -8437,13 +8437,13 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="D213" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E213" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="F213" t="s">
         <v>366</v>
@@ -8457,13 +8457,13 @@
         <v>13</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="D214" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E214" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="F214" t="s">
         <v>281</v>
@@ -8477,13 +8477,13 @@
         <v>14</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="D215" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E215" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="F215" t="s">
         <v>366</v>
@@ -8497,13 +8497,13 @@
         <v>15</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="D216" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E216" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="F216" t="s">
         <v>366</v>
@@ -8517,13 +8517,13 @@
         <v>16</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E217" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="F217" t="s">
         <v>366</v>
@@ -8537,13 +8537,13 @@
         <v>17</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E218" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8554,13 +8554,13 @@
         <v>18</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="E219" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>128</v>
@@ -8574,10 +8574,10 @@
         <v>19</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8588,10 +8588,10 @@
         <v>20</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -8647,7 +8647,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>237</v>
@@ -8664,7 +8664,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>237</v>
@@ -8681,7 +8681,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>237</v>
@@ -8698,7 +8698,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>237</v>
@@ -8715,7 +8715,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>237</v>
@@ -8732,7 +8732,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>276</v>
@@ -8749,7 +8749,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>276</v>
@@ -8766,7 +8766,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>276</v>
@@ -8783,7 +8783,7 @@
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>276</v>
@@ -8800,7 +8800,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>276</v>
@@ -8817,7 +8817,7 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>324</v>
@@ -8834,7 +8834,7 @@
         <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>324</v>
@@ -8851,7 +8851,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>324</v>
@@ -8868,7 +8868,7 @@
         <v>19</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>324</v>
@@ -8885,7 +8885,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>324</v>
@@ -8902,7 +8902,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>364</v>
@@ -8919,7 +8919,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>364</v>
@@ -8936,7 +8936,7 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>364</v>
@@ -8953,7 +8953,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>364</v>
@@ -8970,7 +8970,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>364</v>
@@ -8987,7 +8987,7 @@
         <v>16</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>403</v>
@@ -9004,7 +9004,7 @@
         <v>17</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>403</v>
@@ -9021,7 +9021,7 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>403</v>
@@ -9038,7 +9038,7 @@
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>403</v>
@@ -9055,7 +9055,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>403</v>
@@ -9072,7 +9072,7 @@
         <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>443</v>
@@ -9089,7 +9089,7 @@
         <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>443</v>
@@ -9106,7 +9106,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>443</v>
@@ -9123,7 +9123,7 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>443</v>
@@ -9140,7 +9140,7 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>443</v>
@@ -9157,7 +9157,7 @@
         <v>16</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>485</v>
@@ -9174,7 +9174,7 @@
         <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>485</v>
@@ -9191,7 +9191,7 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>485</v>
@@ -9208,7 +9208,7 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>485</v>
@@ -9225,7 +9225,7 @@
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>485</v>
@@ -9242,7 +9242,7 @@
         <v>16</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>529</v>
@@ -9259,7 +9259,7 @@
         <v>17</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>529</v>
@@ -9276,7 +9276,7 @@
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>529</v>
@@ -9293,7 +9293,7 @@
         <v>19</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>529</v>
@@ -9310,7 +9310,7 @@
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>529</v>
@@ -9327,7 +9327,7 @@
         <v>16</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>539</v>
@@ -9344,7 +9344,7 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>539</v>
@@ -9361,7 +9361,7 @@
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>539</v>
@@ -9378,7 +9378,7 @@
         <v>19</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>539</v>
@@ -9395,7 +9395,7 @@
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>539</v>
@@ -9412,7 +9412,7 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>564</v>
@@ -9429,7 +9429,7 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>564</v>
@@ -9446,7 +9446,7 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>564</v>
@@ -9463,7 +9463,7 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>564</v>
@@ -9480,7 +9480,7 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>564</v>
@@ -9497,10 +9497,10 @@
         <v>16</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9514,10 +9514,10 @@
         <v>17</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9531,10 +9531,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9548,10 +9548,10 @@
         <v>19</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9565,15 +9565,15 @@
         <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4794D4DA-529C-4ADA-815D-660F68455283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E496D2-239C-443D-A221-A3F18704352F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4425" yWindow="1260" windowWidth="28800" windowHeight="15225" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="39270" yWindow="450" windowWidth="28800" windowHeight="15225" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="751">
   <si>
     <t>pFS2</t>
   </si>
@@ -3706,6 +3706,12 @@
       <c r="B74" t="s">
         <v>737</v>
       </c>
+      <c r="C74" t="s">
+        <v>118</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
@@ -3713,6 +3719,12 @@
       </c>
       <c r="B75" t="s">
         <v>737</v>
+      </c>
+      <c r="C75" t="s">
+        <v>118</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:4">

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E496D2-239C-443D-A221-A3F18704352F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B211A54-2CCE-4067-9E6D-5EBE5AEB4BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39270" yWindow="450" windowWidth="28800" windowHeight="15225" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="721">
   <si>
     <t>pFS2</t>
   </si>
@@ -285,51 +285,6 @@
     <t>DlocationC</t>
   </si>
   <si>
-    <t>wsscale0</t>
-  </si>
-  <si>
-    <t>wsscaleB</t>
-  </si>
-  <si>
-    <t>wsscalerh</t>
-  </si>
-  <si>
-    <t>wsscalet</t>
-  </si>
-  <si>
-    <t>wsscaleC</t>
-  </si>
-  <si>
-    <t>wsshape0</t>
-  </si>
-  <si>
-    <t>wsshapeB</t>
-  </si>
-  <si>
-    <t>wsshaperh</t>
-  </si>
-  <si>
-    <t>wsshapet</t>
-  </si>
-  <si>
-    <t>wsshapeC</t>
-  </si>
-  <si>
-    <t>wslocation0</t>
-  </si>
-  <si>
-    <t>wslocationB</t>
-  </si>
-  <si>
-    <t>wslocationrh</t>
-  </si>
-  <si>
-    <t>wslocationt</t>
-  </si>
-  <si>
-    <t>wslocationC</t>
-  </si>
-  <si>
     <t>Qa</t>
   </si>
   <si>
@@ -682,51 +637,6 @@
   </si>
   <si>
     <t>Slope of competition in relationship for Weibull location parameter of D distribution</t>
-  </si>
-  <si>
-    <t>Constant in the relationship for Weibull scale parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of DBH in relationship for Weibull scale parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of relative height in relationship for Weibull scale parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of age in relationship for Weibull scale parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of competition in relationship for Weibull scale parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Constant in the relationship for Weibull shape parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of DBH in relationship for Weibull shape parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of relative height in relationship for Weibull shape parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of age in relationship for Weibull shape parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of competition in relationship for Weibull shape parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Constant in the relationship for Weibull location parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of DBH in relationship for Weibull location parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of relative height in relationship for Weibull location parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of age in relationship for Weibull location parameter of ws distribution</t>
-  </si>
-  <si>
-    <t>Slope of competition in relationship for Weibull location parameter of ws distribution</t>
   </si>
   <si>
     <t>group_id</t>
@@ -2693,16 +2603,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2710,10 +2620,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2724,10 +2634,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D3">
         <v>0.15</v>
@@ -2738,10 +2648,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D4">
         <v>9.5000000000000001E-2</v>
@@ -2752,10 +2662,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D5">
         <v>2.4</v>
@@ -2766,10 +2676,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D6">
         <v>0.8</v>
@@ -2780,10 +2690,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D7">
         <v>0.25</v>
@@ -2794,10 +2704,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D8">
         <v>2.7E-2</v>
@@ -2808,10 +2718,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D9">
         <v>1E-3</v>
@@ -2822,10 +2732,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D10">
         <v>12</v>
@@ -2836,10 +2746,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D11">
         <v>1.4999999999999999E-2</v>
@@ -2850,7 +2760,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -2864,7 +2774,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -2878,10 +2788,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D14">
         <v>8.5</v>
@@ -2892,10 +2802,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C15" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D15">
         <v>16</v>
@@ -2906,10 +2816,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D16">
         <v>40</v>
@@ -2920,10 +2830,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -2934,10 +2844,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>724</v>
+        <v>694</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D18">
         <v>0.7</v>
@@ -2948,10 +2858,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D19">
         <v>9</v>
@@ -2962,10 +2872,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D20">
         <v>1.4</v>
@@ -2976,10 +2886,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D21">
         <v>0.7</v>
@@ -2990,10 +2900,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -3004,10 +2914,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3018,10 +2928,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -3032,10 +2942,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D25">
         <v>50</v>
@@ -3046,10 +2956,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -3060,10 +2970,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D27">
         <v>0.95</v>
@@ -3074,10 +2984,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -3088,10 +2998,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -3102,10 +3012,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -3116,10 +3026,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -3130,10 +3040,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="D32">
         <v>300</v>
@@ -3144,10 +3054,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D33">
         <v>1.5</v>
@@ -3155,10 +3065,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>597</v>
+        <v>567</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>603</v>
+        <v>573</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -3167,10 +3077,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>598</v>
+        <v>568</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>604</v>
+        <v>574</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -3179,10 +3089,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>599</v>
+        <v>569</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>605</v>
+        <v>575</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -3191,10 +3101,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>600</v>
+        <v>570</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>606</v>
+        <v>576</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -3203,10 +3113,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>601</v>
+        <v>571</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>607</v>
+        <v>577</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -3215,10 +3125,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>602</v>
+        <v>572</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>608</v>
+        <v>578</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -3230,10 +3140,10 @@
         <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -3244,10 +3154,10 @@
         <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="C41" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D41">
         <v>0.2</v>
@@ -3258,10 +3168,10 @@
         <v>35</v>
       </c>
       <c r="B42" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D42">
         <v>0.2</v>
@@ -3272,10 +3182,10 @@
         <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D43">
         <v>11</v>
@@ -3286,10 +3196,10 @@
         <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C44" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -3300,10 +3210,10 @@
         <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D45">
         <v>2.5</v>
@@ -3314,10 +3224,10 @@
         <v>39</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C46" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D46">
         <v>0.5</v>
@@ -3325,10 +3235,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>710</v>
+        <v>680</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>711</v>
+        <v>681</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -3340,10 +3250,10 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -3354,10 +3264,10 @@
         <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C49" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D49">
         <v>0.15</v>
@@ -3368,10 +3278,10 @@
         <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -3382,10 +3292,10 @@
         <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="C51" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D51">
         <v>5</v>
@@ -3396,10 +3306,10 @@
         <v>44</v>
       </c>
       <c r="B52" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C52" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D52">
         <v>0.06</v>
@@ -3410,10 +3320,10 @@
         <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C53" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D53">
         <v>0.47</v>
@@ -3424,10 +3334,10 @@
         <v>46</v>
       </c>
       <c r="B54" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C54" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3438,10 +3348,10 @@
         <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="C55" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D55">
         <v>0.02</v>
@@ -3452,10 +3362,10 @@
         <v>48</v>
       </c>
       <c r="B56" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D56">
         <v>3.33</v>
@@ -3466,10 +3376,10 @@
         <v>49</v>
       </c>
       <c r="B57" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="C57" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D57">
         <v>0.05</v>
@@ -3480,10 +3390,10 @@
         <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="C58" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D58">
         <v>0.2</v>
@@ -3494,10 +3404,10 @@
         <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C59" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D59">
         <v>0.66</v>
@@ -3508,10 +3418,10 @@
         <v>52</v>
       </c>
       <c r="B60" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C60" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -3522,10 +3432,10 @@
         <v>53</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C61" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D61">
         <v>4.4000000000000004</v>
@@ -3536,10 +3446,10 @@
         <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C62" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="D62">
         <v>27</v>
@@ -3550,10 +3460,10 @@
         <v>55</v>
       </c>
       <c r="B63" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D63">
         <v>0.75</v>
@@ -3564,10 +3474,10 @@
         <v>56</v>
       </c>
       <c r="B64" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D64">
         <v>0.15</v>
@@ -3578,10 +3488,10 @@
         <v>57</v>
       </c>
       <c r="B65" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C65" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3592,10 +3502,10 @@
         <v>58</v>
       </c>
       <c r="B66" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="C66" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D66">
         <v>0.45</v>
@@ -3606,10 +3516,10 @@
         <v>59</v>
       </c>
       <c r="B67" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="D67">
         <v>0.45</v>
@@ -3620,10 +3530,10 @@
         <v>60</v>
       </c>
       <c r="B68" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="C68" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -3634,10 +3544,10 @@
         <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C69" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D69">
         <v>3</v>
@@ -3645,13 +3555,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
-        <v>708</v>
+        <v>678</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>709</v>
+        <v>679</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="D70" s="1">
         <v>1.3</v>
@@ -3662,10 +3572,10 @@
         <v>61</v>
       </c>
       <c r="B71" t="s">
-        <v>737</v>
+        <v>707</v>
       </c>
       <c r="C71" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -3673,13 +3583,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>725</v>
+        <v>695</v>
       </c>
       <c r="B72" t="s">
-        <v>737</v>
+        <v>707</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3687,13 +3597,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>726</v>
+        <v>696</v>
       </c>
       <c r="B73" t="s">
-        <v>737</v>
+        <v>707</v>
       </c>
       <c r="C73" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -3701,13 +3611,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>735</v>
+        <v>705</v>
       </c>
       <c r="B74" t="s">
-        <v>737</v>
+        <v>707</v>
       </c>
       <c r="C74" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -3715,13 +3625,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>736</v>
+        <v>706</v>
       </c>
       <c r="B75" t="s">
-        <v>737</v>
+        <v>707</v>
       </c>
       <c r="C75" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -3732,10 +3642,10 @@
         <v>62</v>
       </c>
       <c r="B76" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C76" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -3746,10 +3656,10 @@
         <v>63</v>
       </c>
       <c r="B77" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="C77" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3760,10 +3670,10 @@
         <v>64</v>
       </c>
       <c r="B78" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C78" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3774,10 +3684,10 @@
         <v>65</v>
       </c>
       <c r="B79" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C79" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3788,10 +3698,10 @@
         <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>738</v>
+        <v>708</v>
       </c>
       <c r="C80" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3799,13 +3709,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>727</v>
+        <v>697</v>
       </c>
       <c r="B81" t="s">
-        <v>738</v>
+        <v>708</v>
       </c>
       <c r="C81" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3813,13 +3723,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>728</v>
+        <v>698</v>
       </c>
       <c r="B82" t="s">
-        <v>738</v>
+        <v>708</v>
       </c>
       <c r="C82" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -3827,13 +3737,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>729</v>
+        <v>699</v>
       </c>
       <c r="B83" t="s">
-        <v>738</v>
+        <v>708</v>
       </c>
       <c r="C83" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -3841,13 +3751,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>730</v>
+        <v>700</v>
       </c>
       <c r="B84" t="s">
-        <v>738</v>
+        <v>708</v>
       </c>
       <c r="C84" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3858,10 +3768,10 @@
         <v>68</v>
       </c>
       <c r="B85" t="s">
-        <v>739</v>
+        <v>709</v>
       </c>
       <c r="C85" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3869,13 +3779,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>731</v>
+        <v>701</v>
       </c>
       <c r="B86" t="s">
-        <v>739</v>
+        <v>709</v>
       </c>
       <c r="C86" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3883,13 +3793,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>732</v>
+        <v>702</v>
       </c>
       <c r="B87" t="s">
-        <v>739</v>
+        <v>709</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3897,13 +3807,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>733</v>
+        <v>703</v>
       </c>
       <c r="B88" t="s">
-        <v>739</v>
+        <v>709</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -3911,13 +3821,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>734</v>
+        <v>704</v>
       </c>
       <c r="B89" t="s">
-        <v>739</v>
+        <v>709</v>
       </c>
       <c r="C89" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3925,13 +3835,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="B90" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="C90" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D90">
         <v>-90</v>
@@ -3939,13 +3849,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B91" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C91" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D91">
         <v>0.8</v>
@@ -3953,13 +3863,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B92" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="C92" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="D92">
         <v>24</v>
@@ -3967,13 +3877,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="B93" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C93" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D93">
         <v>2.2999999999999998</v>
@@ -3991,21 +3901,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF000D6-A72C-6444-9177-22D437B8361A}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <cols>
+    <col min="2" max="2" width="73.625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B1" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D1" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4013,10 +3926,10 @@
         <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -4027,10 +3940,10 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -4041,10 +3954,10 @@
         <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -4055,10 +3968,10 @@
         <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -4069,10 +3982,10 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -4083,10 +3996,10 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -4097,10 +4010,10 @@
         <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -4111,10 +4024,10 @@
         <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -4125,10 +4038,10 @@
         <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -4139,10 +4052,10 @@
         <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -4153,10 +4066,10 @@
         <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -4167,10 +4080,10 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4181,10 +4094,10 @@
         <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C14" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -4195,10 +4108,10 @@
         <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -4209,222 +4122,12 @@
         <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="D16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" t="s">
-        <v>217</v>
-      </c>
-      <c r="C17" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" t="s">
-        <v>218</v>
-      </c>
-      <c r="C18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" t="s">
-        <v>219</v>
-      </c>
-      <c r="C19" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" t="s">
-        <v>220</v>
-      </c>
-      <c r="C20" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" t="s">
-        <v>221</v>
-      </c>
-      <c r="C21" t="s">
-        <v>118</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" t="s">
-        <v>222</v>
-      </c>
-      <c r="C22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" t="s">
-        <v>223</v>
-      </c>
-      <c r="C23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" t="s">
-        <v>224</v>
-      </c>
-      <c r="C24" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" t="s">
-        <v>225</v>
-      </c>
-      <c r="C25" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" t="s">
-        <v>226</v>
-      </c>
-      <c r="C26" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C27" t="s">
-        <v>118</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" t="s">
-        <v>228</v>
-      </c>
-      <c r="C28" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" t="s">
-        <v>229</v>
-      </c>
-      <c r="C29" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>97</v>
-      </c>
-      <c r="B30" t="s">
-        <v>230</v>
-      </c>
-      <c r="C30" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" t="s">
-        <v>231</v>
-      </c>
-      <c r="C31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31">
         <v>0</v>
       </c>
     </row>
@@ -4449,25 +4152,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="B1" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="C1" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="D1" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="E1" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="F1" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="G1" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4478,19 +4181,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="F2" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="G2" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4501,19 +4204,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="F3" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="G3" t="s">
-        <v>242</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4524,19 +4227,19 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="F4" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="G4" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4547,19 +4250,19 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="G5" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4570,19 +4273,19 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="D6" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="E6" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="F6" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="G6" t="s">
-        <v>251</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4593,19 +4296,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="D7" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="E7" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="F7" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="G7" t="s">
-        <v>255</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4616,19 +4319,19 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="E8" t="s">
-        <v>256</v>
+        <v>226</v>
       </c>
       <c r="F8" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="G8" t="s">
-        <v>258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4639,19 +4342,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="D9" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="E9" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="F9" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="G9" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4662,19 +4365,19 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="E10" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="F10" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="G10" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -4685,16 +4388,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="D11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E11" t="s">
         <v>237</v>
       </c>
-      <c r="E11" t="s">
-        <v>267</v>
-      </c>
       <c r="G11" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -4705,19 +4408,19 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>269</v>
+        <v>239</v>
       </c>
       <c r="D12" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="E12" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="F12" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="G12" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4728,10 +4431,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="D13" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4742,10 +4445,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="D14" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4756,10 +4459,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>274</v>
+        <v>244</v>
       </c>
       <c r="D15" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4770,10 +4473,10 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="D16" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -4784,10 +4487,10 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>644</v>
+        <v>614</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -4798,10 +4501,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>645</v>
+        <v>615</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4812,10 +4515,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>646</v>
+        <v>616</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4826,10 +4529,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>647</v>
+        <v>617</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -4840,10 +4543,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>648</v>
+        <v>618</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -4854,19 +4557,19 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E22" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="F22" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="G22" t="s">
-        <v>278</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4877,19 +4580,19 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="D23" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E23" t="s">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="F23" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="G23" t="s">
-        <v>282</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4900,19 +4603,19 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="D24" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E24" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="F24" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="G24" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4923,19 +4626,19 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="D25" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E25" t="s">
-        <v>288</v>
+        <v>258</v>
       </c>
       <c r="F25" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="G25" t="s">
-        <v>290</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4946,19 +4649,19 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E26" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
       <c r="F26" t="s">
-        <v>293</v>
+        <v>263</v>
       </c>
       <c r="G26" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -4969,19 +4672,19 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E27" t="s">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="F27" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="G27" t="s">
-        <v>297</v>
+        <v>267</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -4992,19 +4695,19 @@
         <v>7</v>
       </c>
       <c r="C28" t="s">
-        <v>298</v>
+        <v>268</v>
       </c>
       <c r="D28" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E28" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="F28" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G28" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -5015,19 +4718,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="D29" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E29" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="F29" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="G29" t="s">
-        <v>303</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -5038,19 +4741,19 @@
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="D30" t="s">
+        <v>246</v>
+      </c>
+      <c r="E30" t="s">
+        <v>275</v>
+      </c>
+      <c r="F30" t="s">
+        <v>266</v>
+      </c>
+      <c r="G30" t="s">
         <v>276</v>
-      </c>
-      <c r="E30" t="s">
-        <v>305</v>
-      </c>
-      <c r="F30" t="s">
-        <v>296</v>
-      </c>
-      <c r="G30" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -5061,19 +4764,19 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="D31" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E31" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="F31" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="G31" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -5084,19 +4787,19 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="D32" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E32" t="s">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="F32" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="G32" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -5107,19 +4810,19 @@
         <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="D33" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E33" t="s">
-        <v>316</v>
+        <v>286</v>
       </c>
       <c r="F33" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="G33" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -5130,19 +4833,19 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="D34" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="E34" t="s">
-        <v>319</v>
+        <v>289</v>
       </c>
       <c r="F34" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="G34" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -5153,10 +4856,10 @@
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="D35" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -5167,10 +4870,10 @@
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>322</v>
+        <v>292</v>
       </c>
       <c r="D36" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -5181,10 +4884,10 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>649</v>
+        <v>619</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -5195,10 +4898,10 @@
         <v>17</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -5209,10 +4912,10 @@
         <v>18</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>651</v>
+        <v>621</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -5223,10 +4926,10 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>652</v>
+        <v>622</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -5237,10 +4940,10 @@
         <v>20</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>653</v>
+        <v>623</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -5251,19 +4954,19 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="D42" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E42" t="s">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="F42" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G42" t="s">
-        <v>326</v>
+        <v>296</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -5274,19 +4977,19 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
       <c r="D43" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E43" t="s">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="F43" t="s">
-        <v>329</v>
+        <v>299</v>
       </c>
       <c r="G43" t="s">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -5297,19 +5000,19 @@
         <v>3</v>
       </c>
       <c r="C44" t="s">
-        <v>331</v>
+        <v>301</v>
       </c>
       <c r="D44" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E44" t="s">
-        <v>332</v>
+        <v>302</v>
       </c>
       <c r="F44" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="G44" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -5320,19 +5023,19 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="D45" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E45" t="s">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="F45" t="s">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="G45" t="s">
-        <v>337</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -5343,16 +5046,16 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="D46" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E46" t="s">
-        <v>339</v>
+        <v>309</v>
       </c>
       <c r="G46" t="s">
-        <v>340</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -5363,19 +5066,19 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>341</v>
+        <v>311</v>
       </c>
       <c r="D47" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E47" t="s">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="F47" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="G47" t="s">
-        <v>344</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -5386,19 +5089,19 @@
         <v>7</v>
       </c>
       <c r="C48" t="s">
-        <v>345</v>
+        <v>315</v>
       </c>
       <c r="D48" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E48" t="s">
-        <v>346</v>
+        <v>316</v>
       </c>
       <c r="F48" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G48" t="s">
-        <v>347</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5409,19 +5112,19 @@
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="D49" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E49" t="s">
-        <v>349</v>
+        <v>319</v>
       </c>
       <c r="F49" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G49" t="s">
-        <v>350</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -5432,19 +5135,19 @@
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>351</v>
+        <v>321</v>
       </c>
       <c r="D50" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E50" t="s">
-        <v>352</v>
+        <v>322</v>
       </c>
       <c r="F50" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G50" t="s">
-        <v>353</v>
+        <v>323</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -5455,19 +5158,19 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>354</v>
+        <v>324</v>
       </c>
       <c r="D51" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E51" t="s">
-        <v>355</v>
+        <v>325</v>
       </c>
       <c r="F51" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="G51" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -5478,19 +5181,19 @@
         <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>358</v>
+        <v>328</v>
       </c>
       <c r="D52" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E52" t="s">
-        <v>359</v>
+        <v>329</v>
       </c>
       <c r="F52" t="s">
-        <v>261</v>
+        <v>231</v>
       </c>
       <c r="G52" t="s">
-        <v>360</v>
+        <v>330</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -5501,13 +5204,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>712</v>
+        <v>682</v>
       </c>
       <c r="D53" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="E53" t="s">
-        <v>713</v>
+        <v>683</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5518,10 +5221,10 @@
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>361</v>
+        <v>331</v>
       </c>
       <c r="D54" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -5532,10 +5235,10 @@
         <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="D55" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -5546,10 +5249,10 @@
         <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>363</v>
+        <v>333</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -5560,10 +5263,10 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>654</v>
+        <v>624</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -5574,10 +5277,10 @@
         <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>655</v>
+        <v>625</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -5588,10 +5291,10 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>656</v>
+        <v>626</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -5602,10 +5305,10 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>657</v>
+        <v>627</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -5616,10 +5319,10 @@
         <v>20</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>658</v>
+        <v>628</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -5630,19 +5333,19 @@
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D62" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="E62" t="s">
-        <v>365</v>
+        <v>335</v>
       </c>
       <c r="F62" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="G62" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5653,19 +5356,19 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D63" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="E63" t="s">
-        <v>368</v>
+        <v>338</v>
       </c>
       <c r="F63" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="G63" t="s">
-        <v>369</v>
+        <v>339</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5676,19 +5379,19 @@
         <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="D64" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="E64" t="s">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="F64" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="G64" t="s">
-        <v>371</v>
+        <v>341</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -5699,19 +5402,19 @@
         <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="D65" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="E65" t="s">
-        <v>373</v>
+        <v>343</v>
       </c>
       <c r="F65" t="s">
-        <v>374</v>
+        <v>344</v>
       </c>
       <c r="G65" t="s">
-        <v>375</v>
+        <v>345</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -5722,19 +5425,19 @@
         <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>376</v>
+        <v>346</v>
       </c>
       <c r="D66" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="E66" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="F66" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="G66" t="s">
-        <v>379</v>
+        <v>349</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5745,16 +5448,16 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="D67" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="E67" t="s">
-        <v>381</v>
+        <v>351</v>
       </c>
       <c r="G67" t="s">
-        <v>382</v>
+        <v>352</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -5765,19 +5468,19 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="D68" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="E68" t="s">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="F68" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="G68" t="s">
-        <v>385</v>
+        <v>355</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5788,19 +5491,19 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="D69" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="E69" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="F69" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="G69" t="s">
-        <v>388</v>
+        <v>358</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -5811,19 +5514,19 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
-        <v>389</v>
+        <v>359</v>
       </c>
       <c r="D70" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="E70" t="s">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="F70" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="G70" t="s">
-        <v>391</v>
+        <v>361</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -5834,19 +5537,19 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>392</v>
+        <v>362</v>
       </c>
       <c r="D71" t="s">
+        <v>334</v>
+      </c>
+      <c r="E71" t="s">
+        <v>363</v>
+      </c>
+      <c r="F71" t="s">
+        <v>336</v>
+      </c>
+      <c r="G71" t="s">
         <v>364</v>
-      </c>
-      <c r="E71" t="s">
-        <v>393</v>
-      </c>
-      <c r="F71" t="s">
-        <v>366</v>
-      </c>
-      <c r="G71" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -5857,19 +5560,19 @@
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="D72" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="E72" t="s">
-        <v>396</v>
+        <v>366</v>
       </c>
       <c r="F72" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="G72" t="s">
-        <v>397</v>
+        <v>367</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -5880,10 +5583,10 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>398</v>
+        <v>368</v>
       </c>
       <c r="D73" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5894,10 +5597,10 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="D74" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -5908,10 +5611,10 @@
         <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="D75" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -5922,10 +5625,10 @@
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>401</v>
+        <v>371</v>
       </c>
       <c r="D76" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -5936,10 +5639,10 @@
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>659</v>
+        <v>629</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -5950,10 +5653,10 @@
         <v>17</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5964,10 +5667,10 @@
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>661</v>
+        <v>631</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -5978,10 +5681,10 @@
         <v>19</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>662</v>
+        <v>632</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5992,10 +5695,10 @@
         <v>20</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>663</v>
+        <v>633</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -6006,19 +5709,19 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="D82" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E82" t="s">
-        <v>404</v>
+        <v>374</v>
       </c>
       <c r="F82" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G82" t="s">
-        <v>405</v>
+        <v>375</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -6029,19 +5732,19 @@
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>406</v>
+        <v>376</v>
       </c>
       <c r="D83" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E83" t="s">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="F83" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G83" t="s">
-        <v>408</v>
+        <v>378</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -6052,19 +5755,19 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="D84" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E84" t="s">
-        <v>410</v>
+        <v>380</v>
       </c>
       <c r="F84" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G84" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -6075,19 +5778,19 @@
         <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>412</v>
+        <v>382</v>
       </c>
       <c r="D85" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E85" t="s">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="F85" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G85" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -6098,19 +5801,19 @@
         <v>5</v>
       </c>
       <c r="C86" t="s">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="D86" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E86" t="s">
-        <v>416</v>
+        <v>386</v>
       </c>
       <c r="F86" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G86" t="s">
-        <v>417</v>
+        <v>387</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -6121,19 +5824,19 @@
         <v>6</v>
       </c>
       <c r="C87" t="s">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="D87" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E87" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="F87" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G87" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -6144,19 +5847,19 @@
         <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
       <c r="D88" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E88" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="F88" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G88" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -6167,19 +5870,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="D89" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E89" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="F89" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G89" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -6190,19 +5893,19 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="D90" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E90" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="F90" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G90" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6213,19 +5916,19 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="D91" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E91" t="s">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="F91" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G91" t="s">
-        <v>432</v>
+        <v>402</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6236,19 +5939,19 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>433</v>
+        <v>403</v>
       </c>
       <c r="D92" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E92" t="s">
-        <v>434</v>
+        <v>404</v>
       </c>
       <c r="F92" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G92" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6259,16 +5962,16 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="D93" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="E93" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="G93" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6279,10 +5982,10 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="D94" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6293,10 +5996,10 @@
         <v>14</v>
       </c>
       <c r="C95" t="s">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="D95" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6307,10 +6010,10 @@
         <v>15</v>
       </c>
       <c r="C96" t="s">
-        <v>441</v>
+        <v>411</v>
       </c>
       <c r="D96" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6321,10 +6024,10 @@
         <v>16</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>664</v>
+        <v>634</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6335,10 +6038,10 @@
         <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>665</v>
+        <v>635</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -6349,10 +6052,10 @@
         <v>18</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>666</v>
+        <v>636</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -6363,10 +6066,10 @@
         <v>19</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>667</v>
+        <v>637</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -6377,10 +6080,10 @@
         <v>20</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>668</v>
+        <v>638</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -6391,19 +6094,19 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="D102" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E102" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="F102" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="G102" t="s">
-        <v>445</v>
+        <v>415</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -6414,19 +6117,19 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
       <c r="D103" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E103" t="s">
-        <v>447</v>
+        <v>417</v>
       </c>
       <c r="F103" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="G103" t="s">
-        <v>448</v>
+        <v>418</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -6437,19 +6140,19 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>596</v>
+        <v>566</v>
       </c>
       <c r="D104" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E104" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
       <c r="F104" t="s">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="G104" t="s">
-        <v>451</v>
+        <v>421</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6460,19 +6163,19 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>452</v>
+        <v>422</v>
       </c>
       <c r="D105" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E105" t="s">
-        <v>453</v>
+        <v>423</v>
       </c>
       <c r="F105" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G105" t="s">
-        <v>452</v>
+        <v>422</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6483,19 +6186,19 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>454</v>
+        <v>424</v>
       </c>
       <c r="D106" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E106" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="F106" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
       <c r="G106" t="s">
-        <v>457</v>
+        <v>427</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6506,19 +6209,19 @@
         <v>6</v>
       </c>
       <c r="C107" t="s">
-        <v>458</v>
+        <v>428</v>
       </c>
       <c r="D107" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E107" t="s">
-        <v>459</v>
+        <v>429</v>
       </c>
       <c r="F107" t="s">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="G107" t="s">
-        <v>461</v>
+        <v>431</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6529,19 +6232,19 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>462</v>
+        <v>432</v>
       </c>
       <c r="D108" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E108" t="s">
-        <v>463</v>
+        <v>433</v>
       </c>
       <c r="F108" t="s">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="G108" t="s">
-        <v>464</v>
+        <v>434</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6552,19 +6255,19 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="D109" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E109" t="s">
-        <v>466</v>
+        <v>436</v>
       </c>
       <c r="F109" t="s">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="G109" t="s">
-        <v>467</v>
+        <v>437</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6575,19 +6278,19 @@
         <v>9</v>
       </c>
       <c r="C110" t="s">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="D110" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E110" t="s">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="F110" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G110" t="s">
-        <v>470</v>
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1">
@@ -6598,19 +6301,19 @@
         <v>10</v>
       </c>
       <c r="C111" t="s">
-        <v>471</v>
+        <v>441</v>
       </c>
       <c r="D111" t="s">
+        <v>413</v>
+      </c>
+      <c r="E111" t="s">
+        <v>442</v>
+      </c>
+      <c r="F111" t="s">
+        <v>103</v>
+      </c>
+      <c r="G111" t="s">
         <v>443</v>
-      </c>
-      <c r="E111" t="s">
-        <v>472</v>
-      </c>
-      <c r="F111" t="s">
-        <v>118</v>
-      </c>
-      <c r="G111" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6621,19 +6324,19 @@
         <v>11</v>
       </c>
       <c r="C112" t="s">
-        <v>474</v>
+        <v>444</v>
       </c>
       <c r="D112" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E112" t="s">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="F112" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G112" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6644,19 +6347,19 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
       <c r="D113" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E113" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="F113" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G113" t="s">
-        <v>477</v>
+        <v>447</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6667,19 +6370,19 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
       <c r="D114" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="E114" t="s">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="F114" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
       <c r="G114" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -6690,10 +6393,10 @@
         <v>14</v>
       </c>
       <c r="C115" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="D115" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6704,10 +6407,10 @@
         <v>15</v>
       </c>
       <c r="C116" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
       <c r="D116" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -6718,10 +6421,10 @@
         <v>16</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>669</v>
+        <v>639</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -6732,10 +6435,10 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>670</v>
+        <v>640</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -6746,10 +6449,10 @@
         <v>18</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>671</v>
+        <v>641</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -6760,10 +6463,10 @@
         <v>19</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>672</v>
+        <v>642</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6774,10 +6477,10 @@
         <v>20</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>673</v>
+        <v>643</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6788,19 +6491,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>484</v>
+        <v>454</v>
       </c>
       <c r="D122" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E122" t="s">
-        <v>486</v>
+        <v>456</v>
       </c>
       <c r="F122" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
       <c r="G122" t="s">
-        <v>486</v>
+        <v>456</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6811,19 +6514,19 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>488</v>
+        <v>458</v>
       </c>
       <c r="D123" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E123" t="s">
-        <v>489</v>
+        <v>459</v>
       </c>
       <c r="F123" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
       <c r="G123" t="s">
-        <v>489</v>
+        <v>459</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6834,19 +6537,19 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="D124" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E124" t="s">
-        <v>491</v>
+        <v>461</v>
       </c>
       <c r="F124" t="s">
-        <v>492</v>
+        <v>462</v>
       </c>
       <c r="G124" t="s">
-        <v>493</v>
+        <v>463</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -6857,19 +6560,19 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>494</v>
+        <v>464</v>
       </c>
       <c r="D125" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E125" t="s">
-        <v>495</v>
+        <v>465</v>
       </c>
       <c r="F125" t="s">
-        <v>496</v>
+        <v>466</v>
       </c>
       <c r="G125" t="s">
-        <v>497</v>
+        <v>467</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6880,19 +6583,19 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>498</v>
+        <v>468</v>
       </c>
       <c r="D126" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E126" t="s">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="F126" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G126" t="s">
-        <v>500</v>
+        <v>470</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -6903,19 +6606,19 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>501</v>
+        <v>471</v>
       </c>
       <c r="D127" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E127" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="F127" t="s">
-        <v>496</v>
+        <v>466</v>
       </c>
       <c r="G127" t="s">
-        <v>503</v>
+        <v>473</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -6926,19 +6629,19 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>504</v>
+        <v>474</v>
       </c>
       <c r="D128" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E128" t="s">
-        <v>505</v>
+        <v>475</v>
       </c>
       <c r="F128" t="s">
-        <v>496</v>
+        <v>466</v>
       </c>
       <c r="G128" t="s">
-        <v>506</v>
+        <v>476</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -6949,19 +6652,19 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>507</v>
+        <v>477</v>
       </c>
       <c r="D129" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E129" t="s">
-        <v>508</v>
+        <v>478</v>
       </c>
       <c r="F129" t="s">
-        <v>509</v>
+        <v>479</v>
       </c>
       <c r="G129" t="s">
-        <v>510</v>
+        <v>480</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6972,19 +6675,19 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>511</v>
+        <v>481</v>
       </c>
       <c r="D130" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E130" t="s">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="F130" t="s">
-        <v>509</v>
+        <v>479</v>
       </c>
       <c r="G130" t="s">
-        <v>513</v>
+        <v>483</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6995,19 +6698,19 @@
         <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>514</v>
+        <v>484</v>
       </c>
       <c r="D131" t="s">
+        <v>455</v>
+      </c>
+      <c r="E131" t="s">
         <v>485</v>
       </c>
-      <c r="E131" t="s">
-        <v>515</v>
-      </c>
       <c r="F131" t="s">
-        <v>492</v>
+        <v>462</v>
       </c>
       <c r="G131" t="s">
-        <v>516</v>
+        <v>486</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -7018,19 +6721,19 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>517</v>
+        <v>487</v>
       </c>
       <c r="D132" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E132" t="s">
-        <v>518</v>
+        <v>488</v>
       </c>
       <c r="F132" t="s">
-        <v>492</v>
+        <v>462</v>
       </c>
       <c r="G132" t="s">
-        <v>519</v>
+        <v>489</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -7041,19 +6744,19 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>520</v>
+        <v>490</v>
       </c>
       <c r="D133" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E133" t="s">
-        <v>521</v>
+        <v>491</v>
       </c>
       <c r="F133" t="s">
-        <v>496</v>
+        <v>466</v>
       </c>
       <c r="G133" t="s">
-        <v>522</v>
+        <v>492</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -7064,19 +6767,19 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="D134" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="E134" t="s">
-        <v>524</v>
+        <v>494</v>
       </c>
       <c r="F134" t="s">
-        <v>496</v>
+        <v>466</v>
       </c>
       <c r="G134" t="s">
-        <v>525</v>
+        <v>495</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -7087,10 +6790,10 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>526</v>
+        <v>496</v>
       </c>
       <c r="D135" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -7101,10 +6804,10 @@
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>527</v>
+        <v>497</v>
       </c>
       <c r="D136" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -7115,10 +6818,10 @@
         <v>16</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>674</v>
+        <v>644</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -7129,10 +6832,10 @@
         <v>17</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>675</v>
+        <v>645</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -7143,10 +6846,10 @@
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>676</v>
+        <v>646</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -7157,10 +6860,10 @@
         <v>19</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>677</v>
+        <v>647</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -7171,10 +6874,10 @@
         <v>20</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>678</v>
+        <v>648</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -7185,19 +6888,19 @@
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>528</v>
+        <v>498</v>
       </c>
       <c r="D142" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="E142" t="s">
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="F142" t="s">
-        <v>531</v>
+        <v>501</v>
       </c>
       <c r="G142" t="s">
-        <v>532</v>
+        <v>502</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7208,19 +6911,19 @@
         <v>2</v>
       </c>
       <c r="C143" t="s">
-        <v>533</v>
+        <v>503</v>
       </c>
       <c r="D143" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="E143" t="s">
-        <v>534</v>
+        <v>504</v>
       </c>
       <c r="F143" t="s">
-        <v>535</v>
+        <v>505</v>
       </c>
       <c r="G143" t="s">
-        <v>533</v>
+        <v>503</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7231,19 +6934,19 @@
         <v>3</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>609</v>
+        <v>579</v>
       </c>
       <c r="D144" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="E144" t="s">
-        <v>614</v>
+        <v>584</v>
       </c>
       <c r="F144" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="G144" t="s">
-        <v>536</v>
+        <v>506</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -7254,10 +6957,10 @@
         <v>4</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>615</v>
+        <v>585</v>
       </c>
       <c r="D145" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -7268,10 +6971,10 @@
         <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>616</v>
+        <v>586</v>
       </c>
       <c r="D146" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -7282,10 +6985,10 @@
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>617</v>
+        <v>587</v>
       </c>
       <c r="D147" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -7296,13 +6999,13 @@
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>704</v>
+        <v>674</v>
       </c>
       <c r="D148" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="E148" t="s">
-        <v>706</v>
+        <v>676</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -7313,13 +7016,13 @@
         <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>705</v>
+        <v>675</v>
       </c>
       <c r="D149" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="E149" t="s">
-        <v>707</v>
+        <v>677</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -7330,13 +7033,13 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>610</v>
+        <v>580</v>
       </c>
       <c r="D150" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="E150" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -7347,13 +7050,13 @@
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>611</v>
+        <v>581</v>
       </c>
       <c r="D151" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="E151" t="s">
-        <v>618</v>
+        <v>588</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -7364,10 +7067,10 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>722</v>
+        <v>692</v>
       </c>
       <c r="D152" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -7378,10 +7081,10 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>723</v>
+        <v>693</v>
       </c>
       <c r="D153" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -7392,10 +7095,10 @@
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>612</v>
+        <v>582</v>
       </c>
       <c r="D154" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -7406,10 +7109,10 @@
         <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>613</v>
+        <v>583</v>
       </c>
       <c r="D155" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -7420,10 +7123,10 @@
         <v>15</v>
       </c>
       <c r="C156" t="s">
-        <v>537</v>
+        <v>507</v>
       </c>
       <c r="D156" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -7434,10 +7137,10 @@
         <v>16</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>679</v>
+        <v>649</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -7448,10 +7151,10 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -7462,10 +7165,10 @@
         <v>18</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>681</v>
+        <v>651</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -7476,10 +7179,10 @@
         <v>19</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>682</v>
+        <v>652</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -7490,10 +7193,10 @@
         <v>20</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>683</v>
+        <v>653</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7504,19 +7207,19 @@
         <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>538</v>
+        <v>508</v>
       </c>
       <c r="D162" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
       <c r="E162" t="s">
-        <v>540</v>
+        <v>510</v>
       </c>
       <c r="F162" t="s">
-        <v>541</v>
+        <v>511</v>
       </c>
       <c r="G162" t="s">
-        <v>542</v>
+        <v>512</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7527,19 +7230,19 @@
         <v>2</v>
       </c>
       <c r="C163" t="s">
-        <v>543</v>
+        <v>513</v>
       </c>
       <c r="D163" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
       <c r="E163" t="s">
-        <v>544</v>
+        <v>514</v>
       </c>
       <c r="F163" t="s">
-        <v>541</v>
+        <v>511</v>
       </c>
       <c r="G163" t="s">
-        <v>545</v>
+        <v>515</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7550,16 +7253,16 @@
         <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>546</v>
+        <v>516</v>
       </c>
       <c r="D164" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
       <c r="E164" t="s">
-        <v>547</v>
+        <v>517</v>
       </c>
       <c r="G164" t="s">
-        <v>546</v>
+        <v>516</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7570,16 +7273,16 @@
         <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>548</v>
+        <v>518</v>
       </c>
       <c r="D165" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
       <c r="E165" t="s">
-        <v>549</v>
+        <v>519</v>
       </c>
       <c r="G165" t="s">
-        <v>548</v>
+        <v>518</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7590,19 +7293,19 @@
         <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="D166" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
       <c r="E166" t="s">
-        <v>551</v>
+        <v>521</v>
       </c>
       <c r="F166" t="s">
-        <v>264</v>
+        <v>234</v>
       </c>
       <c r="G166" t="s">
-        <v>552</v>
+        <v>522</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7613,10 +7316,10 @@
         <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>553</v>
+        <v>523</v>
       </c>
       <c r="D167" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7627,10 +7330,10 @@
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>554</v>
+        <v>524</v>
       </c>
       <c r="D168" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7641,10 +7344,10 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>555</v>
+        <v>525</v>
       </c>
       <c r="D169" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7655,10 +7358,10 @@
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
       <c r="D170" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7669,10 +7372,10 @@
         <v>10</v>
       </c>
       <c r="C171" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="D171" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7683,10 +7386,10 @@
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="D172" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7697,10 +7400,10 @@
         <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>559</v>
+        <v>529</v>
       </c>
       <c r="D173" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7711,10 +7414,10 @@
         <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="D174" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7725,10 +7428,10 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>561</v>
+        <v>531</v>
       </c>
       <c r="D175" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7739,10 +7442,10 @@
         <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>562</v>
+        <v>532</v>
       </c>
       <c r="D176" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7753,10 +7456,10 @@
         <v>16</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>684</v>
+        <v>654</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -7767,10 +7470,10 @@
         <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -7781,10 +7484,10 @@
         <v>18</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>686</v>
+        <v>656</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -7795,10 +7498,10 @@
         <v>19</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>687</v>
+        <v>657</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -7809,10 +7512,10 @@
         <v>20</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>688</v>
+        <v>658</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -7823,19 +7526,19 @@
         <v>1</v>
       </c>
       <c r="C182" t="s">
-        <v>563</v>
+        <v>533</v>
       </c>
       <c r="D182" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E182" t="s">
-        <v>565</v>
+        <v>535</v>
       </c>
       <c r="F182" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G182" t="s">
-        <v>566</v>
+        <v>536</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -7846,19 +7549,19 @@
         <v>2</v>
       </c>
       <c r="C183" t="s">
-        <v>567</v>
+        <v>537</v>
       </c>
       <c r="D183" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E183" t="s">
-        <v>568</v>
+        <v>538</v>
       </c>
       <c r="F183" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G183" t="s">
-        <v>569</v>
+        <v>539</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -7869,19 +7572,19 @@
         <v>3</v>
       </c>
       <c r="C184" t="s">
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="D184" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E184" t="s">
-        <v>571</v>
+        <v>541</v>
       </c>
       <c r="F184" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G184" t="s">
-        <v>572</v>
+        <v>542</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -7892,19 +7595,19 @@
         <v>4</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>740</v>
+        <v>710</v>
       </c>
       <c r="D185" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E185" t="s">
-        <v>573</v>
+        <v>543</v>
       </c>
       <c r="F185" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G185" t="s">
-        <v>574</v>
+        <v>544</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -7915,19 +7618,19 @@
         <v>5</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>741</v>
+        <v>711</v>
       </c>
       <c r="D186" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E186" t="s">
-        <v>575</v>
+        <v>545</v>
       </c>
       <c r="F186" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G186" t="s">
-        <v>576</v>
+        <v>546</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -7938,19 +7641,19 @@
         <v>6</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>742</v>
+        <v>712</v>
       </c>
       <c r="D187" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E187" t="s">
-        <v>577</v>
+        <v>547</v>
       </c>
       <c r="F187" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="G187" t="s">
-        <v>578</v>
+        <v>548</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7961,19 +7664,19 @@
         <v>7</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>743</v>
+        <v>713</v>
       </c>
       <c r="D188" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E188" t="s">
-        <v>579</v>
+        <v>549</v>
       </c>
       <c r="F188" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="G188" t="s">
-        <v>580</v>
+        <v>550</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7984,19 +7687,19 @@
         <v>8</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>744</v>
+        <v>714</v>
       </c>
       <c r="D189" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E189" t="s">
-        <v>581</v>
+        <v>551</v>
       </c>
       <c r="F189" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="G189" t="s">
-        <v>582</v>
+        <v>552</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -8007,19 +7710,19 @@
         <v>9</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>745</v>
+        <v>715</v>
       </c>
       <c r="D190" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E190" t="s">
-        <v>583</v>
+        <v>553</v>
       </c>
       <c r="F190" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="G190" t="s">
-        <v>584</v>
+        <v>554</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -8030,19 +7733,19 @@
         <v>10</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>746</v>
+        <v>716</v>
       </c>
       <c r="D191" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E191" t="s">
-        <v>585</v>
+        <v>555</v>
       </c>
       <c r="F191" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="G191" t="s">
-        <v>586</v>
+        <v>556</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -8053,19 +7756,19 @@
         <v>11</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>747</v>
+        <v>717</v>
       </c>
       <c r="D192" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E192" t="s">
-        <v>587</v>
+        <v>557</v>
       </c>
       <c r="F192" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="G192" t="s">
-        <v>588</v>
+        <v>558</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -8076,19 +7779,19 @@
         <v>12</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>748</v>
+        <v>718</v>
       </c>
       <c r="D193" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E193" t="s">
-        <v>589</v>
+        <v>559</v>
       </c>
       <c r="F193" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="G193" t="s">
-        <v>590</v>
+        <v>560</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -8099,19 +7802,19 @@
         <v>13</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>749</v>
+        <v>719</v>
       </c>
       <c r="D194" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E194" t="s">
-        <v>591</v>
+        <v>561</v>
       </c>
       <c r="F194" t="s">
-        <v>343</v>
+        <v>313</v>
       </c>
       <c r="G194" t="s">
-        <v>592</v>
+        <v>562</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -8122,19 +7825,19 @@
         <v>14</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="D195" t="s">
+        <v>534</v>
+      </c>
+      <c r="E195" t="s">
+        <v>563</v>
+      </c>
+      <c r="F195" t="s">
+        <v>313</v>
+      </c>
+      <c r="G195" t="s">
         <v>564</v>
-      </c>
-      <c r="E195" t="s">
-        <v>593</v>
-      </c>
-      <c r="F195" t="s">
-        <v>343</v>
-      </c>
-      <c r="G195" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -8145,10 +7848,10 @@
         <v>15</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>595</v>
+        <v>565</v>
       </c>
       <c r="D196" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -8159,10 +7862,10 @@
         <v>16</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>689</v>
+        <v>659</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -8173,10 +7876,10 @@
         <v>17</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>690</v>
+        <v>660</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -8187,10 +7890,10 @@
         <v>18</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>691</v>
+        <v>661</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -8201,10 +7904,10 @@
         <v>19</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>692</v>
+        <v>662</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -8215,10 +7918,10 @@
         <v>20</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>693</v>
+        <v>663</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -8229,16 +7932,16 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>620</v>
+        <v>590</v>
       </c>
       <c r="D202" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E202" t="s">
-        <v>624</v>
+        <v>594</v>
       </c>
       <c r="F202" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -8249,16 +7952,16 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>621</v>
+        <v>591</v>
       </c>
       <c r="D203" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E203" t="s">
-        <v>625</v>
+        <v>595</v>
       </c>
       <c r="F203" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -8269,16 +7972,16 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>622</v>
+        <v>592</v>
       </c>
       <c r="D204" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E204" t="s">
-        <v>626</v>
+        <v>596</v>
       </c>
       <c r="F204" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -8289,16 +7992,16 @@
         <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>623</v>
+        <v>593</v>
       </c>
       <c r="D205" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E205" t="s">
-        <v>627</v>
+        <v>597</v>
       </c>
       <c r="F205" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -8309,16 +8012,16 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>628</v>
+        <v>598</v>
       </c>
       <c r="D206" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E206" t="s">
-        <v>632</v>
+        <v>602</v>
       </c>
       <c r="F206" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -8329,16 +8032,16 @@
         <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>629</v>
+        <v>599</v>
       </c>
       <c r="D207" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E207" t="s">
-        <v>633</v>
+        <v>603</v>
       </c>
       <c r="F207" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -8349,16 +8052,16 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="D208" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E208" t="s">
-        <v>634</v>
+        <v>604</v>
       </c>
       <c r="F208" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -8369,16 +8072,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>631</v>
+        <v>601</v>
       </c>
       <c r="D209" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E209" t="s">
-        <v>635</v>
+        <v>605</v>
       </c>
       <c r="F209" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -8389,16 +8092,16 @@
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>636</v>
+        <v>606</v>
       </c>
       <c r="D210" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E210" t="s">
-        <v>640</v>
+        <v>610</v>
       </c>
       <c r="F210" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -8409,16 +8112,16 @@
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>637</v>
+        <v>607</v>
       </c>
       <c r="D211" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E211" t="s">
-        <v>641</v>
+        <v>611</v>
       </c>
       <c r="F211" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -8429,16 +8132,16 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>638</v>
+        <v>608</v>
       </c>
       <c r="D212" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E212" t="s">
-        <v>642</v>
+        <v>612</v>
       </c>
       <c r="F212" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -8449,16 +8152,16 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>639</v>
+        <v>609</v>
       </c>
       <c r="D213" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E213" t="s">
-        <v>643</v>
+        <v>613</v>
       </c>
       <c r="F213" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -8469,16 +8172,16 @@
         <v>13</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="D214" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E214" t="s">
-        <v>716</v>
+        <v>686</v>
       </c>
       <c r="F214" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -8489,16 +8192,16 @@
         <v>14</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>701</v>
+        <v>671</v>
       </c>
       <c r="D215" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E215" t="s">
-        <v>717</v>
+        <v>687</v>
       </c>
       <c r="F215" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8509,16 +8212,16 @@
         <v>15</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>702</v>
+        <v>672</v>
       </c>
       <c r="D216" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E216" t="s">
-        <v>718</v>
+        <v>688</v>
       </c>
       <c r="F216" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -8529,16 +8232,16 @@
         <v>16</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>703</v>
+        <v>673</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E217" t="s">
-        <v>721</v>
+        <v>691</v>
       </c>
       <c r="F217" t="s">
-        <v>366</v>
+        <v>336</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -8549,13 +8252,13 @@
         <v>17</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>714</v>
+        <v>684</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E218" t="s">
-        <v>719</v>
+        <v>689</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8566,16 +8269,16 @@
         <v>18</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>715</v>
+        <v>685</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
       <c r="E219" t="s">
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -8586,10 +8289,10 @@
         <v>19</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>697</v>
+        <v>667</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8600,10 +8303,10 @@
         <v>20</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>698</v>
+        <v>668</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -8629,16 +8332,16 @@
     <row r="1" spans="1:5">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8659,10 +8362,10 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>644</v>
+        <v>614</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8676,10 +8379,10 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>645</v>
+        <v>615</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8693,10 +8396,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>646</v>
+        <v>616</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8710,10 +8413,10 @@
         <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>647</v>
+        <v>617</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8727,10 +8430,10 @@
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>648</v>
+        <v>618</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8744,10 +8447,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>649</v>
+        <v>619</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8761,10 +8464,10 @@
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8778,10 +8481,10 @@
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>651</v>
+        <v>621</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8795,10 +8498,10 @@
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>652</v>
+        <v>622</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8812,10 +8515,10 @@
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>653</v>
+        <v>623</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8829,10 +8532,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>654</v>
+        <v>624</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8846,10 +8549,10 @@
         <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>655</v>
+        <v>625</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8863,10 +8566,10 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>656</v>
+        <v>626</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8880,10 +8583,10 @@
         <v>19</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>657</v>
+        <v>627</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8897,10 +8600,10 @@
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>658</v>
+        <v>628</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>324</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8914,10 +8617,10 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>659</v>
+        <v>629</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8931,10 +8634,10 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8948,10 +8651,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>661</v>
+        <v>631</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8965,10 +8668,10 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>662</v>
+        <v>632</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8982,10 +8685,10 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>663</v>
+        <v>633</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8999,10 +8702,10 @@
         <v>16</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>664</v>
+        <v>634</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9016,10 +8719,10 @@
         <v>17</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>665</v>
+        <v>635</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9033,10 +8736,10 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>666</v>
+        <v>636</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9050,10 +8753,10 @@
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>667</v>
+        <v>637</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -9067,10 +8770,10 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>668</v>
+        <v>638</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>403</v>
+        <v>373</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9084,10 +8787,10 @@
         <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>669</v>
+        <v>639</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9101,10 +8804,10 @@
         <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>670</v>
+        <v>640</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9118,10 +8821,10 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>671</v>
+        <v>641</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9135,10 +8838,10 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>672</v>
+        <v>642</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9152,10 +8855,10 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>673</v>
+        <v>643</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9169,10 +8872,10 @@
         <v>16</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>674</v>
+        <v>644</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9186,10 +8889,10 @@
         <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>675</v>
+        <v>645</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9203,10 +8906,10 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>676</v>
+        <v>646</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9220,10 +8923,10 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>677</v>
+        <v>647</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9237,10 +8940,10 @@
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>678</v>
+        <v>648</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9254,10 +8957,10 @@
         <v>16</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>679</v>
+        <v>649</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9271,10 +8974,10 @@
         <v>17</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -9288,10 +8991,10 @@
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>681</v>
+        <v>651</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -9305,10 +9008,10 @@
         <v>19</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>682</v>
+        <v>652</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -9322,10 +9025,10 @@
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>683</v>
+        <v>653</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>529</v>
+        <v>499</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -9339,10 +9042,10 @@
         <v>16</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>684</v>
+        <v>654</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9356,10 +9059,10 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9373,10 +9076,10 @@
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>686</v>
+        <v>656</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9390,10 +9093,10 @@
         <v>19</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>687</v>
+        <v>657</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -9407,10 +9110,10 @@
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>688</v>
+        <v>658</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>539</v>
+        <v>509</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -9424,10 +9127,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>689</v>
+        <v>659</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -9441,10 +9144,10 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>690</v>
+        <v>660</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -9458,10 +9161,10 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>691</v>
+        <v>661</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -9475,10 +9178,10 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>692</v>
+        <v>662</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -9492,10 +9195,10 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>693</v>
+        <v>663</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>564</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -9509,10 +9212,10 @@
         <v>16</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>694</v>
+        <v>664</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9526,10 +9229,10 @@
         <v>17</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>695</v>
+        <v>665</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9543,10 +9246,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>696</v>
+        <v>666</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9560,10 +9263,10 @@
         <v>19</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>697</v>
+        <v>667</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9577,15 +9280,15 @@
         <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>698</v>
+        <v>668</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>619</v>
+        <v>589</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>699</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation - Copy before adding crown_width_option_baseline_to_start5\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B211A54-2CCE-4067-9E6D-5EBE5AEB4BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C9E117-6C3D-4F4D-8756-7E3AE82304A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="721">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="722">
   <si>
     <t>pFS2</t>
   </si>
@@ -1137,12 +1137,6 @@
     <t>incrWS</t>
   </si>
   <si>
-    <t>var_4_12</t>
-  </si>
-  <si>
-    <t>var_4_13</t>
-  </si>
-  <si>
     <t>var_4_14</t>
   </si>
   <si>
@@ -2194,6 +2188,15 @@
   </si>
   <si>
     <t>var_10_14</t>
+  </si>
+  <si>
+    <t>biom_incr_foliage_def</t>
+  </si>
+  <si>
+    <t>biom_incr_stem_def</t>
+  </si>
+  <si>
+    <t>Increment due to use of non-structural carbohydrates following defoliation</t>
   </si>
 </sst>
 </file>
@@ -2844,7 +2847,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C18" t="s">
         <v>103</v>
@@ -3065,10 +3068,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
@@ -3077,10 +3080,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -3089,10 +3092,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
@@ -3101,10 +3104,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -3113,10 +3116,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
@@ -3125,10 +3128,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
@@ -3235,10 +3238,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
@@ -3555,10 +3558,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>266</v>
@@ -3572,7 +3575,7 @@
         <v>61</v>
       </c>
       <c r="B71" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C71" t="s">
         <v>103</v>
@@ -3583,10 +3586,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B72" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C72" t="s">
         <v>103</v>
@@ -3597,10 +3600,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B73" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C73" t="s">
         <v>103</v>
@@ -3611,10 +3614,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
+        <v>703</v>
+      </c>
+      <c r="B74" t="s">
         <v>705</v>
-      </c>
-      <c r="B74" t="s">
-        <v>707</v>
       </c>
       <c r="C74" t="s">
         <v>103</v>
@@ -3625,10 +3628,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B75" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C75" t="s">
         <v>103</v>
@@ -3698,7 +3701,7 @@
         <v>67</v>
       </c>
       <c r="B80" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C80" t="s">
         <v>103</v>
@@ -3709,10 +3712,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B81" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C81" t="s">
         <v>103</v>
@@ -3723,10 +3726,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B82" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C82" t="s">
         <v>103</v>
@@ -3737,10 +3740,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B83" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C83" t="s">
         <v>103</v>
@@ -3751,10 +3754,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B84" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C84" t="s">
         <v>103</v>
@@ -3768,7 +3771,7 @@
         <v>68</v>
       </c>
       <c r="B85" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C85" t="s">
         <v>103</v>
@@ -3779,10 +3782,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B86" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C86" t="s">
         <v>103</v>
@@ -3793,10 +3796,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B87" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C87" t="s">
         <v>103</v>
@@ -3807,10 +3810,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B88" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C88" t="s">
         <v>103</v>
@@ -3821,10 +3824,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B89" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C89" t="s">
         <v>103</v>
@@ -4487,7 +4490,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>207</v>
@@ -4501,7 +4504,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>207</v>
@@ -4515,7 +4518,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>207</v>
@@ -4529,7 +4532,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>207</v>
@@ -4543,7 +4546,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>207</v>
@@ -4884,7 +4887,7 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>246</v>
@@ -4898,7 +4901,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>246</v>
@@ -4912,7 +4915,7 @@
         <v>18</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>246</v>
@@ -4926,7 +4929,7 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>246</v>
@@ -4940,7 +4943,7 @@
         <v>20</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>246</v>
@@ -5204,13 +5207,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D53" t="s">
         <v>294</v>
       </c>
       <c r="E53" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5263,7 +5266,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>294</v>
@@ -5277,7 +5280,7 @@
         <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>294</v>
@@ -5291,7 +5294,7 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>294</v>
@@ -5305,7 +5308,7 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>294</v>
@@ -5319,7 +5322,7 @@
         <v>20</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>294</v>
@@ -5583,10 +5586,16 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>368</v>
+        <v>719</v>
       </c>
       <c r="D73" t="s">
         <v>334</v>
+      </c>
+      <c r="E73" t="s">
+        <v>721</v>
+      </c>
+      <c r="F73" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5597,10 +5606,16 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>369</v>
+        <v>720</v>
       </c>
       <c r="D74" t="s">
         <v>334</v>
+      </c>
+      <c r="E74" t="s">
+        <v>721</v>
+      </c>
+      <c r="F74" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -5611,7 +5626,7 @@
         <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D75" t="s">
         <v>334</v>
@@ -5625,7 +5640,7 @@
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D76" t="s">
         <v>334</v>
@@ -5639,7 +5654,7 @@
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>334</v>
@@ -5653,7 +5668,7 @@
         <v>17</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>334</v>
@@ -5667,7 +5682,7 @@
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>334</v>
@@ -5681,7 +5696,7 @@
         <v>19</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>334</v>
@@ -5695,7 +5710,7 @@
         <v>20</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>334</v>
@@ -5709,19 +5724,19 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
+        <v>370</v>
+      </c>
+      <c r="D82" t="s">
+        <v>371</v>
+      </c>
+      <c r="E82" t="s">
         <v>372</v>
-      </c>
-      <c r="D82" t="s">
-        <v>373</v>
-      </c>
-      <c r="E82" t="s">
-        <v>374</v>
       </c>
       <c r="F82" t="s">
         <v>103</v>
       </c>
       <c r="G82" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -5732,19 +5747,19 @@
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D83" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E83" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F83" t="s">
         <v>103</v>
       </c>
       <c r="G83" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -5755,19 +5770,19 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D84" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E84" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F84" t="s">
         <v>103</v>
       </c>
       <c r="G84" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -5778,19 +5793,19 @@
         <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D85" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E85" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F85" t="s">
         <v>103</v>
       </c>
       <c r="G85" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -5801,19 +5816,19 @@
         <v>5</v>
       </c>
       <c r="C86" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D86" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E86" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F86" t="s">
         <v>103</v>
       </c>
       <c r="G86" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -5824,19 +5839,19 @@
         <v>6</v>
       </c>
       <c r="C87" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D87" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E87" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F87" t="s">
         <v>103</v>
       </c>
       <c r="G87" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -5847,19 +5862,19 @@
         <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D88" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E88" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F88" t="s">
         <v>103</v>
       </c>
       <c r="G88" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -5870,19 +5885,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D89" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E89" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F89" t="s">
         <v>103</v>
       </c>
       <c r="G89" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -5893,19 +5908,19 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D90" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E90" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F90" t="s">
         <v>103</v>
       </c>
       <c r="G90" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -5916,19 +5931,19 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D91" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E91" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F91" t="s">
         <v>103</v>
       </c>
       <c r="G91" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -5939,19 +5954,19 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D92" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E92" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F92" t="s">
         <v>103</v>
       </c>
       <c r="G92" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -5962,16 +5977,16 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
+        <v>404</v>
+      </c>
+      <c r="D93" t="s">
+        <v>371</v>
+      </c>
+      <c r="E93" t="s">
+        <v>405</v>
+      </c>
+      <c r="G93" t="s">
         <v>406</v>
-      </c>
-      <c r="D93" t="s">
-        <v>373</v>
-      </c>
-      <c r="E93" t="s">
-        <v>407</v>
-      </c>
-      <c r="G93" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -5982,10 +5997,10 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D94" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -5996,10 +6011,10 @@
         <v>14</v>
       </c>
       <c r="C95" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D95" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6010,10 +6025,10 @@
         <v>15</v>
       </c>
       <c r="C96" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D96" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6024,10 +6039,10 @@
         <v>16</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6038,10 +6053,10 @@
         <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -6052,10 +6067,10 @@
         <v>18</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -6066,10 +6081,10 @@
         <v>19</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -6080,10 +6095,10 @@
         <v>20</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -6094,19 +6109,19 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
+        <v>410</v>
+      </c>
+      <c r="D102" t="s">
+        <v>411</v>
+      </c>
+      <c r="E102" t="s">
         <v>412</v>
-      </c>
-      <c r="D102" t="s">
-        <v>413</v>
-      </c>
-      <c r="E102" t="s">
-        <v>414</v>
       </c>
       <c r="F102" t="s">
         <v>336</v>
       </c>
       <c r="G102" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -6117,19 +6132,19 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D103" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E103" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F103" t="s">
         <v>336</v>
       </c>
       <c r="G103" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -6140,19 +6155,19 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="D104" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E104" t="s">
+        <v>417</v>
+      </c>
+      <c r="F104" t="s">
+        <v>418</v>
+      </c>
+      <c r="G104" t="s">
         <v>419</v>
-      </c>
-      <c r="F104" t="s">
-        <v>420</v>
-      </c>
-      <c r="G104" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6163,19 +6178,19 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D105" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E105" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F105" t="s">
         <v>103</v>
       </c>
       <c r="G105" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6186,19 +6201,19 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
+        <v>422</v>
+      </c>
+      <c r="D106" t="s">
+        <v>411</v>
+      </c>
+      <c r="E106" t="s">
+        <v>423</v>
+      </c>
+      <c r="F106" t="s">
         <v>424</v>
       </c>
-      <c r="D106" t="s">
-        <v>413</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="G106" t="s">
         <v>425</v>
-      </c>
-      <c r="F106" t="s">
-        <v>426</v>
-      </c>
-      <c r="G106" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6209,19 +6224,19 @@
         <v>6</v>
       </c>
       <c r="C107" t="s">
+        <v>426</v>
+      </c>
+      <c r="D107" t="s">
+        <v>411</v>
+      </c>
+      <c r="E107" t="s">
+        <v>427</v>
+      </c>
+      <c r="F107" t="s">
         <v>428</v>
       </c>
-      <c r="D107" t="s">
-        <v>413</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>429</v>
-      </c>
-      <c r="F107" t="s">
-        <v>430</v>
-      </c>
-      <c r="G107" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6232,19 +6247,19 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
+        <v>430</v>
+      </c>
+      <c r="D108" t="s">
+        <v>411</v>
+      </c>
+      <c r="E108" t="s">
+        <v>431</v>
+      </c>
+      <c r="F108" t="s">
+        <v>428</v>
+      </c>
+      <c r="G108" t="s">
         <v>432</v>
-      </c>
-      <c r="D108" t="s">
-        <v>413</v>
-      </c>
-      <c r="E108" t="s">
-        <v>433</v>
-      </c>
-      <c r="F108" t="s">
-        <v>430</v>
-      </c>
-      <c r="G108" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6255,19 +6270,19 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
+        <v>433</v>
+      </c>
+      <c r="D109" t="s">
+        <v>411</v>
+      </c>
+      <c r="E109" t="s">
+        <v>434</v>
+      </c>
+      <c r="F109" t="s">
+        <v>428</v>
+      </c>
+      <c r="G109" t="s">
         <v>435</v>
-      </c>
-      <c r="D109" t="s">
-        <v>413</v>
-      </c>
-      <c r="E109" t="s">
-        <v>436</v>
-      </c>
-      <c r="F109" t="s">
-        <v>430</v>
-      </c>
-      <c r="G109" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6278,19 +6293,19 @@
         <v>9</v>
       </c>
       <c r="C110" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D110" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E110" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F110" t="s">
         <v>103</v>
       </c>
       <c r="G110" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1">
@@ -6301,19 +6316,19 @@
         <v>10</v>
       </c>
       <c r="C111" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D111" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E111" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F111" t="s">
         <v>103</v>
       </c>
       <c r="G111" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6324,19 +6339,19 @@
         <v>11</v>
       </c>
       <c r="C112" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D112" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E112" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F112" t="s">
         <v>103</v>
       </c>
       <c r="G112" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6347,19 +6362,19 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D113" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E113" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F113" t="s">
         <v>103</v>
       </c>
       <c r="G113" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6370,19 +6385,19 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D114" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E114" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F114" t="s">
         <v>336</v>
       </c>
       <c r="G114" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -6393,10 +6408,10 @@
         <v>14</v>
       </c>
       <c r="C115" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D115" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6407,10 +6422,10 @@
         <v>15</v>
       </c>
       <c r="C116" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D116" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -6421,10 +6436,10 @@
         <v>16</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -6435,10 +6450,10 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -6449,10 +6464,10 @@
         <v>18</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -6463,10 +6478,10 @@
         <v>19</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6477,10 +6492,10 @@
         <v>20</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6491,19 +6506,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
+        <v>452</v>
+      </c>
+      <c r="D122" t="s">
+        <v>453</v>
+      </c>
+      <c r="E122" t="s">
         <v>454</v>
       </c>
-      <c r="D122" t="s">
+      <c r="F122" t="s">
         <v>455</v>
       </c>
-      <c r="E122" t="s">
-        <v>456</v>
-      </c>
-      <c r="F122" t="s">
-        <v>457</v>
-      </c>
       <c r="G122" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6514,19 +6529,19 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D123" t="s">
+        <v>453</v>
+      </c>
+      <c r="E123" t="s">
+        <v>457</v>
+      </c>
+      <c r="F123" t="s">
         <v>455</v>
       </c>
-      <c r="E123" t="s">
-        <v>459</v>
-      </c>
-      <c r="F123" t="s">
+      <c r="G123" t="s">
         <v>457</v>
-      </c>
-      <c r="G123" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6537,19 +6552,19 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
+        <v>458</v>
+      </c>
+      <c r="D124" t="s">
+        <v>453</v>
+      </c>
+      <c r="E124" t="s">
+        <v>459</v>
+      </c>
+      <c r="F124" t="s">
         <v>460</v>
       </c>
-      <c r="D124" t="s">
-        <v>455</v>
-      </c>
-      <c r="E124" t="s">
+      <c r="G124" t="s">
         <v>461</v>
-      </c>
-      <c r="F124" t="s">
-        <v>462</v>
-      </c>
-      <c r="G124" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -6560,19 +6575,19 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
+        <v>462</v>
+      </c>
+      <c r="D125" t="s">
+        <v>453</v>
+      </c>
+      <c r="E125" t="s">
+        <v>463</v>
+      </c>
+      <c r="F125" t="s">
         <v>464</v>
       </c>
-      <c r="D125" t="s">
-        <v>455</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="G125" t="s">
         <v>465</v>
-      </c>
-      <c r="F125" t="s">
-        <v>466</v>
-      </c>
-      <c r="G125" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6583,19 +6598,19 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D126" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E126" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F126" t="s">
         <v>103</v>
       </c>
       <c r="G126" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -6606,19 +6621,19 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
+        <v>469</v>
+      </c>
+      <c r="D127" t="s">
+        <v>453</v>
+      </c>
+      <c r="E127" t="s">
+        <v>470</v>
+      </c>
+      <c r="F127" t="s">
+        <v>464</v>
+      </c>
+      <c r="G127" t="s">
         <v>471</v>
-      </c>
-      <c r="D127" t="s">
-        <v>455</v>
-      </c>
-      <c r="E127" t="s">
-        <v>472</v>
-      </c>
-      <c r="F127" t="s">
-        <v>466</v>
-      </c>
-      <c r="G127" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -6629,19 +6644,19 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
+        <v>472</v>
+      </c>
+      <c r="D128" t="s">
+        <v>453</v>
+      </c>
+      <c r="E128" t="s">
+        <v>473</v>
+      </c>
+      <c r="F128" t="s">
+        <v>464</v>
+      </c>
+      <c r="G128" t="s">
         <v>474</v>
-      </c>
-      <c r="D128" t="s">
-        <v>455</v>
-      </c>
-      <c r="E128" t="s">
-        <v>475</v>
-      </c>
-      <c r="F128" t="s">
-        <v>466</v>
-      </c>
-      <c r="G128" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -6652,19 +6667,19 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>475</v>
+      </c>
+      <c r="D129" t="s">
+        <v>453</v>
+      </c>
+      <c r="E129" t="s">
+        <v>476</v>
+      </c>
+      <c r="F129" t="s">
         <v>477</v>
       </c>
-      <c r="D129" t="s">
-        <v>455</v>
-      </c>
-      <c r="E129" t="s">
+      <c r="G129" t="s">
         <v>478</v>
-      </c>
-      <c r="F129" t="s">
-        <v>479</v>
-      </c>
-      <c r="G129" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6675,19 +6690,19 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
+        <v>479</v>
+      </c>
+      <c r="D130" t="s">
+        <v>453</v>
+      </c>
+      <c r="E130" t="s">
+        <v>480</v>
+      </c>
+      <c r="F130" t="s">
+        <v>477</v>
+      </c>
+      <c r="G130" t="s">
         <v>481</v>
-      </c>
-      <c r="D130" t="s">
-        <v>455</v>
-      </c>
-      <c r="E130" t="s">
-        <v>482</v>
-      </c>
-      <c r="F130" t="s">
-        <v>479</v>
-      </c>
-      <c r="G130" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6698,19 +6713,19 @@
         <v>10</v>
       </c>
       <c r="C131" t="s">
+        <v>482</v>
+      </c>
+      <c r="D131" t="s">
+        <v>453</v>
+      </c>
+      <c r="E131" t="s">
+        <v>483</v>
+      </c>
+      <c r="F131" t="s">
+        <v>460</v>
+      </c>
+      <c r="G131" t="s">
         <v>484</v>
-      </c>
-      <c r="D131" t="s">
-        <v>455</v>
-      </c>
-      <c r="E131" t="s">
-        <v>485</v>
-      </c>
-      <c r="F131" t="s">
-        <v>462</v>
-      </c>
-      <c r="G131" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -6721,19 +6736,19 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
+        <v>485</v>
+      </c>
+      <c r="D132" t="s">
+        <v>453</v>
+      </c>
+      <c r="E132" t="s">
+        <v>486</v>
+      </c>
+      <c r="F132" t="s">
+        <v>460</v>
+      </c>
+      <c r="G132" t="s">
         <v>487</v>
-      </c>
-      <c r="D132" t="s">
-        <v>455</v>
-      </c>
-      <c r="E132" t="s">
-        <v>488</v>
-      </c>
-      <c r="F132" t="s">
-        <v>462</v>
-      </c>
-      <c r="G132" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -6744,19 +6759,19 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
+        <v>488</v>
+      </c>
+      <c r="D133" t="s">
+        <v>453</v>
+      </c>
+      <c r="E133" t="s">
+        <v>489</v>
+      </c>
+      <c r="F133" t="s">
+        <v>464</v>
+      </c>
+      <c r="G133" t="s">
         <v>490</v>
-      </c>
-      <c r="D133" t="s">
-        <v>455</v>
-      </c>
-      <c r="E133" t="s">
-        <v>491</v>
-      </c>
-      <c r="F133" t="s">
-        <v>466</v>
-      </c>
-      <c r="G133" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -6767,19 +6782,19 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
+        <v>491</v>
+      </c>
+      <c r="D134" t="s">
+        <v>453</v>
+      </c>
+      <c r="E134" t="s">
+        <v>492</v>
+      </c>
+      <c r="F134" t="s">
+        <v>464</v>
+      </c>
+      <c r="G134" t="s">
         <v>493</v>
-      </c>
-      <c r="D134" t="s">
-        <v>455</v>
-      </c>
-      <c r="E134" t="s">
-        <v>494</v>
-      </c>
-      <c r="F134" t="s">
-        <v>466</v>
-      </c>
-      <c r="G134" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -6790,10 +6805,10 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D135" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -6804,10 +6819,10 @@
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D136" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -6818,10 +6833,10 @@
         <v>16</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -6832,10 +6847,10 @@
         <v>17</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -6846,10 +6861,10 @@
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -6860,10 +6875,10 @@
         <v>19</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -6874,10 +6889,10 @@
         <v>20</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -6888,19 +6903,19 @@
         <v>1</v>
       </c>
       <c r="C142" t="s">
+        <v>496</v>
+      </c>
+      <c r="D142" t="s">
+        <v>497</v>
+      </c>
+      <c r="E142" t="s">
         <v>498</v>
       </c>
-      <c r="D142" t="s">
+      <c r="F142" t="s">
         <v>499</v>
       </c>
-      <c r="E142" t="s">
+      <c r="G142" t="s">
         <v>500</v>
-      </c>
-      <c r="F142" t="s">
-        <v>501</v>
-      </c>
-      <c r="G142" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -6911,19 +6926,19 @@
         <v>2</v>
       </c>
       <c r="C143" t="s">
+        <v>501</v>
+      </c>
+      <c r="D143" t="s">
+        <v>497</v>
+      </c>
+      <c r="E143" t="s">
+        <v>502</v>
+      </c>
+      <c r="F143" t="s">
         <v>503</v>
       </c>
-      <c r="D143" t="s">
-        <v>499</v>
-      </c>
-      <c r="E143" t="s">
-        <v>504</v>
-      </c>
-      <c r="F143" t="s">
-        <v>505</v>
-      </c>
       <c r="G143" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -6934,19 +6949,19 @@
         <v>3</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D144" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E144" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F144" t="s">
         <v>251</v>
       </c>
       <c r="G144" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -6957,10 +6972,10 @@
         <v>4</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D145" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -6971,10 +6986,10 @@
         <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D146" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -6985,10 +7000,10 @@
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D147" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -6999,13 +7014,13 @@
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="D148" t="s">
+        <v>497</v>
+      </c>
+      <c r="E148" t="s">
         <v>674</v>
-      </c>
-      <c r="D148" t="s">
-        <v>499</v>
-      </c>
-      <c r="E148" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -7016,13 +7031,13 @@
         <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="D149" t="s">
+        <v>497</v>
+      </c>
+      <c r="E149" t="s">
         <v>675</v>
-      </c>
-      <c r="D149" t="s">
-        <v>499</v>
-      </c>
-      <c r="E149" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -7033,10 +7048,10 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D150" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E150" t="s">
         <v>262</v>
@@ -7050,13 +7065,13 @@
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D151" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E151" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -7067,10 +7082,10 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D152" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -7081,10 +7096,10 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D153" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -7095,10 +7110,10 @@
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D154" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -7109,10 +7124,10 @@
         <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D155" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -7123,10 +7138,10 @@
         <v>15</v>
       </c>
       <c r="C156" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D156" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -7137,10 +7152,10 @@
         <v>16</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -7151,10 +7166,10 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -7165,10 +7180,10 @@
         <v>18</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -7179,10 +7194,10 @@
         <v>19</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -7193,10 +7208,10 @@
         <v>20</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7207,19 +7222,19 @@
         <v>1</v>
       </c>
       <c r="C162" t="s">
+        <v>506</v>
+      </c>
+      <c r="D162" t="s">
+        <v>507</v>
+      </c>
+      <c r="E162" t="s">
         <v>508</v>
       </c>
-      <c r="D162" t="s">
+      <c r="F162" t="s">
         <v>509</v>
       </c>
-      <c r="E162" t="s">
+      <c r="G162" t="s">
         <v>510</v>
-      </c>
-      <c r="F162" t="s">
-        <v>511</v>
-      </c>
-      <c r="G162" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7230,19 +7245,19 @@
         <v>2</v>
       </c>
       <c r="C163" t="s">
+        <v>511</v>
+      </c>
+      <c r="D163" t="s">
+        <v>507</v>
+      </c>
+      <c r="E163" t="s">
+        <v>512</v>
+      </c>
+      <c r="F163" t="s">
+        <v>509</v>
+      </c>
+      <c r="G163" t="s">
         <v>513</v>
-      </c>
-      <c r="D163" t="s">
-        <v>509</v>
-      </c>
-      <c r="E163" t="s">
-        <v>514</v>
-      </c>
-      <c r="F163" t="s">
-        <v>511</v>
-      </c>
-      <c r="G163" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7253,16 +7268,16 @@
         <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D164" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E164" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G164" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7273,16 +7288,16 @@
         <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D165" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E165" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G165" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7293,19 +7308,19 @@
         <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D166" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E166" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F166" t="s">
         <v>234</v>
       </c>
       <c r="G166" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7316,10 +7331,10 @@
         <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D167" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7330,10 +7345,10 @@
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D168" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7344,10 +7359,10 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D169" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7358,10 +7373,10 @@
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D170" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7372,10 +7387,10 @@
         <v>10</v>
       </c>
       <c r="C171" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D171" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7386,10 +7401,10 @@
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D172" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7400,10 +7415,10 @@
         <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D173" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7414,10 +7429,10 @@
         <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D174" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7428,10 +7443,10 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D175" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7442,10 +7457,10 @@
         <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D176" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7456,10 +7471,10 @@
         <v>16</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -7470,10 +7485,10 @@
         <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -7484,10 +7499,10 @@
         <v>18</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -7498,10 +7513,10 @@
         <v>19</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -7512,10 +7527,10 @@
         <v>20</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -7526,19 +7541,19 @@
         <v>1</v>
       </c>
       <c r="C182" t="s">
+        <v>531</v>
+      </c>
+      <c r="D182" t="s">
+        <v>532</v>
+      </c>
+      <c r="E182" t="s">
         <v>533</v>
-      </c>
-      <c r="D182" t="s">
-        <v>534</v>
-      </c>
-      <c r="E182" t="s">
-        <v>535</v>
       </c>
       <c r="F182" t="s">
         <v>103</v>
       </c>
       <c r="G182" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -7549,19 +7564,19 @@
         <v>2</v>
       </c>
       <c r="C183" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D183" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E183" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F183" t="s">
         <v>103</v>
       </c>
       <c r="G183" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -7572,19 +7587,19 @@
         <v>3</v>
       </c>
       <c r="C184" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D184" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E184" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F184" t="s">
         <v>103</v>
       </c>
       <c r="G184" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -7595,19 +7610,19 @@
         <v>4</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D185" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E185" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F185" t="s">
         <v>103</v>
       </c>
       <c r="G185" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -7618,19 +7633,19 @@
         <v>5</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D186" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E186" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F186" t="s">
         <v>103</v>
       </c>
       <c r="G186" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -7641,19 +7656,19 @@
         <v>6</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D187" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E187" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F187" t="s">
         <v>103</v>
       </c>
       <c r="G187" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7664,19 +7679,19 @@
         <v>7</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D188" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E188" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F188" t="s">
         <v>313</v>
       </c>
       <c r="G188" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7687,19 +7702,19 @@
         <v>8</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D189" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E189" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F189" t="s">
         <v>313</v>
       </c>
       <c r="G189" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -7710,19 +7725,19 @@
         <v>9</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D190" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E190" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F190" t="s">
         <v>313</v>
       </c>
       <c r="G190" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -7733,19 +7748,19 @@
         <v>10</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D191" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E191" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F191" t="s">
         <v>313</v>
       </c>
       <c r="G191" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -7756,19 +7771,19 @@
         <v>11</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D192" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E192" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F192" t="s">
         <v>313</v>
       </c>
       <c r="G192" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -7779,19 +7794,19 @@
         <v>12</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D193" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E193" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F193" t="s">
         <v>313</v>
       </c>
       <c r="G193" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -7802,19 +7817,19 @@
         <v>13</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D194" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E194" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F194" t="s">
         <v>313</v>
       </c>
       <c r="G194" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -7825,19 +7840,19 @@
         <v>14</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D195" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E195" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="F195" t="s">
         <v>313</v>
       </c>
       <c r="G195" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -7848,10 +7863,10 @@
         <v>15</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D196" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -7862,10 +7877,10 @@
         <v>16</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -7876,10 +7891,10 @@
         <v>17</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -7890,10 +7905,10 @@
         <v>18</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -7904,10 +7919,10 @@
         <v>19</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -7918,10 +7933,10 @@
         <v>20</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -7932,13 +7947,13 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D202" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E202" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F202" t="s">
         <v>251</v>
@@ -7952,13 +7967,13 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D203" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E203" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F203" t="s">
         <v>336</v>
@@ -7972,13 +7987,13 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D204" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E204" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F204" t="s">
         <v>336</v>
@@ -7992,13 +8007,13 @@
         <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D205" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E205" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F205" t="s">
         <v>336</v>
@@ -8012,13 +8027,13 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D206" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E206" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F206" t="s">
         <v>251</v>
@@ -8032,13 +8047,13 @@
         <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D207" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E207" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F207" t="s">
         <v>336</v>
@@ -8052,13 +8067,13 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D208" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E208" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F208" t="s">
         <v>336</v>
@@ -8072,13 +8087,13 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D209" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E209" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F209" t="s">
         <v>336</v>
@@ -8092,13 +8107,13 @@
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D210" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E210" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F210" t="s">
         <v>251</v>
@@ -8112,13 +8127,13 @@
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D211" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E211" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="F211" t="s">
         <v>336</v>
@@ -8132,13 +8147,13 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D212" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E212" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F212" t="s">
         <v>336</v>
@@ -8152,13 +8167,13 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D213" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E213" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F213" t="s">
         <v>336</v>
@@ -8172,13 +8187,13 @@
         <v>13</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D214" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E214" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F214" t="s">
         <v>251</v>
@@ -8192,13 +8207,13 @@
         <v>14</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D215" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E215" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F215" t="s">
         <v>336</v>
@@ -8212,13 +8227,13 @@
         <v>15</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D216" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E216" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F216" t="s">
         <v>336</v>
@@ -8232,13 +8247,13 @@
         <v>16</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E217" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F217" t="s">
         <v>336</v>
@@ -8252,13 +8267,13 @@
         <v>17</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E218" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8269,13 +8284,13 @@
         <v>18</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E219" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>113</v>
@@ -8289,10 +8304,10 @@
         <v>19</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8303,10 +8318,10 @@
         <v>20</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -8362,7 +8377,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>207</v>
@@ -8379,7 +8394,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>207</v>
@@ -8396,7 +8411,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>207</v>
@@ -8413,7 +8428,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>207</v>
@@ -8430,7 +8445,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>207</v>
@@ -8447,7 +8462,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>246</v>
@@ -8464,7 +8479,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>246</v>
@@ -8481,7 +8496,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>246</v>
@@ -8498,7 +8513,7 @@
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>246</v>
@@ -8515,7 +8530,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>246</v>
@@ -8532,7 +8547,7 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>294</v>
@@ -8549,7 +8564,7 @@
         <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>294</v>
@@ -8566,7 +8581,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>294</v>
@@ -8583,7 +8598,7 @@
         <v>19</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>294</v>
@@ -8600,7 +8615,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>294</v>
@@ -8617,7 +8632,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>334</v>
@@ -8634,7 +8649,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>334</v>
@@ -8651,7 +8666,7 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>334</v>
@@ -8668,7 +8683,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>334</v>
@@ -8685,7 +8700,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>334</v>
@@ -8702,10 +8717,10 @@
         <v>16</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8719,10 +8734,10 @@
         <v>17</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8736,10 +8751,10 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8753,10 +8768,10 @@
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8770,10 +8785,10 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8787,10 +8802,10 @@
         <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8804,10 +8819,10 @@
         <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8821,10 +8836,10 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8838,10 +8853,10 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8855,10 +8870,10 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8872,10 +8887,10 @@
         <v>16</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8889,10 +8904,10 @@
         <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8906,10 +8921,10 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8923,10 +8938,10 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8940,10 +8955,10 @@
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8957,10 +8972,10 @@
         <v>16</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8974,10 +8989,10 @@
         <v>17</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -8991,10 +9006,10 @@
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -9008,10 +9023,10 @@
         <v>19</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -9025,10 +9040,10 @@
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -9042,10 +9057,10 @@
         <v>16</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9059,10 +9074,10 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9076,10 +9091,10 @@
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9093,10 +9108,10 @@
         <v>19</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -9110,10 +9125,10 @@
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -9127,10 +9142,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -9144,10 +9159,10 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -9161,10 +9176,10 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -9178,10 +9193,10 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -9195,10 +9210,10 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -9212,10 +9227,10 @@
         <v>16</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9229,10 +9244,10 @@
         <v>17</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9246,10 +9261,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9263,10 +9278,10 @@
         <v>19</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9280,15 +9295,15 @@
         <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation - Copy before adding crown_width_option_baseline_to_start5\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C9E117-6C3D-4F4D-8756-7E3AE82304A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B729FDBE-40D5-4AB8-BF7E-C7D5E73B80E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="8730" yWindow="3435" windowWidth="19125" windowHeight="11235" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="719">
   <si>
     <t>pFS2</t>
   </si>
@@ -2172,24 +2172,6 @@
     <t>var_10_8</t>
   </si>
   <si>
-    <t>var_10_9</t>
-  </si>
-  <si>
-    <t>var_10_10</t>
-  </si>
-  <si>
-    <t>var_10_11</t>
-  </si>
-  <si>
-    <t>var_10_12</t>
-  </si>
-  <si>
-    <t>var_10_13</t>
-  </si>
-  <si>
-    <t>var_10_14</t>
-  </si>
-  <si>
     <t>biom_incr_foliage_def</t>
   </si>
   <si>
@@ -2197,13 +2179,22 @@
   </si>
   <si>
     <t>Increment due to use of non-structural carbohydrates following defoliation</t>
+  </si>
+  <si>
+    <t>prop_carbs</t>
+  </si>
+  <si>
+    <t>biom_foliage_adj_pre_def</t>
+  </si>
+  <si>
+    <t>growing_season_length</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2247,6 +2238,13 @@
       <name val="Lucida Grande"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2275,7 +2273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2283,6 +2281,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5586,13 +5585,13 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D73" t="s">
         <v>334</v>
       </c>
       <c r="E73" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="F73" t="s">
         <v>336</v>
@@ -5606,13 +5605,13 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="D74" t="s">
         <v>334</v>
       </c>
       <c r="E74" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="F74" t="s">
         <v>336</v>
@@ -7724,8 +7723,8 @@
       <c r="B190">
         <v>9</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>713</v>
+      <c r="C190" s="7" t="s">
+        <v>716</v>
       </c>
       <c r="D190" t="s">
         <v>532</v>
@@ -7747,8 +7746,8 @@
       <c r="B191">
         <v>10</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>714</v>
+      <c r="C191" s="7" t="s">
+        <v>717</v>
       </c>
       <c r="D191" t="s">
         <v>532</v>
@@ -7770,8 +7769,8 @@
       <c r="B192">
         <v>11</v>
       </c>
-      <c r="C192" s="1" t="s">
-        <v>715</v>
+      <c r="C192" s="7" t="s">
+        <v>683</v>
       </c>
       <c r="D192" t="s">
         <v>532</v>
@@ -7793,8 +7792,8 @@
       <c r="B193">
         <v>12</v>
       </c>
-      <c r="C193" s="1" t="s">
-        <v>716</v>
+      <c r="C193" s="7" t="s">
+        <v>718</v>
       </c>
       <c r="D193" t="s">
         <v>532</v>
@@ -7816,8 +7815,8 @@
       <c r="B194">
         <v>13</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>717</v>
+      <c r="C194" s="7" t="s">
+        <v>436</v>
       </c>
       <c r="D194" t="s">
         <v>532</v>
@@ -7839,8 +7838,8 @@
       <c r="B195">
         <v>14</v>
       </c>
-      <c r="C195" s="1" t="s">
-        <v>718</v>
+      <c r="C195" s="7" t="s">
+        <v>445</v>
       </c>
       <c r="D195" t="s">
         <v>532</v>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation - Copy before adding crown_width_option_baseline_to_start5\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B729FDBE-40D5-4AB8-BF7E-C7D5E73B80E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899CF2E2-79C7-476C-88DE-FAC311F277AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8730" yWindow="3435" windowWidth="19125" windowHeight="11235" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="718">
   <si>
     <t>pFS2</t>
   </si>
@@ -2167,9 +2167,6 @@
   </si>
   <si>
     <t>var_10_7</t>
-  </si>
-  <si>
-    <t>var_10_8</t>
   </si>
   <si>
     <t>biom_incr_foliage_def</t>
@@ -5585,13 +5582,13 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D73" t="s">
         <v>334</v>
       </c>
       <c r="E73" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F73" t="s">
         <v>336</v>
@@ -5605,13 +5602,13 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D74" t="s">
         <v>334</v>
       </c>
       <c r="E74" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F74" t="s">
         <v>336</v>
@@ -7700,8 +7697,8 @@
       <c r="B189">
         <v>8</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>712</v>
+      <c r="C189" s="7" t="s">
+        <v>10</v>
       </c>
       <c r="D189" t="s">
         <v>532</v>
@@ -7724,7 +7721,7 @@
         <v>9</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D190" t="s">
         <v>532</v>
@@ -7747,7 +7744,7 @@
         <v>10</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D191" t="s">
         <v>532</v>
@@ -7793,7 +7790,7 @@
         <v>12</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D193" t="s">
         <v>532</v>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation - Copy before adding crown_width_option_baseline_to_start5\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation - Copy before adding crown_width_option_baseline_to_start7\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899CF2E2-79C7-476C-88DE-FAC311F277AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63EED44-9527-41BB-A249-A5B7233C8EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8730" yWindow="3435" windowWidth="19125" windowHeight="11235" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="722">
   <si>
     <t>pFS2</t>
   </si>
@@ -2178,20 +2178,32 @@
     <t>Increment due to use of non-structural carbohydrates following defoliation</t>
   </si>
   <si>
-    <t>prop_carbs</t>
-  </si>
-  <si>
-    <t>biom_foliage_adj_pre_def</t>
-  </si>
-  <si>
-    <t>growing_season_length</t>
+    <t>var_10_8</t>
+  </si>
+  <si>
+    <t>var_10_9</t>
+  </si>
+  <si>
+    <t>var_10_10</t>
+  </si>
+  <si>
+    <t>var_10_11</t>
+  </si>
+  <si>
+    <t>var_10_12</t>
+  </si>
+  <si>
+    <t>var_10_13</t>
+  </si>
+  <si>
+    <t>var_10_14</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2235,13 +2247,6 @@
       <name val="Lucida Grande"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2270,7 +2275,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2278,7 +2283,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7697,8 +7701,8 @@
       <c r="B189">
         <v>8</v>
       </c>
-      <c r="C189" s="7" t="s">
-        <v>10</v>
+      <c r="C189" s="1" t="s">
+        <v>715</v>
       </c>
       <c r="D189" t="s">
         <v>532</v>
@@ -7720,8 +7724,8 @@
       <c r="B190">
         <v>9</v>
       </c>
-      <c r="C190" s="7" t="s">
-        <v>715</v>
+      <c r="C190" s="1" t="s">
+        <v>716</v>
       </c>
       <c r="D190" t="s">
         <v>532</v>
@@ -7743,8 +7747,8 @@
       <c r="B191">
         <v>10</v>
       </c>
-      <c r="C191" s="7" t="s">
-        <v>716</v>
+      <c r="C191" s="1" t="s">
+        <v>717</v>
       </c>
       <c r="D191" t="s">
         <v>532</v>
@@ -7766,8 +7770,8 @@
       <c r="B192">
         <v>11</v>
       </c>
-      <c r="C192" s="7" t="s">
-        <v>683</v>
+      <c r="C192" s="1" t="s">
+        <v>718</v>
       </c>
       <c r="D192" t="s">
         <v>532</v>
@@ -7789,8 +7793,8 @@
       <c r="B193">
         <v>12</v>
       </c>
-      <c r="C193" s="7" t="s">
-        <v>717</v>
+      <c r="C193" s="1" t="s">
+        <v>719</v>
       </c>
       <c r="D193" t="s">
         <v>532</v>
@@ -7812,8 +7816,8 @@
       <c r="B194">
         <v>13</v>
       </c>
-      <c r="C194" s="7" t="s">
-        <v>436</v>
+      <c r="C194" s="1" t="s">
+        <v>720</v>
       </c>
       <c r="D194" t="s">
         <v>532</v>
@@ -7835,8 +7839,8 @@
       <c r="B195">
         <v>14</v>
       </c>
-      <c r="C195" s="7" t="s">
-        <v>445</v>
+      <c r="C195" s="1" t="s">
+        <v>721</v>
       </c>
       <c r="D195" t="s">
         <v>532</v>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation - Copy before adding crown_width_option_baseline_to_start7\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation - Copy before adding crown_width_option_baseline_to_start8\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63EED44-9527-41BB-A249-A5B7233C8EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0832C5C5-BCD6-4ED4-91FB-204AED1F0736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="718">
   <si>
     <t>pFS2</t>
   </si>
@@ -1728,33 +1728,6 @@
     <t>apar</t>
   </si>
   <si>
-    <t>beta0</t>
-  </si>
-  <si>
-    <t>betaB</t>
-  </si>
-  <si>
-    <t>betaN</t>
-  </si>
-  <si>
-    <t>betafN</t>
-  </si>
-  <si>
-    <t>betafT</t>
-  </si>
-  <si>
-    <t>betafPhys</t>
-  </si>
-  <si>
-    <t>constant for self-thinning when mort_model = 2</t>
-  </si>
-  <si>
-    <t>Power for B when mort_model = 2</t>
-  </si>
-  <si>
-    <t>Power in tree density when mort_model = 2</t>
-  </si>
-  <si>
     <t>Power in fertility modifier when mort_model = 2</t>
   </si>
   <si>
@@ -2197,6 +2170,21 @@
   </si>
   <si>
     <t>var_10_14</t>
+  </si>
+  <si>
+    <t>thinIntercept</t>
+  </si>
+  <si>
+    <t>thinfN</t>
+  </si>
+  <si>
+    <t>thinfT</t>
+  </si>
+  <si>
+    <t>thinfPhys</t>
+  </si>
+  <si>
+    <t>Intercept for self-thinning rule when mort_model = 2</t>
   </si>
 </sst>
 </file>
@@ -2598,7 +2586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E287297-02C0-BF44-BF0C-8FADE2A87F8F}">
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="2" max="2" width="80" bestFit="1" customWidth="1"/>
@@ -2847,7 +2835,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="C18" t="s">
         <v>103</v>
@@ -3068,46 +3056,46 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>565</v>
+        <v>713</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>571</v>
+        <v>717</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
-        <v>-20.399999999999999</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>566</v>
+        <v>714</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
-        <v>1.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>567</v>
+        <v>715</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
-        <v>2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>568</v>
+        <v>716</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
@@ -3115,467 +3103,471 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+      <c r="B38" t="s">
+        <v>141</v>
+      </c>
+      <c r="C38" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1">
-        <v>0</v>
+      <c r="A39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39">
+        <v>0.2</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B40" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C40" t="s">
         <v>103</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="D41">
-        <v>0.2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="D42">
-        <v>0.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C43" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D43">
-        <v>11</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" t="s">
-        <v>147</v>
-      </c>
-      <c r="C45" t="s">
-        <v>130</v>
-      </c>
-      <c r="D45">
-        <v>2.5</v>
+      <c r="A45" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C46" t="s">
+        <v>130</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" t="s">
         <v>103</v>
       </c>
-      <c r="D46">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1">
-        <v>0</v>
+      <c r="D47">
+        <v>0.15</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="D48">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
         <v>103</v>
       </c>
       <c r="D49">
-        <v>0.15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B50" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C50" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C51" t="s">
         <v>103</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B52" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D52">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="D53">
-        <v>0.47</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C54" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D55">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B56" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="D56">
-        <v>3.33</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C57" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="D57">
-        <v>0.05</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C58" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D58">
-        <v>0.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B59" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="D59">
-        <v>0.66</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C60" t="s">
         <v>165</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B61" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C61" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D61">
-        <v>4.4000000000000004</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B62" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C62" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D62">
-        <v>27</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B63" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="D63">
-        <v>0.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="D64">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B65" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C65" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C66" t="s">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="D66">
-        <v>0.45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C67" t="s">
-        <v>172</v>
+        <v>103</v>
       </c>
       <c r="D67">
-        <v>0.45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" t="s">
-        <v>174</v>
-      </c>
-      <c r="C68" t="s">
-        <v>130</v>
-      </c>
-      <c r="D68">
-        <v>4</v>
+      <c r="A68" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1.3</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B69" t="s">
-        <v>175</v>
+        <v>696</v>
       </c>
       <c r="C69" t="s">
         <v>103</v>
       </c>
       <c r="D69">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D70" s="1">
-        <v>1.3</v>
+      <c r="A70" t="s">
+        <v>684</v>
+      </c>
+      <c r="B70" t="s">
+        <v>696</v>
+      </c>
+      <c r="C70" t="s">
+        <v>103</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>61</v>
+        <v>685</v>
       </c>
       <c r="B71" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="C71" t="s">
         <v>103</v>
@@ -3586,10 +3578,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B72" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="C72" t="s">
         <v>103</v>
@@ -3600,10 +3592,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B73" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="C73" t="s">
         <v>103</v>
@@ -3614,10 +3606,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>703</v>
+        <v>62</v>
       </c>
       <c r="B74" t="s">
-        <v>705</v>
+        <v>176</v>
       </c>
       <c r="C74" t="s">
         <v>103</v>
@@ -3628,10 +3620,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>704</v>
+        <v>63</v>
       </c>
       <c r="B75" t="s">
-        <v>705</v>
+        <v>177</v>
       </c>
       <c r="C75" t="s">
         <v>103</v>
@@ -3642,10 +3634,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B76" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C76" t="s">
         <v>103</v>
@@ -3656,10 +3648,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C77" t="s">
         <v>103</v>
@@ -3670,10 +3662,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B78" t="s">
-        <v>178</v>
+        <v>697</v>
       </c>
       <c r="C78" t="s">
         <v>103</v>
@@ -3684,10 +3676,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>65</v>
+        <v>686</v>
       </c>
       <c r="B79" t="s">
-        <v>179</v>
+        <v>697</v>
       </c>
       <c r="C79" t="s">
         <v>103</v>
@@ -3698,10 +3690,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>67</v>
+        <v>687</v>
       </c>
       <c r="B80" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="C80" t="s">
         <v>103</v>
@@ -3712,10 +3704,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="B81" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="C81" t="s">
         <v>103</v>
@@ -3726,10 +3718,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="B82" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="C82" t="s">
         <v>103</v>
@@ -3740,10 +3732,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>697</v>
+        <v>68</v>
       </c>
       <c r="B83" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="C83" t="s">
         <v>103</v>
@@ -3754,10 +3746,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
+        <v>690</v>
+      </c>
+      <c r="B84" t="s">
         <v>698</v>
-      </c>
-      <c r="B84" t="s">
-        <v>706</v>
       </c>
       <c r="C84" t="s">
         <v>103</v>
@@ -3768,10 +3760,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>68</v>
+        <v>691</v>
       </c>
       <c r="B85" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="C85" t="s">
         <v>103</v>
@@ -3782,10 +3774,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="B86" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="C86" t="s">
         <v>103</v>
@@ -3796,10 +3788,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
       <c r="B87" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="C87" t="s">
         <v>103</v>
@@ -3810,85 +3802,57 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>701</v>
+        <v>84</v>
       </c>
       <c r="B88" t="s">
-        <v>707</v>
+        <v>180</v>
       </c>
       <c r="C88" t="s">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>702</v>
+        <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>707</v>
+        <v>182</v>
       </c>
       <c r="C89" t="s">
         <v>103</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C90" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D90">
-        <v>-90</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B91" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C91" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="D91">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" t="s">
-        <v>86</v>
-      </c>
-      <c r="B92" t="s">
-        <v>183</v>
-      </c>
-      <c r="C92" t="s">
-        <v>184</v>
-      </c>
-      <c r="D92">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" t="s">
-        <v>87</v>
-      </c>
-      <c r="B93" t="s">
-        <v>185</v>
-      </c>
-      <c r="C93" t="s">
-        <v>186</v>
-      </c>
-      <c r="D93">
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -4490,7 +4454,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>207</v>
@@ -4504,7 +4468,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>207</v>
@@ -4518,7 +4482,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>207</v>
@@ -4532,7 +4496,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>207</v>
@@ -4546,7 +4510,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>207</v>
@@ -4887,7 +4851,7 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>246</v>
@@ -4901,7 +4865,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>246</v>
@@ -4915,7 +4879,7 @@
         <v>18</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>246</v>
@@ -4929,7 +4893,7 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>246</v>
@@ -4943,7 +4907,7 @@
         <v>20</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>246</v>
@@ -5207,13 +5171,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="D53" t="s">
         <v>294</v>
       </c>
       <c r="E53" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5266,7 +5230,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>294</v>
@@ -5280,7 +5244,7 @@
         <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>294</v>
@@ -5294,7 +5258,7 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>294</v>
@@ -5308,7 +5272,7 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>294</v>
@@ -5322,7 +5286,7 @@
         <v>20</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>294</v>
@@ -5586,13 +5550,13 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="D73" t="s">
         <v>334</v>
       </c>
       <c r="E73" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="F73" t="s">
         <v>336</v>
@@ -5606,13 +5570,13 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="D74" t="s">
         <v>334</v>
       </c>
       <c r="E74" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="F74" t="s">
         <v>336</v>
@@ -5654,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>334</v>
@@ -5668,7 +5632,7 @@
         <v>17</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>334</v>
@@ -5682,7 +5646,7 @@
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>334</v>
@@ -5696,7 +5660,7 @@
         <v>19</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>334</v>
@@ -5710,7 +5674,7 @@
         <v>20</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>334</v>
@@ -6039,7 +6003,7 @@
         <v>16</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>371</v>
@@ -6053,7 +6017,7 @@
         <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>371</v>
@@ -6067,7 +6031,7 @@
         <v>18</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>371</v>
@@ -6081,7 +6045,7 @@
         <v>19</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>371</v>
@@ -6095,7 +6059,7 @@
         <v>20</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>371</v>
@@ -6436,7 +6400,7 @@
         <v>16</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>411</v>
@@ -6450,7 +6414,7 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>411</v>
@@ -6464,7 +6428,7 @@
         <v>18</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>411</v>
@@ -6478,7 +6442,7 @@
         <v>19</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>411</v>
@@ -6492,7 +6456,7 @@
         <v>20</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>411</v>
@@ -6833,7 +6797,7 @@
         <v>16</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>453</v>
@@ -6847,7 +6811,7 @@
         <v>17</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>453</v>
@@ -6861,7 +6825,7 @@
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>453</v>
@@ -6875,7 +6839,7 @@
         <v>19</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>453</v>
@@ -6889,7 +6853,7 @@
         <v>20</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>453</v>
@@ -6949,13 +6913,13 @@
         <v>3</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="D144" t="s">
         <v>497</v>
       </c>
       <c r="E144" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="F144" t="s">
         <v>251</v>
@@ -6972,7 +6936,7 @@
         <v>4</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="D145" t="s">
         <v>497</v>
@@ -6986,7 +6950,7 @@
         <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="D146" t="s">
         <v>497</v>
@@ -7000,7 +6964,7 @@
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="D147" t="s">
         <v>497</v>
@@ -7014,13 +6978,13 @@
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="D148" t="s">
         <v>497</v>
       </c>
       <c r="E148" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -7031,13 +6995,13 @@
         <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="D149" t="s">
         <v>497</v>
       </c>
       <c r="E149" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -7048,7 +7012,7 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="D150" t="s">
         <v>497</v>
@@ -7065,13 +7029,13 @@
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="D151" t="s">
         <v>497</v>
       </c>
       <c r="E151" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -7082,7 +7046,7 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="D152" t="s">
         <v>497</v>
@@ -7096,7 +7060,7 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="D153" t="s">
         <v>497</v>
@@ -7110,7 +7074,7 @@
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="D154" t="s">
         <v>497</v>
@@ -7124,7 +7088,7 @@
         <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="D155" t="s">
         <v>497</v>
@@ -7152,7 +7116,7 @@
         <v>16</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>497</v>
@@ -7166,7 +7130,7 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>497</v>
@@ -7180,7 +7144,7 @@
         <v>18</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>497</v>
@@ -7194,7 +7158,7 @@
         <v>19</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>497</v>
@@ -7208,7 +7172,7 @@
         <v>20</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>497</v>
@@ -7471,7 +7435,7 @@
         <v>16</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>507</v>
@@ -7485,7 +7449,7 @@
         <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>507</v>
@@ -7499,7 +7463,7 @@
         <v>18</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>507</v>
@@ -7513,7 +7477,7 @@
         <v>19</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>507</v>
@@ -7527,7 +7491,7 @@
         <v>20</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>507</v>
@@ -7610,7 +7574,7 @@
         <v>4</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="D185" t="s">
         <v>532</v>
@@ -7633,7 +7597,7 @@
         <v>5</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="D186" t="s">
         <v>532</v>
@@ -7656,7 +7620,7 @@
         <v>6</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="D187" t="s">
         <v>532</v>
@@ -7679,7 +7643,7 @@
         <v>7</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="D188" t="s">
         <v>532</v>
@@ -7702,7 +7666,7 @@
         <v>8</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="D189" t="s">
         <v>532</v>
@@ -7725,7 +7689,7 @@
         <v>9</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="D190" t="s">
         <v>532</v>
@@ -7748,7 +7712,7 @@
         <v>10</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="D191" t="s">
         <v>532</v>
@@ -7771,7 +7735,7 @@
         <v>11</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="D192" t="s">
         <v>532</v>
@@ -7794,7 +7758,7 @@
         <v>12</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="D193" t="s">
         <v>532</v>
@@ -7817,7 +7781,7 @@
         <v>13</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="D194" t="s">
         <v>532</v>
@@ -7840,7 +7804,7 @@
         <v>14</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="D195" t="s">
         <v>532</v>
@@ -7877,7 +7841,7 @@
         <v>16</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>532</v>
@@ -7891,7 +7855,7 @@
         <v>17</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>532</v>
@@ -7905,7 +7869,7 @@
         <v>18</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>532</v>
@@ -7919,7 +7883,7 @@
         <v>19</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>532</v>
@@ -7933,7 +7897,7 @@
         <v>20</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>532</v>
@@ -7947,13 +7911,13 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="D202" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E202" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="F202" t="s">
         <v>251</v>
@@ -7967,13 +7931,13 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="D203" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E203" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="F203" t="s">
         <v>336</v>
@@ -7987,13 +7951,13 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="D204" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E204" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="F204" t="s">
         <v>336</v>
@@ -8007,13 +7971,13 @@
         <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="D205" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E205" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="F205" t="s">
         <v>336</v>
@@ -8027,13 +7991,13 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="D206" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E206" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="F206" t="s">
         <v>251</v>
@@ -8047,13 +8011,13 @@
         <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="D207" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E207" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="F207" t="s">
         <v>336</v>
@@ -8067,13 +8031,13 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="D208" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E208" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="F208" t="s">
         <v>336</v>
@@ -8087,13 +8051,13 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="D209" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E209" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="F209" t="s">
         <v>336</v>
@@ -8107,13 +8071,13 @@
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D210" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E210" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="F210" t="s">
         <v>251</v>
@@ -8127,13 +8091,13 @@
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="D211" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E211" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="F211" t="s">
         <v>336</v>
@@ -8147,13 +8111,13 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="D212" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E212" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="F212" t="s">
         <v>336</v>
@@ -8167,13 +8131,13 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="D213" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E213" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="F213" t="s">
         <v>336</v>
@@ -8187,13 +8151,13 @@
         <v>13</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="D214" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E214" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="F214" t="s">
         <v>251</v>
@@ -8207,13 +8171,13 @@
         <v>14</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="D215" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E215" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="F215" t="s">
         <v>336</v>
@@ -8227,13 +8191,13 @@
         <v>15</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="D216" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E216" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="F216" t="s">
         <v>336</v>
@@ -8247,13 +8211,13 @@
         <v>16</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E217" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="F217" t="s">
         <v>336</v>
@@ -8267,13 +8231,13 @@
         <v>17</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E218" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8284,13 +8248,13 @@
         <v>18</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="E219" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>113</v>
@@ -8304,10 +8268,10 @@
         <v>19</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8318,10 +8282,10 @@
         <v>20</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -8377,7 +8341,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>207</v>
@@ -8394,7 +8358,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>207</v>
@@ -8411,7 +8375,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>207</v>
@@ -8428,7 +8392,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>207</v>
@@ -8445,7 +8409,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>207</v>
@@ -8462,7 +8426,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>246</v>
@@ -8479,7 +8443,7 @@
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>246</v>
@@ -8496,7 +8460,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>246</v>
@@ -8513,7 +8477,7 @@
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>246</v>
@@ -8530,7 +8494,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>246</v>
@@ -8547,7 +8511,7 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>294</v>
@@ -8564,7 +8528,7 @@
         <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>294</v>
@@ -8581,7 +8545,7 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>294</v>
@@ -8598,7 +8562,7 @@
         <v>19</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>294</v>
@@ -8615,7 +8579,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>294</v>
@@ -8632,7 +8596,7 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>334</v>
@@ -8649,7 +8613,7 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>334</v>
@@ -8666,7 +8630,7 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>334</v>
@@ -8683,7 +8647,7 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>334</v>
@@ -8700,7 +8664,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>334</v>
@@ -8717,7 +8681,7 @@
         <v>16</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>371</v>
@@ -8734,7 +8698,7 @@
         <v>17</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>371</v>
@@ -8751,7 +8715,7 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>371</v>
@@ -8768,7 +8732,7 @@
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>371</v>
@@ -8785,7 +8749,7 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>371</v>
@@ -8802,7 +8766,7 @@
         <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>411</v>
@@ -8819,7 +8783,7 @@
         <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>411</v>
@@ -8836,7 +8800,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>411</v>
@@ -8853,7 +8817,7 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>411</v>
@@ -8870,7 +8834,7 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>411</v>
@@ -8887,7 +8851,7 @@
         <v>16</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>453</v>
@@ -8904,7 +8868,7 @@
         <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>453</v>
@@ -8921,7 +8885,7 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>453</v>
@@ -8938,7 +8902,7 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>453</v>
@@ -8955,7 +8919,7 @@
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>453</v>
@@ -8972,7 +8936,7 @@
         <v>16</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>497</v>
@@ -8989,7 +8953,7 @@
         <v>17</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>497</v>
@@ -9006,7 +8970,7 @@
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>497</v>
@@ -9023,7 +8987,7 @@
         <v>19</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>497</v>
@@ -9040,7 +9004,7 @@
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>497</v>
@@ -9057,7 +9021,7 @@
         <v>16</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>507</v>
@@ -9074,7 +9038,7 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>507</v>
@@ -9091,7 +9055,7 @@
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>507</v>
@@ -9108,7 +9072,7 @@
         <v>19</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>507</v>
@@ -9125,7 +9089,7 @@
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>507</v>
@@ -9142,7 +9106,7 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>532</v>
@@ -9159,7 +9123,7 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>532</v>
@@ -9176,7 +9140,7 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>532</v>
@@ -9193,7 +9157,7 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>532</v>
@@ -9210,7 +9174,7 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>532</v>
@@ -9227,10 +9191,10 @@
         <v>16</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9244,10 +9208,10 @@
         <v>17</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9261,10 +9225,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9278,10 +9242,10 @@
         <v>19</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9295,15 +9259,15 @@
         <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation - Copy before adding crown_width_option_baseline_to_start8\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0832C5C5-BCD6-4ED4-91FB-204AED1F0736}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A20CA1E-2584-452A-B5C8-D6DB4FE5F73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="728">
   <si>
     <t>pFS2</t>
   </si>
@@ -2185,6 +2185,36 @@
   </si>
   <si>
     <t>Intercept for self-thinning rule when mort_model = 2</t>
+  </si>
+  <si>
+    <t>ln(trees ha-1)</t>
+  </si>
+  <si>
+    <t>beta0</t>
+  </si>
+  <si>
+    <t>constant for self-thinning when mort_model = 2</t>
+  </si>
+  <si>
+    <t>betaB</t>
+  </si>
+  <si>
+    <t>Power for B when mort_model = 2</t>
+  </si>
+  <si>
+    <t>betaN</t>
+  </si>
+  <si>
+    <t>Power in tree density when mort_model = 2</t>
+  </si>
+  <si>
+    <t>betafN</t>
+  </si>
+  <si>
+    <t>betafT</t>
+  </si>
+  <si>
+    <t>betafPhys</t>
   </si>
 </sst>
 </file>
@@ -2586,7 +2616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E287297-02C0-BF44-BF0C-8FADE2A87F8F}">
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="2" max="2" width="80" bestFit="1" customWidth="1"/>
@@ -3061,7 +3091,9 @@
       <c r="B34" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="C34" s="1"/>
+      <c r="C34" s="1" t="s">
+        <v>718</v>
+      </c>
       <c r="D34" s="1">
         <v>12</v>
       </c>
@@ -3073,7 +3105,9 @@
       <c r="B35" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C35" s="1"/>
+      <c r="C35" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
@@ -3085,7 +3119,9 @@
       <c r="B36" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="C36" s="1"/>
+      <c r="C36" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
@@ -3097,533 +3133,535 @@
       <c r="B37" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="C37" s="1"/>
+      <c r="C37" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="D37" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" t="s">
-        <v>141</v>
-      </c>
-      <c r="C38" t="s">
-        <v>103</v>
-      </c>
-      <c r="D38">
+      <c r="A38" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="1">
+        <v>-20.399999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" s="1">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" t="s">
-        <v>142</v>
-      </c>
-      <c r="C39" t="s">
-        <v>103</v>
-      </c>
-      <c r="D39">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" t="s">
-        <v>143</v>
-      </c>
-      <c r="C40" t="s">
-        <v>103</v>
-      </c>
-      <c r="D40">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" t="s">
-        <v>144</v>
-      </c>
-      <c r="C41" t="s">
-        <v>145</v>
-      </c>
-      <c r="D41">
-        <v>11</v>
-      </c>
-    </row>
     <row r="42" spans="1:4">
-      <c r="A42" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" t="s">
-        <v>146</v>
-      </c>
-      <c r="C42" t="s">
-        <v>145</v>
-      </c>
-      <c r="D42">
-        <v>4</v>
+      <c r="A42" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" t="s">
-        <v>147</v>
-      </c>
-      <c r="C43" t="s">
-        <v>130</v>
-      </c>
-      <c r="D43">
-        <v>2.5</v>
+      <c r="A43" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C44" t="s">
         <v>103</v>
       </c>
       <c r="D44">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1">
-        <v>0</v>
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45">
+        <v>0.2</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="D47">
-        <v>0.15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C49" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C50" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="D50">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" t="s">
-        <v>155</v>
-      </c>
-      <c r="C51" t="s">
-        <v>103</v>
-      </c>
-      <c r="D51">
-        <v>0.47</v>
+      <c r="A51" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C52" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C53" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="D53">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B54" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
       </c>
       <c r="D54">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B55" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="D55">
-        <v>0.05</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B56" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C56" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D56">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C57" t="s">
         <v>103</v>
       </c>
       <c r="D57">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B58" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C58" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C59" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D59">
-        <v>4.4000000000000004</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B60" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C60" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="D60">
-        <v>27</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B61" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="D61">
-        <v>0.75</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B62" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="D62">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B63" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C63" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B64" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C64" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D64">
-        <v>0.45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B65" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D65">
-        <v>0.45</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B66" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C66" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C67" t="s">
         <v>103</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D68" s="1">
-        <v>1.3</v>
+      <c r="A68" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68" t="s">
+        <v>169</v>
+      </c>
+      <c r="C68" t="s">
+        <v>103</v>
+      </c>
+      <c r="D68">
+        <v>0.15</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B69" t="s">
-        <v>696</v>
+        <v>170</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>684</v>
+        <v>58</v>
       </c>
       <c r="B70" t="s">
-        <v>696</v>
+        <v>171</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>685</v>
+        <v>59</v>
       </c>
       <c r="B71" t="s">
-        <v>696</v>
+        <v>173</v>
       </c>
       <c r="C71" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>694</v>
+        <v>60</v>
       </c>
       <c r="B72" t="s">
-        <v>696</v>
+        <v>174</v>
       </c>
       <c r="C72" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>695</v>
+        <v>66</v>
       </c>
       <c r="B73" t="s">
-        <v>696</v>
+        <v>175</v>
       </c>
       <c r="C73" t="s">
         <v>103</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B74" t="s">
-        <v>176</v>
-      </c>
-      <c r="C74" t="s">
-        <v>103</v>
-      </c>
-      <c r="D74">
-        <v>0</v>
+      <c r="A74" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D74" s="1">
+        <v>1.3</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B75" t="s">
-        <v>177</v>
+        <v>696</v>
       </c>
       <c r="C75" t="s">
         <v>103</v>
@@ -3634,10 +3672,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>64</v>
+        <v>684</v>
       </c>
       <c r="B76" t="s">
-        <v>178</v>
+        <v>696</v>
       </c>
       <c r="C76" t="s">
         <v>103</v>
@@ -3648,10 +3686,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>65</v>
+        <v>685</v>
       </c>
       <c r="B77" t="s">
-        <v>179</v>
+        <v>696</v>
       </c>
       <c r="C77" t="s">
         <v>103</v>
@@ -3662,10 +3700,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>694</v>
       </c>
       <c r="B78" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C78" t="s">
         <v>103</v>
@@ -3676,10 +3714,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="B79" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C79" t="s">
         <v>103</v>
@@ -3690,10 +3728,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>687</v>
+        <v>62</v>
       </c>
       <c r="B80" t="s">
-        <v>697</v>
+        <v>176</v>
       </c>
       <c r="C80" t="s">
         <v>103</v>
@@ -3704,10 +3742,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>688</v>
+        <v>63</v>
       </c>
       <c r="B81" t="s">
-        <v>697</v>
+        <v>177</v>
       </c>
       <c r="C81" t="s">
         <v>103</v>
@@ -3718,10 +3756,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>689</v>
+        <v>64</v>
       </c>
       <c r="B82" t="s">
-        <v>697</v>
+        <v>178</v>
       </c>
       <c r="C82" t="s">
         <v>103</v>
@@ -3732,10 +3770,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>698</v>
+        <v>179</v>
       </c>
       <c r="C83" t="s">
         <v>103</v>
@@ -3746,10 +3784,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>690</v>
+        <v>67</v>
       </c>
       <c r="B84" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C84" t="s">
         <v>103</v>
@@ -3760,10 +3798,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B85" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C85" t="s">
         <v>103</v>
@@ -3774,10 +3812,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="B86" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C86" t="s">
         <v>103</v>
@@ -3788,10 +3826,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="B87" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C87" t="s">
         <v>103</v>
@@ -3802,57 +3840,141 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>689</v>
       </c>
       <c r="B88" t="s">
-        <v>180</v>
+        <v>697</v>
       </c>
       <c r="C88" t="s">
-        <v>181</v>
+        <v>103</v>
       </c>
       <c r="D88">
-        <v>-90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B89" t="s">
-        <v>182</v>
+        <v>698</v>
       </c>
       <c r="C89" t="s">
         <v>103</v>
       </c>
       <c r="D89">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>86</v>
+        <v>690</v>
       </c>
       <c r="B90" t="s">
-        <v>183</v>
+        <v>698</v>
       </c>
       <c r="C90" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="D90">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
+        <v>691</v>
+      </c>
+      <c r="B91" t="s">
+        <v>698</v>
+      </c>
+      <c r="C91" t="s">
+        <v>103</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>692</v>
+      </c>
+      <c r="B92" t="s">
+        <v>698</v>
+      </c>
+      <c r="C92" t="s">
+        <v>103</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>693</v>
+      </c>
+      <c r="B93" t="s">
+        <v>698</v>
+      </c>
+      <c r="C93" t="s">
+        <v>103</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>84</v>
+      </c>
+      <c r="B94" t="s">
+        <v>180</v>
+      </c>
+      <c r="C94" t="s">
+        <v>181</v>
+      </c>
+      <c r="D94">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>85</v>
+      </c>
+      <c r="B95" t="s">
+        <v>182</v>
+      </c>
+      <c r="C95" t="s">
+        <v>103</v>
+      </c>
+      <c r="D95">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>86</v>
+      </c>
+      <c r="B96" t="s">
+        <v>183</v>
+      </c>
+      <c r="C96" t="s">
+        <v>184</v>
+      </c>
+      <c r="D96">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
         <v>87</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B97" t="s">
         <v>185</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C97" t="s">
         <v>186</v>
       </c>
-      <c r="D91">
+      <c r="D97">
         <v>2.2999999999999998</v>
       </c>
     </row>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation - Copy before adding crown_width_option_baseline_to_start8\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A20CA1E-2584-452A-B5C8-D6DB4FE5F73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE52741-CD98-414D-93C6-C8D1C4FB94AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="731">
   <si>
     <t>pFS2</t>
   </si>
@@ -447,15 +447,9 @@
     <t>Shape of mortality response</t>
   </si>
   <si>
-    <t>Max. stem mass per tree @ 1000 trees/hectare</t>
-  </si>
-  <si>
     <t>kg/tree</t>
   </si>
   <si>
-    <t>Power in self-thinning rule</t>
-  </si>
-  <si>
     <t>Fraction mean single-tree foliage biomass lost per dead tree</t>
   </si>
   <si>
@@ -1728,15 +1722,6 @@
     <t>apar</t>
   </si>
   <si>
-    <t>Power in fertility modifier when mort_model = 2</t>
-  </si>
-  <si>
-    <t>Power in temperature modifier when mort_model = 2</t>
-  </si>
-  <si>
-    <t>Power in physmod modifier when mort_model = 2</t>
-  </si>
-  <si>
     <t>mort_thinn_total</t>
   </si>
   <si>
@@ -2127,9 +2112,6 @@
     <t>Parameter of crown diameter equation</t>
   </si>
   <si>
-    <t>Parameter of crown length equation</t>
-  </si>
-  <si>
     <t>var_10_4</t>
   </si>
   <si>
@@ -2184,30 +2166,18 @@
     <t>thinfPhys</t>
   </si>
   <si>
-    <t>Intercept for self-thinning rule when mort_model = 2</t>
-  </si>
-  <si>
     <t>ln(trees ha-1)</t>
   </si>
   <si>
     <t>beta0</t>
   </si>
   <si>
-    <t>constant for self-thinning when mort_model = 2</t>
-  </si>
-  <si>
     <t>betaB</t>
   </si>
   <si>
-    <t>Power for B when mort_model = 2</t>
-  </si>
-  <si>
     <t>betaN</t>
   </si>
   <si>
-    <t>Power in tree density when mort_model = 2</t>
-  </si>
-  <si>
     <t>betafN</t>
   </si>
   <si>
@@ -2215,6 +2185,45 @@
   </si>
   <si>
     <t>betafPhys</t>
+  </si>
+  <si>
+    <t>Maximum stem mass per tree @ N = 1000 trees/hectare (mort_model = 1)</t>
+  </si>
+  <si>
+    <t>Power in self-thinning rule (mort_model = 1 or 2)</t>
+  </si>
+  <si>
+    <t>Intercept for self-thinning rule (mort_model = 2)</t>
+  </si>
+  <si>
+    <t>Power in fertility modifier (mort_model = 2)</t>
+  </si>
+  <si>
+    <t>Power in temperature modifier (mort_model = 2)</t>
+  </si>
+  <si>
+    <t>Power in physmod modifier (mort_model = 2)</t>
+  </si>
+  <si>
+    <t>constant for self-thinning (mort_model = 3)</t>
+  </si>
+  <si>
+    <t>Power for B (mort_model = 3)</t>
+  </si>
+  <si>
+    <t>Power in tree density (mort_model = 3)</t>
+  </si>
+  <si>
+    <t>Power in nutrition modifier (mort_model = 3)</t>
+  </si>
+  <si>
+    <t>Power in temperature modifier (mort_model = 3)</t>
+  </si>
+  <si>
+    <t>Power in physmod modifier (mort_model = 3)</t>
+  </si>
+  <si>
+    <t>Parameter of crown ratio equation</t>
   </si>
 </sst>
 </file>
@@ -2865,7 +2874,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="C18" t="s">
         <v>103</v>
@@ -3061,10 +3070,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>718</v>
+      </c>
+      <c r="C32" t="s">
         <v>138</v>
-      </c>
-      <c r="C32" t="s">
-        <v>139</v>
       </c>
       <c r="D32">
         <v>300</v>
@@ -3075,7 +3084,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>719</v>
       </c>
       <c r="C33" t="s">
         <v>103</v>
@@ -3086,13 +3095,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>717</v>
+        <v>707</v>
+      </c>
+      <c r="B34" t="s">
+        <v>720</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="D34" s="1">
         <v>12</v>
@@ -3100,10 +3109,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>565</v>
+        <v>708</v>
+      </c>
+      <c r="B35" t="s">
+        <v>721</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>103</v>
@@ -3114,10 +3123,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>566</v>
+        <v>709</v>
+      </c>
+      <c r="B36" t="s">
+        <v>722</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>103</v>
@@ -3128,10 +3137,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>567</v>
+        <v>710</v>
+      </c>
+      <c r="B37" t="s">
+        <v>723</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>103</v>
@@ -3142,10 +3151,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>720</v>
+        <v>712</v>
+      </c>
+      <c r="B38" t="s">
+        <v>724</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>103</v>
@@ -3156,10 +3165,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>722</v>
+        <v>713</v>
+      </c>
+      <c r="B39" t="s">
+        <v>725</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>103</v>
@@ -3170,10 +3179,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>724</v>
+        <v>714</v>
+      </c>
+      <c r="B40" t="s">
+        <v>726</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>103</v>
@@ -3184,10 +3193,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>565</v>
+        <v>715</v>
+      </c>
+      <c r="B41" t="s">
+        <v>727</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>103</v>
@@ -3198,10 +3207,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>566</v>
+        <v>716</v>
+      </c>
+      <c r="B42" t="s">
+        <v>728</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>103</v>
@@ -3212,10 +3221,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>567</v>
+        <v>717</v>
+      </c>
+      <c r="B43" t="s">
+        <v>729</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>103</v>
@@ -3229,7 +3238,7 @@
         <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
         <v>103</v>
@@ -3243,7 +3252,7 @@
         <v>34</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
         <v>103</v>
@@ -3257,7 +3266,7 @@
         <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -3271,10 +3280,10 @@
         <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C47" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D47">
         <v>11</v>
@@ -3285,10 +3294,10 @@
         <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D48">
         <v>4</v>
@@ -3299,7 +3308,7 @@
         <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C49" t="s">
         <v>130</v>
@@ -3313,7 +3322,7 @@
         <v>39</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C50" t="s">
         <v>103</v>
@@ -3324,10 +3333,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="1" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1">
@@ -3339,7 +3348,7 @@
         <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C52" t="s">
         <v>130</v>
@@ -3353,7 +3362,7 @@
         <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C53" t="s">
         <v>103</v>
@@ -3367,7 +3376,7 @@
         <v>42</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
@@ -3381,7 +3390,7 @@
         <v>43</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C55" t="s">
         <v>103</v>
@@ -3395,10 +3404,10 @@
         <v>44</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C56" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D56">
         <v>0.06</v>
@@ -3409,7 +3418,7 @@
         <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C57" t="s">
         <v>103</v>
@@ -3423,10 +3432,10 @@
         <v>46</v>
       </c>
       <c r="B58" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C58" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -3437,10 +3446,10 @@
         <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C59" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D59">
         <v>0.02</v>
@@ -3451,7 +3460,7 @@
         <v>48</v>
       </c>
       <c r="B60" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C60" t="s">
         <v>103</v>
@@ -3465,10 +3474,10 @@
         <v>49</v>
       </c>
       <c r="B61" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C61" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D61">
         <v>0.05</v>
@@ -3479,10 +3488,10 @@
         <v>50</v>
       </c>
       <c r="B62" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C62" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D62">
         <v>0.2</v>
@@ -3493,7 +3502,7 @@
         <v>51</v>
       </c>
       <c r="B63" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C63" t="s">
         <v>103</v>
@@ -3507,10 +3516,10 @@
         <v>52</v>
       </c>
       <c r="B64" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C64" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D64">
         <v>2</v>
@@ -3521,10 +3530,10 @@
         <v>53</v>
       </c>
       <c r="B65" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C65" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D65">
         <v>4.4000000000000004</v>
@@ -3535,10 +3544,10 @@
         <v>54</v>
       </c>
       <c r="B66" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C66" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D66">
         <v>27</v>
@@ -3549,7 +3558,7 @@
         <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C67" t="s">
         <v>103</v>
@@ -3563,7 +3572,7 @@
         <v>56</v>
       </c>
       <c r="B68" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C68" t="s">
         <v>103</v>
@@ -3577,7 +3586,7 @@
         <v>57</v>
       </c>
       <c r="B69" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C69" t="s">
         <v>130</v>
@@ -3591,10 +3600,10 @@
         <v>58</v>
       </c>
       <c r="B70" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C70" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D70">
         <v>0.45</v>
@@ -3605,10 +3614,10 @@
         <v>59</v>
       </c>
       <c r="B71" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C71" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D71">
         <v>0.45</v>
@@ -3619,7 +3628,7 @@
         <v>60</v>
       </c>
       <c r="B72" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C72" t="s">
         <v>130</v>
@@ -3633,7 +3642,7 @@
         <v>66</v>
       </c>
       <c r="B73" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C73" t="s">
         <v>103</v>
@@ -3644,13 +3653,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="1" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D74" s="1">
         <v>1.3</v>
@@ -3661,7 +3670,7 @@
         <v>61</v>
       </c>
       <c r="B75" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C75" t="s">
         <v>103</v>
@@ -3672,10 +3681,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B76" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C76" t="s">
         <v>103</v>
@@ -3686,10 +3695,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="B77" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C77" t="s">
         <v>103</v>
@@ -3700,10 +3709,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="B78" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C78" t="s">
         <v>103</v>
@@ -3714,10 +3723,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="B79" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C79" t="s">
         <v>103</v>
@@ -3731,7 +3740,7 @@
         <v>62</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C80" t="s">
         <v>103</v>
@@ -3745,7 +3754,7 @@
         <v>63</v>
       </c>
       <c r="B81" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C81" t="s">
         <v>103</v>
@@ -3759,7 +3768,7 @@
         <v>64</v>
       </c>
       <c r="B82" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
         <v>103</v>
@@ -3773,7 +3782,7 @@
         <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C83" t="s">
         <v>103</v>
@@ -3787,7 +3796,7 @@
         <v>67</v>
       </c>
       <c r="B84" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C84" t="s">
         <v>103</v>
@@ -3798,10 +3807,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="B85" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C85" t="s">
         <v>103</v>
@@ -3812,10 +3821,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="B86" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C86" t="s">
         <v>103</v>
@@ -3826,10 +3835,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="B87" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C87" t="s">
         <v>103</v>
@@ -3840,10 +3849,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="B88" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C88" t="s">
         <v>103</v>
@@ -3857,7 +3866,7 @@
         <v>68</v>
       </c>
       <c r="B89" t="s">
-        <v>698</v>
+        <v>730</v>
       </c>
       <c r="C89" t="s">
         <v>103</v>
@@ -3868,10 +3877,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="B90" t="s">
-        <v>698</v>
+        <v>730</v>
       </c>
       <c r="C90" t="s">
         <v>103</v>
@@ -3882,10 +3891,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B91" t="s">
-        <v>698</v>
+        <v>730</v>
       </c>
       <c r="C91" t="s">
         <v>103</v>
@@ -3896,10 +3905,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="B92" t="s">
-        <v>698</v>
+        <v>730</v>
       </c>
       <c r="C92" t="s">
         <v>103</v>
@@ -3910,10 +3919,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="B93" t="s">
-        <v>698</v>
+        <v>730</v>
       </c>
       <c r="C93" t="s">
         <v>103</v>
@@ -3927,10 +3936,10 @@
         <v>84</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C94" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D94">
         <v>-90</v>
@@ -3941,7 +3950,7 @@
         <v>85</v>
       </c>
       <c r="B95" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C95" t="s">
         <v>103</v>
@@ -3955,10 +3964,10 @@
         <v>86</v>
       </c>
       <c r="B96" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C96" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D96">
         <v>24</v>
@@ -3969,10 +3978,10 @@
         <v>87</v>
       </c>
       <c r="B97" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C97" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D97">
         <v>2.2999999999999998</v>
@@ -4015,7 +4024,7 @@
         <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -4029,7 +4038,7 @@
         <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C3" t="s">
         <v>103</v>
@@ -4043,7 +4052,7 @@
         <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C4" t="s">
         <v>103</v>
@@ -4057,7 +4066,7 @@
         <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
@@ -4071,7 +4080,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
         <v>103</v>
@@ -4085,7 +4094,7 @@
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C7" t="s">
         <v>103</v>
@@ -4099,7 +4108,7 @@
         <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
         <v>103</v>
@@ -4113,7 +4122,7 @@
         <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C9" t="s">
         <v>103</v>
@@ -4127,7 +4136,7 @@
         <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C10" t="s">
         <v>103</v>
@@ -4141,7 +4150,7 @@
         <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C11" t="s">
         <v>103</v>
@@ -4155,7 +4164,7 @@
         <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C12" t="s">
         <v>103</v>
@@ -4169,7 +4178,7 @@
         <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C13" t="s">
         <v>103</v>
@@ -4183,7 +4192,7 @@
         <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C14" t="s">
         <v>103</v>
@@ -4197,7 +4206,7 @@
         <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C15" t="s">
         <v>103</v>
@@ -4211,7 +4220,7 @@
         <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C16" t="s">
         <v>103</v>
@@ -4241,16 +4250,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1" t="s">
         <v>202</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>203</v>
-      </c>
-      <c r="C1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D1" t="s">
-        <v>205</v>
       </c>
       <c r="E1" t="s">
         <v>99</v>
@@ -4259,7 +4268,7 @@
         <v>100</v>
       </c>
       <c r="G1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4273,16 +4282,16 @@
         <v>93</v>
       </c>
       <c r="D2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F2" t="s">
         <v>207</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>208</v>
-      </c>
-      <c r="F2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4296,16 +4305,16 @@
         <v>94</v>
       </c>
       <c r="D3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F3" t="s">
         <v>207</v>
       </c>
-      <c r="E3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F3" t="s">
-        <v>209</v>
-      </c>
       <c r="G3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4319,16 +4328,16 @@
         <v>95</v>
       </c>
       <c r="D4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" t="s">
+        <v>211</v>
+      </c>
+      <c r="F4" t="s">
         <v>207</v>
       </c>
-      <c r="E4" t="s">
-        <v>213</v>
-      </c>
-      <c r="F4" t="s">
-        <v>209</v>
-      </c>
       <c r="G4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4342,16 +4351,16 @@
         <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" t="s">
         <v>215</v>
-      </c>
-      <c r="F5" t="s">
-        <v>216</v>
-      </c>
-      <c r="G5" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4362,19 +4371,19 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" t="s">
         <v>218</v>
       </c>
-      <c r="D6" t="s">
-        <v>207</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>219</v>
-      </c>
-      <c r="F6" t="s">
-        <v>220</v>
-      </c>
-      <c r="G6" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -4385,19 +4394,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F7" t="s">
         <v>222</v>
       </c>
-      <c r="D7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>223</v>
-      </c>
-      <c r="F7" t="s">
-        <v>224</v>
-      </c>
-      <c r="G7" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -4411,16 +4420,16 @@
         <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E8" t="s">
+        <v>224</v>
+      </c>
+      <c r="F8" t="s">
+        <v>225</v>
+      </c>
+      <c r="G8" t="s">
         <v>226</v>
-      </c>
-      <c r="F8" t="s">
-        <v>227</v>
-      </c>
-      <c r="G8" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -4431,19 +4440,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E9" t="s">
+        <v>228</v>
+      </c>
+      <c r="F9" t="s">
         <v>229</v>
       </c>
-      <c r="D9" t="s">
-        <v>207</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>230</v>
-      </c>
-      <c r="F9" t="s">
-        <v>231</v>
-      </c>
-      <c r="G9" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -4457,16 +4466,16 @@
         <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" t="s">
+        <v>232</v>
+      </c>
+      <c r="G10" t="s">
         <v>233</v>
-      </c>
-      <c r="F10" t="s">
-        <v>234</v>
-      </c>
-      <c r="G10" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -4477,16 +4486,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" t="s">
+        <v>205</v>
+      </c>
+      <c r="E11" t="s">
+        <v>235</v>
+      </c>
+      <c r="G11" t="s">
         <v>236</v>
-      </c>
-      <c r="D11" t="s">
-        <v>207</v>
-      </c>
-      <c r="E11" t="s">
-        <v>237</v>
-      </c>
-      <c r="G11" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -4497,19 +4506,19 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
+        <v>237</v>
+      </c>
+      <c r="D12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E12" t="s">
+        <v>238</v>
+      </c>
+      <c r="F12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G12" t="s">
         <v>239</v>
-      </c>
-      <c r="D12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E12" t="s">
-        <v>240</v>
-      </c>
-      <c r="F12" t="s">
-        <v>227</v>
-      </c>
-      <c r="G12" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -4520,10 +4529,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4534,10 +4543,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -4548,10 +4557,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4562,10 +4571,10 @@
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -4576,10 +4585,10 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -4590,10 +4599,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4604,10 +4613,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -4618,10 +4627,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -4632,10 +4641,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -4649,16 +4658,16 @@
         <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F22" t="s">
         <v>130</v>
       </c>
       <c r="G22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4669,19 +4678,19 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
+        <v>247</v>
+      </c>
+      <c r="D23" t="s">
+        <v>244</v>
+      </c>
+      <c r="E23" t="s">
+        <v>248</v>
+      </c>
+      <c r="F23" t="s">
         <v>249</v>
       </c>
-      <c r="D23" t="s">
-        <v>246</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>250</v>
-      </c>
-      <c r="F23" t="s">
-        <v>251</v>
-      </c>
-      <c r="G23" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -4692,19 +4701,19 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
+        <v>251</v>
+      </c>
+      <c r="D24" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" t="s">
+        <v>252</v>
+      </c>
+      <c r="F24" t="s">
         <v>253</v>
       </c>
-      <c r="D24" t="s">
-        <v>246</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>254</v>
-      </c>
-      <c r="F24" t="s">
-        <v>255</v>
-      </c>
-      <c r="G24" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -4715,19 +4724,19 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
+        <v>255</v>
+      </c>
+      <c r="D25" t="s">
+        <v>244</v>
+      </c>
+      <c r="E25" t="s">
+        <v>256</v>
+      </c>
+      <c r="F25" t="s">
         <v>257</v>
       </c>
-      <c r="D25" t="s">
-        <v>246</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
         <v>258</v>
-      </c>
-      <c r="F25" t="s">
-        <v>259</v>
-      </c>
-      <c r="G25" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -4738,19 +4747,19 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
+        <v>259</v>
+      </c>
+      <c r="D26" t="s">
+        <v>244</v>
+      </c>
+      <c r="E26" t="s">
+        <v>260</v>
+      </c>
+      <c r="F26" t="s">
         <v>261</v>
       </c>
-      <c r="D26" t="s">
-        <v>246</v>
-      </c>
-      <c r="E26" t="s">
-        <v>262</v>
-      </c>
-      <c r="F26" t="s">
-        <v>263</v>
-      </c>
       <c r="G26" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -4761,19 +4770,19 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" t="s">
+        <v>244</v>
+      </c>
+      <c r="E27" t="s">
+        <v>263</v>
+      </c>
+      <c r="F27" t="s">
         <v>264</v>
       </c>
-      <c r="D27" t="s">
-        <v>246</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
         <v>265</v>
-      </c>
-      <c r="F27" t="s">
-        <v>266</v>
-      </c>
-      <c r="G27" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -4784,19 +4793,19 @@
         <v>7</v>
       </c>
       <c r="C28" t="s">
+        <v>266</v>
+      </c>
+      <c r="D28" t="s">
+        <v>244</v>
+      </c>
+      <c r="E28" t="s">
+        <v>267</v>
+      </c>
+      <c r="F28" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" t="s">
         <v>268</v>
-      </c>
-      <c r="D28" t="s">
-        <v>246</v>
-      </c>
-      <c r="E28" t="s">
-        <v>269</v>
-      </c>
-      <c r="F28" t="s">
-        <v>103</v>
-      </c>
-      <c r="G28" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -4807,19 +4816,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>269</v>
+      </c>
+      <c r="D29" t="s">
+        <v>244</v>
+      </c>
+      <c r="E29" t="s">
+        <v>270</v>
+      </c>
+      <c r="F29" t="s">
+        <v>264</v>
+      </c>
+      <c r="G29" t="s">
         <v>271</v>
-      </c>
-      <c r="D29" t="s">
-        <v>246</v>
-      </c>
-      <c r="E29" t="s">
-        <v>272</v>
-      </c>
-      <c r="F29" t="s">
-        <v>266</v>
-      </c>
-      <c r="G29" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -4830,19 +4839,19 @@
         <v>9</v>
       </c>
       <c r="C30" t="s">
+        <v>272</v>
+      </c>
+      <c r="D30" t="s">
+        <v>244</v>
+      </c>
+      <c r="E30" t="s">
+        <v>273</v>
+      </c>
+      <c r="F30" t="s">
+        <v>264</v>
+      </c>
+      <c r="G30" t="s">
         <v>274</v>
-      </c>
-      <c r="D30" t="s">
-        <v>246</v>
-      </c>
-      <c r="E30" t="s">
-        <v>275</v>
-      </c>
-      <c r="F30" t="s">
-        <v>266</v>
-      </c>
-      <c r="G30" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -4853,19 +4862,19 @@
         <v>10</v>
       </c>
       <c r="C31" t="s">
+        <v>275</v>
+      </c>
+      <c r="D31" t="s">
+        <v>244</v>
+      </c>
+      <c r="E31" t="s">
+        <v>276</v>
+      </c>
+      <c r="F31" t="s">
         <v>277</v>
       </c>
-      <c r="D31" t="s">
-        <v>246</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>278</v>
-      </c>
-      <c r="F31" t="s">
-        <v>279</v>
-      </c>
-      <c r="G31" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -4876,19 +4885,19 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
+        <v>279</v>
+      </c>
+      <c r="D32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E32" t="s">
+        <v>280</v>
+      </c>
+      <c r="F32" t="s">
         <v>281</v>
       </c>
-      <c r="D32" t="s">
-        <v>246</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>282</v>
-      </c>
-      <c r="F32" t="s">
-        <v>283</v>
-      </c>
-      <c r="G32" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -4899,19 +4908,19 @@
         <v>12</v>
       </c>
       <c r="C33" t="s">
+        <v>283</v>
+      </c>
+      <c r="D33" t="s">
+        <v>244</v>
+      </c>
+      <c r="E33" t="s">
+        <v>284</v>
+      </c>
+      <c r="F33" t="s">
+        <v>277</v>
+      </c>
+      <c r="G33" t="s">
         <v>285</v>
-      </c>
-      <c r="D33" t="s">
-        <v>246</v>
-      </c>
-      <c r="E33" t="s">
-        <v>286</v>
-      </c>
-      <c r="F33" t="s">
-        <v>279</v>
-      </c>
-      <c r="G33" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -4922,19 +4931,19 @@
         <v>13</v>
       </c>
       <c r="C34" t="s">
+        <v>286</v>
+      </c>
+      <c r="D34" t="s">
+        <v>244</v>
+      </c>
+      <c r="E34" t="s">
+        <v>287</v>
+      </c>
+      <c r="F34" t="s">
+        <v>277</v>
+      </c>
+      <c r="G34" t="s">
         <v>288</v>
-      </c>
-      <c r="D34" t="s">
-        <v>246</v>
-      </c>
-      <c r="E34" t="s">
-        <v>289</v>
-      </c>
-      <c r="F34" t="s">
-        <v>279</v>
-      </c>
-      <c r="G34" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -4945,10 +4954,10 @@
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D35" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -4959,10 +4968,10 @@
         <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D36" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -4973,10 +4982,10 @@
         <v>16</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4987,10 +4996,10 @@
         <v>17</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -5001,10 +5010,10 @@
         <v>18</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -5015,10 +5024,10 @@
         <v>19</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -5029,10 +5038,10 @@
         <v>20</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -5043,19 +5052,19 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
+        <v>291</v>
+      </c>
+      <c r="D42" t="s">
+        <v>292</v>
+      </c>
+      <c r="E42" t="s">
         <v>293</v>
       </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
+        <v>103</v>
+      </c>
+      <c r="G42" t="s">
         <v>294</v>
-      </c>
-      <c r="E42" t="s">
-        <v>295</v>
-      </c>
-      <c r="F42" t="s">
-        <v>103</v>
-      </c>
-      <c r="G42" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -5066,19 +5075,19 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
+        <v>295</v>
+      </c>
+      <c r="D43" t="s">
+        <v>292</v>
+      </c>
+      <c r="E43" t="s">
+        <v>296</v>
+      </c>
+      <c r="F43" t="s">
         <v>297</v>
       </c>
-      <c r="D43" t="s">
-        <v>294</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="G43" t="s">
         <v>298</v>
-      </c>
-      <c r="F43" t="s">
-        <v>299</v>
-      </c>
-      <c r="G43" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -5089,19 +5098,19 @@
         <v>3</v>
       </c>
       <c r="C44" t="s">
+        <v>299</v>
+      </c>
+      <c r="D44" t="s">
+        <v>292</v>
+      </c>
+      <c r="E44" t="s">
+        <v>300</v>
+      </c>
+      <c r="F44" t="s">
         <v>301</v>
       </c>
-      <c r="D44" t="s">
-        <v>294</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="G44" t="s">
         <v>302</v>
-      </c>
-      <c r="F44" t="s">
-        <v>303</v>
-      </c>
-      <c r="G44" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -5112,19 +5121,19 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
+        <v>303</v>
+      </c>
+      <c r="D45" t="s">
+        <v>292</v>
+      </c>
+      <c r="E45" t="s">
+        <v>304</v>
+      </c>
+      <c r="F45" t="s">
+        <v>301</v>
+      </c>
+      <c r="G45" t="s">
         <v>305</v>
-      </c>
-      <c r="D45" t="s">
-        <v>294</v>
-      </c>
-      <c r="E45" t="s">
-        <v>306</v>
-      </c>
-      <c r="F45" t="s">
-        <v>303</v>
-      </c>
-      <c r="G45" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -5135,16 +5144,16 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
+        <v>306</v>
+      </c>
+      <c r="D46" t="s">
+        <v>292</v>
+      </c>
+      <c r="E46" t="s">
+        <v>307</v>
+      </c>
+      <c r="G46" t="s">
         <v>308</v>
-      </c>
-      <c r="D46" t="s">
-        <v>294</v>
-      </c>
-      <c r="E46" t="s">
-        <v>309</v>
-      </c>
-      <c r="G46" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -5155,19 +5164,19 @@
         <v>6</v>
       </c>
       <c r="C47" t="s">
+        <v>309</v>
+      </c>
+      <c r="D47" t="s">
+        <v>292</v>
+      </c>
+      <c r="E47" t="s">
+        <v>310</v>
+      </c>
+      <c r="F47" t="s">
         <v>311</v>
       </c>
-      <c r="D47" t="s">
-        <v>294</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>312</v>
-      </c>
-      <c r="F47" t="s">
-        <v>313</v>
-      </c>
-      <c r="G47" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -5178,19 +5187,19 @@
         <v>7</v>
       </c>
       <c r="C48" t="s">
+        <v>313</v>
+      </c>
+      <c r="D48" t="s">
+        <v>292</v>
+      </c>
+      <c r="E48" t="s">
+        <v>314</v>
+      </c>
+      <c r="F48" t="s">
+        <v>103</v>
+      </c>
+      <c r="G48" t="s">
         <v>315</v>
-      </c>
-      <c r="D48" t="s">
-        <v>294</v>
-      </c>
-      <c r="E48" t="s">
-        <v>316</v>
-      </c>
-      <c r="F48" t="s">
-        <v>103</v>
-      </c>
-      <c r="G48" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -5201,19 +5210,19 @@
         <v>8</v>
       </c>
       <c r="C49" t="s">
+        <v>316</v>
+      </c>
+      <c r="D49" t="s">
+        <v>292</v>
+      </c>
+      <c r="E49" t="s">
+        <v>317</v>
+      </c>
+      <c r="F49" t="s">
+        <v>103</v>
+      </c>
+      <c r="G49" t="s">
         <v>318</v>
-      </c>
-      <c r="D49" t="s">
-        <v>294</v>
-      </c>
-      <c r="E49" t="s">
-        <v>319</v>
-      </c>
-      <c r="F49" t="s">
-        <v>103</v>
-      </c>
-      <c r="G49" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -5224,19 +5233,19 @@
         <v>9</v>
       </c>
       <c r="C50" t="s">
+        <v>319</v>
+      </c>
+      <c r="D50" t="s">
+        <v>292</v>
+      </c>
+      <c r="E50" t="s">
+        <v>320</v>
+      </c>
+      <c r="F50" t="s">
+        <v>103</v>
+      </c>
+      <c r="G50" t="s">
         <v>321</v>
-      </c>
-      <c r="D50" t="s">
-        <v>294</v>
-      </c>
-      <c r="E50" t="s">
-        <v>322</v>
-      </c>
-      <c r="F50" t="s">
-        <v>103</v>
-      </c>
-      <c r="G50" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -5247,19 +5256,19 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
+        <v>322</v>
+      </c>
+      <c r="D51" t="s">
+        <v>292</v>
+      </c>
+      <c r="E51" t="s">
+        <v>323</v>
+      </c>
+      <c r="F51" t="s">
         <v>324</v>
       </c>
-      <c r="D51" t="s">
-        <v>294</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="G51" t="s">
         <v>325</v>
-      </c>
-      <c r="F51" t="s">
-        <v>326</v>
-      </c>
-      <c r="G51" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -5270,19 +5279,19 @@
         <v>11</v>
       </c>
       <c r="C52" t="s">
+        <v>326</v>
+      </c>
+      <c r="D52" t="s">
+        <v>292</v>
+      </c>
+      <c r="E52" t="s">
+        <v>327</v>
+      </c>
+      <c r="F52" t="s">
+        <v>229</v>
+      </c>
+      <c r="G52" t="s">
         <v>328</v>
-      </c>
-      <c r="D52" t="s">
-        <v>294</v>
-      </c>
-      <c r="E52" t="s">
-        <v>329</v>
-      </c>
-      <c r="F52" t="s">
-        <v>231</v>
-      </c>
-      <c r="G52" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -5293,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="D53" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E53" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -5310,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D54" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -5324,10 +5333,10 @@
         <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D55" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -5338,10 +5347,10 @@
         <v>15</v>
       </c>
       <c r="C56" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D56" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -5352,10 +5361,10 @@
         <v>16</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -5366,10 +5375,10 @@
         <v>17</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -5380,10 +5389,10 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -5394,10 +5403,10 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -5408,10 +5417,10 @@
         <v>20</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -5425,16 +5434,16 @@
         <v>91</v>
       </c>
       <c r="D62" t="s">
+        <v>332</v>
+      </c>
+      <c r="E62" t="s">
+        <v>333</v>
+      </c>
+      <c r="F62" t="s">
         <v>334</v>
       </c>
-      <c r="E62" t="s">
+      <c r="G62" t="s">
         <v>335</v>
-      </c>
-      <c r="F62" t="s">
-        <v>336</v>
-      </c>
-      <c r="G62" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -5448,16 +5457,16 @@
         <v>90</v>
       </c>
       <c r="D63" t="s">
+        <v>332</v>
+      </c>
+      <c r="E63" t="s">
+        <v>336</v>
+      </c>
+      <c r="F63" t="s">
         <v>334</v>
       </c>
-      <c r="E63" t="s">
-        <v>338</v>
-      </c>
-      <c r="F63" t="s">
-        <v>336</v>
-      </c>
       <c r="G63" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -5471,16 +5480,16 @@
         <v>89</v>
       </c>
       <c r="D64" t="s">
+        <v>332</v>
+      </c>
+      <c r="E64" t="s">
+        <v>338</v>
+      </c>
+      <c r="F64" t="s">
         <v>334</v>
       </c>
-      <c r="E64" t="s">
-        <v>340</v>
-      </c>
-      <c r="F64" t="s">
-        <v>336</v>
-      </c>
       <c r="G64" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -5491,19 +5500,19 @@
         <v>4</v>
       </c>
       <c r="C65" t="s">
+        <v>340</v>
+      </c>
+      <c r="D65" t="s">
+        <v>332</v>
+      </c>
+      <c r="E65" t="s">
+        <v>341</v>
+      </c>
+      <c r="F65" t="s">
         <v>342</v>
       </c>
-      <c r="D65" t="s">
-        <v>334</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="G65" t="s">
         <v>343</v>
-      </c>
-      <c r="F65" t="s">
-        <v>344</v>
-      </c>
-      <c r="G65" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -5514,19 +5523,19 @@
         <v>5</v>
       </c>
       <c r="C66" t="s">
+        <v>344</v>
+      </c>
+      <c r="D66" t="s">
+        <v>332</v>
+      </c>
+      <c r="E66" t="s">
+        <v>345</v>
+      </c>
+      <c r="F66" t="s">
         <v>346</v>
       </c>
-      <c r="D66" t="s">
-        <v>334</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>347</v>
-      </c>
-      <c r="F66" t="s">
-        <v>348</v>
-      </c>
-      <c r="G66" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -5537,16 +5546,16 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
+        <v>348</v>
+      </c>
+      <c r="D67" t="s">
+        <v>332</v>
+      </c>
+      <c r="E67" t="s">
+        <v>349</v>
+      </c>
+      <c r="G67" t="s">
         <v>350</v>
-      </c>
-      <c r="D67" t="s">
-        <v>334</v>
-      </c>
-      <c r="E67" t="s">
-        <v>351</v>
-      </c>
-      <c r="G67" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -5557,19 +5566,19 @@
         <v>7</v>
       </c>
       <c r="C68" t="s">
+        <v>351</v>
+      </c>
+      <c r="D68" t="s">
+        <v>332</v>
+      </c>
+      <c r="E68" t="s">
+        <v>352</v>
+      </c>
+      <c r="F68" t="s">
+        <v>334</v>
+      </c>
+      <c r="G68" t="s">
         <v>353</v>
-      </c>
-      <c r="D68" t="s">
-        <v>334</v>
-      </c>
-      <c r="E68" t="s">
-        <v>354</v>
-      </c>
-      <c r="F68" t="s">
-        <v>336</v>
-      </c>
-      <c r="G68" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -5580,19 +5589,19 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
+        <v>354</v>
+      </c>
+      <c r="D69" t="s">
+        <v>332</v>
+      </c>
+      <c r="E69" t="s">
+        <v>355</v>
+      </c>
+      <c r="F69" t="s">
+        <v>334</v>
+      </c>
+      <c r="G69" t="s">
         <v>356</v>
-      </c>
-      <c r="D69" t="s">
-        <v>334</v>
-      </c>
-      <c r="E69" t="s">
-        <v>357</v>
-      </c>
-      <c r="F69" t="s">
-        <v>336</v>
-      </c>
-      <c r="G69" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -5603,19 +5612,19 @@
         <v>9</v>
       </c>
       <c r="C70" t="s">
+        <v>357</v>
+      </c>
+      <c r="D70" t="s">
+        <v>332</v>
+      </c>
+      <c r="E70" t="s">
+        <v>358</v>
+      </c>
+      <c r="F70" t="s">
+        <v>334</v>
+      </c>
+      <c r="G70" t="s">
         <v>359</v>
-      </c>
-      <c r="D70" t="s">
-        <v>334</v>
-      </c>
-      <c r="E70" t="s">
-        <v>360</v>
-      </c>
-      <c r="F70" t="s">
-        <v>336</v>
-      </c>
-      <c r="G70" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -5626,19 +5635,19 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
+        <v>360</v>
+      </c>
+      <c r="D71" t="s">
+        <v>332</v>
+      </c>
+      <c r="E71" t="s">
+        <v>361</v>
+      </c>
+      <c r="F71" t="s">
+        <v>334</v>
+      </c>
+      <c r="G71" t="s">
         <v>362</v>
-      </c>
-      <c r="D71" t="s">
-        <v>334</v>
-      </c>
-      <c r="E71" t="s">
-        <v>363</v>
-      </c>
-      <c r="F71" t="s">
-        <v>336</v>
-      </c>
-      <c r="G71" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -5649,19 +5658,19 @@
         <v>11</v>
       </c>
       <c r="C72" t="s">
+        <v>363</v>
+      </c>
+      <c r="D72" t="s">
+        <v>332</v>
+      </c>
+      <c r="E72" t="s">
+        <v>364</v>
+      </c>
+      <c r="F72" t="s">
+        <v>334</v>
+      </c>
+      <c r="G72" t="s">
         <v>365</v>
-      </c>
-      <c r="D72" t="s">
-        <v>334</v>
-      </c>
-      <c r="E72" t="s">
-        <v>366</v>
-      </c>
-      <c r="F72" t="s">
-        <v>336</v>
-      </c>
-      <c r="G72" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -5672,16 +5681,16 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D73" t="s">
+        <v>332</v>
+      </c>
+      <c r="E73" t="s">
+        <v>699</v>
+      </c>
+      <c r="F73" t="s">
         <v>334</v>
-      </c>
-      <c r="E73" t="s">
-        <v>705</v>
-      </c>
-      <c r="F73" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5692,16 +5701,16 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D74" t="s">
+        <v>332</v>
+      </c>
+      <c r="E74" t="s">
+        <v>699</v>
+      </c>
+      <c r="F74" t="s">
         <v>334</v>
-      </c>
-      <c r="E74" t="s">
-        <v>705</v>
-      </c>
-      <c r="F74" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -5712,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="C75" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -5726,10 +5735,10 @@
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -5740,10 +5749,10 @@
         <v>16</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -5754,10 +5763,10 @@
         <v>17</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -5768,10 +5777,10 @@
         <v>18</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -5782,10 +5791,10 @@
         <v>19</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -5796,10 +5805,10 @@
         <v>20</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -5810,19 +5819,19 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
+        <v>368</v>
+      </c>
+      <c r="D82" t="s">
+        <v>369</v>
+      </c>
+      <c r="E82" t="s">
         <v>370</v>
       </c>
-      <c r="D82" t="s">
+      <c r="F82" t="s">
+        <v>103</v>
+      </c>
+      <c r="G82" t="s">
         <v>371</v>
-      </c>
-      <c r="E82" t="s">
-        <v>372</v>
-      </c>
-      <c r="F82" t="s">
-        <v>103</v>
-      </c>
-      <c r="G82" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -5833,19 +5842,19 @@
         <v>2</v>
       </c>
       <c r="C83" t="s">
+        <v>372</v>
+      </c>
+      <c r="D83" t="s">
+        <v>369</v>
+      </c>
+      <c r="E83" t="s">
+        <v>373</v>
+      </c>
+      <c r="F83" t="s">
+        <v>103</v>
+      </c>
+      <c r="G83" t="s">
         <v>374</v>
-      </c>
-      <c r="D83" t="s">
-        <v>371</v>
-      </c>
-      <c r="E83" t="s">
-        <v>375</v>
-      </c>
-      <c r="F83" t="s">
-        <v>103</v>
-      </c>
-      <c r="G83" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -5856,19 +5865,19 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
+        <v>375</v>
+      </c>
+      <c r="D84" t="s">
+        <v>369</v>
+      </c>
+      <c r="E84" t="s">
+        <v>376</v>
+      </c>
+      <c r="F84" t="s">
+        <v>103</v>
+      </c>
+      <c r="G84" t="s">
         <v>377</v>
-      </c>
-      <c r="D84" t="s">
-        <v>371</v>
-      </c>
-      <c r="E84" t="s">
-        <v>378</v>
-      </c>
-      <c r="F84" t="s">
-        <v>103</v>
-      </c>
-      <c r="G84" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -5879,19 +5888,19 @@
         <v>4</v>
       </c>
       <c r="C85" t="s">
+        <v>378</v>
+      </c>
+      <c r="D85" t="s">
+        <v>369</v>
+      </c>
+      <c r="E85" t="s">
+        <v>379</v>
+      </c>
+      <c r="F85" t="s">
+        <v>103</v>
+      </c>
+      <c r="G85" t="s">
         <v>380</v>
-      </c>
-      <c r="D85" t="s">
-        <v>371</v>
-      </c>
-      <c r="E85" t="s">
-        <v>381</v>
-      </c>
-      <c r="F85" t="s">
-        <v>103</v>
-      </c>
-      <c r="G85" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -5902,19 +5911,19 @@
         <v>5</v>
       </c>
       <c r="C86" t="s">
+        <v>381</v>
+      </c>
+      <c r="D86" t="s">
+        <v>369</v>
+      </c>
+      <c r="E86" t="s">
+        <v>382</v>
+      </c>
+      <c r="F86" t="s">
+        <v>103</v>
+      </c>
+      <c r="G86" t="s">
         <v>383</v>
-      </c>
-      <c r="D86" t="s">
-        <v>371</v>
-      </c>
-      <c r="E86" t="s">
-        <v>384</v>
-      </c>
-      <c r="F86" t="s">
-        <v>103</v>
-      </c>
-      <c r="G86" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -5925,19 +5934,19 @@
         <v>6</v>
       </c>
       <c r="C87" t="s">
+        <v>384</v>
+      </c>
+      <c r="D87" t="s">
+        <v>369</v>
+      </c>
+      <c r="E87" t="s">
+        <v>385</v>
+      </c>
+      <c r="F87" t="s">
+        <v>103</v>
+      </c>
+      <c r="G87" t="s">
         <v>386</v>
-      </c>
-      <c r="D87" t="s">
-        <v>371</v>
-      </c>
-      <c r="E87" t="s">
-        <v>387</v>
-      </c>
-      <c r="F87" t="s">
-        <v>103</v>
-      </c>
-      <c r="G87" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -5948,19 +5957,19 @@
         <v>7</v>
       </c>
       <c r="C88" t="s">
+        <v>387</v>
+      </c>
+      <c r="D88" t="s">
+        <v>369</v>
+      </c>
+      <c r="E88" t="s">
+        <v>388</v>
+      </c>
+      <c r="F88" t="s">
+        <v>103</v>
+      </c>
+      <c r="G88" t="s">
         <v>389</v>
-      </c>
-      <c r="D88" t="s">
-        <v>371</v>
-      </c>
-      <c r="E88" t="s">
-        <v>390</v>
-      </c>
-      <c r="F88" t="s">
-        <v>103</v>
-      </c>
-      <c r="G88" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -5971,19 +5980,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
+        <v>390</v>
+      </c>
+      <c r="D89" t="s">
+        <v>369</v>
+      </c>
+      <c r="E89" t="s">
+        <v>391</v>
+      </c>
+      <c r="F89" t="s">
+        <v>103</v>
+      </c>
+      <c r="G89" t="s">
         <v>392</v>
-      </c>
-      <c r="D89" t="s">
-        <v>371</v>
-      </c>
-      <c r="E89" t="s">
-        <v>393</v>
-      </c>
-      <c r="F89" t="s">
-        <v>103</v>
-      </c>
-      <c r="G89" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -5994,19 +6003,19 @@
         <v>9</v>
       </c>
       <c r="C90" t="s">
+        <v>393</v>
+      </c>
+      <c r="D90" t="s">
+        <v>369</v>
+      </c>
+      <c r="E90" t="s">
+        <v>394</v>
+      </c>
+      <c r="F90" t="s">
+        <v>103</v>
+      </c>
+      <c r="G90" t="s">
         <v>395</v>
-      </c>
-      <c r="D90" t="s">
-        <v>371</v>
-      </c>
-      <c r="E90" t="s">
-        <v>396</v>
-      </c>
-      <c r="F90" t="s">
-        <v>103</v>
-      </c>
-      <c r="G90" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -6017,19 +6026,19 @@
         <v>10</v>
       </c>
       <c r="C91" t="s">
+        <v>396</v>
+      </c>
+      <c r="D91" t="s">
+        <v>369</v>
+      </c>
+      <c r="E91" t="s">
+        <v>397</v>
+      </c>
+      <c r="F91" t="s">
+        <v>103</v>
+      </c>
+      <c r="G91" t="s">
         <v>398</v>
-      </c>
-      <c r="D91" t="s">
-        <v>371</v>
-      </c>
-      <c r="E91" t="s">
-        <v>399</v>
-      </c>
-      <c r="F91" t="s">
-        <v>103</v>
-      </c>
-      <c r="G91" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -6040,19 +6049,19 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
+        <v>399</v>
+      </c>
+      <c r="D92" t="s">
+        <v>369</v>
+      </c>
+      <c r="E92" t="s">
+        <v>400</v>
+      </c>
+      <c r="F92" t="s">
+        <v>103</v>
+      </c>
+      <c r="G92" t="s">
         <v>401</v>
-      </c>
-      <c r="D92" t="s">
-        <v>371</v>
-      </c>
-      <c r="E92" t="s">
-        <v>402</v>
-      </c>
-      <c r="F92" t="s">
-        <v>103</v>
-      </c>
-      <c r="G92" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -6063,16 +6072,16 @@
         <v>12</v>
       </c>
       <c r="C93" t="s">
+        <v>402</v>
+      </c>
+      <c r="D93" t="s">
+        <v>369</v>
+      </c>
+      <c r="E93" t="s">
+        <v>403</v>
+      </c>
+      <c r="G93" t="s">
         <v>404</v>
-      </c>
-      <c r="D93" t="s">
-        <v>371</v>
-      </c>
-      <c r="E93" t="s">
-        <v>405</v>
-      </c>
-      <c r="G93" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -6083,10 +6092,10 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D94" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -6097,10 +6106,10 @@
         <v>14</v>
       </c>
       <c r="C95" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D95" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -6111,10 +6120,10 @@
         <v>15</v>
       </c>
       <c r="C96" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D96" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -6125,10 +6134,10 @@
         <v>16</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -6139,10 +6148,10 @@
         <v>17</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -6153,10 +6162,10 @@
         <v>18</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -6167,10 +6176,10 @@
         <v>19</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -6181,10 +6190,10 @@
         <v>20</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -6195,19 +6204,19 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
+        <v>408</v>
+      </c>
+      <c r="D102" t="s">
+        <v>409</v>
+      </c>
+      <c r="E102" t="s">
         <v>410</v>
       </c>
-      <c r="D102" t="s">
+      <c r="F102" t="s">
+        <v>334</v>
+      </c>
+      <c r="G102" t="s">
         <v>411</v>
-      </c>
-      <c r="E102" t="s">
-        <v>412</v>
-      </c>
-      <c r="F102" t="s">
-        <v>336</v>
-      </c>
-      <c r="G102" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -6218,19 +6227,19 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
+        <v>412</v>
+      </c>
+      <c r="D103" t="s">
+        <v>409</v>
+      </c>
+      <c r="E103" t="s">
+        <v>413</v>
+      </c>
+      <c r="F103" t="s">
+        <v>334</v>
+      </c>
+      <c r="G103" t="s">
         <v>414</v>
-      </c>
-      <c r="D103" t="s">
-        <v>411</v>
-      </c>
-      <c r="E103" t="s">
-        <v>415</v>
-      </c>
-      <c r="F103" t="s">
-        <v>336</v>
-      </c>
-      <c r="G103" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -6241,19 +6250,19 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D104" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E104" t="s">
+        <v>415</v>
+      </c>
+      <c r="F104" t="s">
+        <v>416</v>
+      </c>
+      <c r="G104" t="s">
         <v>417</v>
-      </c>
-      <c r="F104" t="s">
-        <v>418</v>
-      </c>
-      <c r="G104" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -6264,19 +6273,19 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D105" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E105" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F105" t="s">
         <v>103</v>
       </c>
       <c r="G105" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -6287,19 +6296,19 @@
         <v>5</v>
       </c>
       <c r="C106" t="s">
+        <v>420</v>
+      </c>
+      <c r="D106" t="s">
+        <v>409</v>
+      </c>
+      <c r="E106" t="s">
+        <v>421</v>
+      </c>
+      <c r="F106" t="s">
         <v>422</v>
       </c>
-      <c r="D106" t="s">
-        <v>411</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="G106" t="s">
         <v>423</v>
-      </c>
-      <c r="F106" t="s">
-        <v>424</v>
-      </c>
-      <c r="G106" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -6310,19 +6319,19 @@
         <v>6</v>
       </c>
       <c r="C107" t="s">
+        <v>424</v>
+      </c>
+      <c r="D107" t="s">
+        <v>409</v>
+      </c>
+      <c r="E107" t="s">
+        <v>425</v>
+      </c>
+      <c r="F107" t="s">
         <v>426</v>
       </c>
-      <c r="D107" t="s">
-        <v>411</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="G107" t="s">
         <v>427</v>
-      </c>
-      <c r="F107" t="s">
-        <v>428</v>
-      </c>
-      <c r="G107" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -6333,19 +6342,19 @@
         <v>7</v>
       </c>
       <c r="C108" t="s">
+        <v>428</v>
+      </c>
+      <c r="D108" t="s">
+        <v>409</v>
+      </c>
+      <c r="E108" t="s">
+        <v>429</v>
+      </c>
+      <c r="F108" t="s">
+        <v>426</v>
+      </c>
+      <c r="G108" t="s">
         <v>430</v>
-      </c>
-      <c r="D108" t="s">
-        <v>411</v>
-      </c>
-      <c r="E108" t="s">
-        <v>431</v>
-      </c>
-      <c r="F108" t="s">
-        <v>428</v>
-      </c>
-      <c r="G108" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -6356,19 +6365,19 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
+        <v>431</v>
+      </c>
+      <c r="D109" t="s">
+        <v>409</v>
+      </c>
+      <c r="E109" t="s">
+        <v>432</v>
+      </c>
+      <c r="F109" t="s">
+        <v>426</v>
+      </c>
+      <c r="G109" t="s">
         <v>433</v>
-      </c>
-      <c r="D109" t="s">
-        <v>411</v>
-      </c>
-      <c r="E109" t="s">
-        <v>434</v>
-      </c>
-      <c r="F109" t="s">
-        <v>428</v>
-      </c>
-      <c r="G109" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -6379,19 +6388,19 @@
         <v>9</v>
       </c>
       <c r="C110" t="s">
+        <v>434</v>
+      </c>
+      <c r="D110" t="s">
+        <v>409</v>
+      </c>
+      <c r="E110" t="s">
+        <v>435</v>
+      </c>
+      <c r="F110" t="s">
+        <v>103</v>
+      </c>
+      <c r="G110" t="s">
         <v>436</v>
-      </c>
-      <c r="D110" t="s">
-        <v>411</v>
-      </c>
-      <c r="E110" t="s">
-        <v>437</v>
-      </c>
-      <c r="F110" t="s">
-        <v>103</v>
-      </c>
-      <c r="G110" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1">
@@ -6402,19 +6411,19 @@
         <v>10</v>
       </c>
       <c r="C111" t="s">
+        <v>437</v>
+      </c>
+      <c r="D111" t="s">
+        <v>409</v>
+      </c>
+      <c r="E111" t="s">
+        <v>438</v>
+      </c>
+      <c r="F111" t="s">
+        <v>103</v>
+      </c>
+      <c r="G111" t="s">
         <v>439</v>
-      </c>
-      <c r="D111" t="s">
-        <v>411</v>
-      </c>
-      <c r="E111" t="s">
-        <v>440</v>
-      </c>
-      <c r="F111" t="s">
-        <v>103</v>
-      </c>
-      <c r="G111" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -6425,19 +6434,19 @@
         <v>11</v>
       </c>
       <c r="C112" t="s">
+        <v>440</v>
+      </c>
+      <c r="D112" t="s">
+        <v>409</v>
+      </c>
+      <c r="E112" t="s">
+        <v>441</v>
+      </c>
+      <c r="F112" t="s">
+        <v>103</v>
+      </c>
+      <c r="G112" t="s">
         <v>442</v>
-      </c>
-      <c r="D112" t="s">
-        <v>411</v>
-      </c>
-      <c r="E112" t="s">
-        <v>443</v>
-      </c>
-      <c r="F112" t="s">
-        <v>103</v>
-      </c>
-      <c r="G112" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -6448,19 +6457,19 @@
         <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D113" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E113" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F113" t="s">
         <v>103</v>
       </c>
       <c r="G113" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -6471,19 +6480,19 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
+        <v>445</v>
+      </c>
+      <c r="D114" t="s">
+        <v>409</v>
+      </c>
+      <c r="E114" t="s">
+        <v>446</v>
+      </c>
+      <c r="F114" t="s">
+        <v>334</v>
+      </c>
+      <c r="G114" t="s">
         <v>447</v>
-      </c>
-      <c r="D114" t="s">
-        <v>411</v>
-      </c>
-      <c r="E114" t="s">
-        <v>448</v>
-      </c>
-      <c r="F114" t="s">
-        <v>336</v>
-      </c>
-      <c r="G114" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -6494,10 +6503,10 @@
         <v>14</v>
       </c>
       <c r="C115" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D115" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -6508,10 +6517,10 @@
         <v>15</v>
       </c>
       <c r="C116" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D116" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -6522,10 +6531,10 @@
         <v>16</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -6536,10 +6545,10 @@
         <v>17</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -6550,10 +6559,10 @@
         <v>18</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -6564,10 +6573,10 @@
         <v>19</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -6578,10 +6587,10 @@
         <v>20</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -6592,19 +6601,19 @@
         <v>1</v>
       </c>
       <c r="C122" t="s">
+        <v>450</v>
+      </c>
+      <c r="D122" t="s">
+        <v>451</v>
+      </c>
+      <c r="E122" t="s">
         <v>452</v>
       </c>
-      <c r="D122" t="s">
+      <c r="F122" t="s">
         <v>453</v>
       </c>
-      <c r="E122" t="s">
-        <v>454</v>
-      </c>
-      <c r="F122" t="s">
-        <v>455</v>
-      </c>
       <c r="G122" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -6615,19 +6624,19 @@
         <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D123" t="s">
+        <v>451</v>
+      </c>
+      <c r="E123" t="s">
+        <v>455</v>
+      </c>
+      <c r="F123" t="s">
         <v>453</v>
       </c>
-      <c r="E123" t="s">
-        <v>457</v>
-      </c>
-      <c r="F123" t="s">
+      <c r="G123" t="s">
         <v>455</v>
-      </c>
-      <c r="G123" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -6638,19 +6647,19 @@
         <v>3</v>
       </c>
       <c r="C124" t="s">
+        <v>456</v>
+      </c>
+      <c r="D124" t="s">
+        <v>451</v>
+      </c>
+      <c r="E124" t="s">
+        <v>457</v>
+      </c>
+      <c r="F124" t="s">
         <v>458</v>
       </c>
-      <c r="D124" t="s">
-        <v>453</v>
-      </c>
-      <c r="E124" t="s">
+      <c r="G124" t="s">
         <v>459</v>
-      </c>
-      <c r="F124" t="s">
-        <v>460</v>
-      </c>
-      <c r="G124" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -6661,19 +6670,19 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
+        <v>460</v>
+      </c>
+      <c r="D125" t="s">
+        <v>451</v>
+      </c>
+      <c r="E125" t="s">
+        <v>461</v>
+      </c>
+      <c r="F125" t="s">
         <v>462</v>
       </c>
-      <c r="D125" t="s">
-        <v>453</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="G125" t="s">
         <v>463</v>
-      </c>
-      <c r="F125" t="s">
-        <v>464</v>
-      </c>
-      <c r="G125" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -6684,19 +6693,19 @@
         <v>5</v>
       </c>
       <c r="C126" t="s">
+        <v>464</v>
+      </c>
+      <c r="D126" t="s">
+        <v>451</v>
+      </c>
+      <c r="E126" t="s">
+        <v>465</v>
+      </c>
+      <c r="F126" t="s">
+        <v>103</v>
+      </c>
+      <c r="G126" t="s">
         <v>466</v>
-      </c>
-      <c r="D126" t="s">
-        <v>453</v>
-      </c>
-      <c r="E126" t="s">
-        <v>467</v>
-      </c>
-      <c r="F126" t="s">
-        <v>103</v>
-      </c>
-      <c r="G126" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -6707,19 +6716,19 @@
         <v>6</v>
       </c>
       <c r="C127" t="s">
+        <v>467</v>
+      </c>
+      <c r="D127" t="s">
+        <v>451</v>
+      </c>
+      <c r="E127" t="s">
+        <v>468</v>
+      </c>
+      <c r="F127" t="s">
+        <v>462</v>
+      </c>
+      <c r="G127" t="s">
         <v>469</v>
-      </c>
-      <c r="D127" t="s">
-        <v>453</v>
-      </c>
-      <c r="E127" t="s">
-        <v>470</v>
-      </c>
-      <c r="F127" t="s">
-        <v>464</v>
-      </c>
-      <c r="G127" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -6730,19 +6739,19 @@
         <v>7</v>
       </c>
       <c r="C128" t="s">
+        <v>470</v>
+      </c>
+      <c r="D128" t="s">
+        <v>451</v>
+      </c>
+      <c r="E128" t="s">
+        <v>471</v>
+      </c>
+      <c r="F128" t="s">
+        <v>462</v>
+      </c>
+      <c r="G128" t="s">
         <v>472</v>
-      </c>
-      <c r="D128" t="s">
-        <v>453</v>
-      </c>
-      <c r="E128" t="s">
-        <v>473</v>
-      </c>
-      <c r="F128" t="s">
-        <v>464</v>
-      </c>
-      <c r="G128" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -6753,19 +6762,19 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>473</v>
+      </c>
+      <c r="D129" t="s">
+        <v>451</v>
+      </c>
+      <c r="E129" t="s">
+        <v>474</v>
+      </c>
+      <c r="F129" t="s">
         <v>475</v>
       </c>
-      <c r="D129" t="s">
-        <v>453</v>
-      </c>
-      <c r="E129" t="s">
+      <c r="G129" t="s">
         <v>476</v>
-      </c>
-      <c r="F129" t="s">
-        <v>477</v>
-      </c>
-      <c r="G129" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -6776,19 +6785,19 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
+        <v>477</v>
+      </c>
+      <c r="D130" t="s">
+        <v>451</v>
+      </c>
+      <c r="E130" t="s">
+        <v>478</v>
+      </c>
+      <c r="F130" t="s">
+        <v>475</v>
+      </c>
+      <c r="G130" t="s">
         <v>479</v>
-      </c>
-      <c r="D130" t="s">
-        <v>453</v>
-      </c>
-      <c r="E130" t="s">
-        <v>480</v>
-      </c>
-      <c r="F130" t="s">
-        <v>477</v>
-      </c>
-      <c r="G130" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -6799,19 +6808,19 @@
         <v>10</v>
       </c>
       <c r="C131" t="s">
+        <v>480</v>
+      </c>
+      <c r="D131" t="s">
+        <v>451</v>
+      </c>
+      <c r="E131" t="s">
+        <v>481</v>
+      </c>
+      <c r="F131" t="s">
+        <v>458</v>
+      </c>
+      <c r="G131" t="s">
         <v>482</v>
-      </c>
-      <c r="D131" t="s">
-        <v>453</v>
-      </c>
-      <c r="E131" t="s">
-        <v>483</v>
-      </c>
-      <c r="F131" t="s">
-        <v>460</v>
-      </c>
-      <c r="G131" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -6822,19 +6831,19 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
+        <v>483</v>
+      </c>
+      <c r="D132" t="s">
+        <v>451</v>
+      </c>
+      <c r="E132" t="s">
+        <v>484</v>
+      </c>
+      <c r="F132" t="s">
+        <v>458</v>
+      </c>
+      <c r="G132" t="s">
         <v>485</v>
-      </c>
-      <c r="D132" t="s">
-        <v>453</v>
-      </c>
-      <c r="E132" t="s">
-        <v>486</v>
-      </c>
-      <c r="F132" t="s">
-        <v>460</v>
-      </c>
-      <c r="G132" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -6845,19 +6854,19 @@
         <v>12</v>
       </c>
       <c r="C133" t="s">
+        <v>486</v>
+      </c>
+      <c r="D133" t="s">
+        <v>451</v>
+      </c>
+      <c r="E133" t="s">
+        <v>487</v>
+      </c>
+      <c r="F133" t="s">
+        <v>462</v>
+      </c>
+      <c r="G133" t="s">
         <v>488</v>
-      </c>
-      <c r="D133" t="s">
-        <v>453</v>
-      </c>
-      <c r="E133" t="s">
-        <v>489</v>
-      </c>
-      <c r="F133" t="s">
-        <v>464</v>
-      </c>
-      <c r="G133" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -6868,19 +6877,19 @@
         <v>13</v>
       </c>
       <c r="C134" t="s">
+        <v>489</v>
+      </c>
+      <c r="D134" t="s">
+        <v>451</v>
+      </c>
+      <c r="E134" t="s">
+        <v>490</v>
+      </c>
+      <c r="F134" t="s">
+        <v>462</v>
+      </c>
+      <c r="G134" t="s">
         <v>491</v>
-      </c>
-      <c r="D134" t="s">
-        <v>453</v>
-      </c>
-      <c r="E134" t="s">
-        <v>492</v>
-      </c>
-      <c r="F134" t="s">
-        <v>464</v>
-      </c>
-      <c r="G134" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -6891,10 +6900,10 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D135" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -6905,10 +6914,10 @@
         <v>15</v>
       </c>
       <c r="C136" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D136" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -6919,10 +6928,10 @@
         <v>16</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -6933,10 +6942,10 @@
         <v>17</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -6947,10 +6956,10 @@
         <v>18</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -6961,10 +6970,10 @@
         <v>19</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -6975,10 +6984,10 @@
         <v>20</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -6989,19 +6998,19 @@
         <v>1</v>
       </c>
       <c r="C142" t="s">
+        <v>494</v>
+      </c>
+      <c r="D142" t="s">
+        <v>495</v>
+      </c>
+      <c r="E142" t="s">
         <v>496</v>
       </c>
-      <c r="D142" t="s">
+      <c r="F142" t="s">
         <v>497</v>
       </c>
-      <c r="E142" t="s">
+      <c r="G142" t="s">
         <v>498</v>
-      </c>
-      <c r="F142" t="s">
-        <v>499</v>
-      </c>
-      <c r="G142" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -7012,19 +7021,19 @@
         <v>2</v>
       </c>
       <c r="C143" t="s">
+        <v>499</v>
+      </c>
+      <c r="D143" t="s">
+        <v>495</v>
+      </c>
+      <c r="E143" t="s">
+        <v>500</v>
+      </c>
+      <c r="F143" t="s">
         <v>501</v>
       </c>
-      <c r="D143" t="s">
-        <v>497</v>
-      </c>
-      <c r="E143" t="s">
-        <v>502</v>
-      </c>
-      <c r="F143" t="s">
-        <v>503</v>
-      </c>
       <c r="G143" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -7035,19 +7044,19 @@
         <v>3</v>
       </c>
       <c r="C144" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D144" t="s">
+        <v>495</v>
+      </c>
+      <c r="E144" t="s">
         <v>568</v>
       </c>
-      <c r="D144" t="s">
-        <v>497</v>
-      </c>
-      <c r="E144" t="s">
-        <v>573</v>
-      </c>
       <c r="F144" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G144" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -7058,10 +7067,10 @@
         <v>4</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="D145" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -7072,10 +7081,10 @@
         <v>5</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="D146" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -7086,10 +7095,10 @@
         <v>6</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="D147" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -7100,13 +7109,13 @@
         <v>7</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="D148" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E148" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -7117,13 +7126,13 @@
         <v>8</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="D149" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E149" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -7134,13 +7143,13 @@
         <v>9</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="D150" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E150" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -7151,13 +7160,13 @@
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="D151" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E151" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -7168,10 +7177,10 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="D152" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -7182,10 +7191,10 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D153" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -7196,10 +7205,10 @@
         <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="D154" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -7210,10 +7219,10 @@
         <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="D155" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -7224,10 +7233,10 @@
         <v>15</v>
       </c>
       <c r="C156" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D156" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -7238,10 +7247,10 @@
         <v>16</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -7252,10 +7261,10 @@
         <v>17</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -7266,10 +7275,10 @@
         <v>18</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -7280,10 +7289,10 @@
         <v>19</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -7294,10 +7303,10 @@
         <v>20</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -7308,19 +7317,19 @@
         <v>1</v>
       </c>
       <c r="C162" t="s">
+        <v>504</v>
+      </c>
+      <c r="D162" t="s">
+        <v>505</v>
+      </c>
+      <c r="E162" t="s">
         <v>506</v>
       </c>
-      <c r="D162" t="s">
+      <c r="F162" t="s">
         <v>507</v>
       </c>
-      <c r="E162" t="s">
+      <c r="G162" t="s">
         <v>508</v>
-      </c>
-      <c r="F162" t="s">
-        <v>509</v>
-      </c>
-      <c r="G162" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -7331,19 +7340,19 @@
         <v>2</v>
       </c>
       <c r="C163" t="s">
+        <v>509</v>
+      </c>
+      <c r="D163" t="s">
+        <v>505</v>
+      </c>
+      <c r="E163" t="s">
+        <v>510</v>
+      </c>
+      <c r="F163" t="s">
+        <v>507</v>
+      </c>
+      <c r="G163" t="s">
         <v>511</v>
-      </c>
-      <c r="D163" t="s">
-        <v>507</v>
-      </c>
-      <c r="E163" t="s">
-        <v>512</v>
-      </c>
-      <c r="F163" t="s">
-        <v>509</v>
-      </c>
-      <c r="G163" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -7354,16 +7363,16 @@
         <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D164" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E164" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G164" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -7374,16 +7383,16 @@
         <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="D165" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E165" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G165" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -7394,19 +7403,19 @@
         <v>5</v>
       </c>
       <c r="C166" t="s">
+        <v>516</v>
+      </c>
+      <c r="D166" t="s">
+        <v>505</v>
+      </c>
+      <c r="E166" t="s">
+        <v>517</v>
+      </c>
+      <c r="F166" t="s">
+        <v>232</v>
+      </c>
+      <c r="G166" t="s">
         <v>518</v>
-      </c>
-      <c r="D166" t="s">
-        <v>507</v>
-      </c>
-      <c r="E166" t="s">
-        <v>519</v>
-      </c>
-      <c r="F166" t="s">
-        <v>234</v>
-      </c>
-      <c r="G166" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -7417,10 +7426,10 @@
         <v>6</v>
       </c>
       <c r="C167" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D167" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -7431,10 +7440,10 @@
         <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D168" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -7445,10 +7454,10 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D169" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -7459,10 +7468,10 @@
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D170" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -7473,10 +7482,10 @@
         <v>10</v>
       </c>
       <c r="C171" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D171" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -7487,10 +7496,10 @@
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D172" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -7501,10 +7510,10 @@
         <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D173" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -7515,10 +7524,10 @@
         <v>13</v>
       </c>
       <c r="C174" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D174" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -7529,10 +7538,10 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D175" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -7543,10 +7552,10 @@
         <v>15</v>
       </c>
       <c r="C176" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D176" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -7557,10 +7566,10 @@
         <v>16</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -7571,10 +7580,10 @@
         <v>17</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -7585,10 +7594,10 @@
         <v>18</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -7599,10 +7608,10 @@
         <v>19</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -7613,10 +7622,10 @@
         <v>20</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -7627,19 +7636,19 @@
         <v>1</v>
       </c>
       <c r="C182" t="s">
+        <v>529</v>
+      </c>
+      <c r="D182" t="s">
+        <v>530</v>
+      </c>
+      <c r="E182" t="s">
         <v>531</v>
       </c>
-      <c r="D182" t="s">
+      <c r="F182" t="s">
+        <v>103</v>
+      </c>
+      <c r="G182" t="s">
         <v>532</v>
-      </c>
-      <c r="E182" t="s">
-        <v>533</v>
-      </c>
-      <c r="F182" t="s">
-        <v>103</v>
-      </c>
-      <c r="G182" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -7650,19 +7659,19 @@
         <v>2</v>
       </c>
       <c r="C183" t="s">
+        <v>533</v>
+      </c>
+      <c r="D183" t="s">
+        <v>530</v>
+      </c>
+      <c r="E183" t="s">
+        <v>534</v>
+      </c>
+      <c r="F183" t="s">
+        <v>103</v>
+      </c>
+      <c r="G183" t="s">
         <v>535</v>
-      </c>
-      <c r="D183" t="s">
-        <v>532</v>
-      </c>
-      <c r="E183" t="s">
-        <v>536</v>
-      </c>
-      <c r="F183" t="s">
-        <v>103</v>
-      </c>
-      <c r="G183" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -7673,19 +7682,19 @@
         <v>3</v>
       </c>
       <c r="C184" t="s">
+        <v>536</v>
+      </c>
+      <c r="D184" t="s">
+        <v>530</v>
+      </c>
+      <c r="E184" t="s">
+        <v>537</v>
+      </c>
+      <c r="F184" t="s">
+        <v>103</v>
+      </c>
+      <c r="G184" t="s">
         <v>538</v>
-      </c>
-      <c r="D184" t="s">
-        <v>532</v>
-      </c>
-      <c r="E184" t="s">
-        <v>539</v>
-      </c>
-      <c r="F184" t="s">
-        <v>103</v>
-      </c>
-      <c r="G184" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -7696,19 +7705,19 @@
         <v>4</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D185" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E185" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F185" t="s">
         <v>103</v>
       </c>
       <c r="G185" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -7719,19 +7728,19 @@
         <v>5</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D186" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E186" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F186" t="s">
         <v>103</v>
       </c>
       <c r="G186" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -7742,19 +7751,19 @@
         <v>6</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="D187" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E187" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F187" t="s">
         <v>103</v>
       </c>
       <c r="G187" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -7765,19 +7774,19 @@
         <v>7</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="D188" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E188" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F188" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G188" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -7788,19 +7797,19 @@
         <v>8</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="D189" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E189" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F189" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G189" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -7811,19 +7820,19 @@
         <v>9</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="D190" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E190" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F190" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G190" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -7834,19 +7843,19 @@
         <v>10</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D191" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E191" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F191" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G191" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -7857,19 +7866,19 @@
         <v>11</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="D192" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E192" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F192" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G192" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -7880,19 +7889,19 @@
         <v>12</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="D193" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E193" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F193" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G193" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -7903,19 +7912,19 @@
         <v>13</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="D194" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E194" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F194" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G194" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -7926,19 +7935,19 @@
         <v>14</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="D195" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E195" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F195" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G195" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -7949,10 +7958,10 @@
         <v>15</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D196" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -7963,10 +7972,10 @@
         <v>16</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -7977,10 +7986,10 @@
         <v>17</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -7991,10 +8000,10 @@
         <v>18</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -8005,10 +8014,10 @@
         <v>19</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -8019,10 +8028,10 @@
         <v>20</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -8033,16 +8042,16 @@
         <v>1</v>
       </c>
       <c r="C202" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="D202" t="s">
+        <v>573</v>
+      </c>
+      <c r="E202" t="s">
         <v>578</v>
       </c>
-      <c r="E202" t="s">
-        <v>583</v>
-      </c>
       <c r="F202" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -8053,16 +8062,16 @@
         <v>2</v>
       </c>
       <c r="C203" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="D203" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E203" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="F203" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -8073,16 +8082,16 @@
         <v>3</v>
       </c>
       <c r="C204" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="D204" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E204" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="F204" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -8093,16 +8102,16 @@
         <v>4</v>
       </c>
       <c r="C205" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D205" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E205" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="F205" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -8113,16 +8122,16 @@
         <v>5</v>
       </c>
       <c r="C206" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="D206" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E206" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F206" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -8133,16 +8142,16 @@
         <v>6</v>
       </c>
       <c r="C207" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D207" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E207" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F207" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -8153,16 +8162,16 @@
         <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="D208" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E208" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="F208" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -8173,16 +8182,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D209" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E209" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F209" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -8193,16 +8202,16 @@
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="D210" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E210" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="F210" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -8213,16 +8222,16 @@
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="D211" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E211" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="F211" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -8233,16 +8242,16 @@
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="D212" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E212" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="F212" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -8253,16 +8262,16 @@
         <v>12</v>
       </c>
       <c r="C213" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="D213" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E213" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="F213" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -8273,16 +8282,16 @@
         <v>13</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="D214" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E214" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="F214" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -8293,16 +8302,16 @@
         <v>14</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="D215" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E215" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="F215" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -8313,16 +8322,16 @@
         <v>15</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="D216" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E216" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="F216" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -8333,16 +8342,16 @@
         <v>16</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E217" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="F217" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -8353,13 +8362,13 @@
         <v>17</v>
       </c>
       <c r="C218" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="E218" t="s">
         <v>673</v>
-      </c>
-      <c r="D218" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="E218" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8370,13 +8379,13 @@
         <v>18</v>
       </c>
       <c r="C219" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="D219" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="E219" t="s">
         <v>674</v>
-      </c>
-      <c r="D219" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="E219" t="s">
-        <v>679</v>
       </c>
       <c r="F219" s="4" t="s">
         <v>113</v>
@@ -8390,10 +8399,10 @@
         <v>19</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -8404,10 +8413,10 @@
         <v>20</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -8433,16 +8442,16 @@
     <row r="1" spans="1:5">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8463,10 +8472,10 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8480,10 +8489,10 @@
         <v>17</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8497,10 +8506,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8514,10 +8523,10 @@
         <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8531,10 +8540,10 @@
         <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8548,10 +8557,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8565,10 +8574,10 @@
         <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8582,10 +8591,10 @@
         <v>18</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8599,10 +8608,10 @@
         <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8616,10 +8625,10 @@
         <v>20</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8633,10 +8642,10 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8650,10 +8659,10 @@
         <v>17</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8667,10 +8676,10 @@
         <v>18</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8684,10 +8693,10 @@
         <v>19</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8701,10 +8710,10 @@
         <v>20</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8718,10 +8727,10 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8735,10 +8744,10 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8752,10 +8761,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8769,10 +8778,10 @@
         <v>19</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8786,10 +8795,10 @@
         <v>20</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8803,10 +8812,10 @@
         <v>16</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8820,10 +8829,10 @@
         <v>17</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8837,10 +8846,10 @@
         <v>18</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8854,10 +8863,10 @@
         <v>19</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8871,10 +8880,10 @@
         <v>20</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8888,10 +8897,10 @@
         <v>16</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8905,10 +8914,10 @@
         <v>17</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8922,10 +8931,10 @@
         <v>18</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8939,10 +8948,10 @@
         <v>19</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8956,10 +8965,10 @@
         <v>20</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8973,10 +8982,10 @@
         <v>16</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8990,10 +8999,10 @@
         <v>17</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9007,10 +9016,10 @@
         <v>18</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9024,10 +9033,10 @@
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9041,10 +9050,10 @@
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9058,10 +9067,10 @@
         <v>16</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9075,10 +9084,10 @@
         <v>17</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -9092,10 +9101,10 @@
         <v>18</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -9109,10 +9118,10 @@
         <v>19</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -9126,10 +9135,10 @@
         <v>20</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -9143,10 +9152,10 @@
         <v>16</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9160,10 +9169,10 @@
         <v>17</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9177,10 +9186,10 @@
         <v>18</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9194,10 +9203,10 @@
         <v>19</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -9211,10 +9220,10 @@
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -9228,10 +9237,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -9245,10 +9254,10 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -9262,10 +9271,10 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -9279,10 +9288,10 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -9296,10 +9305,10 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -9313,10 +9322,10 @@
         <v>16</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9330,10 +9339,10 @@
         <v>17</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9347,10 +9356,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9364,10 +9373,10 @@
         <v>19</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9381,15 +9390,15 @@
         <v>20</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation - Copy before adding crown_width_option_baseline_to_start8\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE52741-CD98-414D-93C6-C8D1C4FB94AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8E2B3C-CCD8-482F-99F8-2F8352F296FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -21,17 +21,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">output!$A$1:$G$221</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="710">
   <si>
     <t>pFS2</t>
   </si>
@@ -2154,73 +2165,10 @@
     <t>var_10_14</t>
   </si>
   <si>
-    <t>thinIntercept</t>
-  </si>
-  <si>
-    <t>thinfN</t>
-  </si>
-  <si>
-    <t>thinfT</t>
-  </si>
-  <si>
-    <t>thinfPhys</t>
-  </si>
-  <si>
-    <t>ln(trees ha-1)</t>
-  </si>
-  <si>
-    <t>beta0</t>
-  </si>
-  <si>
-    <t>betaB</t>
-  </si>
-  <si>
-    <t>betaN</t>
-  </si>
-  <si>
-    <t>betafN</t>
-  </si>
-  <si>
-    <t>betafT</t>
-  </si>
-  <si>
-    <t>betafPhys</t>
-  </si>
-  <si>
     <t>Maximum stem mass per tree @ N = 1000 trees/hectare (mort_model = 1)</t>
   </si>
   <si>
     <t>Power in self-thinning rule (mort_model = 1 or 2)</t>
-  </si>
-  <si>
-    <t>Intercept for self-thinning rule (mort_model = 2)</t>
-  </si>
-  <si>
-    <t>Power in fertility modifier (mort_model = 2)</t>
-  </si>
-  <si>
-    <t>Power in temperature modifier (mort_model = 2)</t>
-  </si>
-  <si>
-    <t>Power in physmod modifier (mort_model = 2)</t>
-  </si>
-  <si>
-    <t>constant for self-thinning (mort_model = 3)</t>
-  </si>
-  <si>
-    <t>Power for B (mort_model = 3)</t>
-  </si>
-  <si>
-    <t>Power in tree density (mort_model = 3)</t>
-  </si>
-  <si>
-    <t>Power in nutrition modifier (mort_model = 3)</t>
-  </si>
-  <si>
-    <t>Power in temperature modifier (mort_model = 3)</t>
-  </si>
-  <si>
-    <t>Power in physmod modifier (mort_model = 3)</t>
   </si>
   <si>
     <t>Parameter of crown ratio equation</t>
@@ -2625,7 +2573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E287297-02C0-BF44-BF0C-8FADE2A87F8F}">
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="2" max="2" width="80" bestFit="1" customWidth="1"/>
@@ -3070,7 +3018,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="C32" t="s">
         <v>138</v>
@@ -3084,7 +3032,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="C33" t="s">
         <v>103</v>
@@ -3094,151 +3042,149 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="1" t="s">
-        <v>707</v>
+      <c r="A34" t="s">
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>720</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="D34" s="1">
-        <v>12</v>
+        <v>139</v>
+      </c>
+      <c r="C34" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="1" t="s">
-        <v>708</v>
+      <c r="A35" t="s">
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>721</v>
-      </c>
-      <c r="C35" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="1">
-        <v>0</v>
+      <c r="D35">
+        <v>0.2</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="1" t="s">
-        <v>709</v>
+      <c r="A36" t="s">
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>722</v>
-      </c>
-      <c r="C36" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="1">
-        <v>0</v>
+      <c r="D36">
+        <v>0.2</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="1" t="s">
-        <v>710</v>
+      <c r="A37" t="s">
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>723</v>
-      </c>
-      <c r="C37" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" t="s">
+        <v>143</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" t="s">
         <v>103</v>
       </c>
-      <c r="D37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="B38" t="s">
-        <v>724</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D38" s="1">
-        <v>-20.399999999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="B39" t="s">
-        <v>725</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D39" s="1">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="B40" t="s">
-        <v>726</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D40" s="1">
-        <v>2.6</v>
+      <c r="D40">
+        <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="B41" t="s">
-        <v>727</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>103</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C41" s="1"/>
       <c r="D41" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="1" t="s">
-        <v>716</v>
+      <c r="A42" t="s">
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>728</v>
-      </c>
-      <c r="C42" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C42" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>148</v>
+      </c>
+      <c r="C43" t="s">
         <v>103</v>
       </c>
-      <c r="D42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="B43" t="s">
-        <v>729</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D43" s="1">
-        <v>0</v>
+      <c r="D43">
+        <v>0.15</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C44" t="s">
         <v>103</v>
@@ -3249,428 +3195,430 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C45" t="s">
         <v>103</v>
       </c>
       <c r="D45">
-        <v>0.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="D46">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C47" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="D47">
-        <v>11</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C48" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C49" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="D49">
-        <v>2.5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
         <v>103</v>
       </c>
       <c r="D50">
-        <v>0.5</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1">
-        <v>0</v>
+      <c r="A51" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>158</v>
+      </c>
+      <c r="C51" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51">
+        <v>0.05</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C52" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C53" t="s">
         <v>103</v>
       </c>
       <c r="D53">
-        <v>0.15</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C55" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C56" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D56">
-        <v>0.06</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C57" t="s">
         <v>103</v>
       </c>
       <c r="D57">
-        <v>0.47</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="C58" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="D59">
-        <v>0.02</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="D60">
-        <v>3.33</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C61" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D61">
-        <v>0.05</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C62" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="D62">
-        <v>0.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C63" t="s">
         <v>103</v>
       </c>
       <c r="D63">
-        <v>0.66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B64" t="s">
-        <v>162</v>
-      </c>
-      <c r="C64" t="s">
-        <v>163</v>
-      </c>
-      <c r="D64">
-        <v>2</v>
+      <c r="A64" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1.3</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>164</v>
+        <v>691</v>
       </c>
       <c r="C65" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="D65">
-        <v>4.4000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>54</v>
+        <v>679</v>
       </c>
       <c r="B66" t="s">
-        <v>165</v>
+        <v>691</v>
       </c>
       <c r="C66" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
       <c r="D66">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>55</v>
+        <v>680</v>
       </c>
       <c r="B67" t="s">
-        <v>166</v>
+        <v>691</v>
       </c>
       <c r="C67" t="s">
         <v>103</v>
       </c>
       <c r="D67">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>56</v>
+        <v>689</v>
       </c>
       <c r="B68" t="s">
-        <v>167</v>
+        <v>691</v>
       </c>
       <c r="C68" t="s">
         <v>103</v>
       </c>
       <c r="D68">
-        <v>0.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>690</v>
       </c>
       <c r="B69" t="s">
-        <v>168</v>
+        <v>691</v>
       </c>
       <c r="C69" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B70" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C70" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="D70">
-        <v>0.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B71" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C71" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="D71">
-        <v>0.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B72" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C72" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B73" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C73" t="s">
         <v>103</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D74" s="1">
-        <v>1.3</v>
+      <c r="A74" t="s">
+        <v>67</v>
+      </c>
+      <c r="B74" t="s">
+        <v>692</v>
+      </c>
+      <c r="C74" t="s">
+        <v>103</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>61</v>
+        <v>681</v>
       </c>
       <c r="B75" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C75" t="s">
         <v>103</v>
@@ -3681,10 +3629,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B76" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C76" t="s">
         <v>103</v>
@@ -3695,10 +3643,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B77" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C77" t="s">
         <v>103</v>
@@ -3709,10 +3657,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="B78" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C78" t="s">
         <v>103</v>
@@ -3723,10 +3671,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>690</v>
+        <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="C79" t="s">
         <v>103</v>
@@ -3737,10 +3685,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>62</v>
+        <v>685</v>
       </c>
       <c r="B80" t="s">
-        <v>174</v>
+        <v>709</v>
       </c>
       <c r="C80" t="s">
         <v>103</v>
@@ -3751,10 +3699,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>63</v>
+        <v>686</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
+        <v>709</v>
       </c>
       <c r="C81" t="s">
         <v>103</v>
@@ -3765,10 +3713,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>64</v>
+        <v>687</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>709</v>
       </c>
       <c r="C82" t="s">
         <v>103</v>
@@ -3779,10 +3727,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>65</v>
+        <v>688</v>
       </c>
       <c r="B83" t="s">
-        <v>177</v>
+        <v>709</v>
       </c>
       <c r="C83" t="s">
         <v>103</v>
@@ -3793,197 +3741,57 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>692</v>
+        <v>178</v>
       </c>
       <c r="C84" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>681</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>692</v>
+        <v>180</v>
       </c>
       <c r="C85" t="s">
         <v>103</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>682</v>
+        <v>86</v>
       </c>
       <c r="B86" t="s">
-        <v>692</v>
+        <v>181</v>
       </c>
       <c r="C86" t="s">
-        <v>103</v>
+        <v>182</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>683</v>
+        <v>87</v>
       </c>
       <c r="B87" t="s">
-        <v>692</v>
+        <v>183</v>
       </c>
       <c r="C87" t="s">
-        <v>103</v>
+        <v>184</v>
       </c>
       <c r="D87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" t="s">
-        <v>684</v>
-      </c>
-      <c r="B88" t="s">
-        <v>692</v>
-      </c>
-      <c r="C88" t="s">
-        <v>103</v>
-      </c>
-      <c r="D88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" t="s">
-        <v>68</v>
-      </c>
-      <c r="B89" t="s">
-        <v>730</v>
-      </c>
-      <c r="C89" t="s">
-        <v>103</v>
-      </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" t="s">
-        <v>685</v>
-      </c>
-      <c r="B90" t="s">
-        <v>730</v>
-      </c>
-      <c r="C90" t="s">
-        <v>103</v>
-      </c>
-      <c r="D90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" t="s">
-        <v>686</v>
-      </c>
-      <c r="B91" t="s">
-        <v>730</v>
-      </c>
-      <c r="C91" t="s">
-        <v>103</v>
-      </c>
-      <c r="D91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" t="s">
-        <v>687</v>
-      </c>
-      <c r="B92" t="s">
-        <v>730</v>
-      </c>
-      <c r="C92" t="s">
-        <v>103</v>
-      </c>
-      <c r="D92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" t="s">
-        <v>688</v>
-      </c>
-      <c r="B93" t="s">
-        <v>730</v>
-      </c>
-      <c r="C93" t="s">
-        <v>103</v>
-      </c>
-      <c r="D93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" t="s">
-        <v>84</v>
-      </c>
-      <c r="B94" t="s">
-        <v>178</v>
-      </c>
-      <c r="C94" t="s">
-        <v>179</v>
-      </c>
-      <c r="D94">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" t="s">
-        <v>85</v>
-      </c>
-      <c r="B95" t="s">
-        <v>180</v>
-      </c>
-      <c r="C95" t="s">
-        <v>103</v>
-      </c>
-      <c r="D95">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" t="s">
-        <v>86</v>
-      </c>
-      <c r="B96" t="s">
-        <v>181</v>
-      </c>
-      <c r="C96" t="s">
-        <v>182</v>
-      </c>
-      <c r="D96">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" t="s">
-        <v>87</v>
-      </c>
-      <c r="B97" t="s">
-        <v>183</v>
-      </c>
-      <c r="C97" t="s">
-        <v>184</v>
-      </c>
-      <c r="D97">
         <v>2.2999999999999998</v>
       </c>
     </row>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation - Copy before adding crown_width_option_baseline_to_start8\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation2\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8E2B3C-CCD8-482F-99F8-2F8352F296FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442BC11E-450B-47D6-AEDC-2C8AF52FE263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="8" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="709">
   <si>
     <t>pFS2</t>
   </si>
@@ -2135,15 +2135,6 @@
     <t>var_10_7</t>
   </si>
   <si>
-    <t>biom_incr_foliage_def</t>
-  </si>
-  <si>
-    <t>biom_incr_stem_def</t>
-  </si>
-  <si>
-    <t>Increment due to use of non-structural carbohydrates following defoliation</t>
-  </si>
-  <si>
     <t>var_10_8</t>
   </si>
   <si>
@@ -2172,6 +2163,12 @@
   </si>
   <si>
     <t>Parameter of crown ratio equation</t>
+  </si>
+  <si>
+    <t>var_4_12</t>
+  </si>
+  <si>
+    <t>var_4_13</t>
   </si>
 </sst>
 </file>
@@ -3018,7 +3015,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C32" t="s">
         <v>138</v>
@@ -3032,7 +3029,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C33" t="s">
         <v>103</v>
@@ -3674,7 +3671,7 @@
         <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C79" t="s">
         <v>103</v>
@@ -3688,7 +3685,7 @@
         <v>685</v>
       </c>
       <c r="B80" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C80" t="s">
         <v>103</v>
@@ -3702,7 +3699,7 @@
         <v>686</v>
       </c>
       <c r="B81" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C81" t="s">
         <v>103</v>
@@ -3716,7 +3713,7 @@
         <v>687</v>
       </c>
       <c r="B82" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C82" t="s">
         <v>103</v>
@@ -3730,7 +3727,7 @@
         <v>688</v>
       </c>
       <c r="B83" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C83" t="s">
         <v>103</v>
@@ -5489,16 +5486,10 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>697</v>
+        <v>707</v>
       </c>
       <c r="D73" t="s">
         <v>332</v>
-      </c>
-      <c r="E73" t="s">
-        <v>699</v>
-      </c>
-      <c r="F73" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -5509,16 +5500,10 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="D74" t="s">
         <v>332</v>
-      </c>
-      <c r="E74" t="s">
-        <v>699</v>
-      </c>
-      <c r="F74" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -7605,7 +7590,7 @@
         <v>8</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D189" t="s">
         <v>530</v>
@@ -7628,7 +7613,7 @@
         <v>9</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D190" t="s">
         <v>530</v>
@@ -7651,7 +7636,7 @@
         <v>10</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D191" t="s">
         <v>530</v>
@@ -7674,7 +7659,7 @@
         <v>11</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D192" t="s">
         <v>530</v>
@@ -7697,7 +7682,7 @@
         <v>12</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D193" t="s">
         <v>530</v>
@@ -7720,7 +7705,7 @@
         <v>13</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D194" t="s">
         <v>530</v>
@@ -7743,7 +7728,7 @@
         <v>14</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D195" t="s">
         <v>530</v>

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation2\data-raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442BC11E-450B-47D6-AEDC-2C8AF52FE263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361E04DA-59D5-426C-994C-093B10A6608E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="708">
   <si>
     <t>pFS2</t>
   </si>
@@ -2051,9 +2051,6 @@
     <t>def_type</t>
   </si>
   <si>
-    <t>def_recover_t</t>
-  </si>
-  <si>
     <t>Number of trees removed due to defoliation</t>
   </si>
   <si>
@@ -2066,9 +2063,6 @@
     <t>Defoliation type (1 = Pruning; 2 = Epicormic; 3 = Coppice; 4 = Stand-replacing)</t>
   </si>
   <si>
-    <t>Maximum number of months required to recover the pre-defoliation foliage biomass (pruning or epicormic responses) or foliage + stem mass (coppice responses) of the trees that survived the defoliation event.</t>
-  </si>
-  <si>
     <t>Foliage biomass removed due to defoliation</t>
   </si>
   <si>
@@ -2169,6 +2163,9 @@
   </si>
   <si>
     <t>var_4_13</t>
+  </si>
+  <si>
+    <t>height_rel_wt</t>
   </si>
 </sst>
 </file>
@@ -2220,7 +2217,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2230,6 +2227,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2247,7 +2250,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2255,6 +2258,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2819,7 +2823,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C18" t="s">
         <v>103</v>
@@ -3015,7 +3019,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C32" t="s">
         <v>138</v>
@@ -3029,7 +3033,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C33" t="s">
         <v>103</v>
@@ -3475,7 +3479,7 @@
         <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C65" t="s">
         <v>103</v>
@@ -3486,10 +3490,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B66" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C66" t="s">
         <v>103</v>
@@ -3500,10 +3504,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B67" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C67" t="s">
         <v>103</v>
@@ -3514,10 +3518,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
+        <v>687</v>
+      </c>
+      <c r="B68" t="s">
         <v>689</v>
-      </c>
-      <c r="B68" t="s">
-        <v>691</v>
       </c>
       <c r="C68" t="s">
         <v>103</v>
@@ -3528,10 +3532,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B69" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C69" t="s">
         <v>103</v>
@@ -3601,7 +3605,7 @@
         <v>67</v>
       </c>
       <c r="B74" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C74" t="s">
         <v>103</v>
@@ -3612,10 +3616,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B75" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C75" t="s">
         <v>103</v>
@@ -3626,10 +3630,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B76" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C76" t="s">
         <v>103</v>
@@ -3640,10 +3644,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B77" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C77" t="s">
         <v>103</v>
@@ -3654,10 +3658,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B78" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C78" t="s">
         <v>103</v>
@@ -3671,7 +3675,7 @@
         <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C79" t="s">
         <v>103</v>
@@ -3682,10 +3686,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B80" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C80" t="s">
         <v>103</v>
@@ -3696,10 +3700,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B81" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C81" t="s">
         <v>103</v>
@@ -3710,10 +3714,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B82" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C82" t="s">
         <v>103</v>
@@ -3724,10 +3728,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B83" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C83" t="s">
         <v>103</v>
@@ -5486,7 +5490,7 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D73" t="s">
         <v>332</v>
@@ -5500,7 +5504,7 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D74" t="s">
         <v>332</v>
@@ -6970,7 +6974,7 @@
         <v>11</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D152" t="s">
         <v>495</v>
@@ -6984,7 +6988,7 @@
         <v>12</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D153" t="s">
         <v>495</v>
@@ -7498,7 +7502,7 @@
         <v>4</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D185" t="s">
         <v>530</v>
@@ -7521,7 +7525,7 @@
         <v>5</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D186" t="s">
         <v>530</v>
@@ -7544,7 +7548,7 @@
         <v>6</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D187" t="s">
         <v>530</v>
@@ -7567,7 +7571,7 @@
         <v>7</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D188" t="s">
         <v>530</v>
@@ -7590,7 +7594,7 @@
         <v>8</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D189" t="s">
         <v>530</v>
@@ -7613,7 +7617,7 @@
         <v>9</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D190" t="s">
         <v>530</v>
@@ -7636,7 +7640,7 @@
         <v>10</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D191" t="s">
         <v>530</v>
@@ -7659,7 +7663,7 @@
         <v>11</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D192" t="s">
         <v>530</v>
@@ -7682,7 +7686,7 @@
         <v>12</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D193" t="s">
         <v>530</v>
@@ -7705,7 +7709,7 @@
         <v>13</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D194" t="s">
         <v>530</v>
@@ -7728,7 +7732,7 @@
         <v>14</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D195" t="s">
         <v>530</v>
@@ -8081,7 +8085,7 @@
         <v>573</v>
       </c>
       <c r="E214" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F214" t="s">
         <v>249</v>
@@ -8101,7 +8105,7 @@
         <v>573</v>
       </c>
       <c r="E215" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F215" t="s">
         <v>334</v>
@@ -8121,7 +8125,7 @@
         <v>573</v>
       </c>
       <c r="E216" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F216" t="s">
         <v>334</v>
@@ -8141,7 +8145,7 @@
         <v>573</v>
       </c>
       <c r="E217" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F217" t="s">
         <v>334</v>
@@ -8161,7 +8165,7 @@
         <v>573</v>
       </c>
       <c r="E218" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -8171,18 +8175,13 @@
       <c r="B219" s="4">
         <v>18</v>
       </c>
-      <c r="C219" s="6" t="s">
-        <v>669</v>
+      <c r="C219" s="7" t="s">
+        <v>707</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="E219" t="s">
-        <v>674</v>
-      </c>
-      <c r="F219" s="4" t="s">
-        <v>113</v>
-      </c>
+      <c r="F219" s="4"/>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="4">

--- a/data-raw/data.default.xlsx
+++ b/data-raw/data.default.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Forrester\Models\3-PG\r3PG_mortality_management_defoliation\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361E04DA-59D5-426C-994C-093B10A6608E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB46EAA8-1A96-45DC-9C18-9BC8C4A690BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{61EEFE5B-6AE1-A641-A9AB-273DC4213F59}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="707">
   <si>
     <t>pFS2</t>
   </si>
@@ -2163,9 +2163,6 @@
   </si>
   <si>
     <t>var_4_13</t>
-  </si>
-  <si>
-    <t>height_rel_wt</t>
   </si>
 </sst>
 </file>
@@ -2217,7 +2214,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2227,12 +2224,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2250,7 +2241,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2258,7 +2249,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8175,8 +8165,8 @@
       <c r="B219" s="4">
         <v>18</v>
       </c>
-      <c r="C219" s="7" t="s">
-        <v>707</v>
+      <c r="C219" s="4" t="s">
+        <v>650</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>573</v>
